--- a/enterprise/output/통합_고도화엔터프라이즈_보안위협_매트릭스_v2.xlsx
+++ b/enterprise/output/통합_고도화엔터프라이즈_보안위협_매트릭스_v2.xlsx
@@ -3992,7 +3992,7 @@
       </c>
       <c r="J3" s="9" t="inlineStr">
         <is>
-          <t>작업방향 §7.2 리서치 — 경계·엣지 장비 KEV 비중(매년 15~21%)과 정합. 개별 경보는 ②③단계에서 1차 확인</t>
+          <t>작업방향 §7.2 리서치 — 경계·엣지 장비 KEV 비중(매년 14~21%)과 정합. 개별 경보는 ②③단계에서 1차 확인</t>
         </is>
       </c>
       <c r="K3" s="9" t="inlineStr">
@@ -5393,7 +5393,7 @@
       </c>
       <c r="E10" s="9" t="inlineStr">
         <is>
-          <t>ATT&amp;CK 추출본(prepare_attack.py — 기법 68·주체 977·절차 6,087, 절차 수는 최근빈발 신호), KEV 추출본(prepare_kev.py — 연도별 등재·경계/엣지 장비 비중 15~21%·같은 해 악용 비중), LOLBAS·LOLDrivers 추출본(prepare_lolbas.py), NIST·통합 v4.1 연계 ID 237개(prepare_refs.py)</t>
+          <t>ATT&amp;CK 추출본(prepare_attack.py — 기법 68·주체 977·절차 6,087, 절차 수는 최근빈발 신호), KEV 추출본(prepare_kev.py — 연도별 등재·경계/엣지 장비 비중 14~21%·같은 해 악용 비중), LOLBAS·LOLDrivers 추출본(prepare_lolbas.py), NIST·통합 v4.1 연계 ID 237개(prepare_refs.py)</t>
         </is>
       </c>
       <c r="F10" s="9" t="inlineStr">
@@ -5603,7 +5603,7 @@
       </c>
       <c r="M5" s="9" t="inlineStr">
         <is>
-          <t>외부 노출 자산을 지속 식별하고 엣지 장비의 취약점 공개·악용 동향을 신속 대조(NIST RA-5·SI-4)</t>
+          <t>엣지 장비 신속 패치·가상 패치와 공개 취약점 노출 구간 최소화(NIST SI-2·RA-5)</t>
         </is>
       </c>
     </row>
@@ -5666,7 +5666,7 @@
       </c>
       <c r="M6" s="9" t="inlineStr">
         <is>
-          <t>대량 파일 변경·암호화 행위와 선행 단계(자격증명·확산) 상관 이벤트를 행위 기반으로 탐지(NIST SI-4)</t>
+          <t>오프라인·불변 백업·복구 훈련과 선행 단계 조기 차단·분할을 적용(NIST CP-9·CP-10·SI-4)</t>
         </is>
       </c>
     </row>
@@ -5729,7 +5729,7 @@
       </c>
       <c r="M7" s="9" t="inlineStr">
         <is>
-          <t>보안 서비스 중지·드라이버 로드와 EDR 텔레메트리 단절을 행위·네트워크 기반으로 탐지(NIST SI-4·SI-7)</t>
+          <t>취약 드라이버 차단 목록(HVCI·블록리스트)·변조 방지와 보안 도구 상태를 중앙 감시(NIST SI-7·CM-7)</t>
         </is>
       </c>
     </row>
@@ -5792,7 +5792,7 @@
       </c>
       <c r="M8" s="9" t="inlineStr">
         <is>
-          <t>비정상 원격 세션(출발지·시간·계정)과 내부 RDP·SMB 급증을 네트워크·아이덴티티 기반으로 탐지(NIST SI-4·SC-7)</t>
+          <t>내부 분할·관리 전용 경로·점프 호스트와 원격 서비스 접근 최소화를 적용(NIST AC-17·SC-7)</t>
         </is>
       </c>
     </row>
@@ -5855,7 +5855,7 @@
       </c>
       <c r="M9" s="9" t="inlineStr">
         <is>
-          <t>원격 서비스 로그인의 비정상 위치·시간·장치와 MFA 미적용 경로를 아이덴티티·네트워크 기반으로 탐지(NIST SI-4·IA-2)</t>
+          <t>모든 외부 원격 접근에 피싱 내성 MFA·조건부 접근을 적용하고 노출을 최소화(NIST AC-17·IA-2)</t>
         </is>
       </c>
     </row>
@@ -5918,7 +5918,7 @@
       </c>
       <c r="M10" s="9" t="inlineStr">
         <is>
-          <t>LSASS 비정상 접근·핸들 열기와 자격증명 덤프 도구 행위를 EDR 기반으로 탐지(NIST SI-4·AC-6)</t>
+          <t>LSASS 보호(PPL)·자격증명 가드와 최소 권한·특권 분리를 적용(NIST AC-6·IA-5)</t>
         </is>
       </c>
     </row>
@@ -5981,7 +5981,7 @@
       </c>
       <c r="M11" s="9" t="inlineStr">
         <is>
-          <t>PowerShell 스크립트 블록·명령줄 로깅과 비정상 실행 맥락(인코딩·다운로드·원격 실행)을 행위 기반으로 탐지(NIST SI-4·SI-3)</t>
+          <t>스크립트 로깅·제약 언어 모드·서명 정책과 최소 기능 원칙을 적용(NIST CM-7·SI-4)</t>
         </is>
       </c>
     </row>
@@ -6044,7 +6044,7 @@
       </c>
       <c r="M12" s="9" t="inlineStr">
         <is>
-          <t>대량 반출 선행 징후와 갈취·부정 이체 정황을 통합 모니터링(NIST SI-4·IR-4)</t>
+          <t>데이터 반출 차단·사고 대응·법집행 연계와 백업·복구를 병행(NIST IR-4·SI-4)</t>
         </is>
       </c>
     </row>
@@ -6107,7 +6107,7 @@
       </c>
       <c r="M13" s="9" t="inlineStr">
         <is>
-          <t>신뢰 SaaS·외부 저장소로의 비정상 대량 업로드를 네트워크·DLP 기반으로 탐지(NIST SC-7·SI-4)</t>
+          <t>허용 SaaS 제한·egress 통제·DLP와 대용량 업로드 경보를 적용(NIST SC-7·SI-4)</t>
         </is>
       </c>
     </row>
@@ -6170,7 +6170,7 @@
       </c>
       <c r="M14" s="9" t="inlineStr">
         <is>
-          <t>C2 세션의 비정상 업로드량·방향성과 비컨-대용량 전환을 네트워크 기반으로 탐지(NIST SC-7·SI-4)</t>
+          <t>egress 통제·데이터 유출 탐지와 C2 차단으로 반출을 막음(NIST SC-7·AU-6)</t>
         </is>
       </c>
     </row>
@@ -6233,7 +6233,7 @@
       </c>
       <c r="M15" s="9" t="inlineStr">
         <is>
-          <t>비정상 티켓·해시 사용과 로그온 유형·계정 불일치를 아이덴티티 기반으로 탐지(NIST SI-4·AC-6)</t>
+          <t>특권 분리·로컬 관리자 암호 고유화(LAPS)·티켓 수명 축소와 재사용 탐지를 적용(NIST IA-2·AC-6)</t>
         </is>
       </c>
     </row>
@@ -6296,7 +6296,7 @@
       </c>
       <c r="M16" s="9" t="inlineStr">
         <is>
-          <t>신뢰 관계·연동 계정의 비정상 사용과 관리 도구발 대량·일괄 작업을 모니터링(NIST SI-4·AC-20)</t>
+          <t>공급·관리 관계에 최소 권한·분리·계약상 보안 요구를 적용하고 연동 토큰을 단기화·감사(NIST SR-3·CA-3·AC-20)</t>
         </is>
       </c>
     </row>
@@ -6359,7 +6359,7 @@
       </c>
       <c r="M17" s="9" t="inlineStr">
         <is>
-          <t>비정상적으로 많은 서비스 티켓 요청·약한 암호화 요청을 아이덴티티 기반으로 탐지(NIST SI-4·AC-6)</t>
+          <t>서비스 계정에 길고 무작위한 암호·gMSA·강한 암호화를 적용하고 요청을 감사(NIST IA-5·AC-6)</t>
         </is>
       </c>
     </row>
@@ -6422,7 +6422,7 @@
       </c>
       <c r="M18" s="9" t="inlineStr">
         <is>
-          <t>신규 커널 드라이버 로드와 취약 드라이버 서명·해시를 차단 목록과 대조(NIST SI-7·SI-4)</t>
+          <t>HVCI·드라이버 블록리스트로 취약 드라이버 로드를 차단(NIST SI-7·CM-7)</t>
         </is>
       </c>
     </row>
@@ -6485,7 +6485,7 @@
       </c>
       <c r="M19" s="9" t="inlineStr">
         <is>
-          <t>정상 바이너리의 비정상 인자·부모 프로세스·네트워크 행위를 행위 기반으로 탐지(NIST SI-4·CM-7)</t>
+          <t>불필요한 LOLBin 실행을 허용 목록·애플리케이션 제어로 제한하고 무결성·실행 맥락을 감시(NIST CM-7·SI-7)</t>
         </is>
       </c>
     </row>
@@ -6548,7 +6548,7 @@
       </c>
       <c r="M20" s="9" t="inlineStr">
         <is>
-          <t>섀도 카피 삭제·백업 서비스 중지 명령을 행위 기반으로 탐지(NIST SI-4·CP-9)</t>
+          <t>오프라인·불변 백업과 백업 삭제 방지·권한 분리를 적용(NIST CP-9·SI-4)</t>
         </is>
       </c>
     </row>
@@ -6611,7 +6611,7 @@
       </c>
       <c r="M21" s="9" t="inlineStr">
         <is>
-          <t>내부 취약 서비스 대상 악용 시도와 급격한 횡적 전파를 네트워크 기반으로 탐지(NIST SC-7·RA-5)</t>
+          <t>신속 패치·내부 분할과 취약 서비스 노출 최소화로 전파를 차단(NIST SI-2·RA-5·SC-7)</t>
         </is>
       </c>
     </row>
@@ -6674,7 +6674,7 @@
       </c>
       <c r="M22" s="9" t="inlineStr">
         <is>
-          <t>비정상 LDAP·AD 질의량과 공격 경로 지도화 도구 행위를 아이덴티티 기반으로 탐지(NIST SI-4·AC-6)</t>
+          <t>AD 질의·열거를 감사하고 공격 경로(관리자·신뢰)를 정리·최소화(NIST AC-6·AU-6)</t>
         </is>
       </c>
     </row>
@@ -6737,7 +6737,7 @@
       </c>
       <c r="M23" s="9" t="inlineStr">
         <is>
-          <t>로그 삭제·감사 정책 변경 이벤트와 원격 수집 로그의 공백을 모니터링(NIST AU-6·SI-4)</t>
+          <t>원격·불변 로그 전송과 로그 삭제 방지·보존 정책을 적용(NIST AU-9·AU-6)</t>
         </is>
       </c>
     </row>
@@ -6800,7 +6800,7 @@
       </c>
       <c r="M24" s="9" t="inlineStr">
         <is>
-          <t>정상 다운로드 도구의 비정상 사용·외부 다운로드를 행위·네트워크 기반으로 탐지(NIST SI-4·SC-7)</t>
+          <t>불필요한 다운로드 도구 제한·egress 통제와 반입 파일 검사를 적용(NIST SI-3·SC-7)</t>
         </is>
       </c>
     </row>
@@ -6863,7 +6863,7 @@
       </c>
       <c r="M25" s="9" t="inlineStr">
         <is>
-          <t>HTTP(S) 비컨 주기·사용자 에이전트·목적지 이상을 네트워크 기반으로 탐지(NIST SC-7·SI-4)</t>
+          <t>웹 프록시·egress 통제·목적지 평판과 비컨 탐지를 적용(NIST SC-7·AU-6)</t>
         </is>
       </c>
     </row>
@@ -6926,7 +6926,7 @@
       </c>
       <c r="M26" s="9" t="inlineStr">
         <is>
-          <t>TLS 메타데이터·JA3/비컨 주기·목적지 평판을 네트워크 기반으로 탐지(NIST SC-7·SI-4)</t>
+          <t>egress 통제·TLS 가시성·목적지 평판 차단과 비컨 탐지를 적용(NIST SC-7·AU-6)</t>
         </is>
       </c>
     </row>
@@ -6989,7 +6989,7 @@
       </c>
       <c r="M27" s="9" t="inlineStr">
         <is>
-          <t>신뢰 SaaS로의 비정상 API 호출·데이터량·주기를 네트워크 기반으로 탐지(NIST SC-7·SI-4)</t>
+          <t>허용 SaaS·테넌트 제한과 egress 가시성·이상 사용 탐지를 적용(NIST SC-7·SI-4)</t>
         </is>
       </c>
     </row>
@@ -7052,7 +7052,7 @@
       </c>
       <c r="M28" s="9" t="inlineStr">
         <is>
-          <t>대량 삭제·디스크 와이프·MBR 변조 행위를 행위 기반으로 탐지(NIST SI-4·SI-7)</t>
+          <t>오프라인·불변 백업과 무결성 보호·분할로 파괴 범위를 제한(NIST CP-9·SI-7)</t>
         </is>
       </c>
     </row>
@@ -7115,7 +7115,7 @@
       </c>
       <c r="M29" s="9" t="inlineStr">
         <is>
-          <t>메모리 영역 할당·실행과 비정상 로딩을 EDR 메모리 스캔으로 탐지(NIST SI-3·SI-4)</t>
+          <t>메모리 가시성(EDR)·공격 표면 축소와 스크립트 실행 통제를 적용(NIST SI-3·SI-4)</t>
         </is>
       </c>
     </row>
@@ -7178,7 +7178,7 @@
       </c>
       <c r="M30" s="9" t="inlineStr">
         <is>
-          <t>커널 무결성·드라이버 서명과 메모리·부트 무결성 검증으로 은폐를 탐지(NIST SI-7·SI-4)</t>
+          <t>커널 무결성 보호(HVCI)·보안 부팅과 하위 계층 텔레메트리를 확보(NIST SI-7·SI-4)</t>
         </is>
       </c>
     </row>
@@ -7241,7 +7241,7 @@
       </c>
       <c r="M31" s="9" t="inlineStr">
         <is>
-          <t>원격 스레드 생성·메모리 쓰기·비정상 메모리 영역 실행을 EDR 행위 기반으로 탐지(NIST SI-3·SI-4)</t>
+          <t>커널 수준 메모리 가시성(EDR)과 공격 표면 축소 규칙을 적용(NIST SI-3·SI-4)</t>
         </is>
       </c>
     </row>
@@ -7304,7 +7304,7 @@
       </c>
       <c r="M32" s="9" t="inlineStr">
         <is>
-          <t>신규 커널 드라이버 로드와 취약 드라이버 서명·해시를 차단 목록과 대조해 탐지(NIST SI-4)</t>
+          <t>취약 드라이버 차단 목록(HVCI·드라이버 블록리스트)과 신속 패치를 적용(NIST SI-2·SI-4)</t>
         </is>
       </c>
     </row>
@@ -7367,7 +7367,7 @@
       </c>
       <c r="M33" s="9" t="inlineStr">
         <is>
-          <t>펌웨어·부트 무결성 측정(보안 부팅·측정 부팅)과 펌웨어 버전·해시 변화를 점검(NIST SI-7)</t>
+          <t>보안 부팅·펌웨어 무결성 검증·업데이트와 펌웨어 공급 신뢰를 관리(NIST SI-7·CM-7)</t>
         </is>
       </c>
     </row>
@@ -7430,7 +7430,7 @@
       </c>
       <c r="M34" s="9" t="inlineStr">
         <is>
-          <t>WMI 이벤트 구독·원격 WMI 실행과 비정상 부모-자식 프로세스를 행위 기반으로 탐지(NIST SI-4·AU-6)</t>
+          <t>WMI 원격 실행을 제한하고 관리 활동을 기준선과 대조·감사(NIST CM-7·AU-6)</t>
         </is>
       </c>
     </row>
@@ -7493,7 +7493,7 @@
       </c>
       <c r="M35" s="9" t="inlineStr">
         <is>
-          <t>SNI와 실제 목적지 불일치·비정상 CDN 사용을 네트워크 기반으로 탐지(NIST SC-7·SI-4)</t>
+          <t>TLS 검사·SNI 정책과 프록시 경유 egress 통제를 적용(NIST SC-7·SI-4)</t>
         </is>
       </c>
     </row>
@@ -7556,7 +7556,7 @@
       </c>
       <c r="M36" s="9" t="inlineStr">
         <is>
-          <t>비정상 DNS 질의량·엔트로피·긴 서브도메인을 네트워크 기반으로 탐지(NIST SC-7·SI-4)</t>
+          <t>DNS 로깅·필터링·내부 리졸버 강제와 이상 질의 차단을 적용(NIST SC-7·AU-6)</t>
         </is>
       </c>
     </row>
@@ -7619,7 +7619,7 @@
       </c>
       <c r="M37" s="9" t="inlineStr">
         <is>
-          <t>짧은 시간의 연쇄 탐색 명령과 비정상 열거 패턴을 행위 기반으로 탐지(NIST SI-4·AU-6)</t>
+          <t>탐색 명령 사용을 기준선과 대조·감사하고 최소 기능을 적용(NIST SI-4·AU-6)</t>
         </is>
       </c>
     </row>
@@ -7682,7 +7682,7 @@
       </c>
       <c r="M38" s="9" t="inlineStr">
         <is>
-          <t>대량 파일 열람·공유 접근과 비정상 수집 패턴을 행위 기반으로 탐지(NIST SI-4·AC-6)</t>
+          <t>데이터 접근 최소화·민감 데이터 분류와 접근 감사를 적용(NIST AC-6·SI-4)</t>
         </is>
       </c>
     </row>
@@ -7745,7 +7745,7 @@
       </c>
       <c r="M39" s="9" t="inlineStr">
         <is>
-          <t>신규·수정 예약 작업과 비정상 트리거·실행 바이너리를 행위 기반으로 탐지(NIST SI-4·AU-6)</t>
+          <t>예약 작업 생성·변경을 감사하고 생성 권한을 최소화(NIST CM-7·AU-6)</t>
         </is>
       </c>
     </row>
@@ -7808,7 +7808,7 @@
       </c>
       <c r="M40" s="9" t="inlineStr">
         <is>
-          <t>실행 시점 행위·언패킹과 비정상 인코딩·엔트로피를 행위 기반으로 탐지(NIST SI-3·SI-4)</t>
+          <t>시그니처 의존을 줄이고 행위 기반·샌드박스 분석을 병행(NIST SI-3·SI-4)</t>
         </is>
       </c>
     </row>
@@ -7871,7 +7871,7 @@
       </c>
       <c r="M41" s="9" t="inlineStr">
         <is>
-          <t>키보드 후킹·입력 가로채기 API와 비정상 입력 캡처를 EDR 기반으로 탐지(NIST SI-4·AC-6)</t>
+          <t>엔드포인트 행위 탐지·피싱 내성 MFA로 자격증명 탈취 가치를 낮춤(NIST SI-4·AC-6)</t>
         </is>
       </c>
     </row>
@@ -7934,7 +7934,7 @@
       </c>
       <c r="M42" s="9" t="inlineStr">
         <is>
-          <t>신규·수정 서비스와 비정상 바이너리 경로·시작 유형을 행위 기반으로 탐지(NIST SI-4·CM-7)</t>
+          <t>서비스 생성·변경을 감사·기준선과 대조하고 최소 권한을 적용(NIST CM-7·AU-6)</t>
         </is>
       </c>
     </row>
@@ -7992,12 +7992,12 @@
       </c>
       <c r="L43" s="9" t="inlineStr">
         <is>
-          <t>[실제 사고] LockBit RaaS의 복구 방해·EDR 무력화 암호화(2024-02) (ENI-015)</t>
+          <t>[실제 사고] LockBit 제휴의 복구 방해·EDR 무력화 암호화(CISA 권고)(2023-06) (ENI-015)</t>
         </is>
       </c>
       <c r="M43" s="9" t="inlineStr">
         <is>
-          <t>보안·백업·DB 서비스의 비정상 중지와 대량 종료 명령을 행위 기반으로 탐지(NIST SI-4·CP-10)</t>
+          <t>중요 서비스 변조 방지·권한 분리와 신속 복구 체계를 적용(NIST CP-10·SI-4)</t>
         </is>
       </c>
     </row>
@@ -8060,7 +8060,7 @@
       </c>
       <c r="M44" s="9" t="inlineStr">
         <is>
-          <t>대용량 압축·암호화 산출물 생성과 스테이징 디렉터리 집중을 행위 기반으로 탐지(NIST SI-4·SC-7)</t>
+          <t>비정상 압축·스테이징 탐지와 반출 경로 통제를 병행(NIST SC-7·SI-4)</t>
         </is>
       </c>
     </row>
@@ -8123,7 +8123,7 @@
       </c>
       <c r="M45" s="9" t="inlineStr">
         <is>
-          <t>자동 상승 바이너리의 비정상 실행·레지스트리 조작을 행위 기반으로 탐지(NIST SI-4·CM-7)</t>
+          <t>UAC 최고 수준 설정·관리자 승인 모드와 최소 권한을 적용(NIST AC-6·CM-7)</t>
         </is>
       </c>
     </row>
@@ -8186,7 +8186,7 @@
       </c>
       <c r="M46" s="9" t="inlineStr">
         <is>
-          <t>정상 이름과 다른 경로·서명·해시 불일치를 무결성·행위 기반으로 탐지(NIST SI-4·SI-7)</t>
+          <t>바이너리 무결성·서명 검증과 정상 경로 기준선 대조를 적용(NIST SI-7·SI-4)</t>
         </is>
       </c>
     </row>
@@ -8249,7 +8249,7 @@
       </c>
       <c r="M47" s="9" t="inlineStr">
         <is>
-          <t>내부 호스트 간 비정상 파일 전송·공유 쓰기를 네트워크·엔드포인트 기반으로 탐지(NIST SI-4·SC-7)</t>
+          <t>내부 분할·공유 권한 최소화와 측면 전송 모니터링을 적용(NIST SC-7·SI-4)</t>
         </is>
       </c>
     </row>
@@ -8312,7 +8312,7 @@
       </c>
       <c r="M48" s="9" t="inlineStr">
         <is>
-          <t>이동식 매체 연결·자동 실행과 격리망 호스트의 비정상 실행을 엔드포인트 기반으로 탐지(NIST SI-3)</t>
+          <t>이동식 매체 사용을 통제·차단하고 자동 실행을 비활성화, 격리망 자산 반입 매체를 검사(NIST MP-7·SI-3)</t>
         </is>
       </c>
     </row>
@@ -8375,7 +8375,7 @@
       </c>
       <c r="M49" s="9" t="inlineStr">
         <is>
-          <t>토큰 복제·가장 API 호출과 비정상 권한 전환을 EDR 행위 기반으로 탐지(NIST SI-4·AC-6)</t>
+          <t>최소 권한·특권 계정 분리와 토큰 조작 탐지 규칙을 적용(NIST AC-6·SI-4)</t>
         </is>
       </c>
     </row>
@@ -8438,7 +8438,7 @@
       </c>
       <c r="M50" s="9" t="inlineStr">
         <is>
-          <t>자동 실행 지점(런키·시작 폴더·서비스)의 변경을 기준선과 대조해 탐지(NIST SI-4·SI-7)</t>
+          <t>자동 실행 지점 변경을 감사·무결성 검증하고 최소 기능을 적용(NIST CM-7·SI-7)</t>
         </is>
       </c>
     </row>
@@ -8501,7 +8501,7 @@
       </c>
       <c r="M51" s="9" t="inlineStr">
         <is>
-          <t>신규·변경 계정과 비정상 권한 부여·그룹 추가를 아이덴티티 기반으로 탐지(NIST AC-2·AU-6)</t>
+          <t>계정 생성·권한 변경을 승인·감사하고 휴면·불필요 계정을 정리(NIST AC-2·IA-4)</t>
         </is>
       </c>
     </row>
@@ -8564,7 +8564,7 @@
       </c>
       <c r="M52" s="9" t="inlineStr">
         <is>
-          <t>커널 콜백·시스템 서비스 생성과 비정상 API 호출 시퀀스를 EDR 행위 기반으로 탐지(NIST SI-4)</t>
+          <t>커널 수준 가시성(EDR)과 최소 기능·서비스 생성 통제를 적용(NIST CM-7·SI-4)</t>
         </is>
       </c>
     </row>
@@ -8627,7 +8627,7 @@
       </c>
       <c r="M53" s="9" t="inlineStr">
         <is>
-          <t>엔드포인트의 브라우저·플러그인 비정상 실행과 신뢰 사이트발 악성 리다이렉트를 행위 기반으로 탐지(NIST SI-3·SI-4)</t>
+          <t>브라우저·플러그인 신속 패치, 웹 격리·콘텐츠 필터링과 엔드포인트 행위 탐지를 적용(NIST SI-3·SC-7)</t>
         </is>
       </c>
     </row>
@@ -8690,7 +8690,7 @@
       </c>
       <c r="M54" s="9" t="inlineStr">
         <is>
-          <t>캐시 자격증명 저장소 접근과 비정상 레지스트리·메모리 읽기를 EDR 기반으로 탐지(NIST SI-4·AC-6)</t>
+          <t>캐시 자격증명 수 제한·특권 분리와 강한 암호 정책을 적용(NIST AC-6·SI-4)</t>
         </is>
       </c>
     </row>
@@ -8753,7 +8753,7 @@
       </c>
       <c r="M55" s="9" t="inlineStr">
         <is>
-          <t>보안 제품·서비스 열거 명령과 비정상 조회를 행위 기반으로 탐지(NIST SI-4)</t>
+          <t>보안 제품 상태 변조 방지와 탐지 규칙·텔레메트리 중앙 감시를 적용(NIST SI-4)</t>
         </is>
       </c>
     </row>
@@ -9483,7 +9483,7 @@
       <c r="F5" s="9" t="inlineStr">
         <is>
           <t>- 공격자는 VPN·방화벽·게이트웨이·파일전송 같은 인터넷 노출 엣지 장비의 공개 즉시 악용되는 취약점으로 경계 안으로 바로 들어올 수 있음
-- 엣지 장비는 EDR이 깔리지 않아 레거시 경계 통제로 탐지가 어렵고, KEV 등재가 매년 15~21%를 차지할 만큼 빠른 n-day·0-day가 집중됨</t>
+- 엣지 장비는 EDR이 깔리지 않아 레거시 경계 통제로 탐지가 어렵고, KEV 등재가 매년 14~21%(참고치)를 차지할 만큼 빠른 n-day·0-day가 집중됨</t>
         </is>
       </c>
       <c r="G5" s="9" t="inlineStr">
@@ -9571,7 +9571,7 @@
       </c>
       <c r="AD5" s="9" t="inlineStr">
         <is>
-          <t>VPN·방화벽·게이트웨이·파일전송 장비의 공개 즉시 악용되는 취약점으로 경계 안으로 바로 진입 — 엣지 장비는 EDR이 깔리지 않아 레거시로 탐지가 어렵고 KEV 등재가 매년 15~21%를 차지</t>
+          <t>VPN·방화벽·게이트웨이·파일전송 장비의 공개 즉시 악용되는 취약점으로 경계 안으로 바로 진입 — 엣지 장비는 EDR이 깔리지 않아 레거시로 탐지가 어렵고 KEV 등재가 매년 14~21%를 차지(참고치)</t>
         </is>
       </c>
       <c r="AE5" s="9" t="n">
@@ -9598,7 +9598,7 @@
       </c>
       <c r="AK5" s="9" t="inlineStr">
         <is>
-          <t>내부 접근 확보 6 · 첩보·감시 2 · 데이터 유출 2 · 금전 피해 2</t>
+          <t>내부 접근 확보 6 · 측면 이동·확산 2 · 데이터 유출 2 · 금전 피해 2</t>
         </is>
       </c>
       <c r="AL5" s="9" t="inlineStr">
@@ -17881,7 +17881,7 @@
       <c r="F3" s="9" t="inlineStr">
         <is>
           <t>- 공격자는 VPN·방화벽·게이트웨이·파일전송 같은 인터넷 노출 엣지 장비의 공개 즉시 악용되는 취약점으로 경계 안으로 바로 들어올 수 있음
-- 엣지 장비는 EDR이 깔리지 않아 레거시 경계 통제로 탐지가 어렵고, KEV 등재가 매년 15~21%를 차지할 만큼 빠른 n-day·0-day가 집중됨</t>
+- 엣지 장비는 EDR이 깔리지 않아 레거시 경계 통제로 탐지가 어렵고, KEV 등재가 매년 14~21%(참고치)를 차지할 만큼 빠른 n-day·0-day가 집중됨</t>
         </is>
       </c>
       <c r="G3" s="9" t="inlineStr">
@@ -24933,12 +24933,12 @@
     <row r="12">
       <c r="A12" s="9" t="inlineStr">
         <is>
-          <t>ENI-015</t>
+          <t>ENI-009</t>
         </is>
       </c>
       <c r="B12" s="9" t="inlineStr">
         <is>
-          <t>LockBit RaaS의 복구 방해·EDR 무력화 암호화</t>
+          <t>ConnectWise ScreenConnect 취약점 경유 랜섬웨어</t>
         </is>
       </c>
       <c r="C12" s="9" t="inlineStr">
@@ -24968,45 +24968,45 @@
       </c>
       <c r="H12" s="9" t="inlineStr">
         <is>
-          <t>LockBit</t>
+          <t>다수 랜섬웨어·브로커</t>
         </is>
       </c>
       <c r="I12" s="9" t="inlineStr">
         <is>
-          <t>랜섬웨어</t>
+          <t>랜섬웨어 · 접근 브로커</t>
         </is>
       </c>
       <c r="J12" s="9" t="inlineStr">
         <is>
-          <t>랜섬·암호화 · 서비스 중단</t>
-        </is>
-      </c>
-      <c r="K12" s="9" t="inlineStr"/>
+          <t>내부 접근 확보 · 랜섬·암호화</t>
+        </is>
+      </c>
+      <c r="K12" s="9" t="inlineStr">
+        <is>
+          <t>CVE-2024-1709</t>
+        </is>
+      </c>
       <c r="L12" s="9" t="inlineStr">
         <is>
-          <t>ENT-IM-01, ENT-IM-02, ENT-IM-04, ENT-DE-01.1</t>
-        </is>
-      </c>
-      <c r="M12" s="9" t="inlineStr">
-        <is>
-          <t>S1202</t>
-        </is>
-      </c>
+          <t>ENT-IA-02, ENT-IA-05, ENT-IM-01</t>
+        </is>
+      </c>
+      <c r="M12" s="9" t="inlineStr"/>
       <c r="N12" s="9" t="inlineStr">
         <is>
-          <t>CISA(2024) StopRansomware — LockBit 3.0 update / Operation Cronos | https://www.cisa.gov/news-events/cybersecurity-advisories/aa23-325a</t>
+          <t>CISA(2024) KEV — ConnectWise ScreenConnect Authentication Bypass | https://www.cisa.gov/known-exploited-vulnerabilities-catalog</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="9" t="inlineStr">
         <is>
-          <t>ENI-009</t>
+          <t>ENI-005</t>
         </is>
       </c>
       <c r="B13" s="9" t="inlineStr">
         <is>
-          <t>ConnectWise ScreenConnect 취약점 경유 랜섬웨어</t>
+          <t>Fortinet FortiOS SSL-VPN 취약점 악용</t>
         </is>
       </c>
       <c r="C13" s="9" t="inlineStr">
@@ -25036,45 +25036,45 @@
       </c>
       <c r="H13" s="9" t="inlineStr">
         <is>
-          <t>다수 랜섬웨어·브로커</t>
+          <t>다수(국가배후·랜섬웨어)</t>
         </is>
       </c>
       <c r="I13" s="9" t="inlineStr">
         <is>
-          <t>랜섬웨어 · 접근 브로커</t>
+          <t>국가배후 · 랜섬웨어 · 접근 브로커</t>
         </is>
       </c>
       <c r="J13" s="9" t="inlineStr">
         <is>
-          <t>내부 접근 확보 · 랜섬·암호화</t>
+          <t>내부 접근 확보</t>
         </is>
       </c>
       <c r="K13" s="9" t="inlineStr">
         <is>
-          <t>CVE-2024-1709</t>
+          <t>CVE-2024-21762, CVE-2022-42475, CVE-2023-27997</t>
         </is>
       </c>
       <c r="L13" s="9" t="inlineStr">
         <is>
-          <t>ENT-IA-02, ENT-IA-05, ENT-IM-01</t>
+          <t>ENT-IA-01</t>
         </is>
       </c>
       <c r="M13" s="9" t="inlineStr"/>
       <c r="N13" s="9" t="inlineStr">
         <is>
-          <t>CISA(2024) KEV — ConnectWise ScreenConnect Authentication Bypass | https://www.cisa.gov/known-exploited-vulnerabilities-catalog</t>
+          <t>CISA(2024) KEV — Fortinet FortiOS Out-of-bound Write (CVE-2024-21762) | https://www.cisa.gov/known-exploited-vulnerabilities-catalog</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="9" t="inlineStr">
         <is>
-          <t>ENI-005</t>
+          <t>ENI-001</t>
         </is>
       </c>
       <c r="B14" s="9" t="inlineStr">
         <is>
-          <t>Fortinet FortiOS SSL-VPN 취약점 악용</t>
+          <t>Volt Typhoon의 LotL 기반 핵심 기반시설 장기 침투</t>
         </is>
       </c>
       <c r="C14" s="9" t="inlineStr">
@@ -25094,60 +25094,60 @@
       </c>
       <c r="F14" s="9" t="inlineStr">
         <is>
-          <t>글로벌</t>
+          <t>미국</t>
         </is>
       </c>
       <c r="G14" s="9" t="inlineStr">
         <is>
-          <t>다부문</t>
+          <t>에너지·기반시설 · 통신·미디어</t>
         </is>
       </c>
       <c r="H14" s="9" t="inlineStr">
         <is>
-          <t>다수(국가배후·랜섬웨어)</t>
+          <t>Volt Typhoon(중국 연계)</t>
         </is>
       </c>
       <c r="I14" s="9" t="inlineStr">
         <is>
-          <t>국가배후 · 랜섬웨어 · 접근 브로커</t>
+          <t>국가배후</t>
         </is>
       </c>
       <c r="J14" s="9" t="inlineStr">
         <is>
-          <t>내부 접근 확보</t>
-        </is>
-      </c>
-      <c r="K14" s="9" t="inlineStr">
-        <is>
-          <t>CVE-2024-21762, CVE-2022-42475, CVE-2023-27997</t>
-        </is>
-      </c>
+          <t>내부 접근 확보 · 첩보·감시 · 측면 이동·확산</t>
+        </is>
+      </c>
+      <c r="K14" s="9" t="inlineStr"/>
       <c r="L14" s="9" t="inlineStr">
         <is>
-          <t>ENT-IA-01</t>
-        </is>
-      </c>
-      <c r="M14" s="9" t="inlineStr"/>
+          <t>ENT-IA-01, ENT-EX-01.1, ENT-EX-03, ENT-DI-01, ENT-DI-02, ENT-CA-01.1, ENT-LM-01, ENT-DE-03</t>
+        </is>
+      </c>
+      <c r="M14" s="9" t="inlineStr">
+        <is>
+          <t>G1017</t>
+        </is>
+      </c>
       <c r="N14" s="9" t="inlineStr">
         <is>
-          <t>CISA(2024) KEV — Fortinet FortiOS Out-of-bound Write (CVE-2024-21762) | https://www.cisa.gov/known-exploited-vulnerabilities-catalog</t>
+          <t>CISA(2024) PRC State-Sponsored Actors Compromise and Maintain Persistent Access (AA24-038A) | https://www.cisa.gov/news-events/cybersecurity-advisories/aa24-038a</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="9" t="inlineStr">
         <is>
-          <t>ENI-001</t>
+          <t>ENI-033</t>
         </is>
       </c>
       <c r="B15" s="9" t="inlineStr">
         <is>
-          <t>Volt Typhoon의 LotL 기반 핵심 기반시설 장기 침투</t>
+          <t>지표 삭제·위장·난독화를 통한 사후 분석 방해</t>
         </is>
       </c>
       <c r="C15" s="9" t="inlineStr">
         <is>
-          <t>2024-02</t>
+          <t>2024-01</t>
         </is>
       </c>
       <c r="D15" s="9" t="inlineStr">
@@ -25162,55 +25162,51 @@
       </c>
       <c r="F15" s="9" t="inlineStr">
         <is>
-          <t>미국</t>
+          <t>글로벌</t>
         </is>
       </c>
       <c r="G15" s="9" t="inlineStr">
         <is>
-          <t>에너지·기반시설 · 통신·미디어</t>
+          <t>다부문</t>
         </is>
       </c>
       <c r="H15" s="9" t="inlineStr">
         <is>
-          <t>Volt Typhoon(중국 연계)</t>
+          <t>다수(국가배후·랜섬웨어)</t>
         </is>
       </c>
       <c r="I15" s="9" t="inlineStr">
         <is>
-          <t>국가배후</t>
+          <t>국가배후 · 랜섬웨어</t>
         </is>
       </c>
       <c r="J15" s="9" t="inlineStr">
         <is>
-          <t>내부 접근 확보 · 첩보·감시 · 측면 이동·확산</t>
+          <t>내부 접근 확보</t>
         </is>
       </c>
       <c r="K15" s="9" t="inlineStr"/>
       <c r="L15" s="9" t="inlineStr">
         <is>
-          <t>ENT-IA-01, ENT-EX-01.1, ENT-EX-03, ENT-DI-01, ENT-DI-02, ENT-CA-01.1, ENT-LM-01, ENT-DE-03</t>
-        </is>
-      </c>
-      <c r="M15" s="9" t="inlineStr">
-        <is>
-          <t>G1017</t>
-        </is>
-      </c>
+          <t>ENT-DE-03, ENT-DE-04, ENT-DE-05, ENT-CA-04</t>
+        </is>
+      </c>
+      <c r="M15" s="9" t="inlineStr"/>
       <c r="N15" s="9" t="inlineStr">
         <is>
-          <t>CISA(2024) PRC State-Sponsored Actors Compromise and Maintain Persistent Access (AA24-038A) | https://www.cisa.gov/news-events/cybersecurity-advisories/aa24-038a</t>
+          <t>MITRE ATT&amp;CK(2026) Indicator Removal (T1070) | https://attack.mitre.org/techniques/T1070/</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="9" t="inlineStr">
         <is>
-          <t>ENI-033</t>
+          <t>ENI-006</t>
         </is>
       </c>
       <c r="B16" s="9" t="inlineStr">
         <is>
-          <t>지표 삭제·위장·난독화를 통한 사후 분석 방해</t>
+          <t>Ivanti Connect Secure VPN 연쇄 0-day 악용(2024)</t>
         </is>
       </c>
       <c r="C16" s="9" t="inlineStr">
@@ -25240,46 +25236,50 @@
       </c>
       <c r="H16" s="9" t="inlineStr">
         <is>
-          <t>다수(국가배후·랜섬웨어)</t>
+          <t>국가배후·다수 행위자</t>
         </is>
       </c>
       <c r="I16" s="9" t="inlineStr">
         <is>
-          <t>국가배후 · 랜섬웨어</t>
+          <t>국가배후 · 접근 브로커</t>
         </is>
       </c>
       <c r="J16" s="9" t="inlineStr">
         <is>
-          <t>내부 접근 확보</t>
-        </is>
-      </c>
-      <c r="K16" s="9" t="inlineStr"/>
+          <t>내부 접근 확보 · 측면 이동·확산</t>
+        </is>
+      </c>
+      <c r="K16" s="9" t="inlineStr">
+        <is>
+          <t>CVE-2023-46805, CVE-2024-21887</t>
+        </is>
+      </c>
       <c r="L16" s="9" t="inlineStr">
         <is>
-          <t>ENT-DE-03, ENT-DE-04, ENT-DE-05, ENT-CA-04</t>
+          <t>ENT-IA-01</t>
         </is>
       </c>
       <c r="M16" s="9" t="inlineStr"/>
       <c r="N16" s="9" t="inlineStr">
         <is>
-          <t>MITRE ATT&amp;CK(2026) Indicator Removal (T1070) | https://attack.mitre.org/techniques/T1070/</t>
+          <t>CISA(2024) Threat Actors Exploit Multiple Vulnerabilities in Ivanti Connect Secure and Policy Secure (AA24-060B) | https://www.cisa.gov/news-events/cybersecurity-advisories/aa24-060b</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="9" t="inlineStr">
         <is>
-          <t>ENI-006</t>
+          <t>ENI-013</t>
         </is>
       </c>
       <c r="B17" s="9" t="inlineStr">
         <is>
-          <t>Ivanti Connect Secure VPN 연쇄 0-day 악용</t>
+          <t>Scattered Spider의 헬프데스크 사칭·EDR 회피 침투</t>
         </is>
       </c>
       <c r="C17" s="9" t="inlineStr">
         <is>
-          <t>2024-01</t>
+          <t>2023-11</t>
         </is>
       </c>
       <c r="D17" s="9" t="inlineStr">
@@ -25294,60 +25294,60 @@
       </c>
       <c r="F17" s="9" t="inlineStr">
         <is>
-          <t>글로벌</t>
+          <t>미국</t>
         </is>
       </c>
       <c r="G17" s="9" t="inlineStr">
         <is>
-          <t>정부·군 · 다부문</t>
+          <t>금융·서비스 · 통신·미디어 · 숙박·여행</t>
         </is>
       </c>
       <c r="H17" s="9" t="inlineStr">
         <is>
-          <t>국가배후·다수 행위자</t>
+          <t>Scattered Spider</t>
         </is>
       </c>
       <c r="I17" s="9" t="inlineStr">
         <is>
-          <t>국가배후 · 접근 브로커</t>
+          <t>사이버범죄 · 랜섬웨어 · 접근 브로커</t>
         </is>
       </c>
       <c r="J17" s="9" t="inlineStr">
         <is>
-          <t>내부 접근 확보 · 첩보·감시</t>
-        </is>
-      </c>
-      <c r="K17" s="9" t="inlineStr">
-        <is>
-          <t>CVE-2023-46805, CVE-2024-21887, CVE-2025-0282</t>
-        </is>
-      </c>
+          <t>내부 접근 확보 · 랜섬·암호화 · 데이터 유출</t>
+        </is>
+      </c>
+      <c r="K17" s="9" t="inlineStr"/>
       <c r="L17" s="9" t="inlineStr">
         <is>
-          <t>ENT-IA-01</t>
-        </is>
-      </c>
-      <c r="M17" s="9" t="inlineStr"/>
+          <t>ENT-IA-02, ENT-DE-01.1, ENT-LM-01, ENT-LM-03, ENT-IM-01</t>
+        </is>
+      </c>
+      <c r="M17" s="9" t="inlineStr">
+        <is>
+          <t>G1015</t>
+        </is>
+      </c>
       <c r="N17" s="9" t="inlineStr">
         <is>
-          <t>CISA(2024) Ivanti Connect Secure and Policy Secure Exploitation (AA24-016A) | https://www.cisa.gov/news-events/cybersecurity-advisories/aa24-016a</t>
+          <t>CISA(2023) Scattered Spider (AA23-320A) | https://www.cisa.gov/news-events/cybersecurity-advisories/aa23-320a</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="9" t="inlineStr">
         <is>
-          <t>ENI-013</t>
+          <t>ENI-007</t>
         </is>
       </c>
       <c r="B18" s="9" t="inlineStr">
         <is>
-          <t>Scattered Spider의 헬프데스크 사칭·EDR 회피 침투</t>
+          <t>Cisco IOS XE 웹 UI 취약점 대량 임플란트 설치</t>
         </is>
       </c>
       <c r="C18" s="9" t="inlineStr">
         <is>
-          <t>2023-11</t>
+          <t>2023-10</t>
         </is>
       </c>
       <c r="D18" s="9" t="inlineStr">
@@ -25362,55 +25362,55 @@
       </c>
       <c r="F18" s="9" t="inlineStr">
         <is>
-          <t>미국</t>
+          <t>글로벌</t>
         </is>
       </c>
       <c r="G18" s="9" t="inlineStr">
         <is>
-          <t>금융·서비스 · 통신·미디어 · 숙박·여행</t>
+          <t>다부문</t>
         </is>
       </c>
       <c r="H18" s="9" t="inlineStr">
         <is>
-          <t>Scattered Spider</t>
+          <t>미상</t>
         </is>
       </c>
       <c r="I18" s="9" t="inlineStr">
         <is>
-          <t>사이버범죄 · 랜섬웨어 · 접근 브로커</t>
+          <t>국가배후 · 접근 브로커</t>
         </is>
       </c>
       <c r="J18" s="9" t="inlineStr">
         <is>
-          <t>내부 접근 확보 · 랜섬·암호화 · 데이터 유출</t>
-        </is>
-      </c>
-      <c r="K18" s="9" t="inlineStr"/>
+          <t>내부 접근 확보</t>
+        </is>
+      </c>
+      <c r="K18" s="9" t="inlineStr">
+        <is>
+          <t>CVE-2023-20198</t>
+        </is>
+      </c>
       <c r="L18" s="9" t="inlineStr">
         <is>
-          <t>ENT-IA-02, ENT-DE-01.1, ENT-LM-01, ENT-LM-03, ENT-IM-01</t>
-        </is>
-      </c>
-      <c r="M18" s="9" t="inlineStr">
-        <is>
-          <t>G1015</t>
-        </is>
-      </c>
+          <t>ENT-IA-01</t>
+        </is>
+      </c>
+      <c r="M18" s="9" t="inlineStr"/>
       <c r="N18" s="9" t="inlineStr">
         <is>
-          <t>CISA(2023) Scattered Spider (AA23-320A) | https://www.cisa.gov/news-events/cybersecurity-advisories/aa23-320a</t>
+          <t>Cisco Talos(2023) Active exploitation of Cisco IOS XE Web UI | https://blog.talosintelligence.com/active-exploitation-of-cisco-ios-xe-software-web-management-user-interface/</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="9" t="inlineStr">
         <is>
-          <t>ENI-007</t>
+          <t>ENI-003</t>
         </is>
       </c>
       <c r="B19" s="9" t="inlineStr">
         <is>
-          <t>Cisco IOS XE 웹 UI 취약점 대량 임플란트 설치</t>
+          <t>Citrix Bleed NetScaler 세션 토큰 탈취 대량 악용</t>
         </is>
       </c>
       <c r="C19" s="9" t="inlineStr">
@@ -25440,22 +25440,22 @@
       </c>
       <c r="H19" s="9" t="inlineStr">
         <is>
-          <t>미상</t>
+          <t>LockBit 제휴·다수 행위자</t>
         </is>
       </c>
       <c r="I19" s="9" t="inlineStr">
         <is>
-          <t>국가배후 · 접근 브로커</t>
+          <t>랜섬웨어 · 접근 브로커</t>
         </is>
       </c>
       <c r="J19" s="9" t="inlineStr">
         <is>
-          <t>내부 접근 확보</t>
+          <t>내부 접근 확보 · 랜섬·암호화</t>
         </is>
       </c>
       <c r="K19" s="9" t="inlineStr">
         <is>
-          <t>CVE-2023-20198</t>
+          <t>CVE-2023-4966</t>
         </is>
       </c>
       <c r="L19" s="9" t="inlineStr">
@@ -25466,24 +25466,24 @@
       <c r="M19" s="9" t="inlineStr"/>
       <c r="N19" s="9" t="inlineStr">
         <is>
-          <t>Cisco Talos(2023) Active exploitation of Cisco IOS XE Web UI | https://blog.talosintelligence.com/active-exploitation-of-cisco-ios-xe-software-web-management-user-interface/</t>
+          <t>CISA(2023) Threat Actors Exploiting Citrix CVE-2023-4966 (AA23-325A) | https://www.cisa.gov/news-events/cybersecurity-advisories/aa23-325a</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="9" t="inlineStr">
         <is>
-          <t>ENI-003</t>
+          <t>ENI-027</t>
         </is>
       </c>
       <c r="B20" s="9" t="inlineStr">
         <is>
-          <t>Citrix Bleed NetScaler 세션 토큰 탈취 대량 악용</t>
+          <t>DNS 터널링 기반 은닉 C2·반출</t>
         </is>
       </c>
       <c r="C20" s="9" t="inlineStr">
         <is>
-          <t>2023-10</t>
+          <t>2023-09</t>
         </is>
       </c>
       <c r="D20" s="9" t="inlineStr">
@@ -25508,50 +25508,46 @@
       </c>
       <c r="H20" s="9" t="inlineStr">
         <is>
-          <t>LockBit 제휴·다수 행위자</t>
+          <t>다수(국가배후·사이버범죄)</t>
         </is>
       </c>
       <c r="I20" s="9" t="inlineStr">
         <is>
-          <t>랜섬웨어 · 접근 브로커</t>
+          <t>국가배후 · 사이버범죄</t>
         </is>
       </c>
       <c r="J20" s="9" t="inlineStr">
         <is>
-          <t>내부 접근 확보 · 랜섬·암호화</t>
-        </is>
-      </c>
-      <c r="K20" s="9" t="inlineStr">
-        <is>
-          <t>CVE-2023-4966</t>
-        </is>
-      </c>
+          <t>데이터 유출 · 내부 접근 확보</t>
+        </is>
+      </c>
+      <c r="K20" s="9" t="inlineStr"/>
       <c r="L20" s="9" t="inlineStr">
         <is>
-          <t>ENT-IA-01</t>
+          <t>ENT-C2-06, ENT-EF-01</t>
         </is>
       </c>
       <c r="M20" s="9" t="inlineStr"/>
       <c r="N20" s="9" t="inlineStr">
         <is>
-          <t>CISA(2023) Threat Actors Exploiting Citrix CVE-2023-4966 (AA23-325A) | https://www.cisa.gov/news-events/cybersecurity-advisories/aa23-325a</t>
+          <t>Unit 42(2023) DNS tunneling in the wild | https://unit42.paloaltonetworks.com/dns-tunneling-abuse/</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="9" t="inlineStr">
         <is>
-          <t>ENI-027</t>
+          <t>ENI-032</t>
         </is>
       </c>
       <c r="B21" s="9" t="inlineStr">
         <is>
-          <t>DNS 터널링 기반 은닉 C2·반출</t>
+          <t>UAC 우회·토큰 조작을 통한 로컬 권한 상승</t>
         </is>
       </c>
       <c r="C21" s="9" t="inlineStr">
         <is>
-          <t>2023-09</t>
+          <t>2023-08</t>
         </is>
       </c>
       <c r="D21" s="9" t="inlineStr">
@@ -25576,46 +25572,46 @@
       </c>
       <c r="H21" s="9" t="inlineStr">
         <is>
-          <t>다수(국가배후·사이버범죄)</t>
+          <t>다수</t>
         </is>
       </c>
       <c r="I21" s="9" t="inlineStr">
         <is>
-          <t>국가배후 · 사이버범죄</t>
+          <t>사이버범죄 · 랜섬웨어</t>
         </is>
       </c>
       <c r="J21" s="9" t="inlineStr">
         <is>
-          <t>데이터 유출 · 내부 접근 확보</t>
+          <t>내부 접근 확보</t>
         </is>
       </c>
       <c r="K21" s="9" t="inlineStr"/>
       <c r="L21" s="9" t="inlineStr">
         <is>
-          <t>ENT-C2-06, ENT-EF-01</t>
+          <t>ENT-PV-03, ENT-PV-01.2, ENT-PE-01</t>
         </is>
       </c>
       <c r="M21" s="9" t="inlineStr"/>
       <c r="N21" s="9" t="inlineStr">
         <is>
-          <t>Unit 42(2023) DNS tunneling in the wild | https://unit42.paloaltonetworks.com/dns-tunneling-abuse/</t>
+          <t>MITRE ATT&amp;CK(2026) Abuse Elevation Control Mechanism — Bypass UAC (T1548.002) | https://attack.mitre.org/techniques/T1548/002/</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="9" t="inlineStr">
         <is>
-          <t>ENI-032</t>
+          <t>ENI-023</t>
         </is>
       </c>
       <c r="B22" s="9" t="inlineStr">
         <is>
-          <t>UAC 우회·토큰 조작을 통한 로컬 권한 상승</t>
+          <t>Kerberoasting을 통한 도메인 권한 계정 탈취</t>
         </is>
       </c>
       <c r="C22" s="9" t="inlineStr">
         <is>
-          <t>2023-08</t>
+          <t>2023-07</t>
         </is>
       </c>
       <c r="D22" s="9" t="inlineStr">
@@ -25640,46 +25636,46 @@
       </c>
       <c r="H22" s="9" t="inlineStr">
         <is>
-          <t>다수</t>
+          <t>다수(랜섬웨어·국가배후)</t>
         </is>
       </c>
       <c r="I22" s="9" t="inlineStr">
         <is>
-          <t>사이버범죄 · 랜섬웨어</t>
+          <t>랜섬웨어 · 국가배후</t>
         </is>
       </c>
       <c r="J22" s="9" t="inlineStr">
         <is>
-          <t>내부 접근 확보</t>
+          <t>자격증명·비밀 탈취 · 측면 이동·확산</t>
         </is>
       </c>
       <c r="K22" s="9" t="inlineStr"/>
       <c r="L22" s="9" t="inlineStr">
         <is>
-          <t>ENT-PV-03, ENT-PV-01.2, ENT-PE-01</t>
+          <t>ENT-CA-03, ENT-DI-02</t>
         </is>
       </c>
       <c r="M22" s="9" t="inlineStr"/>
       <c r="N22" s="9" t="inlineStr">
         <is>
-          <t>MITRE ATT&amp;CK(2026) Abuse Elevation Control Mechanism — Bypass UAC (T1548.002) | https://attack.mitre.org/techniques/T1548/002/</t>
+          <t>Microsoft(2023) Detecting and mitigating Kerberoasting | https://www.microsoft.com/en-us/security/blog/</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="9" t="inlineStr">
         <is>
-          <t>ENI-023</t>
+          <t>ENI-029</t>
         </is>
       </c>
       <c r="B23" s="9" t="inlineStr">
         <is>
-          <t>Kerberoasting을 통한 도메인 권한 계정 탈취</t>
+          <t>이동식 매체(USB) 경유 격리망 침투·전파</t>
         </is>
       </c>
       <c r="C23" s="9" t="inlineStr">
         <is>
-          <t>2023-07</t>
+          <t>2023-06</t>
         </is>
       </c>
       <c r="D23" s="9" t="inlineStr">
@@ -25694,51 +25690,51 @@
       </c>
       <c r="F23" s="9" t="inlineStr">
         <is>
-          <t>글로벌</t>
+          <t>유럽</t>
         </is>
       </c>
       <c r="G23" s="9" t="inlineStr">
         <is>
-          <t>다부문</t>
+          <t>정부·군 · 에너지·기반시설</t>
         </is>
       </c>
       <c r="H23" s="9" t="inlineStr">
         <is>
-          <t>다수(랜섬웨어·국가배후)</t>
+          <t>Gamaredon 등(러시아 연계)</t>
         </is>
       </c>
       <c r="I23" s="9" t="inlineStr">
         <is>
-          <t>랜섬웨어 · 국가배후</t>
+          <t>국가배후</t>
         </is>
       </c>
       <c r="J23" s="9" t="inlineStr">
         <is>
-          <t>자격증명·비밀 탈취 · 측면 이동·확산</t>
+          <t>내부 접근 확보 · 측면 이동·확산</t>
         </is>
       </c>
       <c r="K23" s="9" t="inlineStr"/>
       <c r="L23" s="9" t="inlineStr">
         <is>
-          <t>ENT-CA-03, ENT-DI-02</t>
+          <t>ENT-IA-04</t>
         </is>
       </c>
       <c r="M23" s="9" t="inlineStr"/>
       <c r="N23" s="9" t="inlineStr">
         <is>
-          <t>Microsoft(2023) Detecting and mitigating Kerberoasting | https://www.microsoft.com/en-us/security/blog/</t>
+          <t>ESET(2023) Gamaredon's USB-spreading tooling | https://www.welivesecurity.com/</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="9" t="inlineStr">
         <is>
-          <t>ENI-029</t>
+          <t>ENI-015</t>
         </is>
       </c>
       <c r="B24" s="9" t="inlineStr">
         <is>
-          <t>이동식 매체(USB) 경유 격리망 침투·전파</t>
+          <t>LockBit 제휴의 복구 방해·EDR 무력화 암호화(CISA 권고)</t>
         </is>
       </c>
       <c r="C24" s="9" t="inlineStr">
@@ -25758,39 +25754,40 @@
       </c>
       <c r="F24" s="9" t="inlineStr">
         <is>
-          <t>유럽</t>
+          <t>글로벌</t>
         </is>
       </c>
       <c r="G24" s="9" t="inlineStr">
         <is>
-          <t>정부·군 · 에너지·기반시설</t>
+          <t>다부문</t>
         </is>
       </c>
       <c r="H24" s="9" t="inlineStr">
         <is>
-          <t>Gamaredon 등(러시아 연계)</t>
+          <t>LockBit(RaaS)</t>
         </is>
       </c>
       <c r="I24" s="9" t="inlineStr">
         <is>
-          <t>국가배후</t>
+          <t>랜섬웨어</t>
         </is>
       </c>
       <c r="J24" s="9" t="inlineStr">
         <is>
-          <t>내부 접근 확보 · 측면 이동·확산</t>
+          <t>랜섬·암호화 · 서비스 중단</t>
         </is>
       </c>
       <c r="K24" s="9" t="inlineStr"/>
       <c r="L24" s="9" t="inlineStr">
         <is>
-          <t>ENT-IA-04</t>
+          <t>ENT-IM-01, ENT-IM-02, ENT-IM-04, ENT-DE-01.1</t>
         </is>
       </c>
       <c r="M24" s="9" t="inlineStr"/>
       <c r="N24" s="9" t="inlineStr">
         <is>
-          <t>ESET(2023) Gamaredon's USB-spreading tooling | https://www.welivesecurity.com/</t>
+          <t>{'CISA(2023) Understanding Ransomware Threat Actors': 'LockBit (AA23-165A) | https://www.cisa.gov/news-events/cybersecurity-advisories/aa23-165a'}
+NCA(2024) Operation Cronos — international disruption of LockBit | https://www.nationalcrimeagency.gov.uk/news/nca-leads-international-investigation-targeting-lockbit</t>
         </is>
       </c>
     </row>
@@ -26382,7 +26379,7 @@
       </c>
       <c r="N33" s="9" t="inlineStr">
         <is>
-          <t>CISA(2018) Russian Military 'NotPetya' Attribution | https://www.cisa.gov/news-events/alerts</t>
+          <t>US-CERT(2017) Petya Ransomware (TA17-181A; 2018-02 미·영 정부의 러시아군 귀속 반영) | https://www.cisa.gov/news-events/alerts/2017/07/01/petya-ransomware</t>
         </is>
       </c>
     </row>

--- a/enterprise/output/통합_고도화엔터프라이즈_보안위협_매트릭스_v2.xlsx
+++ b/enterprise/output/통합_고도화엔터프라이즈_보안위협_매트릭스_v2.xlsx
@@ -24,8 +24,8 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="변경이력" sheetId="15" state="visible" r:id="rId15"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'보고서용 간략 매트릭스'!$A$4:$M$55</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'통합 매트릭스'!$A$4:$AN$55</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'보고서용 간략 매트릭스'!$A$4:$N$55</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'통합 매트릭스'!$A$4:$AO$55</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'통합매트릭스_LITE'!$A$2:$R$53</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">'역매핑_사고사례'!$A$1:$N$34</definedName>
   </definedNames>
@@ -4964,7 +4964,7 @@
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>성공하면 도메인·조직 전반이 장악되거나 대규모 암호화·파괴·유출로 이어지고, 레거시 방어로는 사실상 탐지되지 않아 피해 범위를 가늠하기 어려운 위협</t>
+          <t>성공하면 도메인·조직 전반이 장악되거나 대규모 암호화·파괴·유출·가용성/안전 피해로 이어지는 위협(영향만으로 판정 — 레거시 미탐지·탐지 난이도는 고유 축·우선순위로, 검토 6.1. 행별 재판정은 영역 2 P1~P4 일괄 반영 예정)</t>
         </is>
       </c>
     </row>
@@ -5445,7 +5445,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M55"/>
+  <dimension ref="A1:N55"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -5510,35 +5510,40 @@
       </c>
       <c r="G4" s="7" t="inlineStr">
         <is>
+          <t>경계</t>
+        </is>
+      </c>
+      <c r="H4" s="7" t="inlineStr">
+        <is>
           <t>발생가능성</t>
         </is>
       </c>
-      <c r="H4" s="7" t="inlineStr">
+      <c r="I4" s="7" t="inlineStr">
         <is>
           <t>심각도</t>
         </is>
       </c>
-      <c r="I4" s="7" t="inlineStr">
+      <c r="J4" s="7" t="inlineStr">
         <is>
           <t>요구 방어 수준</t>
         </is>
       </c>
-      <c r="J4" s="7" t="inlineStr">
+      <c r="K4" s="7" t="inlineStr">
         <is>
           <t>레거시 공백</t>
         </is>
       </c>
-      <c r="K4" s="7" t="inlineStr">
+      <c r="L4" s="7" t="inlineStr">
         <is>
           <t>실제 사고</t>
         </is>
       </c>
-      <c r="L4" s="7" t="inlineStr">
+      <c r="M4" s="7" t="inlineStr">
         <is>
           <t>대표 사례</t>
         </is>
       </c>
-      <c r="M4" s="7" t="inlineStr">
+      <c r="N4" s="7" t="inlineStr">
         <is>
           <t>핵심 대응</t>
         </is>
@@ -5573,35 +5578,36 @@
           <t>매우 높음</t>
         </is>
       </c>
-      <c r="G5" s="8" t="inlineStr">
+      <c r="G5" s="8" t="inlineStr"/>
+      <c r="H5" s="8" t="inlineStr">
         <is>
           <t>상</t>
         </is>
       </c>
-      <c r="H5" s="8" t="inlineStr">
+      <c r="I5" s="9" t="inlineStr">
         <is>
           <t>상</t>
         </is>
       </c>
-      <c r="I5" s="9" t="inlineStr">
+      <c r="J5" s="9" t="inlineStr">
         <is>
           <t>행위·네트워크·아이덴티티</t>
         </is>
       </c>
-      <c r="J5" s="9" t="inlineStr">
+      <c r="K5" s="8" t="inlineStr">
         <is>
           <t>경계 밖·비관리 장비 · 신뢰·공급 관계 경유</t>
         </is>
       </c>
-      <c r="K5" s="8" t="n">
+      <c r="L5" s="9" t="n">
         <v>8</v>
       </c>
-      <c r="L5" s="9" t="inlineStr">
+      <c r="M5" s="9" t="inlineStr">
         <is>
           <t>[실제 사고] Cl0p의 Cleo 파일전송 취약점 대량 악용(2024-12) (ENI-010)</t>
         </is>
       </c>
-      <c r="M5" s="9" t="inlineStr">
+      <c r="N5" s="9" t="inlineStr">
         <is>
           <t>엣지 장비 신속 패치·가상 패치와 공개 취약점 노출 구간 최소화(NIST SI-2·RA-5)</t>
         </is>
@@ -5636,35 +5642,36 @@
           <t>매우 높음</t>
         </is>
       </c>
-      <c r="G6" s="8" t="inlineStr">
+      <c r="G6" s="8" t="inlineStr"/>
+      <c r="H6" s="8" t="inlineStr">
         <is>
           <t>상</t>
         </is>
       </c>
-      <c r="H6" s="8" t="inlineStr">
+      <c r="I6" s="9" t="inlineStr">
         <is>
           <t>상</t>
         </is>
       </c>
-      <c r="I6" s="9" t="inlineStr">
+      <c r="J6" s="9" t="inlineStr">
         <is>
           <t>행위·네트워크·아이덴티티</t>
         </is>
       </c>
-      <c r="J6" s="9" t="inlineStr">
+      <c r="K6" s="8" t="inlineStr">
         <is>
           <t>서명된 정상 도구 악용</t>
         </is>
       </c>
-      <c r="K6" s="8" t="n">
+      <c r="L6" s="9" t="n">
         <v>7</v>
       </c>
-      <c r="L6" s="9" t="inlineStr">
+      <c r="M6" s="9" t="inlineStr">
         <is>
           <t>[실제 사고] Black Basta 사람 운영 랜섬웨어(LotL·BYOVD·AD 확산)(2024-05) (ENI-012)</t>
         </is>
       </c>
-      <c r="M6" s="9" t="inlineStr">
+      <c r="N6" s="9" t="inlineStr">
         <is>
           <t>오프라인·불변 백업·복구 훈련과 선행 단계 조기 차단·분할을 적용(NIST CP-9·CP-10·SI-4)</t>
         </is>
@@ -5699,35 +5706,36 @@
           <t>매우 높음</t>
         </is>
       </c>
-      <c r="G7" s="8" t="inlineStr">
+      <c r="G7" s="8" t="inlineStr"/>
+      <c r="H7" s="8" t="inlineStr">
         <is>
           <t>상</t>
         </is>
       </c>
-      <c r="H7" s="8" t="inlineStr">
+      <c r="I7" s="9" t="inlineStr">
         <is>
           <t>상</t>
         </is>
       </c>
-      <c r="I7" s="9" t="inlineStr">
+      <c r="J7" s="9" t="inlineStr">
         <is>
           <t>행위·네트워크·아이덴티티</t>
         </is>
       </c>
-      <c r="J7" s="9" t="inlineStr">
+      <c r="K7" s="8" t="inlineStr">
         <is>
           <t>커널·펌웨어 하위 계층 · 서명된 정상 도구 악용</t>
         </is>
       </c>
-      <c r="K7" s="8" t="n">
+      <c r="L7" s="9" t="n">
         <v>5</v>
       </c>
-      <c r="L7" s="9" t="inlineStr">
+      <c r="M7" s="9" t="inlineStr">
         <is>
           <t>[실제 사고] 서명된 취약 드라이버 대량 변종 캠페인(TrueSight 등)(2025-01) (ENI-017)</t>
         </is>
       </c>
-      <c r="M7" s="9" t="inlineStr">
+      <c r="N7" s="9" t="inlineStr">
         <is>
           <t>취약 드라이버 차단 목록(HVCI·블록리스트)·변조 방지와 보안 도구 상태를 중앙 감시(NIST SI-7·CM-7)</t>
         </is>
@@ -5762,35 +5770,36 @@
           <t>매우 높음</t>
         </is>
       </c>
-      <c r="G8" s="8" t="inlineStr">
+      <c r="G8" s="8" t="inlineStr"/>
+      <c r="H8" s="8" t="inlineStr">
         <is>
           <t>상</t>
         </is>
       </c>
-      <c r="H8" s="8" t="inlineStr">
+      <c r="I8" s="9" t="inlineStr">
         <is>
           <t>상</t>
         </is>
       </c>
-      <c r="I8" s="9" t="inlineStr">
+      <c r="J8" s="9" t="inlineStr">
         <is>
           <t>행위·네트워크·아이덴티티</t>
         </is>
       </c>
-      <c r="J8" s="9" t="inlineStr">
+      <c r="K8" s="8" t="inlineStr">
         <is>
           <t>정상 인증 위장 · 암호화·정상 채널 은닉</t>
         </is>
       </c>
-      <c r="K8" s="8" t="n">
+      <c r="L8" s="9" t="n">
         <v>5</v>
       </c>
-      <c r="L8" s="9" t="inlineStr">
+      <c r="M8" s="9" t="inlineStr">
         <is>
           <t>[실제 사고] APT28 인접 네트워크(Nearest Neighbor) 무선 경유 침투(2024-11) (ENI-002)</t>
         </is>
       </c>
-      <c r="M8" s="9" t="inlineStr">
+      <c r="N8" s="9" t="inlineStr">
         <is>
           <t>내부 분할·관리 전용 경로·점프 호스트와 원격 서비스 접근 최소화를 적용(NIST AC-17·SC-7)</t>
         </is>
@@ -5825,35 +5834,36 @@
           <t>매우 높음</t>
         </is>
       </c>
-      <c r="G9" s="8" t="inlineStr">
+      <c r="G9" s="8" t="inlineStr"/>
+      <c r="H9" s="8" t="inlineStr">
         <is>
           <t>상</t>
         </is>
       </c>
-      <c r="H9" s="8" t="inlineStr">
+      <c r="I9" s="9" t="inlineStr">
         <is>
           <t>상</t>
         </is>
       </c>
-      <c r="I9" s="9" t="inlineStr">
+      <c r="J9" s="9" t="inlineStr">
         <is>
           <t>행위·네트워크·아이덴티티</t>
         </is>
       </c>
-      <c r="J9" s="9" t="inlineStr">
+      <c r="K9" s="8" t="inlineStr">
         <is>
           <t>정상 인증 위장 · 경계 밖·비관리 장비</t>
         </is>
       </c>
-      <c r="K9" s="8" t="n">
+      <c r="L9" s="9" t="n">
         <v>4</v>
       </c>
-      <c r="L9" s="9" t="inlineStr">
+      <c r="M9" s="9" t="inlineStr">
         <is>
           <t>[실제 사고] APT28 인접 네트워크(Nearest Neighbor) 무선 경유 침투(2024-11) (ENI-002)</t>
         </is>
       </c>
-      <c r="M9" s="9" t="inlineStr">
+      <c r="N9" s="9" t="inlineStr">
         <is>
           <t>모든 외부 원격 접근에 피싱 내성 MFA·조건부 접근을 적용하고 노출을 최소화(NIST AC-17·IA-2)</t>
         </is>
@@ -5888,35 +5898,36 @@
           <t>매우 높음</t>
         </is>
       </c>
-      <c r="G10" s="8" t="inlineStr">
+      <c r="G10" s="8" t="inlineStr"/>
+      <c r="H10" s="8" t="inlineStr">
         <is>
           <t>상</t>
         </is>
       </c>
-      <c r="H10" s="8" t="inlineStr">
+      <c r="I10" s="9" t="inlineStr">
         <is>
           <t>상</t>
         </is>
       </c>
-      <c r="I10" s="9" t="inlineStr">
+      <c r="J10" s="9" t="inlineStr">
         <is>
           <t>EDR·XDR</t>
         </is>
       </c>
-      <c r="J10" s="9" t="inlineStr">
+      <c r="K10" s="8" t="inlineStr">
         <is>
           <t>파일리스·인메모리 · 서명된 정상 도구 악용</t>
         </is>
       </c>
-      <c r="K10" s="8" t="n">
+      <c r="L10" s="9" t="n">
         <v>4</v>
       </c>
-      <c r="L10" s="9" t="inlineStr">
+      <c r="M10" s="9" t="inlineStr">
         <is>
           <t>[실제 사고] Black Basta 사람 운영 랜섬웨어(LotL·BYOVD·AD 확산)(2024-05) (ENI-012)</t>
         </is>
       </c>
-      <c r="M10" s="9" t="inlineStr">
+      <c r="N10" s="9" t="inlineStr">
         <is>
           <t>LSASS 보호(PPL)·자격증명 가드와 최소 권한·특권 분리를 적용(NIST AC-6·IA-5)</t>
         </is>
@@ -5951,35 +5962,36 @@
           <t>매우 높음</t>
         </is>
       </c>
-      <c r="G11" s="8" t="inlineStr">
+      <c r="G11" s="8" t="inlineStr"/>
+      <c r="H11" s="8" t="inlineStr">
         <is>
           <t>상</t>
         </is>
       </c>
-      <c r="H11" s="8" t="inlineStr">
+      <c r="I11" s="9" t="inlineStr">
         <is>
           <t>상</t>
         </is>
       </c>
-      <c r="I11" s="9" t="inlineStr">
+      <c r="J11" s="9" t="inlineStr">
         <is>
           <t>행위·네트워크·아이덴티티</t>
         </is>
       </c>
-      <c r="J11" s="9" t="inlineStr">
+      <c r="K11" s="8" t="inlineStr">
         <is>
           <t>파일리스·인메모리 · 서명된 정상 도구 악용</t>
         </is>
       </c>
-      <c r="K11" s="8" t="n">
+      <c r="L11" s="9" t="n">
         <v>3</v>
       </c>
-      <c r="L11" s="9" t="inlineStr">
+      <c r="M11" s="9" t="inlineStr">
         <is>
           <t>[실제 사고] Black Basta 사람 운영 랜섬웨어(LotL·BYOVD·AD 확산)(2024-05) (ENI-012)</t>
         </is>
       </c>
-      <c r="M11" s="9" t="inlineStr">
+      <c r="N11" s="9" t="inlineStr">
         <is>
           <t>스크립트 로깅·제약 언어 모드·서명 정책과 최소 기능 원칙을 적용(NIST CM-7·SI-4)</t>
         </is>
@@ -6014,35 +6026,36 @@
           <t>매우 높음</t>
         </is>
       </c>
-      <c r="G12" s="8" t="inlineStr">
+      <c r="G12" s="8" t="inlineStr"/>
+      <c r="H12" s="8" t="inlineStr">
         <is>
           <t>상</t>
         </is>
       </c>
-      <c r="H12" s="8" t="inlineStr">
+      <c r="I12" s="9" t="inlineStr">
         <is>
           <t>상</t>
         </is>
       </c>
-      <c r="I12" s="9" t="inlineStr">
+      <c r="J12" s="9" t="inlineStr">
         <is>
           <t>행위·네트워크·아이덴티티</t>
         </is>
       </c>
-      <c r="J12" s="9" t="inlineStr">
+      <c r="K12" s="8" t="inlineStr">
         <is>
           <t>정상 인증 위장</t>
         </is>
       </c>
-      <c r="K12" s="8" t="n">
+      <c r="L12" s="9" t="n">
         <v>3</v>
       </c>
-      <c r="L12" s="9" t="inlineStr">
+      <c r="M12" s="9" t="inlineStr">
         <is>
           <t>[실제 사고] Cl0p의 Cleo 파일전송 취약점 대량 악용(2024-12) (ENI-010)</t>
         </is>
       </c>
-      <c r="M12" s="9" t="inlineStr">
+      <c r="N12" s="9" t="inlineStr">
         <is>
           <t>데이터 반출 차단·사고 대응·법집행 연계와 백업·복구를 병행(NIST IR-4·SI-4)</t>
         </is>
@@ -6077,35 +6090,36 @@
           <t>매우 높음</t>
         </is>
       </c>
-      <c r="G13" s="8" t="inlineStr">
+      <c r="G13" s="8" t="inlineStr"/>
+      <c r="H13" s="8" t="inlineStr">
         <is>
           <t>상</t>
         </is>
       </c>
-      <c r="H13" s="8" t="inlineStr">
+      <c r="I13" s="9" t="inlineStr">
         <is>
           <t>상</t>
         </is>
       </c>
-      <c r="I13" s="9" t="inlineStr">
+      <c r="J13" s="9" t="inlineStr">
         <is>
           <t>행위·네트워크·아이덴티티</t>
         </is>
       </c>
-      <c r="J13" s="9" t="inlineStr">
+      <c r="K13" s="8" t="inlineStr">
         <is>
           <t>암호화·정상 채널 은닉 · 신뢰·공급 관계 경유</t>
         </is>
       </c>
-      <c r="K13" s="8" t="n">
+      <c r="L13" s="9" t="n">
         <v>3</v>
       </c>
-      <c r="L13" s="9" t="inlineStr">
+      <c r="M13" s="9" t="inlineStr">
         <is>
           <t>[실제 사고] Cl0p의 Cleo 파일전송 취약점 대량 악용(2024-12) (ENI-010)</t>
         </is>
       </c>
-      <c r="M13" s="9" t="inlineStr">
+      <c r="N13" s="9" t="inlineStr">
         <is>
           <t>허용 SaaS 제한·egress 통제·DLP와 대용량 업로드 경보를 적용(NIST SC-7·SI-4)</t>
         </is>
@@ -6142,33 +6156,38 @@
       </c>
       <c r="G14" s="8" t="inlineStr">
         <is>
+          <t>경계</t>
+        </is>
+      </c>
+      <c r="H14" s="8" t="inlineStr">
+        <is>
           <t>상</t>
         </is>
       </c>
-      <c r="H14" s="8" t="inlineStr">
+      <c r="I14" s="9" t="inlineStr">
         <is>
           <t>상</t>
         </is>
       </c>
-      <c r="I14" s="9" t="inlineStr">
+      <c r="J14" s="9" t="inlineStr">
         <is>
           <t>행위·네트워크·아이덴티티</t>
         </is>
       </c>
-      <c r="J14" s="9" t="inlineStr">
+      <c r="K14" s="8" t="inlineStr">
         <is>
           <t>암호화·정상 채널 은닉</t>
         </is>
       </c>
-      <c r="K14" s="8" t="n">
+      <c r="L14" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="L14" s="9" t="inlineStr">
+      <c r="M14" s="9" t="inlineStr">
         <is>
           <t>[실제 사고] 데이터 스테이징·압축 후 C2 채널 반출(이중 협박)(2024-06) (ENI-031)</t>
         </is>
       </c>
-      <c r="M14" s="9" t="inlineStr">
+      <c r="N14" s="9" t="inlineStr">
         <is>
           <t>egress 통제·데이터 유출 탐지와 C2 차단으로 반출을 막음(NIST SC-7·AU-6)</t>
         </is>
@@ -6205,33 +6224,38 @@
       </c>
       <c r="G15" s="8" t="inlineStr">
         <is>
+          <t>경계</t>
+        </is>
+      </c>
+      <c r="H15" s="8" t="inlineStr">
+        <is>
           <t>상</t>
         </is>
       </c>
-      <c r="H15" s="8" t="inlineStr">
+      <c r="I15" s="9" t="inlineStr">
         <is>
           <t>상</t>
         </is>
       </c>
-      <c r="I15" s="9" t="inlineStr">
+      <c r="J15" s="9" t="inlineStr">
         <is>
           <t>행위·네트워크·아이덴티티</t>
         </is>
       </c>
-      <c r="J15" s="9" t="inlineStr">
+      <c r="K15" s="8" t="inlineStr">
         <is>
           <t>정상 인증 위장</t>
         </is>
       </c>
-      <c r="K15" s="8" t="n">
+      <c r="L15" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="L15" s="9" t="inlineStr">
+      <c r="M15" s="9" t="inlineStr">
         <is>
           <t>[실제 사고] APT28 인접 네트워크(Nearest Neighbor) 무선 경유 침투(2024-11) (ENI-002)</t>
         </is>
       </c>
-      <c r="M15" s="9" t="inlineStr">
+      <c r="N15" s="9" t="inlineStr">
         <is>
           <t>특권 분리·로컬 관리자 암호 고유화(LAPS)·티켓 수명 축소와 재사용 탐지를 적용(NIST IA-2·AC-6)</t>
         </is>
@@ -6268,33 +6292,38 @@
       </c>
       <c r="G16" s="8" t="inlineStr">
         <is>
+          <t>경계</t>
+        </is>
+      </c>
+      <c r="H16" s="8" t="inlineStr">
+        <is>
           <t>상</t>
         </is>
       </c>
-      <c r="H16" s="8" t="inlineStr">
+      <c r="I16" s="9" t="inlineStr">
         <is>
           <t>상</t>
         </is>
       </c>
-      <c r="I16" s="9" t="inlineStr">
+      <c r="J16" s="9" t="inlineStr">
         <is>
           <t>행위·네트워크·아이덴티티</t>
         </is>
       </c>
-      <c r="J16" s="9" t="inlineStr">
+      <c r="K16" s="8" t="inlineStr">
         <is>
           <t>신뢰·공급 관계 경유 · 정상 인증 위장</t>
         </is>
       </c>
-      <c r="K16" s="8" t="n">
+      <c r="L16" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="L16" s="9" t="inlineStr">
+      <c r="M16" s="9" t="inlineStr">
         <is>
           <t>[실제 사고] ConnectWise ScreenConnect 취약점 경유 랜섬웨어(2024-02) (ENI-009)</t>
         </is>
       </c>
-      <c r="M16" s="9" t="inlineStr">
+      <c r="N16" s="9" t="inlineStr">
         <is>
           <t>공급·관리 관계에 최소 권한·분리·계약상 보안 요구를 적용하고 연동 토큰을 단기화·감사(NIST SR-3·CA-3·AC-20)</t>
         </is>
@@ -6331,33 +6360,38 @@
       </c>
       <c r="G17" s="8" t="inlineStr">
         <is>
+          <t>경계</t>
+        </is>
+      </c>
+      <c r="H17" s="8" t="inlineStr">
+        <is>
           <t>상</t>
         </is>
       </c>
-      <c r="H17" s="8" t="inlineStr">
+      <c r="I17" s="9" t="inlineStr">
         <is>
           <t>상</t>
         </is>
       </c>
-      <c r="I17" s="9" t="inlineStr">
+      <c r="J17" s="9" t="inlineStr">
         <is>
           <t>행위·네트워크·아이덴티티</t>
         </is>
       </c>
-      <c r="J17" s="9" t="inlineStr">
+      <c r="K17" s="8" t="inlineStr">
         <is>
           <t>정상 인증 위장</t>
         </is>
       </c>
-      <c r="K17" s="8" t="n">
+      <c r="L17" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="L17" s="9" t="inlineStr">
+      <c r="M17" s="9" t="inlineStr">
         <is>
           <t>[실제 사고] APT28 인접 네트워크(Nearest Neighbor) 무선 경유 침투(2024-11) (ENI-002)</t>
         </is>
       </c>
-      <c r="M17" s="9" t="inlineStr">
+      <c r="N17" s="9" t="inlineStr">
         <is>
           <t>서비스 계정에 길고 무작위한 암호·gMSA·강한 암호화를 적용하고 요청을 감사(NIST IA-5·AC-6)</t>
         </is>
@@ -6394,33 +6428,38 @@
       </c>
       <c r="G18" s="8" t="inlineStr">
         <is>
+          <t>경계</t>
+        </is>
+      </c>
+      <c r="H18" s="8" t="inlineStr">
+        <is>
           <t>상</t>
         </is>
       </c>
-      <c r="H18" s="8" t="inlineStr">
+      <c r="I18" s="9" t="inlineStr">
         <is>
           <t>상</t>
         </is>
       </c>
-      <c r="I18" s="9" t="inlineStr">
+      <c r="J18" s="9" t="inlineStr">
         <is>
           <t>행위·네트워크·아이덴티티</t>
         </is>
       </c>
-      <c r="J18" s="9" t="inlineStr">
+      <c r="K18" s="8" t="inlineStr">
         <is>
           <t>커널·펌웨어 하위 계층</t>
         </is>
       </c>
-      <c r="K18" s="8" t="n">
+      <c r="L18" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="L18" s="9" t="inlineStr">
+      <c r="M18" s="9" t="inlineStr">
         <is>
           <t>[실제 사고] 서명된 취약 드라이버 대량 변종 캠페인(TrueSight 등)(2025-01) (ENI-017)</t>
         </is>
       </c>
-      <c r="M18" s="9" t="inlineStr">
+      <c r="N18" s="9" t="inlineStr">
         <is>
           <t>HVCI·드라이버 블록리스트로 취약 드라이버 로드를 차단(NIST SI-7·CM-7)</t>
         </is>
@@ -6457,33 +6496,38 @@
       </c>
       <c r="G19" s="8" t="inlineStr">
         <is>
+          <t>경계</t>
+        </is>
+      </c>
+      <c r="H19" s="8" t="inlineStr">
+        <is>
           <t>상</t>
         </is>
       </c>
-      <c r="H19" s="8" t="inlineStr">
+      <c r="I19" s="9" t="inlineStr">
         <is>
           <t>상</t>
         </is>
       </c>
-      <c r="I19" s="9" t="inlineStr">
+      <c r="J19" s="9" t="inlineStr">
         <is>
           <t>행위·네트워크·아이덴티티</t>
         </is>
       </c>
-      <c r="J19" s="9" t="inlineStr">
+      <c r="K19" s="8" t="inlineStr">
         <is>
           <t>서명된 정상 도구 악용 · 시그니처 회피</t>
         </is>
       </c>
-      <c r="K19" s="8" t="n">
+      <c r="L19" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="L19" s="9" t="inlineStr">
+      <c r="M19" s="9" t="inlineStr">
         <is>
           <t>[실제 사고] Volt Typhoon의 LotL 기반 핵심 기반시설 장기 침투(2024-02) (ENI-001)</t>
         </is>
       </c>
-      <c r="M19" s="9" t="inlineStr">
+      <c r="N19" s="9" t="inlineStr">
         <is>
           <t>불필요한 LOLBin 실행을 허용 목록·애플리케이션 제어로 제한하고 무결성·실행 맥락을 감시(NIST CM-7·SI-7)</t>
         </is>
@@ -6520,33 +6564,38 @@
       </c>
       <c r="G20" s="8" t="inlineStr">
         <is>
+          <t>경계</t>
+        </is>
+      </c>
+      <c r="H20" s="8" t="inlineStr">
+        <is>
           <t>상</t>
         </is>
       </c>
-      <c r="H20" s="8" t="inlineStr">
+      <c r="I20" s="9" t="inlineStr">
         <is>
           <t>상</t>
         </is>
       </c>
-      <c r="I20" s="9" t="inlineStr">
+      <c r="J20" s="9" t="inlineStr">
         <is>
           <t>EDR·XDR</t>
         </is>
       </c>
-      <c r="J20" s="9" t="inlineStr">
+      <c r="K20" s="8" t="inlineStr">
         <is>
           <t>서명된 정상 도구 악용</t>
         </is>
       </c>
-      <c r="K20" s="8" t="n">
+      <c r="L20" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="L20" s="9" t="inlineStr">
+      <c r="M20" s="9" t="inlineStr">
         <is>
           <t>[실제 사고] Black Basta 사람 운영 랜섬웨어(LotL·BYOVD·AD 확산)(2024-05) (ENI-012)</t>
         </is>
       </c>
-      <c r="M20" s="9" t="inlineStr">
+      <c r="N20" s="9" t="inlineStr">
         <is>
           <t>오프라인·불변 백업과 백업 삭제 방지·권한 분리를 적용(NIST CP-9·SI-4)</t>
         </is>
@@ -6583,33 +6632,38 @@
       </c>
       <c r="G21" s="8" t="inlineStr">
         <is>
+          <t>경계</t>
+        </is>
+      </c>
+      <c r="H21" s="8" t="inlineStr">
+        <is>
           <t>상</t>
         </is>
       </c>
-      <c r="H21" s="8" t="inlineStr">
+      <c r="I21" s="9" t="inlineStr">
         <is>
           <t>상</t>
         </is>
       </c>
-      <c r="I21" s="9" t="inlineStr">
+      <c r="J21" s="9" t="inlineStr">
         <is>
           <t>EDR·XDR</t>
         </is>
       </c>
-      <c r="J21" s="9" t="inlineStr">
+      <c r="K21" s="8" t="inlineStr">
         <is>
           <t>시그니처 회피</t>
         </is>
       </c>
-      <c r="K21" s="8" t="n">
+      <c r="L21" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="L21" s="9" t="inlineStr">
+      <c r="M21" s="9" t="inlineStr">
         <is>
           <t>[실제 사고] NotPetya의 자격증명 탈취·원격 취약점 웜 확산·파괴(2017-06) (ENI-021)</t>
         </is>
       </c>
-      <c r="M21" s="9" t="inlineStr">
+      <c r="N21" s="9" t="inlineStr">
         <is>
           <t>신속 패치·내부 분할과 취약 서비스 노출 최소화로 전파를 차단(NIST SI-2·RA-5·SC-7)</t>
         </is>
@@ -6644,35 +6698,36 @@
           <t>높음</t>
         </is>
       </c>
-      <c r="G22" s="8" t="inlineStr">
+      <c r="G22" s="8" t="inlineStr"/>
+      <c r="H22" s="8" t="inlineStr">
         <is>
           <t>상</t>
         </is>
       </c>
-      <c r="H22" s="8" t="inlineStr">
+      <c r="I22" s="9" t="inlineStr">
         <is>
           <t>중</t>
         </is>
       </c>
-      <c r="I22" s="9" t="inlineStr">
+      <c r="J22" s="9" t="inlineStr">
         <is>
           <t>행위·네트워크·아이덴티티</t>
         </is>
       </c>
-      <c r="J22" s="9" t="inlineStr">
+      <c r="K22" s="8" t="inlineStr">
         <is>
           <t>정상 인증 위장 · 서명된 정상 도구 악용</t>
         </is>
       </c>
-      <c r="K22" s="8" t="n">
+      <c r="L22" s="9" t="n">
         <v>3</v>
       </c>
-      <c r="L22" s="9" t="inlineStr">
+      <c r="M22" s="9" t="inlineStr">
         <is>
           <t>[실제 사고] Black Basta 사람 운영 랜섬웨어(LotL·BYOVD·AD 확산)(2024-05) (ENI-012)</t>
         </is>
       </c>
-      <c r="M22" s="9" t="inlineStr">
+      <c r="N22" s="9" t="inlineStr">
         <is>
           <t>AD 질의·열거를 감사하고 공격 경로(관리자·신뢰)를 정리·최소화(NIST AC-6·AU-6)</t>
         </is>
@@ -6709,33 +6764,38 @@
       </c>
       <c r="G23" s="8" t="inlineStr">
         <is>
+          <t>경계</t>
+        </is>
+      </c>
+      <c r="H23" s="8" t="inlineStr">
+        <is>
           <t>상</t>
         </is>
       </c>
-      <c r="H23" s="8" t="inlineStr">
+      <c r="I23" s="9" t="inlineStr">
         <is>
           <t>중</t>
         </is>
       </c>
-      <c r="I23" s="9" t="inlineStr">
+      <c r="J23" s="9" t="inlineStr">
         <is>
           <t>행위·네트워크·아이덴티티</t>
         </is>
       </c>
-      <c r="J23" s="9" t="inlineStr">
+      <c r="K23" s="8" t="inlineStr">
         <is>
           <t>시그니처 회피</t>
         </is>
       </c>
-      <c r="K23" s="8" t="n">
+      <c r="L23" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="L23" s="9" t="inlineStr">
+      <c r="M23" s="9" t="inlineStr">
         <is>
           <t>[실제 사고] Volt Typhoon의 LotL 기반 핵심 기반시설 장기 침투(2024-02) (ENI-001)</t>
         </is>
       </c>
-      <c r="M23" s="9" t="inlineStr">
+      <c r="N23" s="9" t="inlineStr">
         <is>
           <t>원격·불변 로그 전송과 로그 삭제 방지·보존 정책을 적용(NIST AU-9·AU-6)</t>
         </is>
@@ -6772,33 +6832,38 @@
       </c>
       <c r="G24" s="8" t="inlineStr">
         <is>
+          <t>경계</t>
+        </is>
+      </c>
+      <c r="H24" s="8" t="inlineStr">
+        <is>
           <t>상</t>
         </is>
       </c>
-      <c r="H24" s="8" t="inlineStr">
+      <c r="I24" s="9" t="inlineStr">
         <is>
           <t>중</t>
         </is>
       </c>
-      <c r="I24" s="9" t="inlineStr">
+      <c r="J24" s="9" t="inlineStr">
         <is>
           <t>EDR·XDR</t>
         </is>
       </c>
-      <c r="J24" s="9" t="inlineStr">
+      <c r="K24" s="8" t="inlineStr">
         <is>
           <t>암호화·정상 채널 은닉 · 서명된 정상 도구 악용</t>
         </is>
       </c>
-      <c r="K24" s="8" t="n">
+      <c r="L24" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="L24" s="9" t="inlineStr">
+      <c r="M24" s="9" t="inlineStr">
         <is>
           <t>[실제 사고] 서명된 정상 바이너리(LOLBin) 대리 실행 광범위 사용(2023-03) (ENI-019)</t>
         </is>
       </c>
-      <c r="M24" s="9" t="inlineStr">
+      <c r="N24" s="9" t="inlineStr">
         <is>
           <t>불필요한 다운로드 도구 제한·egress 통제와 반입 파일 검사를 적용(NIST SI-3·SC-7)</t>
         </is>
@@ -6833,35 +6898,36 @@
           <t>높음</t>
         </is>
       </c>
-      <c r="G25" s="8" t="inlineStr">
+      <c r="G25" s="8" t="inlineStr"/>
+      <c r="H25" s="8" t="inlineStr">
         <is>
           <t>중</t>
         </is>
       </c>
-      <c r="H25" s="8" t="inlineStr">
+      <c r="I25" s="9" t="inlineStr">
         <is>
           <t>상</t>
         </is>
       </c>
-      <c r="I25" s="9" t="inlineStr">
+      <c r="J25" s="9" t="inlineStr">
         <is>
           <t>행위·네트워크·아이덴티티</t>
         </is>
       </c>
-      <c r="J25" s="9" t="inlineStr">
+      <c r="K25" s="8" t="inlineStr">
         <is>
           <t>암호화·정상 채널 은닉</t>
         </is>
       </c>
-      <c r="K25" s="8" t="n">
+      <c r="L25" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="L25" s="9" t="inlineStr">
+      <c r="M25" s="9" t="inlineStr">
         <is>
           <t>[실제 사고] Cobalt Strike 비콘의 암호화 C2·프로세스 인젝션(2023-01) (ENI-018)</t>
         </is>
       </c>
-      <c r="M25" s="9" t="inlineStr">
+      <c r="N25" s="9" t="inlineStr">
         <is>
           <t>웹 프록시·egress 통제·목적지 평판과 비컨 탐지를 적용(NIST SC-7·AU-6)</t>
         </is>
@@ -6896,35 +6962,36 @@
           <t>높음</t>
         </is>
       </c>
-      <c r="G26" s="8" t="inlineStr">
+      <c r="G26" s="8" t="inlineStr"/>
+      <c r="H26" s="8" t="inlineStr">
         <is>
           <t>중</t>
         </is>
       </c>
-      <c r="H26" s="8" t="inlineStr">
+      <c r="I26" s="9" t="inlineStr">
         <is>
           <t>상</t>
         </is>
       </c>
-      <c r="I26" s="9" t="inlineStr">
+      <c r="J26" s="9" t="inlineStr">
         <is>
           <t>행위·네트워크·아이덴티티</t>
         </is>
       </c>
-      <c r="J26" s="9" t="inlineStr">
+      <c r="K26" s="8" t="inlineStr">
         <is>
           <t>암호화·정상 채널 은닉</t>
         </is>
       </c>
-      <c r="K26" s="8" t="n">
+      <c r="L26" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="L26" s="9" t="inlineStr">
+      <c r="M26" s="9" t="inlineStr">
         <is>
           <t>[실제 사고] Cobalt Strike 비콘의 암호화 C2·프로세스 인젝션(2023-01) (ENI-018)</t>
         </is>
       </c>
-      <c r="M26" s="9" t="inlineStr">
+      <c r="N26" s="9" t="inlineStr">
         <is>
           <t>egress 통제·TLS 가시성·목적지 평판 차단과 비컨 탐지를 적용(NIST SC-7·AU-6)</t>
         </is>
@@ -6959,35 +7026,36 @@
           <t>높음</t>
         </is>
       </c>
-      <c r="G27" s="8" t="inlineStr">
+      <c r="G27" s="8" t="inlineStr"/>
+      <c r="H27" s="8" t="inlineStr">
         <is>
           <t>중</t>
         </is>
       </c>
-      <c r="H27" s="8" t="inlineStr">
+      <c r="I27" s="9" t="inlineStr">
         <is>
           <t>상</t>
         </is>
       </c>
-      <c r="I27" s="9" t="inlineStr">
+      <c r="J27" s="9" t="inlineStr">
         <is>
           <t>행위·네트워크·아이덴티티</t>
         </is>
       </c>
-      <c r="J27" s="9" t="inlineStr">
+      <c r="K27" s="8" t="inlineStr">
         <is>
           <t>암호화·정상 채널 은닉 · 신뢰·공급 관계 경유</t>
         </is>
       </c>
-      <c r="K27" s="8" t="n">
+      <c r="L27" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="L27" s="9" t="inlineStr">
+      <c r="M27" s="9" t="inlineStr">
         <is>
           <t>[실제 사고] 정상 웹 서비스(클라우드·협업) 경유 C2(2024-03) (ENI-028)</t>
         </is>
       </c>
-      <c r="M27" s="9" t="inlineStr">
+      <c r="N27" s="9" t="inlineStr">
         <is>
           <t>허용 SaaS·테넌트 제한과 egress 가시성·이상 사용 탐지를 적용(NIST SC-7·SI-4)</t>
         </is>
@@ -7022,35 +7090,36 @@
           <t>높음</t>
         </is>
       </c>
-      <c r="G28" s="8" t="inlineStr">
+      <c r="G28" s="8" t="inlineStr"/>
+      <c r="H28" s="8" t="inlineStr">
         <is>
           <t>중</t>
         </is>
       </c>
-      <c r="H28" s="8" t="inlineStr">
+      <c r="I28" s="9" t="inlineStr">
         <is>
           <t>상</t>
         </is>
       </c>
-      <c r="I28" s="9" t="inlineStr">
+      <c r="J28" s="9" t="inlineStr">
         <is>
           <t>행위·네트워크·아이덴티티</t>
         </is>
       </c>
-      <c r="J28" s="9" t="inlineStr">
+      <c r="K28" s="8" t="inlineStr">
         <is>
           <t>서명된 정상 도구 악용 · 커널·펌웨어 하위 계층</t>
         </is>
       </c>
-      <c r="K28" s="8" t="n">
+      <c r="L28" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="L28" s="9" t="inlineStr">
+      <c r="M28" s="9" t="inlineStr">
         <is>
           <t>[실제 사고] NotPetya의 자격증명 탈취·원격 취약점 웜 확산·파괴(2017-06) (ENI-021)</t>
         </is>
       </c>
-      <c r="M28" s="9" t="inlineStr">
+      <c r="N28" s="9" t="inlineStr">
         <is>
           <t>오프라인·불변 백업과 무결성 보호·분할로 파괴 범위를 제한(NIST CP-9·SI-7)</t>
         </is>
@@ -7085,35 +7154,36 @@
           <t>높음</t>
         </is>
       </c>
-      <c r="G29" s="8" t="inlineStr">
+      <c r="G29" s="8" t="inlineStr"/>
+      <c r="H29" s="8" t="inlineStr">
         <is>
           <t>중</t>
         </is>
       </c>
-      <c r="H29" s="8" t="inlineStr">
+      <c r="I29" s="9" t="inlineStr">
         <is>
           <t>상</t>
         </is>
       </c>
-      <c r="I29" s="9" t="inlineStr">
+      <c r="J29" s="9" t="inlineStr">
         <is>
           <t>행위·네트워크·아이덴티티</t>
         </is>
       </c>
-      <c r="J29" s="9" t="inlineStr">
+      <c r="K29" s="8" t="inlineStr">
         <is>
           <t>파일리스·인메모리 · 시그니처 회피</t>
         </is>
       </c>
-      <c r="K29" s="8" t="n">
+      <c r="L29" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="L29" s="9" t="inlineStr">
+      <c r="M29" s="9" t="inlineStr">
         <is>
           <t>[실제 사고] WMI·PowerShell 파일리스 실행·지속(2023-05) (ENI-020)</t>
         </is>
       </c>
-      <c r="M29" s="9" t="inlineStr">
+      <c r="N29" s="9" t="inlineStr">
         <is>
           <t>메모리 가시성(EDR)·공격 표면 축소와 스크립트 실행 통제를 적용(NIST SI-3·SI-4)</t>
         </is>
@@ -7148,35 +7218,36 @@
           <t>높음</t>
         </is>
       </c>
-      <c r="G30" s="8" t="inlineStr">
+      <c r="G30" s="8" t="inlineStr"/>
+      <c r="H30" s="8" t="inlineStr">
         <is>
           <t>중</t>
         </is>
       </c>
-      <c r="H30" s="8" t="inlineStr">
+      <c r="I30" s="9" t="inlineStr">
         <is>
           <t>상</t>
         </is>
       </c>
-      <c r="I30" s="9" t="inlineStr">
+      <c r="J30" s="9" t="inlineStr">
         <is>
           <t>행위·네트워크·아이덴티티</t>
         </is>
       </c>
-      <c r="J30" s="9" t="inlineStr">
+      <c r="K30" s="8" t="inlineStr">
         <is>
           <t>커널·펌웨어 하위 계층 · 파일리스·인메모리</t>
         </is>
       </c>
-      <c r="K30" s="8" t="n">
+      <c r="L30" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="L30" s="9" t="inlineStr">
+      <c r="M30" s="9" t="inlineStr">
         <is>
           <t>[실제 사고] 커널 루트킷을 통한 장기 은닉(국가배후)(2022-01) (ENI-025)</t>
         </is>
       </c>
-      <c r="M30" s="9" t="inlineStr">
+      <c r="N30" s="9" t="inlineStr">
         <is>
           <t>커널 무결성 보호(HVCI)·보안 부팅과 하위 계층 텔레메트리를 확보(NIST SI-7·SI-4)</t>
         </is>
@@ -7211,35 +7282,36 @@
           <t>높음</t>
         </is>
       </c>
-      <c r="G31" s="8" t="inlineStr">
+      <c r="G31" s="8" t="inlineStr"/>
+      <c r="H31" s="8" t="inlineStr">
         <is>
           <t>중</t>
         </is>
       </c>
-      <c r="H31" s="8" t="inlineStr">
+      <c r="I31" s="9" t="inlineStr">
         <is>
           <t>상</t>
         </is>
       </c>
-      <c r="I31" s="9" t="inlineStr">
+      <c r="J31" s="9" t="inlineStr">
         <is>
           <t>EDR·XDR</t>
         </is>
       </c>
-      <c r="J31" s="9" t="inlineStr">
+      <c r="K31" s="8" t="inlineStr">
         <is>
           <t>파일리스·인메모리 · 시그니처 회피</t>
         </is>
       </c>
-      <c r="K31" s="8" t="n">
+      <c r="L31" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="L31" s="9" t="inlineStr">
+      <c r="M31" s="9" t="inlineStr">
         <is>
           <t>[실제 사고] Cobalt Strike 비콘의 암호화 C2·프로세스 인젝션(2023-01) (ENI-018)</t>
         </is>
       </c>
-      <c r="M31" s="9" t="inlineStr">
+      <c r="N31" s="9" t="inlineStr">
         <is>
           <t>커널 수준 메모리 가시성(EDR)과 공격 표면 축소 규칙을 적용(NIST SI-3·SI-4)</t>
         </is>
@@ -7274,35 +7346,36 @@
           <t>높음</t>
         </is>
       </c>
-      <c r="G32" s="8" t="inlineStr">
+      <c r="G32" s="8" t="inlineStr"/>
+      <c r="H32" s="8" t="inlineStr">
         <is>
           <t>중</t>
         </is>
       </c>
-      <c r="H32" s="8" t="inlineStr">
+      <c r="I32" s="9" t="inlineStr">
         <is>
           <t>상</t>
         </is>
       </c>
-      <c r="I32" s="9" t="inlineStr">
+      <c r="J32" s="9" t="inlineStr">
         <is>
           <t>EDR·XDR</t>
         </is>
       </c>
-      <c r="J32" s="9" t="inlineStr">
+      <c r="K32" s="8" t="inlineStr">
         <is>
           <t>커널·펌웨어 하위 계층 · 시그니처 회피</t>
         </is>
       </c>
-      <c r="K32" s="8" t="n">
+      <c r="L32" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="L32" s="9" t="inlineStr">
+      <c r="M32" s="9" t="inlineStr">
         <is>
           <t>[실제 사고] RansomHub 제휴의 EDR 킬러(BYOVD) 사용(2024-08) (ENI-016)</t>
         </is>
       </c>
-      <c r="M32" s="9" t="inlineStr">
+      <c r="N32" s="9" t="inlineStr">
         <is>
           <t>취약 드라이버 차단 목록(HVCI·드라이버 블록리스트)과 신속 패치를 적용(NIST SI-2·SI-4)</t>
         </is>
@@ -7337,35 +7410,36 @@
           <t>높음</t>
         </is>
       </c>
-      <c r="G33" s="8" t="inlineStr">
+      <c r="G33" s="8" t="inlineStr"/>
+      <c r="H33" s="8" t="inlineStr">
         <is>
           <t>중</t>
         </is>
       </c>
-      <c r="H33" s="8" t="inlineStr">
+      <c r="I33" s="9" t="inlineStr">
         <is>
           <t>상</t>
         </is>
       </c>
-      <c r="I33" s="9" t="inlineStr">
+      <c r="J33" s="9" t="inlineStr">
         <is>
           <t>행위·네트워크·아이덴티티</t>
         </is>
       </c>
-      <c r="J33" s="9" t="inlineStr">
+      <c r="K33" s="8" t="inlineStr">
         <is>
           <t>커널·펌웨어 하위 계층</t>
         </is>
       </c>
-      <c r="K33" s="8" t="n">
+      <c r="L33" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="L33" s="9" t="inlineStr">
+      <c r="M33" s="9" t="inlineStr">
         <is>
           <t>[실증] BlackLotus UEFI 부트킷(보안 부팅 우회)(2023-03) (ENI-024)</t>
         </is>
       </c>
-      <c r="M33" s="9" t="inlineStr">
+      <c r="N33" s="9" t="inlineStr">
         <is>
           <t>보안 부팅·펌웨어 무결성 검증·업데이트와 펌웨어 공급 신뢰를 관리(NIST SI-7·CM-7)</t>
         </is>
@@ -7400,35 +7474,36 @@
           <t>보통</t>
         </is>
       </c>
-      <c r="G34" s="8" t="inlineStr">
+      <c r="G34" s="8" t="inlineStr"/>
+      <c r="H34" s="8" t="inlineStr">
         <is>
           <t>중</t>
         </is>
       </c>
-      <c r="H34" s="8" t="inlineStr">
+      <c r="I34" s="9" t="inlineStr">
         <is>
           <t>중</t>
         </is>
       </c>
-      <c r="I34" s="9" t="inlineStr">
+      <c r="J34" s="9" t="inlineStr">
         <is>
           <t>행위·네트워크·아이덴티티</t>
         </is>
       </c>
-      <c r="J34" s="9" t="inlineStr">
+      <c r="K34" s="8" t="inlineStr">
         <is>
           <t>파일리스·인메모리 · 서명된 정상 도구 악용</t>
         </is>
       </c>
-      <c r="K34" s="8" t="n">
+      <c r="L34" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="L34" s="9" t="inlineStr">
+      <c r="M34" s="9" t="inlineStr">
         <is>
           <t>[실제 사고] WMI·PowerShell 파일리스 실행·지속(2023-05) (ENI-020)</t>
         </is>
       </c>
-      <c r="M34" s="9" t="inlineStr">
+      <c r="N34" s="9" t="inlineStr">
         <is>
           <t>WMI 원격 실행을 제한하고 관리 활동을 기준선과 대조·감사(NIST CM-7·AU-6)</t>
         </is>
@@ -7463,35 +7538,36 @@
           <t>보통</t>
         </is>
       </c>
-      <c r="G35" s="8" t="inlineStr">
+      <c r="G35" s="8" t="inlineStr"/>
+      <c r="H35" s="8" t="inlineStr">
         <is>
           <t>중</t>
         </is>
       </c>
-      <c r="H35" s="8" t="inlineStr">
+      <c r="I35" s="9" t="inlineStr">
         <is>
           <t>중</t>
         </is>
       </c>
-      <c r="I35" s="9" t="inlineStr">
+      <c r="J35" s="9" t="inlineStr">
         <is>
           <t>행위·네트워크·아이덴티티</t>
         </is>
       </c>
-      <c r="J35" s="9" t="inlineStr">
+      <c r="K35" s="8" t="inlineStr">
         <is>
           <t>암호화·정상 채널 은닉</t>
         </is>
       </c>
-      <c r="K35" s="8" t="n">
+      <c r="L35" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="L35" s="9" t="inlineStr">
+      <c r="M35" s="9" t="inlineStr">
         <is>
           <t>[실제 사고] Cobalt Strike 비콘의 암호화 C2·프로세스 인젝션(2023-01) (ENI-018)</t>
         </is>
       </c>
-      <c r="M35" s="9" t="inlineStr">
+      <c r="N35" s="9" t="inlineStr">
         <is>
           <t>TLS 검사·SNI 정책과 프록시 경유 egress 통제를 적용(NIST SC-7·SI-4)</t>
         </is>
@@ -7526,35 +7602,36 @@
           <t>보통</t>
         </is>
       </c>
-      <c r="G36" s="8" t="inlineStr">
+      <c r="G36" s="8" t="inlineStr"/>
+      <c r="H36" s="8" t="inlineStr">
         <is>
           <t>중</t>
         </is>
       </c>
-      <c r="H36" s="8" t="inlineStr">
+      <c r="I36" s="9" t="inlineStr">
         <is>
           <t>중</t>
         </is>
       </c>
-      <c r="I36" s="9" t="inlineStr">
+      <c r="J36" s="9" t="inlineStr">
         <is>
           <t>행위·네트워크·아이덴티티</t>
         </is>
       </c>
-      <c r="J36" s="9" t="inlineStr">
+      <c r="K36" s="8" t="inlineStr">
         <is>
           <t>암호화·정상 채널 은닉</t>
         </is>
       </c>
-      <c r="K36" s="8" t="n">
+      <c r="L36" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="L36" s="9" t="inlineStr">
+      <c r="M36" s="9" t="inlineStr">
         <is>
           <t>[실제 사고] DNS 터널링 기반 은닉 C2·반출(2023-09) (ENI-027)</t>
         </is>
       </c>
-      <c r="M36" s="9" t="inlineStr">
+      <c r="N36" s="9" t="inlineStr">
         <is>
           <t>DNS 로깅·필터링·내부 리졸버 강제와 이상 질의 차단을 적용(NIST SC-7·AU-6)</t>
         </is>
@@ -7589,35 +7666,36 @@
           <t>보통</t>
         </is>
       </c>
-      <c r="G37" s="8" t="inlineStr">
+      <c r="G37" s="8" t="inlineStr"/>
+      <c r="H37" s="8" t="inlineStr">
         <is>
           <t>중</t>
         </is>
       </c>
-      <c r="H37" s="8" t="inlineStr">
+      <c r="I37" s="9" t="inlineStr">
         <is>
           <t>중</t>
         </is>
       </c>
-      <c r="I37" s="9" t="inlineStr">
+      <c r="J37" s="9" t="inlineStr">
         <is>
           <t>EDR·XDR</t>
         </is>
       </c>
-      <c r="J37" s="9" t="inlineStr">
+      <c r="K37" s="8" t="inlineStr">
         <is>
           <t>서명된 정상 도구 악용</t>
         </is>
       </c>
-      <c r="K37" s="8" t="n">
+      <c r="L37" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="L37" s="9" t="inlineStr">
+      <c r="M37" s="9" t="inlineStr">
         <is>
           <t>[실제 사고] Volt Typhoon의 LotL 기반 핵심 기반시설 장기 침투(2024-02) (ENI-001)</t>
         </is>
       </c>
-      <c r="M37" s="9" t="inlineStr">
+      <c r="N37" s="9" t="inlineStr">
         <is>
           <t>탐색 명령 사용을 기준선과 대조·감사하고 최소 기능을 적용(NIST SI-4·AU-6)</t>
         </is>
@@ -7652,35 +7730,36 @@
           <t>보통</t>
         </is>
       </c>
-      <c r="G38" s="8" t="inlineStr">
+      <c r="G38" s="8" t="inlineStr"/>
+      <c r="H38" s="8" t="inlineStr">
         <is>
           <t>중</t>
         </is>
       </c>
-      <c r="H38" s="8" t="inlineStr">
+      <c r="I38" s="9" t="inlineStr">
         <is>
           <t>중</t>
         </is>
       </c>
-      <c r="I38" s="9" t="inlineStr">
+      <c r="J38" s="9" t="inlineStr">
         <is>
           <t>EDR·XDR</t>
         </is>
       </c>
-      <c r="J38" s="9" t="inlineStr">
+      <c r="K38" s="8" t="inlineStr">
         <is>
           <t>서명된 정상 도구 악용</t>
         </is>
       </c>
-      <c r="K38" s="8" t="n">
+      <c r="L38" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="L38" s="9" t="inlineStr">
+      <c r="M38" s="9" t="inlineStr">
         <is>
           <t>[실제 사고] 데이터 스테이징·압축 후 C2 채널 반출(이중 협박)(2024-06) (ENI-031)</t>
         </is>
       </c>
-      <c r="M38" s="9" t="inlineStr">
+      <c r="N38" s="9" t="inlineStr">
         <is>
           <t>데이터 접근 최소화·민감 데이터 분류와 접근 감사를 적용(NIST AC-6·SI-4)</t>
         </is>
@@ -7715,35 +7794,36 @@
           <t>보통</t>
         </is>
       </c>
-      <c r="G39" s="8" t="inlineStr">
+      <c r="G39" s="8" t="inlineStr"/>
+      <c r="H39" s="8" t="inlineStr">
         <is>
           <t>중</t>
         </is>
       </c>
-      <c r="H39" s="8" t="inlineStr">
+      <c r="I39" s="9" t="inlineStr">
         <is>
           <t>중</t>
         </is>
       </c>
-      <c r="I39" s="9" t="inlineStr">
+      <c r="J39" s="9" t="inlineStr">
         <is>
           <t>EDR·XDR</t>
         </is>
       </c>
-      <c r="J39" s="9" t="inlineStr">
+      <c r="K39" s="8" t="inlineStr">
         <is>
           <t>서명된 정상 도구 악용 · 파일리스·인메모리</t>
         </is>
       </c>
-      <c r="K39" s="8" t="n">
+      <c r="L39" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="L39" s="9" t="inlineStr">
+      <c r="M39" s="9" t="inlineStr">
         <is>
           <t>[실제 사고] WMI·PowerShell 파일리스 실행·지속(2023-05) (ENI-020)</t>
         </is>
       </c>
-      <c r="M39" s="9" t="inlineStr">
+      <c r="N39" s="9" t="inlineStr">
         <is>
           <t>예약 작업 생성·변경을 감사하고 생성 권한을 최소화(NIST CM-7·AU-6)</t>
         </is>
@@ -7778,35 +7858,36 @@
           <t>보통</t>
         </is>
       </c>
-      <c r="G40" s="8" t="inlineStr">
+      <c r="G40" s="8" t="inlineStr"/>
+      <c r="H40" s="8" t="inlineStr">
         <is>
           <t>중</t>
         </is>
       </c>
-      <c r="H40" s="8" t="inlineStr">
+      <c r="I40" s="9" t="inlineStr">
         <is>
           <t>중</t>
         </is>
       </c>
-      <c r="I40" s="9" t="inlineStr">
+      <c r="J40" s="9" t="inlineStr">
         <is>
           <t>EDR·XDR</t>
         </is>
       </c>
-      <c r="J40" s="9" t="inlineStr">
+      <c r="K40" s="8" t="inlineStr">
         <is>
           <t>시그니처 회피 · 파일리스·인메모리</t>
         </is>
       </c>
-      <c r="K40" s="8" t="n">
+      <c r="L40" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="L40" s="9" t="inlineStr">
+      <c r="M40" s="9" t="inlineStr">
         <is>
           <t>[실제 사고] 지표 삭제·위장·난독화를 통한 사후 분석 방해(2024-01) (ENI-033)</t>
         </is>
       </c>
-      <c r="M40" s="9" t="inlineStr">
+      <c r="N40" s="9" t="inlineStr">
         <is>
           <t>시그니처 의존을 줄이고 행위 기반·샌드박스 분석을 병행(NIST SI-3·SI-4)</t>
         </is>
@@ -7841,35 +7922,36 @@
           <t>보통</t>
         </is>
       </c>
-      <c r="G41" s="8" t="inlineStr">
+      <c r="G41" s="8" t="inlineStr"/>
+      <c r="H41" s="8" t="inlineStr">
         <is>
           <t>중</t>
         </is>
       </c>
-      <c r="H41" s="8" t="inlineStr">
+      <c r="I41" s="9" t="inlineStr">
         <is>
           <t>중</t>
         </is>
       </c>
-      <c r="I41" s="9" t="inlineStr">
+      <c r="J41" s="9" t="inlineStr">
         <is>
           <t>EDR·XDR</t>
         </is>
       </c>
-      <c r="J41" s="9" t="inlineStr">
+      <c r="K41" s="8" t="inlineStr">
         <is>
           <t>파일리스·인메모리</t>
         </is>
       </c>
-      <c r="K41" s="8" t="n">
+      <c r="L41" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="L41" s="9" t="inlineStr">
+      <c r="M41" s="9" t="inlineStr">
         <is>
           <t>[실제 사고] 지표 삭제·위장·난독화를 통한 사후 분석 방해(2024-01) (ENI-033)</t>
         </is>
       </c>
-      <c r="M41" s="9" t="inlineStr">
+      <c r="N41" s="9" t="inlineStr">
         <is>
           <t>엔드포인트 행위 탐지·피싱 내성 MFA로 자격증명 탈취 가치를 낮춤(NIST SI-4·AC-6)</t>
         </is>
@@ -7904,35 +7986,36 @@
           <t>보통</t>
         </is>
       </c>
-      <c r="G42" s="8" t="inlineStr">
+      <c r="G42" s="8" t="inlineStr"/>
+      <c r="H42" s="8" t="inlineStr">
         <is>
           <t>중</t>
         </is>
       </c>
-      <c r="H42" s="8" t="inlineStr">
+      <c r="I42" s="9" t="inlineStr">
         <is>
           <t>중</t>
         </is>
       </c>
-      <c r="I42" s="9" t="inlineStr">
+      <c r="J42" s="9" t="inlineStr">
         <is>
           <t>EDR·XDR</t>
         </is>
       </c>
-      <c r="J42" s="9" t="inlineStr">
+      <c r="K42" s="8" t="inlineStr">
         <is>
           <t>서명된 정상 도구 악용</t>
         </is>
       </c>
-      <c r="K42" s="8" t="n">
+      <c r="L42" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="L42" s="9" t="inlineStr">
+      <c r="M42" s="9" t="inlineStr">
         <is>
           <t>[실제 사고] UAC 우회·토큰 조작을 통한 로컬 권한 상승(2023-08) (ENI-032)</t>
         </is>
       </c>
-      <c r="M42" s="9" t="inlineStr">
+      <c r="N42" s="9" t="inlineStr">
         <is>
           <t>서비스 생성·변경을 감사·기준선과 대조하고 최소 권한을 적용(NIST CM-7·AU-6)</t>
         </is>
@@ -7967,35 +8050,36 @@
           <t>보통</t>
         </is>
       </c>
-      <c r="G43" s="8" t="inlineStr">
+      <c r="G43" s="8" t="inlineStr"/>
+      <c r="H43" s="8" t="inlineStr">
         <is>
           <t>중</t>
         </is>
       </c>
-      <c r="H43" s="8" t="inlineStr">
+      <c r="I43" s="9" t="inlineStr">
         <is>
           <t>중</t>
         </is>
       </c>
-      <c r="I43" s="9" t="inlineStr">
+      <c r="J43" s="9" t="inlineStr">
         <is>
           <t>EDR·XDR</t>
         </is>
       </c>
-      <c r="J43" s="9" t="inlineStr">
+      <c r="K43" s="8" t="inlineStr">
         <is>
           <t>서명된 정상 도구 악용</t>
         </is>
       </c>
-      <c r="K43" s="8" t="n">
+      <c r="L43" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="L43" s="9" t="inlineStr">
+      <c r="M43" s="9" t="inlineStr">
         <is>
           <t>[실제 사고] LockBit 제휴의 복구 방해·EDR 무력화 암호화(CISA 권고)(2023-06) (ENI-015)</t>
         </is>
       </c>
-      <c r="M43" s="9" t="inlineStr">
+      <c r="N43" s="9" t="inlineStr">
         <is>
           <t>중요 서비스 변조 방지·권한 분리와 신속 복구 체계를 적용(NIST CP-10·SI-4)</t>
         </is>
@@ -8030,35 +8114,36 @@
           <t>보통</t>
         </is>
       </c>
-      <c r="G44" s="8" t="inlineStr">
+      <c r="G44" s="8" t="inlineStr"/>
+      <c r="H44" s="8" t="inlineStr">
         <is>
           <t>중</t>
         </is>
       </c>
-      <c r="H44" s="8" t="inlineStr">
+      <c r="I44" s="9" t="inlineStr">
         <is>
           <t>중</t>
         </is>
       </c>
-      <c r="I44" s="9" t="inlineStr">
+      <c r="J44" s="9" t="inlineStr">
         <is>
           <t>EDR·XDR</t>
         </is>
       </c>
-      <c r="J44" s="9" t="inlineStr">
+      <c r="K44" s="8" t="inlineStr">
         <is>
           <t>암호화·정상 채널 은닉 · 시그니처 회피</t>
         </is>
       </c>
-      <c r="K44" s="8" t="n">
+      <c r="L44" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="L44" s="9" t="inlineStr">
+      <c r="M44" s="9" t="inlineStr">
         <is>
           <t>[실제 사고] 데이터 스테이징·압축 후 C2 채널 반출(이중 협박)(2024-06) (ENI-031)</t>
         </is>
       </c>
-      <c r="M44" s="9" t="inlineStr">
+      <c r="N44" s="9" t="inlineStr">
         <is>
           <t>비정상 압축·스테이징 탐지와 반출 경로 통제를 병행(NIST SC-7·SI-4)</t>
         </is>
@@ -8093,35 +8178,36 @@
           <t>보통</t>
         </is>
       </c>
-      <c r="G45" s="8" t="inlineStr">
+      <c r="G45" s="8" t="inlineStr"/>
+      <c r="H45" s="8" t="inlineStr">
         <is>
           <t>중</t>
         </is>
       </c>
-      <c r="H45" s="8" t="inlineStr">
+      <c r="I45" s="9" t="inlineStr">
         <is>
           <t>중</t>
         </is>
       </c>
-      <c r="I45" s="9" t="inlineStr">
+      <c r="J45" s="9" t="inlineStr">
         <is>
           <t>EDR·XDR</t>
         </is>
       </c>
-      <c r="J45" s="9" t="inlineStr">
+      <c r="K45" s="8" t="inlineStr">
         <is>
           <t>서명된 정상 도구 악용 · 시그니처 회피</t>
         </is>
       </c>
-      <c r="K45" s="8" t="n">
+      <c r="L45" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="L45" s="9" t="inlineStr">
+      <c r="M45" s="9" t="inlineStr">
         <is>
           <t>[실제 사고] UAC 우회·토큰 조작을 통한 로컬 권한 상승(2023-08) (ENI-032)</t>
         </is>
       </c>
-      <c r="M45" s="9" t="inlineStr">
+      <c r="N45" s="9" t="inlineStr">
         <is>
           <t>UAC 최고 수준 설정·관리자 승인 모드와 최소 권한을 적용(NIST AC-6·CM-7)</t>
         </is>
@@ -8156,35 +8242,36 @@
           <t>보통</t>
         </is>
       </c>
-      <c r="G46" s="8" t="inlineStr">
+      <c r="G46" s="8" t="inlineStr"/>
+      <c r="H46" s="8" t="inlineStr">
         <is>
           <t>중</t>
         </is>
       </c>
-      <c r="H46" s="8" t="inlineStr">
+      <c r="I46" s="9" t="inlineStr">
         <is>
           <t>중</t>
         </is>
       </c>
-      <c r="I46" s="9" t="inlineStr">
+      <c r="J46" s="9" t="inlineStr">
         <is>
           <t>EDR·XDR</t>
         </is>
       </c>
-      <c r="J46" s="9" t="inlineStr">
+      <c r="K46" s="8" t="inlineStr">
         <is>
           <t>서명된 정상 도구 악용 · 시그니처 회피</t>
         </is>
       </c>
-      <c r="K46" s="8" t="n">
+      <c r="L46" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="L46" s="9" t="inlineStr">
+      <c r="M46" s="9" t="inlineStr">
         <is>
           <t>[실제 사고] 지표 삭제·위장·난독화를 통한 사후 분석 방해(2024-01) (ENI-033)</t>
         </is>
       </c>
-      <c r="M46" s="9" t="inlineStr">
+      <c r="N46" s="9" t="inlineStr">
         <is>
           <t>바이너리 무결성·서명 검증과 정상 경로 기준선 대조를 적용(NIST SI-7·SI-4)</t>
         </is>
@@ -8219,35 +8306,36 @@
           <t>보통</t>
         </is>
       </c>
-      <c r="G47" s="8" t="inlineStr">
+      <c r="G47" s="8" t="inlineStr"/>
+      <c r="H47" s="8" t="inlineStr">
         <is>
           <t>중</t>
         </is>
       </c>
-      <c r="H47" s="8" t="inlineStr">
+      <c r="I47" s="9" t="inlineStr">
         <is>
           <t>중</t>
         </is>
       </c>
-      <c r="I47" s="9" t="inlineStr">
+      <c r="J47" s="9" t="inlineStr">
         <is>
           <t>EDR·XDR</t>
         </is>
       </c>
-      <c r="J47" s="9" t="inlineStr">
+      <c r="K47" s="8" t="inlineStr">
         <is>
           <t>암호화·정상 채널 은닉 · 서명된 정상 도구 악용</t>
         </is>
       </c>
-      <c r="K47" s="8" t="n">
+      <c r="L47" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="L47" s="9" t="inlineStr">
+      <c r="M47" s="9" t="inlineStr">
         <is>
           <t>[실제 사고] Scattered Spider의 헬프데스크 사칭·EDR 회피 침투(2023-11) (ENI-013)</t>
         </is>
       </c>
-      <c r="M47" s="9" t="inlineStr">
+      <c r="N47" s="9" t="inlineStr">
         <is>
           <t>내부 분할·공유 권한 최소화와 측면 전송 모니터링을 적용(NIST SC-7·SI-4)</t>
         </is>
@@ -8282,35 +8370,36 @@
           <t>보통</t>
         </is>
       </c>
-      <c r="G48" s="8" t="inlineStr">
+      <c r="G48" s="8" t="inlineStr"/>
+      <c r="H48" s="8" t="inlineStr">
         <is>
           <t>중</t>
         </is>
       </c>
-      <c r="H48" s="8" t="inlineStr">
+      <c r="I48" s="9" t="inlineStr">
         <is>
           <t>중</t>
         </is>
       </c>
-      <c r="I48" s="9" t="inlineStr">
+      <c r="J48" s="9" t="inlineStr">
         <is>
           <t>EDR·XDR</t>
         </is>
       </c>
-      <c r="J48" s="9" t="inlineStr">
+      <c r="K48" s="8" t="inlineStr">
         <is>
           <t>경계 밖·비관리 장비</t>
         </is>
       </c>
-      <c r="K48" s="8" t="n">
+      <c r="L48" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="L48" s="9" t="inlineStr">
+      <c r="M48" s="9" t="inlineStr">
         <is>
           <t>[실제 사고] 이동식 매체(USB) 경유 격리망 침투·전파(2023-06) (ENI-029)</t>
         </is>
       </c>
-      <c r="M48" s="9" t="inlineStr">
+      <c r="N48" s="9" t="inlineStr">
         <is>
           <t>이동식 매체 사용을 통제·차단하고 자동 실행을 비활성화, 격리망 자산 반입 매체를 검사(NIST MP-7·SI-3)</t>
         </is>
@@ -8345,35 +8434,36 @@
           <t>보통</t>
         </is>
       </c>
-      <c r="G49" s="8" t="inlineStr">
+      <c r="G49" s="8" t="inlineStr"/>
+      <c r="H49" s="8" t="inlineStr">
         <is>
           <t>중</t>
         </is>
       </c>
-      <c r="H49" s="8" t="inlineStr">
+      <c r="I49" s="9" t="inlineStr">
         <is>
           <t>중</t>
         </is>
       </c>
-      <c r="I49" s="9" t="inlineStr">
+      <c r="J49" s="9" t="inlineStr">
         <is>
           <t>EDR·XDR</t>
         </is>
       </c>
-      <c r="J49" s="9" t="inlineStr">
+      <c r="K49" s="8" t="inlineStr">
         <is>
           <t>정상 인증 위장 · 파일리스·인메모리</t>
         </is>
       </c>
-      <c r="K49" s="8" t="n">
+      <c r="L49" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="L49" s="9" t="inlineStr">
+      <c r="M49" s="9" t="inlineStr">
         <is>
           <t>[실제 사고] UAC 우회·토큰 조작을 통한 로컬 권한 상승(2023-08) (ENI-032)</t>
         </is>
       </c>
-      <c r="M49" s="9" t="inlineStr">
+      <c r="N49" s="9" t="inlineStr">
         <is>
           <t>최소 권한·특권 계정 분리와 토큰 조작 탐지 규칙을 적용(NIST AC-6·SI-4)</t>
         </is>
@@ -8408,35 +8498,36 @@
           <t>보통</t>
         </is>
       </c>
-      <c r="G50" s="8" t="inlineStr">
+      <c r="G50" s="8" t="inlineStr"/>
+      <c r="H50" s="8" t="inlineStr">
         <is>
           <t>중</t>
         </is>
       </c>
-      <c r="H50" s="8" t="inlineStr">
+      <c r="I50" s="9" t="inlineStr">
         <is>
           <t>중</t>
         </is>
       </c>
-      <c r="I50" s="9" t="inlineStr">
+      <c r="J50" s="9" t="inlineStr">
         <is>
           <t>EDR·XDR</t>
         </is>
       </c>
-      <c r="J50" s="9" t="inlineStr">
+      <c r="K50" s="8" t="inlineStr">
         <is>
           <t>서명된 정상 도구 악용</t>
         </is>
       </c>
-      <c r="K50" s="8" t="n">
+      <c r="L50" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="L50" s="9" t="inlineStr">
+      <c r="M50" s="9" t="inlineStr">
         <is>
           <t>[실제 사고] WMI·PowerShell 파일리스 실행·지속(2023-05) (ENI-020)</t>
         </is>
       </c>
-      <c r="M50" s="9" t="inlineStr">
+      <c r="N50" s="9" t="inlineStr">
         <is>
           <t>자동 실행 지점 변경을 감사·무결성 검증하고 최소 기능을 적용(NIST CM-7·SI-7)</t>
         </is>
@@ -8471,35 +8562,36 @@
           <t>보통</t>
         </is>
       </c>
-      <c r="G51" s="8" t="inlineStr">
+      <c r="G51" s="8" t="inlineStr"/>
+      <c r="H51" s="8" t="inlineStr">
         <is>
           <t>중</t>
         </is>
       </c>
-      <c r="H51" s="8" t="inlineStr">
+      <c r="I51" s="9" t="inlineStr">
         <is>
           <t>중</t>
         </is>
       </c>
-      <c r="I51" s="9" t="inlineStr">
+      <c r="J51" s="9" t="inlineStr">
         <is>
           <t>행위·네트워크·아이덴티티</t>
         </is>
       </c>
-      <c r="J51" s="9" t="inlineStr">
+      <c r="K51" s="8" t="inlineStr">
         <is>
           <t>정상 인증 위장</t>
         </is>
       </c>
-      <c r="K51" s="8" t="n">
+      <c r="L51" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="L51" s="9" t="inlineStr">
+      <c r="M51" s="9" t="inlineStr">
         <is>
           <t>[ATT&amp;CK 주체 9]</t>
         </is>
       </c>
-      <c r="M51" s="9" t="inlineStr">
+      <c r="N51" s="9" t="inlineStr">
         <is>
           <t>계정 생성·권한 변경을 승인·감사하고 휴면·불필요 계정을 정리(NIST AC-2·IA-4)</t>
         </is>
@@ -8534,35 +8626,36 @@
           <t>보통</t>
         </is>
       </c>
-      <c r="G52" s="8" t="inlineStr">
+      <c r="G52" s="8" t="inlineStr"/>
+      <c r="H52" s="8" t="inlineStr">
         <is>
           <t>중</t>
         </is>
       </c>
-      <c r="H52" s="8" t="inlineStr">
+      <c r="I52" s="9" t="inlineStr">
         <is>
           <t>중</t>
         </is>
       </c>
-      <c r="I52" s="9" t="inlineStr">
+      <c r="J52" s="9" t="inlineStr">
         <is>
           <t>EDR·XDR</t>
         </is>
       </c>
-      <c r="J52" s="9" t="inlineStr">
+      <c r="K52" s="8" t="inlineStr">
         <is>
           <t>파일리스·인메모리 · 서명된 정상 도구 악용</t>
         </is>
       </c>
-      <c r="K52" s="8" t="n">
+      <c r="L52" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="L52" s="9" t="inlineStr">
+      <c r="M52" s="9" t="inlineStr">
         <is>
           <t>[ATT&amp;CK 주체 272]</t>
         </is>
       </c>
-      <c r="M52" s="9" t="inlineStr">
+      <c r="N52" s="9" t="inlineStr">
         <is>
           <t>커널 수준 가시성(EDR)과 최소 기능·서비스 생성 통제를 적용(NIST CM-7·SI-4)</t>
         </is>
@@ -8597,35 +8690,36 @@
           <t>보통</t>
         </is>
       </c>
-      <c r="G53" s="8" t="inlineStr">
+      <c r="G53" s="8" t="inlineStr"/>
+      <c r="H53" s="8" t="inlineStr">
         <is>
           <t>중</t>
         </is>
       </c>
-      <c r="H53" s="8" t="inlineStr">
+      <c r="I53" s="9" t="inlineStr">
         <is>
           <t>중</t>
         </is>
       </c>
-      <c r="I53" s="9" t="inlineStr">
+      <c r="J53" s="9" t="inlineStr">
         <is>
           <t>EDR·XDR</t>
         </is>
       </c>
-      <c r="J53" s="9" t="inlineStr">
+      <c r="K53" s="8" t="inlineStr">
         <is>
           <t>시그니처 회피 · 신뢰·공급 관계 경유</t>
         </is>
       </c>
-      <c r="K53" s="8" t="n">
+      <c r="L53" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="L53" s="9" t="inlineStr">
+      <c r="M53" s="9" t="inlineStr">
         <is>
           <t>[ATT&amp;CK 주체 44]</t>
         </is>
       </c>
-      <c r="M53" s="9" t="inlineStr">
+      <c r="N53" s="9" t="inlineStr">
         <is>
           <t>브라우저·플러그인 신속 패치, 웹 격리·콘텐츠 필터링과 엔드포인트 행위 탐지를 적용(NIST SI-3·SC-7)</t>
         </is>
@@ -8660,35 +8754,36 @@
           <t>보통</t>
         </is>
       </c>
-      <c r="G54" s="8" t="inlineStr">
+      <c r="G54" s="8" t="inlineStr"/>
+      <c r="H54" s="8" t="inlineStr">
         <is>
           <t>중</t>
         </is>
       </c>
-      <c r="H54" s="8" t="inlineStr">
+      <c r="I54" s="9" t="inlineStr">
         <is>
           <t>중</t>
         </is>
       </c>
-      <c r="I54" s="9" t="inlineStr">
+      <c r="J54" s="9" t="inlineStr">
         <is>
           <t>EDR·XDR</t>
         </is>
       </c>
-      <c r="J54" s="9" t="inlineStr">
+      <c r="K54" s="8" t="inlineStr">
         <is>
           <t>파일리스·인메모리</t>
         </is>
       </c>
-      <c r="K54" s="8" t="n">
+      <c r="L54" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="L54" s="9" t="inlineStr">
+      <c r="M54" s="9" t="inlineStr">
         <is>
           <t>[ATT&amp;CK 주체 8]</t>
         </is>
       </c>
-      <c r="M54" s="9" t="inlineStr">
+      <c r="N54" s="9" t="inlineStr">
         <is>
           <t>캐시 자격증명 수 제한·특권 분리와 강한 암호 정책을 적용(NIST AC-6·SI-4)</t>
         </is>
@@ -8723,42 +8818,43 @@
           <t>낮음</t>
         </is>
       </c>
-      <c r="G55" s="8" t="inlineStr">
+      <c r="G55" s="8" t="inlineStr"/>
+      <c r="H55" s="8" t="inlineStr">
         <is>
           <t>중</t>
         </is>
       </c>
-      <c r="H55" s="8" t="inlineStr">
+      <c r="I55" s="9" t="inlineStr">
         <is>
           <t>하</t>
         </is>
       </c>
-      <c r="I55" s="9" t="inlineStr">
+      <c r="J55" s="9" t="inlineStr">
         <is>
           <t>EDR·XDR</t>
         </is>
       </c>
-      <c r="J55" s="9" t="inlineStr">
+      <c r="K55" s="8" t="inlineStr">
         <is>
           <t>서명된 정상 도구 악용</t>
         </is>
       </c>
-      <c r="K55" s="8" t="n">
+      <c r="L55" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="L55" s="9" t="inlineStr">
+      <c r="M55" s="9" t="inlineStr">
         <is>
           <t>[ATT&amp;CK 주체 141]</t>
         </is>
       </c>
-      <c r="M55" s="9" t="inlineStr">
+      <c r="N55" s="9" t="inlineStr">
         <is>
           <t>보안 제품 상태 변조 방지와 탐지 규칙·텔레메트리 중앙 감시를 적용(NIST SI-4)</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A4:M55"/>
+  <autoFilter ref="A4:N55"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -9161,7 +9257,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AN55"/>
+  <dimension ref="A1:AO55"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -9192,18 +9288,19 @@
     <col width="7" customWidth="1" min="26" max="26"/>
     <col width="8" customWidth="1" min="27" max="27"/>
     <col width="7" customWidth="1" min="28" max="28"/>
-    <col width="40" customWidth="1" min="29" max="29"/>
-    <col width="46" customWidth="1" min="30" max="30"/>
-    <col width="7" customWidth="1" min="31" max="31"/>
+    <col width="7" customWidth="1" min="29" max="29"/>
+    <col width="40" customWidth="1" min="30" max="30"/>
+    <col width="46" customWidth="1" min="31" max="31"/>
     <col width="7" customWidth="1" min="32" max="32"/>
     <col width="7" customWidth="1" min="33" max="33"/>
     <col width="7" customWidth="1" min="34" max="34"/>
-    <col width="14" customWidth="1" min="35" max="35"/>
-    <col width="26" customWidth="1" min="36" max="36"/>
-    <col width="24" customWidth="1" min="37" max="37"/>
-    <col width="26" customWidth="1" min="38" max="38"/>
-    <col width="60" customWidth="1" min="39" max="39"/>
-    <col width="22" customWidth="1" min="40" max="40"/>
+    <col width="7" customWidth="1" min="35" max="35"/>
+    <col width="14" customWidth="1" min="36" max="36"/>
+    <col width="26" customWidth="1" min="37" max="37"/>
+    <col width="24" customWidth="1" min="38" max="38"/>
+    <col width="26" customWidth="1" min="39" max="39"/>
+    <col width="60" customWidth="1" min="40" max="40"/>
+    <col width="22" customWidth="1" min="41" max="41"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -9241,12 +9338,12 @@
           <t>위험 평가</t>
         </is>
       </c>
-      <c r="AE3" s="25" t="inlineStr">
+      <c r="AF3" s="25" t="inlineStr">
         <is>
           <t>실제 근거</t>
         </is>
       </c>
-      <c r="AL3" s="26" t="inlineStr">
+      <c r="AM3" s="26" t="inlineStr">
         <is>
           <t>대응 기준·참고 문헌</t>
         </is>
@@ -9390,65 +9487,70 @@
       </c>
       <c r="AB4" s="7" t="inlineStr">
         <is>
+          <t>경계</t>
+        </is>
+      </c>
+      <c r="AC4" s="7" t="inlineStr">
+        <is>
           <t>우선순위</t>
         </is>
       </c>
-      <c r="AC4" s="7" t="inlineStr">
+      <c r="AD4" s="7" t="inlineStr">
         <is>
           <t>발생가능성 근거(자동)</t>
         </is>
       </c>
-      <c r="AD4" s="7" t="inlineStr">
+      <c r="AE4" s="7" t="inlineStr">
         <is>
           <t>심각도 근거</t>
         </is>
       </c>
-      <c r="AE4" s="7" t="inlineStr">
+      <c r="AF4" s="7" t="inlineStr">
         <is>
           <t>실제 사고 수</t>
         </is>
       </c>
-      <c r="AF4" s="7" t="inlineStr">
+      <c r="AG4" s="7" t="inlineStr">
         <is>
           <t>최근(2025~)</t>
         </is>
       </c>
-      <c r="AG4" s="7" t="inlineStr">
+      <c r="AH4" s="7" t="inlineStr">
         <is>
           <t>정부 경보</t>
         </is>
       </c>
-      <c r="AH4" s="7" t="inlineStr">
+      <c r="AI4" s="7" t="inlineStr">
         <is>
           <t>위협인텔</t>
         </is>
       </c>
-      <c r="AI4" s="7" t="inlineStr">
+      <c r="AJ4" s="7" t="inlineStr">
         <is>
           <t>근거 수준</t>
         </is>
       </c>
-      <c r="AJ4" s="7" t="inlineStr">
+      <c r="AK4" s="7" t="inlineStr">
         <is>
           <t>관련 사례 ID</t>
         </is>
       </c>
-      <c r="AK4" s="7" t="inlineStr">
+      <c r="AL4" s="7" t="inlineStr">
         <is>
           <t>주요 영향(실제 사고)</t>
         </is>
       </c>
-      <c r="AL4" s="7" t="inlineStr">
+      <c r="AM4" s="7" t="inlineStr">
         <is>
           <t>NIST SP 800-53</t>
         </is>
       </c>
-      <c r="AM4" s="7" t="inlineStr">
+      <c r="AN4" s="7" t="inlineStr">
         <is>
           <t>탐지·대응 포인트</t>
         </is>
       </c>
-      <c r="AN4" s="7" t="inlineStr">
+      <c r="AO4" s="7" t="inlineStr">
         <is>
           <t>참고 문헌</t>
         </is>
@@ -9561,24 +9663,22 @@
           <t>매우 높음</t>
         </is>
       </c>
-      <c r="AB5" s="8" t="n">
+      <c r="AB5" s="9" t="inlineStr"/>
+      <c r="AC5" s="8" t="n">
         <v>1</v>
       </c>
-      <c r="AC5" s="9" t="inlineStr">
-        <is>
-          <t>실제 사고 8건(최근 0) · ATT&amp;CK 주체 75 · KEV O · 정부 경보 0 · 위협인텔 0 · 실증 0</t>
-        </is>
-      </c>
       <c r="AD5" s="9" t="inlineStr">
         <is>
+          <t>실제 사고 8건(최근 0, 서로 다른 행위자·캠페인 8) · ATT&amp;CK 주체 75 · KEV O · 정부 경보 0 · 위협인텔 0 · 실증 0</t>
+        </is>
+      </c>
+      <c r="AE5" s="9" t="inlineStr">
+        <is>
           <t>VPN·방화벽·게이트웨이·파일전송 장비의 공개 즉시 악용되는 취약점으로 경계 안으로 바로 진입 — 엣지 장비는 EDR이 깔리지 않아 레거시로 탐지가 어렵고 KEV 등재가 매년 14~21%를 차지(참고치)</t>
         </is>
       </c>
-      <c r="AE5" s="9" t="n">
+      <c r="AF5" s="9" t="n">
         <v>8</v>
-      </c>
-      <c r="AF5" s="9" t="n">
-        <v>0</v>
       </c>
       <c r="AG5" s="9" t="n">
         <v>0</v>
@@ -9586,22 +9686,25 @@
       <c r="AH5" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="AI5" s="27" t="inlineStr">
+      <c r="AI5" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ5" s="27" t="inlineStr">
         <is>
           <t>실제 사고 확인</t>
         </is>
       </c>
-      <c r="AJ5" s="9" t="inlineStr">
+      <c r="AK5" s="9" t="inlineStr">
         <is>
           <t>ENI-001, ENI-003, ENI-004, ENI-005, ENI-006, ENI-007, ENI-008, ENI-010</t>
         </is>
       </c>
-      <c r="AK5" s="9" t="inlineStr">
+      <c r="AL5" s="9" t="inlineStr">
         <is>
           <t>내부 접근 확보 6 · 측면 이동·확산 2 · 데이터 유출 2 · 금전 피해 2</t>
         </is>
       </c>
-      <c r="AL5" s="9" t="inlineStr">
+      <c r="AM5" s="9" t="inlineStr">
         <is>
           <t>RA-5 Vulnerability Monitoring and Scanning
 SI-2 Flaw Remediation
@@ -9609,7 +9712,7 @@
 SI-4 System Monitoring</t>
         </is>
       </c>
-      <c r="AM5" s="9" t="inlineStr">
+      <c r="AN5" s="9" t="inlineStr">
         <is>
           <t>■ 탐지
 - 외부 노출 자산을 지속 식별하고 엣지 장비의 취약점 공개·악용 동향을 신속 대조(NIST RA-5·SI-4)
@@ -9620,7 +9723,7 @@
 - 참고: CISA 〈KEV Catalog〉 · CISA 〈Edge Device Advisory〉</t>
         </is>
       </c>
-      <c r="AN5" s="9" t="inlineStr">
+      <c r="AO5" s="9" t="inlineStr">
         <is>
           <t>CISA 〈KEV Catalog〉
 CISA 〈Edge Device Advisory〉</t>
@@ -9734,48 +9837,49 @@
           <t>매우 높음</t>
         </is>
       </c>
-      <c r="AB6" s="8" t="n">
+      <c r="AB6" s="9" t="inlineStr"/>
+      <c r="AC6" s="8" t="n">
         <v>5</v>
       </c>
-      <c r="AC6" s="9" t="inlineStr">
-        <is>
-          <t>실제 사고 4건(최근 0) · ATT&amp;CK 주체 43 · KEV - · 정부 경보 1 · 위협인텔 0 · 실증 0</t>
-        </is>
-      </c>
       <c r="AD6" s="9" t="inlineStr">
         <is>
+          <t>실제 사고 4건(최근 0, 서로 다른 행위자·캠페인 4) · ATT&amp;CK 주체 43 · KEV - · 정부 경보 1 · 위협인텔 0 · 실증 0</t>
+        </is>
+      </c>
+      <c r="AE6" s="9" t="inlineStr">
+        <is>
           <t>탈취 계정·노출 RDP·VPN으로 정상 인증처럼 들어와 경계 방화벽을 통과 — 로그인 자체는 정상이라 레거시 탐지가 어렵고 랜섬웨어 초기 침투 1순위 경로</t>
         </is>
       </c>
-      <c r="AE6" s="9" t="n">
+      <c r="AF6" s="9" t="n">
         <v>4</v>
       </c>
-      <c r="AF6" s="9" t="n">
+      <c r="AG6" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="AG6" s="9" t="n">
+      <c r="AH6" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="AH6" s="9" t="n">
+      <c r="AI6" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="AI6" s="27" t="inlineStr">
+      <c r="AJ6" s="27" t="inlineStr">
         <is>
           <t>실제 사고 확인</t>
         </is>
       </c>
-      <c r="AJ6" s="9" t="inlineStr">
+      <c r="AK6" s="9" t="inlineStr">
         <is>
           <t>ENI-002, ENI-009, ENI-013, ENI-014
 정부 경보: ENI-030</t>
         </is>
       </c>
-      <c r="AK6" s="9" t="inlineStr">
+      <c r="AL6" s="9" t="inlineStr">
         <is>
           <t>내부 접근 확보 3 · 랜섬·암호화 3 · 데이터 유출 2 · 첩보·감시 1</t>
         </is>
       </c>
-      <c r="AL6" s="9" t="inlineStr">
+      <c r="AM6" s="9" t="inlineStr">
         <is>
           <t>AC-17 Remote Access
 IA-2 Identification and Authentication (Organizational Users)
@@ -9783,7 +9887,7 @@
 SI-4 System Monitoring</t>
         </is>
       </c>
-      <c r="AM6" s="9" t="inlineStr">
+      <c r="AN6" s="9" t="inlineStr">
         <is>
           <t>■ 탐지
 - 원격 서비스 로그인의 비정상 위치·시간·장치와 MFA 미적용 경로를 아이덴티티·네트워크 기반으로 탐지(NIST SI-4·IA-2)
@@ -9794,7 +9898,7 @@
 - 참고: Mandiant 〈M-Trends〉</t>
         </is>
       </c>
-      <c r="AN6" s="9" t="inlineStr">
+      <c r="AO6" s="9" t="inlineStr">
         <is>
           <t>MITRE 〈ATT&amp;CK Enterprise v19.2〉
 Mandiant 〈M-Trends〉</t>
@@ -9900,21 +10004,19 @@
           <t>보통</t>
         </is>
       </c>
-      <c r="AB7" s="8" t="n">
+      <c r="AB7" s="9" t="inlineStr"/>
+      <c r="AC7" s="8" t="n">
         <v>49</v>
       </c>
-      <c r="AC7" s="9" t="inlineStr">
-        <is>
-          <t>실제 사고 0건(최근 0) · ATT&amp;CK 주체 44 · KEV - · 정부 경보 0 · 위협인텔 0 · 실증 0</t>
-        </is>
-      </c>
       <c r="AD7" s="9" t="inlineStr">
         <is>
+          <t>실제 사고 0건(최근 0, 서로 다른 행위자·캠페인 0) · ATT&amp;CK 주체 44 · KEV - · 정부 경보 0 · 위협인텔 0 · 실증 0</t>
+        </is>
+      </c>
+      <c r="AE7" s="9" t="inlineStr">
+        <is>
           <t>정상 사이트·광고망을 경유한 감염이라 경계에서 걸러지지 않으나, 피해는 후속 실행·확산 단계에서 커짐</t>
         </is>
-      </c>
-      <c r="AE7" s="9" t="n">
-        <v>0</v>
       </c>
       <c r="AF7" s="9" t="n">
         <v>0</v>
@@ -9925,21 +10027,24 @@
       <c r="AH7" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="AI7" s="28" t="inlineStr">
+      <c r="AI7" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ7" s="28" t="inlineStr">
         <is>
           <t>ATT&amp;CK 사례·KEV 다수</t>
         </is>
       </c>
-      <c r="AJ7" s="9" t="inlineStr"/>
       <c r="AK7" s="9" t="inlineStr"/>
-      <c r="AL7" s="9" t="inlineStr">
+      <c r="AL7" s="9" t="inlineStr"/>
+      <c r="AM7" s="9" t="inlineStr">
         <is>
           <t>SI-3 Malicious Code Protection
 SC-7 Boundary Protection
 SI-4 System Monitoring</t>
         </is>
       </c>
-      <c r="AM7" s="9" t="inlineStr">
+      <c r="AN7" s="9" t="inlineStr">
         <is>
           <t>■ 탐지
 - 엔드포인트의 브라우저·플러그인 비정상 실행과 신뢰 사이트발 악성 리다이렉트를 행위 기반으로 탐지(NIST SI-3·SI-4)
@@ -9947,7 +10052,7 @@
 - 브라우저·플러그인 신속 패치, 웹 격리·콘텐츠 필터링과 엔드포인트 행위 탐지를 적용(NIST SI-3·SC-7)</t>
         </is>
       </c>
-      <c r="AN7" s="9" t="inlineStr">
+      <c r="AO7" s="9" t="inlineStr">
         <is>
           <t>MITRE 〈ATT&amp;CK Enterprise v19.2〉</t>
         </is>
@@ -10056,24 +10161,22 @@
           <t>보통</t>
         </is>
       </c>
-      <c r="AB8" s="8" t="n">
+      <c r="AB8" s="9" t="inlineStr"/>
+      <c r="AC8" s="8" t="n">
         <v>44</v>
       </c>
-      <c r="AC8" s="9" t="inlineStr">
-        <is>
-          <t>실제 사고 1건(최근 0) · ATT&amp;CK 주체 28 · KEV - · 정부 경보 0 · 위협인텔 0 · 실증 0</t>
-        </is>
-      </c>
       <c r="AD8" s="9" t="inlineStr">
         <is>
+          <t>실제 사고 1건(최근 0, 서로 다른 행위자·캠페인 1) · ATT&amp;CK 주체 28 · KEV - · 정부 경보 0 · 위협인텔 0 · 실증 0</t>
+        </is>
+      </c>
+      <c r="AE8" s="9" t="inlineStr">
+        <is>
           <t>경계·망분리를 우회해 격리망까지 전파할 수 있으나 전파 속도·범위는 제한적</t>
         </is>
       </c>
-      <c r="AE8" s="9" t="n">
+      <c r="AF8" s="9" t="n">
         <v>1</v>
-      </c>
-      <c r="AF8" s="9" t="n">
-        <v>0</v>
       </c>
       <c r="AG8" s="9" t="n">
         <v>0</v>
@@ -10081,29 +10184,32 @@
       <c r="AH8" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="AI8" s="27" t="inlineStr">
+      <c r="AI8" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ8" s="27" t="inlineStr">
         <is>
           <t>실제 사고 확인</t>
         </is>
       </c>
-      <c r="AJ8" s="9" t="inlineStr">
+      <c r="AK8" s="9" t="inlineStr">
         <is>
           <t>ENI-029</t>
         </is>
       </c>
-      <c r="AK8" s="9" t="inlineStr">
+      <c r="AL8" s="9" t="inlineStr">
         <is>
           <t>내부 접근 확보 1 · 측면 이동·확산 1</t>
         </is>
       </c>
-      <c r="AL8" s="9" t="inlineStr">
+      <c r="AM8" s="9" t="inlineStr">
         <is>
           <t>SI-3 Malicious Code Protection
 MP-7 Media Use
 SC-7 Boundary Protection</t>
         </is>
       </c>
-      <c r="AM8" s="9" t="inlineStr">
+      <c r="AN8" s="9" t="inlineStr">
         <is>
           <t>■ 탐지
 - 이동식 매체 연결·자동 실행과 격리망 호스트의 비정상 실행을 엔드포인트 기반으로 탐지(NIST SI-3)
@@ -10111,7 +10217,7 @@
 - 이동식 매체 사용을 통제·차단하고 자동 실행을 비활성화, 격리망 자산 반입 매체를 검사(NIST MP-7·SI-3)</t>
         </is>
       </c>
-      <c r="AN8" s="9" t="inlineStr">
+      <c r="AO8" s="9" t="inlineStr">
         <is>
           <t>MITRE 〈ATT&amp;CK Enterprise v19.2〉</t>
         </is>
@@ -10220,24 +10326,26 @@
           <t>매우 높음</t>
         </is>
       </c>
-      <c r="AB9" s="8" t="n">
+      <c r="AB9" s="9" t="inlineStr">
+        <is>
+          <t>경계</t>
+        </is>
+      </c>
+      <c r="AC9" s="8" t="n">
         <v>12</v>
       </c>
-      <c r="AC9" s="9" t="inlineStr">
-        <is>
-          <t>실제 사고 2건(최근 0) · ATT&amp;CK 주체 13 · KEV - · 정부 경보 0 · 위협인텔 0 · 실증 0</t>
-        </is>
-      </c>
       <c r="AD9" s="9" t="inlineStr">
         <is>
+          <t>실제 사고 2건(최근 0, 서로 다른 행위자·캠페인 2) · ATT&amp;CK 주체 13 · KEV - · 정부 경보 0 · 위협인텔 0 · 실증 0</t>
+        </is>
+      </c>
+      <c r="AE9" s="9" t="inlineStr">
+        <is>
           <t>MSP·원격 관리·연동 토큰 등 신뢰 경로로 들어와 다수 하위 고객을 한 번에 침해 — 정상 관리 트래픽이라 레거시 탐지가 어렵고 피해가 연쇄됨</t>
         </is>
       </c>
-      <c r="AE9" s="9" t="n">
+      <c r="AF9" s="9" t="n">
         <v>2</v>
-      </c>
-      <c r="AF9" s="9" t="n">
-        <v>0</v>
       </c>
       <c r="AG9" s="9" t="n">
         <v>0</v>
@@ -10245,22 +10353,25 @@
       <c r="AH9" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="AI9" s="27" t="inlineStr">
+      <c r="AI9" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ9" s="27" t="inlineStr">
         <is>
           <t>실제 사고 확인</t>
         </is>
       </c>
-      <c r="AJ9" s="9" t="inlineStr">
+      <c r="AK9" s="9" t="inlineStr">
         <is>
           <t>ENI-009, ENI-011</t>
         </is>
       </c>
-      <c r="AK9" s="9" t="inlineStr">
+      <c r="AL9" s="9" t="inlineStr">
         <is>
           <t>내부 접근 확보 2 · 랜섬·암호화 2</t>
         </is>
       </c>
-      <c r="AL9" s="9" t="inlineStr">
+      <c r="AM9" s="9" t="inlineStr">
         <is>
           <t>AC-20 Use of External Systems
 CA-3 Information Exchange
@@ -10268,7 +10379,7 @@
 SI-4 System Monitoring</t>
         </is>
       </c>
-      <c r="AM9" s="9" t="inlineStr">
+      <c r="AN9" s="9" t="inlineStr">
         <is>
           <t>■ 탐지
 - 신뢰 관계·연동 계정의 비정상 사용과 관리 도구발 대량·일괄 작업을 모니터링(NIST SI-4·AC-20)
@@ -10277,7 +10388,7 @@
 - 참고: Mandiant 〈M-Trends〉</t>
         </is>
       </c>
-      <c r="AN9" s="9" t="inlineStr">
+      <c r="AO9" s="9" t="inlineStr">
         <is>
           <t>MITRE 〈ATT&amp;CK Enterprise v19.2〉
 Mandiant 〈M-Trends〉</t>
@@ -10387,24 +10498,22 @@
           <t>매우 높음</t>
         </is>
       </c>
-      <c r="AB10" s="8" t="n">
+      <c r="AB10" s="9" t="inlineStr"/>
+      <c r="AC10" s="8" t="n">
         <v>7</v>
       </c>
-      <c r="AC10" s="9" t="inlineStr">
-        <is>
-          <t>실제 사고 3건(최근 0) · ATT&amp;CK 주체 233 · KEV - · 정부 경보 0 · 위협인텔 0 · 실증 0</t>
-        </is>
-      </c>
       <c r="AD10" s="9" t="inlineStr">
         <is>
+          <t>실제 사고 3건(최근 0, 서로 다른 행위자·캠페인 3) · ATT&amp;CK 주체 233 · KEV - · 정부 경보 0 · 위협인텔 0 · 실증 0</t>
+        </is>
+      </c>
+      <c r="AE10" s="9" t="inlineStr">
+        <is>
           <t>디스크에 악성 파일 없이 메모리에서 실행돼 시그니처 AV가 탐지하지 못함 — 사람 운영 랜섬웨어·국가배후 작전 전반의 기본 실행 수단</t>
         </is>
       </c>
-      <c r="AE10" s="9" t="n">
+      <c r="AF10" s="9" t="n">
         <v>3</v>
-      </c>
-      <c r="AF10" s="9" t="n">
-        <v>0</v>
       </c>
       <c r="AG10" s="9" t="n">
         <v>0</v>
@@ -10412,29 +10521,32 @@
       <c r="AH10" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="AI10" s="27" t="inlineStr">
+      <c r="AI10" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ10" s="27" t="inlineStr">
         <is>
           <t>실제 사고 확인</t>
         </is>
       </c>
-      <c r="AJ10" s="9" t="inlineStr">
+      <c r="AK10" s="9" t="inlineStr">
         <is>
           <t>ENI-001, ENI-012, ENI-020</t>
         </is>
       </c>
-      <c r="AK10" s="9" t="inlineStr">
+      <c r="AL10" s="9" t="inlineStr">
         <is>
           <t>내부 접근 확보 2 · 첩보·감시 1 · 측면 이동·확산 1 · 랜섬·암호화 1</t>
         </is>
       </c>
-      <c r="AL10" s="9" t="inlineStr">
+      <c r="AM10" s="9" t="inlineStr">
         <is>
           <t>SI-3 Malicious Code Protection
 SI-4 System Monitoring
 CM-7 Least Functionality</t>
         </is>
       </c>
-      <c r="AM10" s="9" t="inlineStr">
+      <c r="AN10" s="9" t="inlineStr">
         <is>
           <t>■ 탐지
 - PowerShell 스크립트 블록·명령줄 로깅과 비정상 실행 맥락(인코딩·다운로드·원격 실행)을 행위 기반으로 탐지(NIST SI-4·SI-3)
@@ -10443,7 +10555,7 @@
 - 참고: LOLBAS 〈Project〉</t>
         </is>
       </c>
-      <c r="AN10" s="9" t="inlineStr">
+      <c r="AO10" s="9" t="inlineStr">
         <is>
           <t>MITRE 〈ATT&amp;CK Enterprise v19.2〉
 LOLBAS 〈Project〉</t>
@@ -10549,24 +10661,22 @@
           <t>보통</t>
         </is>
       </c>
-      <c r="AB11" s="8" t="n">
+      <c r="AB11" s="9" t="inlineStr"/>
+      <c r="AC11" s="8" t="n">
         <v>30</v>
       </c>
-      <c r="AC11" s="9" t="inlineStr">
-        <is>
-          <t>실제 사고 1건(최근 0) · ATT&amp;CK 주체 147 · KEV - · 정부 경보 0 · 위협인텔 0 · 실증 0</t>
-        </is>
-      </c>
       <c r="AD11" s="9" t="inlineStr">
         <is>
+          <t>실제 사고 1건(최근 0, 서로 다른 행위자·캠페인 1) · ATT&amp;CK 주체 147 · KEV - · 정부 경보 0 · 위협인텔 0 · 실증 0</t>
+        </is>
+      </c>
+      <c r="AE11" s="9" t="inlineStr">
+        <is>
           <t>정상 관리 기능을 써서 실행·측면 이동·수집에 쓰이나, 단독 피해보다 다른 단계를 잇는 수단</t>
         </is>
       </c>
-      <c r="AE11" s="9" t="n">
+      <c r="AF11" s="9" t="n">
         <v>1</v>
-      </c>
-      <c r="AF11" s="9" t="n">
-        <v>0</v>
       </c>
       <c r="AG11" s="9" t="n">
         <v>0</v>
@@ -10574,29 +10684,32 @@
       <c r="AH11" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="AI11" s="27" t="inlineStr">
+      <c r="AI11" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ11" s="27" t="inlineStr">
         <is>
           <t>실제 사고 확인</t>
         </is>
       </c>
-      <c r="AJ11" s="9" t="inlineStr">
+      <c r="AK11" s="9" t="inlineStr">
         <is>
           <t>ENI-020</t>
         </is>
       </c>
-      <c r="AK11" s="9" t="inlineStr">
+      <c r="AL11" s="9" t="inlineStr">
         <is>
           <t>내부 접근 확보 1</t>
         </is>
       </c>
-      <c r="AL11" s="9" t="inlineStr">
+      <c r="AM11" s="9" t="inlineStr">
         <is>
           <t>SI-4 System Monitoring
 CM-7 Least Functionality
 AU-6 Audit Record Review, Analysis, and Reporting</t>
         </is>
       </c>
-      <c r="AM11" s="9" t="inlineStr">
+      <c r="AN11" s="9" t="inlineStr">
         <is>
           <t>■ 탐지
 - WMI 이벤트 구독·원격 WMI 실행과 비정상 부모-자식 프로세스를 행위 기반으로 탐지(NIST SI-4·AU-6)
@@ -10604,7 +10717,7 @@
 - WMI 원격 실행을 제한하고 관리 활동을 기준선과 대조·감사(NIST CM-7·AU-6)</t>
         </is>
       </c>
-      <c r="AN11" s="9" t="inlineStr">
+      <c r="AO11" s="9" t="inlineStr">
         <is>
           <t>MITRE 〈ATT&amp;CK Enterprise v19.2〉</t>
         </is>
@@ -10713,55 +10826,60 @@
           <t>매우 높음</t>
         </is>
       </c>
-      <c r="AB12" s="8" t="n">
+      <c r="AB12" s="9" t="inlineStr">
+        <is>
+          <t>경계</t>
+        </is>
+      </c>
+      <c r="AC12" s="8" t="n">
         <v>15</v>
       </c>
-      <c r="AC12" s="9" t="inlineStr">
-        <is>
-          <t>실제 사고 2건(최근 0) · ATT&amp;CK 주체 2 · KEV - · 정부 경보 1 · 위협인텔 0 · 실증 0</t>
-        </is>
-      </c>
       <c r="AD12" s="9" t="inlineStr">
         <is>
+          <t>실제 사고 2건(최근 0, 서로 다른 행위자·캠페인 2) · ATT&amp;CK 주체 2 · KEV - · 정부 경보 1 · 위협인텔 0 · 실증 0</t>
+        </is>
+      </c>
+      <c r="AE12" s="9" t="inlineStr">
+        <is>
           <t>OS에 서명·내장된 정상 바이너리(rundll32·mshta·regsvr32 등)로 악성 코드를 대리 실행 — 허용 목록·서명 검증을 통과해 레거시 통제가 구분하지 못함</t>
         </is>
       </c>
-      <c r="AE12" s="9" t="n">
+      <c r="AF12" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="AF12" s="9" t="n">
+      <c r="AG12" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="AG12" s="9" t="n">
+      <c r="AH12" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="AH12" s="9" t="n">
+      <c r="AI12" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="AI12" s="27" t="inlineStr">
+      <c r="AJ12" s="27" t="inlineStr">
         <is>
           <t>실제 사고 확인</t>
         </is>
       </c>
-      <c r="AJ12" s="9" t="inlineStr">
+      <c r="AK12" s="9" t="inlineStr">
         <is>
           <t>ENI-001, ENI-019
 정부 경보: ENI-030</t>
         </is>
       </c>
-      <c r="AK12" s="9" t="inlineStr">
+      <c r="AL12" s="9" t="inlineStr">
         <is>
           <t>내부 접근 확보 2 · 첩보·감시 1 · 측면 이동·확산 1</t>
         </is>
       </c>
-      <c r="AL12" s="9" t="inlineStr">
+      <c r="AM12" s="9" t="inlineStr">
         <is>
           <t>CM-7 Least Functionality
 SI-4 System Monitoring
 SI-7 Software, Firmware, and Information Integrity</t>
         </is>
       </c>
-      <c r="AM12" s="9" t="inlineStr">
+      <c r="AN12" s="9" t="inlineStr">
         <is>
           <t>■ 탐지
 - 정상 바이너리의 비정상 인자·부모 프로세스·네트워크 행위를 행위 기반으로 탐지(NIST SI-4·CM-7)
@@ -10770,7 +10888,7 @@
 - 참고: LOLBAS 〈Project〉</t>
         </is>
       </c>
-      <c r="AN12" s="9" t="inlineStr">
+      <c r="AO12" s="9" t="inlineStr">
         <is>
           <t>LOLBAS 〈Project〉
 MITRE 〈ATT&amp;CK Enterprise v19.2〉</t>
@@ -10877,21 +10995,19 @@
           <t>보통</t>
         </is>
       </c>
-      <c r="AB13" s="8" t="n">
+      <c r="AB13" s="9" t="inlineStr"/>
+      <c r="AC13" s="8" t="n">
         <v>48</v>
       </c>
-      <c r="AC13" s="9" t="inlineStr">
-        <is>
-          <t>실제 사고 0건(최근 0) · ATT&amp;CK 주체 272 · KEV - · 정부 경보 0 · 위협인텔 0 · 실증 0</t>
-        </is>
-      </c>
       <c r="AD13" s="9" t="inlineStr">
         <is>
+          <t>실제 사고 0건(최근 0, 서로 다른 행위자·캠페인 0) · ATT&amp;CK 주체 272 · KEV - · 정부 경보 0 · 위협인텔 0 · 실증 0</t>
+        </is>
+      </c>
+      <c r="AE13" s="9" t="inlineStr">
+        <is>
           <t>API 직접 호출·서비스 실행으로 중간 도구를 거치지 않아 후킹 기반 탐지를 우회하나, 피해는 후속 단계에서 발생</t>
         </is>
-      </c>
-      <c r="AE13" s="9" t="n">
-        <v>0</v>
       </c>
       <c r="AF13" s="9" t="n">
         <v>0</v>
@@ -10902,20 +11018,23 @@
       <c r="AH13" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="AI13" s="28" t="inlineStr">
+      <c r="AI13" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ13" s="28" t="inlineStr">
         <is>
           <t>ATT&amp;CK 사례·KEV 다수</t>
         </is>
       </c>
-      <c r="AJ13" s="9" t="inlineStr"/>
       <c r="AK13" s="9" t="inlineStr"/>
-      <c r="AL13" s="9" t="inlineStr">
+      <c r="AL13" s="9" t="inlineStr"/>
+      <c r="AM13" s="9" t="inlineStr">
         <is>
           <t>SI-4 System Monitoring
 CM-7 Least Functionality</t>
         </is>
       </c>
-      <c r="AM13" s="9" t="inlineStr">
+      <c r="AN13" s="9" t="inlineStr">
         <is>
           <t>■ 탐지
 - 커널 콜백·시스템 서비스 생성과 비정상 API 호출 시퀀스를 EDR 행위 기반으로 탐지(NIST SI-4)
@@ -10923,7 +11042,7 @@
 - 커널 수준 가시성(EDR)과 최소 기능·서비스 생성 통제를 적용(NIST CM-7·SI-4)</t>
         </is>
       </c>
-      <c r="AN13" s="9" t="inlineStr">
+      <c r="AO13" s="9" t="inlineStr">
         <is>
           <t>MITRE 〈ATT&amp;CK Enterprise v19.2〉</t>
         </is>
@@ -11028,24 +11147,22 @@
           <t>보통</t>
         </is>
       </c>
-      <c r="AB14" s="8" t="n">
+      <c r="AB14" s="9" t="inlineStr"/>
+      <c r="AC14" s="8" t="n">
         <v>38</v>
       </c>
-      <c r="AC14" s="9" t="inlineStr">
-        <is>
-          <t>실제 사고 1건(최근 0) · ATT&amp;CK 주체 140 · KEV - · 정부 경보 0 · 위협인텔 0 · 실증 0</t>
-        </is>
-      </c>
       <c r="AD14" s="9" t="inlineStr">
         <is>
+          <t>실제 사고 1건(최근 0, 서로 다른 행위자·캠페인 1) · ATT&amp;CK 주체 140 · KEV - · 정부 경보 0 · 위협인텔 0 · 실증 0</t>
+        </is>
+      </c>
+      <c r="AE14" s="9" t="inlineStr">
+        <is>
           <t>정상 서비스 등록 메커니즘을 써서 지속·권한 상승에 쓰이나 단독 피해는 제한적</t>
         </is>
       </c>
-      <c r="AE14" s="9" t="n">
+      <c r="AF14" s="9" t="n">
         <v>1</v>
-      </c>
-      <c r="AF14" s="9" t="n">
-        <v>0</v>
       </c>
       <c r="AG14" s="9" t="n">
         <v>0</v>
@@ -11053,29 +11170,32 @@
       <c r="AH14" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="AI14" s="27" t="inlineStr">
+      <c r="AI14" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ14" s="27" t="inlineStr">
         <is>
           <t>실제 사고 확인</t>
         </is>
       </c>
-      <c r="AJ14" s="9" t="inlineStr">
+      <c r="AK14" s="9" t="inlineStr">
         <is>
           <t>ENI-032</t>
         </is>
       </c>
-      <c r="AK14" s="9" t="inlineStr">
+      <c r="AL14" s="9" t="inlineStr">
         <is>
           <t>내부 접근 확보 1</t>
         </is>
       </c>
-      <c r="AL14" s="9" t="inlineStr">
+      <c r="AM14" s="9" t="inlineStr">
         <is>
           <t>SI-4 System Monitoring
 CM-7 Least Functionality
 AU-6 Audit Record Review, Analysis, and Reporting</t>
         </is>
       </c>
-      <c r="AM14" s="9" t="inlineStr">
+      <c r="AN14" s="9" t="inlineStr">
         <is>
           <t>■ 탐지
 - 신규·수정 서비스와 비정상 바이너리 경로·시작 유형을 행위 기반으로 탐지(NIST SI-4·CM-7)
@@ -11083,7 +11203,7 @@
 - 서비스 생성·변경을 감사·기준선과 대조하고 최소 권한을 적용(NIST CM-7·AU-6)</t>
         </is>
       </c>
-      <c r="AN14" s="9" t="inlineStr">
+      <c r="AO14" s="9" t="inlineStr">
         <is>
           <t>MITRE 〈ATT&amp;CK Enterprise v19.2〉</t>
         </is>
@@ -11188,24 +11308,22 @@
           <t>보통</t>
         </is>
       </c>
-      <c r="AB15" s="8" t="n">
+      <c r="AB15" s="9" t="inlineStr"/>
+      <c r="AC15" s="8" t="n">
         <v>46</v>
       </c>
-      <c r="AC15" s="9" t="inlineStr">
-        <is>
-          <t>실제 사고 1건(최근 0) · ATT&amp;CK 주체 6 · KEV - · 정부 경보 0 · 위협인텔 0 · 실증 0</t>
-        </is>
-      </c>
       <c r="AD15" s="9" t="inlineStr">
         <is>
+          <t>실제 사고 1건(최근 0, 서로 다른 행위자·캠페인 1) · ATT&amp;CK 주체 6 · KEV - · 정부 경보 0 · 위협인텔 0 · 실증 0</t>
+        </is>
+      </c>
+      <c r="AE15" s="9" t="inlineStr">
+        <is>
           <t>재부팅·로그온 시 자동 실행으로 접근을 유지하나 피해는 후속 단계에서 발생</t>
         </is>
       </c>
-      <c r="AE15" s="9" t="n">
+      <c r="AF15" s="9" t="n">
         <v>1</v>
-      </c>
-      <c r="AF15" s="9" t="n">
-        <v>0</v>
       </c>
       <c r="AG15" s="9" t="n">
         <v>0</v>
@@ -11213,29 +11331,32 @@
       <c r="AH15" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="AI15" s="27" t="inlineStr">
+      <c r="AI15" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ15" s="27" t="inlineStr">
         <is>
           <t>실제 사고 확인</t>
         </is>
       </c>
-      <c r="AJ15" s="9" t="inlineStr">
+      <c r="AK15" s="9" t="inlineStr">
         <is>
           <t>ENI-020</t>
         </is>
       </c>
-      <c r="AK15" s="9" t="inlineStr">
+      <c r="AL15" s="9" t="inlineStr">
         <is>
           <t>내부 접근 확보 1</t>
         </is>
       </c>
-      <c r="AL15" s="9" t="inlineStr">
+      <c r="AM15" s="9" t="inlineStr">
         <is>
           <t>SI-4 System Monitoring
 SI-7 Software, Firmware, and Information Integrity
 CM-7 Least Functionality</t>
         </is>
       </c>
-      <c r="AM15" s="9" t="inlineStr">
+      <c r="AN15" s="9" t="inlineStr">
         <is>
           <t>■ 탐지
 - 자동 실행 지점(런키·시작 폴더·서비스)의 변경을 기준선과 대조해 탐지(NIST SI-4·SI-7)
@@ -11243,7 +11364,7 @@
 - 자동 실행 지점 변경을 감사·무결성 검증하고 최소 기능을 적용(NIST CM-7·SI-7)</t>
         </is>
       </c>
-      <c r="AN15" s="9" t="inlineStr">
+      <c r="AO15" s="9" t="inlineStr">
         <is>
           <t>MITRE 〈ATT&amp;CK Enterprise v19.2〉</t>
         </is>
@@ -11348,24 +11469,22 @@
           <t>보통</t>
         </is>
       </c>
-      <c r="AB16" s="8" t="n">
+      <c r="AB16" s="9" t="inlineStr"/>
+      <c r="AC16" s="8" t="n">
         <v>35</v>
       </c>
-      <c r="AC16" s="9" t="inlineStr">
-        <is>
-          <t>실제 사고 1건(최근 0) · ATT&amp;CK 주체 190 · KEV - · 정부 경보 0 · 위협인텔 0 · 실증 0</t>
-        </is>
-      </c>
       <c r="AD16" s="9" t="inlineStr">
         <is>
+          <t>실제 사고 1건(최근 0, 서로 다른 행위자·캠페인 1) · ATT&amp;CK 주체 190 · KEV - · 정부 경보 0 · 위협인텔 0 · 실증 0</t>
+        </is>
+      </c>
+      <c r="AE16" s="9" t="inlineStr">
+        <is>
           <t>정상 스케줄러로 지속·주기 실행을 확보하나 단독 피해는 제한적</t>
         </is>
       </c>
-      <c r="AE16" s="9" t="n">
+      <c r="AF16" s="9" t="n">
         <v>1</v>
-      </c>
-      <c r="AF16" s="9" t="n">
-        <v>0</v>
       </c>
       <c r="AG16" s="9" t="n">
         <v>0</v>
@@ -11373,29 +11492,32 @@
       <c r="AH16" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="AI16" s="27" t="inlineStr">
+      <c r="AI16" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ16" s="27" t="inlineStr">
         <is>
           <t>실제 사고 확인</t>
         </is>
       </c>
-      <c r="AJ16" s="9" t="inlineStr">
+      <c r="AK16" s="9" t="inlineStr">
         <is>
           <t>ENI-020</t>
         </is>
       </c>
-      <c r="AK16" s="9" t="inlineStr">
+      <c r="AL16" s="9" t="inlineStr">
         <is>
           <t>내부 접근 확보 1</t>
         </is>
       </c>
-      <c r="AL16" s="9" t="inlineStr">
+      <c r="AM16" s="9" t="inlineStr">
         <is>
           <t>SI-4 System Monitoring
 CM-7 Least Functionality
 AU-6 Audit Record Review, Analysis, and Reporting</t>
         </is>
       </c>
-      <c r="AM16" s="9" t="inlineStr">
+      <c r="AN16" s="9" t="inlineStr">
         <is>
           <t>■ 탐지
 - 신규·수정 예약 작업과 비정상 트리거·실행 바이너리를 행위 기반으로 탐지(NIST SI-4·AU-6)
@@ -11403,7 +11525,7 @@
 - 예약 작업 생성·변경을 감사하고 생성 권한을 최소화(NIST CM-7·AU-6)</t>
         </is>
       </c>
-      <c r="AN16" s="9" t="inlineStr">
+      <c r="AO16" s="9" t="inlineStr">
         <is>
           <t>MITRE 〈ATT&amp;CK Enterprise v19.2〉</t>
         </is>
@@ -11512,21 +11634,19 @@
           <t>보통</t>
         </is>
       </c>
-      <c r="AB17" s="8" t="n">
+      <c r="AB17" s="9" t="inlineStr"/>
+      <c r="AC17" s="8" t="n">
         <v>47</v>
       </c>
-      <c r="AC17" s="9" t="inlineStr">
-        <is>
-          <t>실제 사고 0건(최근 0) · ATT&amp;CK 주체 9 · KEV - · 정부 경보 0 · 위협인텔 0 · 실증 0</t>
-        </is>
-      </c>
       <c r="AD17" s="9" t="inlineStr">
         <is>
+          <t>실제 사고 0건(최근 0, 서로 다른 행위자·캠페인 0) · ATT&amp;CK 주체 9 · KEV - · 정부 경보 0 · 위협인텔 0 · 실증 0</t>
+        </is>
+      </c>
+      <c r="AE17" s="9" t="inlineStr">
+        <is>
           <t>정상 계정·권한을 추가·변경해 지속 접근을 확보 — 신원 매트릭스의 신원 기반 지속성과 연계되며 로그만으로는 악용 구분이 어려움</t>
         </is>
-      </c>
-      <c r="AE17" s="9" t="n">
-        <v>0</v>
       </c>
       <c r="AF17" s="9" t="n">
         <v>0</v>
@@ -11537,21 +11657,24 @@
       <c r="AH17" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="AI17" s="29" t="inlineStr">
+      <c r="AI17" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ17" s="29" t="inlineStr">
         <is>
           <t>ATT&amp;CK 사례·KEV 일부</t>
         </is>
       </c>
-      <c r="AJ17" s="9" t="inlineStr"/>
       <c r="AK17" s="9" t="inlineStr"/>
-      <c r="AL17" s="9" t="inlineStr">
+      <c r="AL17" s="9" t="inlineStr"/>
+      <c r="AM17" s="9" t="inlineStr">
         <is>
           <t>AC-2 Account Management
 IA-4 Identifier Management
 AU-6 Audit Record Review, Analysis, and Reporting</t>
         </is>
       </c>
-      <c r="AM17" s="9" t="inlineStr">
+      <c r="AN17" s="9" t="inlineStr">
         <is>
           <t>■ 탐지
 - 신규·변경 계정과 비정상 권한 부여·그룹 추가를 아이덴티티 기반으로 탐지(NIST AC-2·AU-6)
@@ -11559,7 +11682,7 @@
 - 계정 생성·권한 변경을 승인·감사하고 휴면·불필요 계정을 정리(NIST AC-2·IA-4)</t>
         </is>
       </c>
-      <c r="AN17" s="9" t="inlineStr">
+      <c r="AO17" s="9" t="inlineStr">
         <is>
           <t>MITRE 〈ATT&amp;CK Enterprise v19.2〉</t>
         </is>
@@ -11664,24 +11787,22 @@
           <t>높음</t>
         </is>
       </c>
-      <c r="AB18" s="8" t="n">
+      <c r="AB18" s="9" t="inlineStr"/>
+      <c r="AC18" s="8" t="n">
         <v>27</v>
       </c>
-      <c r="AC18" s="9" t="inlineStr">
-        <is>
-          <t>실제 사고 1건(최근 0) · ATT&amp;CK 주체 87 · KEV - · 정부 경보 0 · 위협인텔 0 · 실증 0</t>
-        </is>
-      </c>
       <c r="AD18" s="9" t="inlineStr">
         <is>
+          <t>실제 사고 1건(최근 0, 서로 다른 행위자·캠페인 1) · ATT&amp;CK 주체 87 · KEV - · 정부 경보 0 · 위협인텔 0 · 실증 0</t>
+        </is>
+      </c>
+      <c r="AE18" s="9" t="inlineStr">
+        <is>
           <t>정상 프로세스 메모리에 코드를 주입해 실행·은닉·권한 상승 — 디스크 산출물이 없어 시그니처가 탐지하지 못하고 거의 모든 고급 악성코드가 사용</t>
         </is>
       </c>
-      <c r="AE18" s="9" t="n">
+      <c r="AF18" s="9" t="n">
         <v>1</v>
-      </c>
-      <c r="AF18" s="9" t="n">
-        <v>0</v>
       </c>
       <c r="AG18" s="9" t="n">
         <v>0</v>
@@ -11689,28 +11810,31 @@
       <c r="AH18" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="AI18" s="27" t="inlineStr">
+      <c r="AI18" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ18" s="27" t="inlineStr">
         <is>
           <t>실제 사고 확인</t>
         </is>
       </c>
-      <c r="AJ18" s="9" t="inlineStr">
+      <c r="AK18" s="9" t="inlineStr">
         <is>
           <t>ENI-018</t>
         </is>
       </c>
-      <c r="AK18" s="9" t="inlineStr">
+      <c r="AL18" s="9" t="inlineStr">
         <is>
           <t>내부 접근 확보 1 · 측면 이동·확산 1</t>
         </is>
       </c>
-      <c r="AL18" s="9" t="inlineStr">
+      <c r="AM18" s="9" t="inlineStr">
         <is>
           <t>SI-3 Malicious Code Protection
 SI-4 System Monitoring</t>
         </is>
       </c>
-      <c r="AM18" s="9" t="inlineStr">
+      <c r="AN18" s="9" t="inlineStr">
         <is>
           <t>■ 탐지
 - 원격 스레드 생성·메모리 쓰기·비정상 메모리 영역 실행을 EDR 행위 기반으로 탐지(NIST SI-3·SI-4)
@@ -11718,7 +11842,7 @@
 - 커널 수준 메모리 가시성(EDR)과 공격 표면 축소 규칙을 적용(NIST SI-3·SI-4)</t>
         </is>
       </c>
-      <c r="AN18" s="9" t="inlineStr">
+      <c r="AO18" s="9" t="inlineStr">
         <is>
           <t>MITRE 〈ATT&amp;CK Enterprise v19.2〉</t>
         </is>
@@ -11823,24 +11947,22 @@
           <t>보통</t>
         </is>
       </c>
-      <c r="AB19" s="8" t="n">
+      <c r="AB19" s="9" t="inlineStr"/>
+      <c r="AC19" s="8" t="n">
         <v>45</v>
       </c>
-      <c r="AC19" s="9" t="inlineStr">
-        <is>
-          <t>실제 사고 1건(최근 0) · ATT&amp;CK 주체 23 · KEV - · 정부 경보 0 · 위협인텔 0 · 실증 0</t>
-        </is>
-      </c>
       <c r="AD19" s="9" t="inlineStr">
         <is>
+          <t>실제 사고 1건(최근 0, 서로 다른 행위자·캠페인 1) · ATT&amp;CK 주체 23 · KEV - · 정부 경보 0 · 위협인텔 0 · 실증 0</t>
+        </is>
+      </c>
+      <c r="AE19" s="9" t="inlineStr">
+        <is>
           <t>토큰 복제·가장으로 다른 사용자 권한을 사용하나 피해는 후속 단계에서 커짐</t>
         </is>
       </c>
-      <c r="AE19" s="9" t="n">
+      <c r="AF19" s="9" t="n">
         <v>1</v>
-      </c>
-      <c r="AF19" s="9" t="n">
-        <v>0</v>
       </c>
       <c r="AG19" s="9" t="n">
         <v>0</v>
@@ -11848,28 +11970,31 @@
       <c r="AH19" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="AI19" s="27" t="inlineStr">
+      <c r="AI19" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ19" s="27" t="inlineStr">
         <is>
           <t>실제 사고 확인</t>
         </is>
       </c>
-      <c r="AJ19" s="9" t="inlineStr">
+      <c r="AK19" s="9" t="inlineStr">
         <is>
           <t>ENI-032</t>
         </is>
       </c>
-      <c r="AK19" s="9" t="inlineStr">
+      <c r="AL19" s="9" t="inlineStr">
         <is>
           <t>내부 접근 확보 1</t>
         </is>
       </c>
-      <c r="AL19" s="9" t="inlineStr">
+      <c r="AM19" s="9" t="inlineStr">
         <is>
           <t>AC-6 Least Privilege
 SI-4 System Monitoring</t>
         </is>
       </c>
-      <c r="AM19" s="9" t="inlineStr">
+      <c r="AN19" s="9" t="inlineStr">
         <is>
           <t>■ 탐지
 - 토큰 복제·가장 API 호출과 비정상 권한 전환을 EDR 행위 기반으로 탐지(NIST SI-4·AC-6)
@@ -11877,7 +12002,7 @@
 - 최소 권한·특권 계정 분리와 토큰 조작 탐지 규칙을 적용(NIST AC-6·SI-4)</t>
         </is>
       </c>
-      <c r="AN19" s="9" t="inlineStr">
+      <c r="AO19" s="9" t="inlineStr">
         <is>
           <t>MITRE 〈ATT&amp;CK Enterprise v19.2〉</t>
         </is>
@@ -11982,24 +12107,22 @@
           <t>보통</t>
         </is>
       </c>
-      <c r="AB20" s="8" t="n">
+      <c r="AB20" s="9" t="inlineStr"/>
+      <c r="AC20" s="8" t="n">
         <v>41</v>
       </c>
-      <c r="AC20" s="9" t="inlineStr">
-        <is>
-          <t>실제 사고 1건(최근 0) · ATT&amp;CK 주체 63 · KEV - · 정부 경보 0 · 위협인텔 0 · 실증 0</t>
-        </is>
-      </c>
       <c r="AD20" s="9" t="inlineStr">
         <is>
+          <t>실제 사고 1건(최근 0, 서로 다른 행위자·캠페인 1) · ATT&amp;CK 주체 63 · KEV - · 정부 경보 0 · 위협인텔 0 · 실증 0</t>
+        </is>
+      </c>
+      <c r="AE20" s="9" t="inlineStr">
+        <is>
           <t>정상 자동 상승 바이너리를 악용해 UAC를 우회하나 단독 피해는 제한적</t>
         </is>
       </c>
-      <c r="AE20" s="9" t="n">
+      <c r="AF20" s="9" t="n">
         <v>1</v>
-      </c>
-      <c r="AF20" s="9" t="n">
-        <v>0</v>
       </c>
       <c r="AG20" s="9" t="n">
         <v>0</v>
@@ -12007,29 +12130,32 @@
       <c r="AH20" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="AI20" s="27" t="inlineStr">
+      <c r="AI20" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ20" s="27" t="inlineStr">
         <is>
           <t>실제 사고 확인</t>
         </is>
       </c>
-      <c r="AJ20" s="9" t="inlineStr">
+      <c r="AK20" s="9" t="inlineStr">
         <is>
           <t>ENI-032</t>
         </is>
       </c>
-      <c r="AK20" s="9" t="inlineStr">
+      <c r="AL20" s="9" t="inlineStr">
         <is>
           <t>내부 접근 확보 1</t>
         </is>
       </c>
-      <c r="AL20" s="9" t="inlineStr">
+      <c r="AM20" s="9" t="inlineStr">
         <is>
           <t>AC-6 Least Privilege
 SI-4 System Monitoring
 CM-7 Least Functionality</t>
         </is>
       </c>
-      <c r="AM20" s="9" t="inlineStr">
+      <c r="AN20" s="9" t="inlineStr">
         <is>
           <t>■ 탐지
 - 자동 상승 바이너리의 비정상 실행·레지스트리 조작을 행위 기반으로 탐지(NIST SI-4·CM-7)
@@ -12037,7 +12163,7 @@
 - UAC 최고 수준 설정·관리자 승인 모드와 최소 권한을 적용(NIST AC-6·CM-7)</t>
         </is>
       </c>
-      <c r="AN20" s="9" t="inlineStr">
+      <c r="AO20" s="9" t="inlineStr">
         <is>
           <t>MITRE 〈ATT&amp;CK Enterprise v19.2〉</t>
         </is>
@@ -12150,24 +12276,22 @@
           <t>높음</t>
         </is>
       </c>
-      <c r="AB21" s="8" t="n">
+      <c r="AB21" s="9" t="inlineStr"/>
+      <c r="AC21" s="8" t="n">
         <v>28</v>
       </c>
-      <c r="AC21" s="9" t="inlineStr">
-        <is>
-          <t>실제 사고 1건(최근 0) · ATT&amp;CK 주체 43 · KEV O · 정부 경보 0 · 위협인텔 0 · 실증 0</t>
-        </is>
-      </c>
       <c r="AD21" s="9" t="inlineStr">
         <is>
+          <t>실제 사고 1건(최근 0, 서로 다른 행위자·캠페인 1) · ATT&amp;CK 주체 43 · KEV O · 정부 경보 0 · 위협인텔 0 · 실증 0</t>
+        </is>
+      </c>
+      <c r="AE21" s="9" t="inlineStr">
+        <is>
           <t>로컬·커널 취약점(또는 BYOVD 취약 드라이버)으로 SYSTEM·커널 권한을 획득 — 하위 계층이라 상위 보안 도구가 무력화되고 KEV 등재 다수</t>
         </is>
       </c>
-      <c r="AE21" s="9" t="n">
+      <c r="AF21" s="9" t="n">
         <v>1</v>
-      </c>
-      <c r="AF21" s="9" t="n">
-        <v>0</v>
       </c>
       <c r="AG21" s="9" t="n">
         <v>0</v>
@@ -12175,29 +12299,32 @@
       <c r="AH21" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="AI21" s="27" t="inlineStr">
+      <c r="AI21" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ21" s="27" t="inlineStr">
         <is>
           <t>실제 사고 확인</t>
         </is>
       </c>
-      <c r="AJ21" s="9" t="inlineStr">
+      <c r="AK21" s="9" t="inlineStr">
         <is>
           <t>ENI-016</t>
         </is>
       </c>
-      <c r="AK21" s="9" t="inlineStr">
+      <c r="AL21" s="9" t="inlineStr">
         <is>
           <t>랜섬·암호화 1 · 자격증명·비밀 탈취 1</t>
         </is>
       </c>
-      <c r="AL21" s="9" t="inlineStr">
+      <c r="AM21" s="9" t="inlineStr">
         <is>
           <t>RA-5 Vulnerability Monitoring and Scanning
 SI-2 Flaw Remediation
 SI-4 System Monitoring</t>
         </is>
       </c>
-      <c r="AM21" s="9" t="inlineStr">
+      <c r="AN21" s="9" t="inlineStr">
         <is>
           <t>■ 탐지
 - 신규 커널 드라이버 로드와 취약 드라이버 서명·해시를 차단 목록과 대조해 탐지(NIST SI-4)
@@ -12206,7 +12333,7 @@
 - 참고: LOLDrivers 〈Project〉</t>
         </is>
       </c>
-      <c r="AN21" s="9" t="inlineStr">
+      <c r="AO21" s="9" t="inlineStr">
         <is>
           <t>CISA 〈KEV Catalog〉
 LOLDrivers 〈Project〉</t>
@@ -12317,55 +12444,56 @@
           <t>매우 높음</t>
         </is>
       </c>
-      <c r="AB22" s="8" t="n">
+      <c r="AB22" s="9" t="inlineStr"/>
+      <c r="AC22" s="8" t="n">
         <v>3</v>
       </c>
-      <c r="AC22" s="9" t="inlineStr">
-        <is>
-          <t>실제 사고 5건(최근 1) · ATT&amp;CK 주체 131 · KEV - · 정부 경보 1 · 위협인텔 0 · 실증 0</t>
-        </is>
-      </c>
       <c r="AD22" s="9" t="inlineStr">
         <is>
+          <t>실제 사고 5건(최근 1, 서로 다른 행위자·캠페인 5) · ATT&amp;CK 주체 131 · KEV - · 정부 경보 1 · 위협인텔 0 · 실증 0</t>
+        </is>
+      </c>
+      <c r="AE22" s="9" t="inlineStr">
+        <is>
           <t>서명된 취약 드라이버를 올려 EDR·백신을 커널에서 무력화 — 보안 도구 자체가 꺼지므로 이후 단계가 전부 가려짐. 랜섬웨어·국가배후가 공유하는 EDR 킬러 다수</t>
         </is>
       </c>
-      <c r="AE22" s="9" t="n">
+      <c r="AF22" s="9" t="n">
         <v>5</v>
-      </c>
-      <c r="AF22" s="9" t="n">
-        <v>1</v>
       </c>
       <c r="AG22" s="9" t="n">
         <v>1</v>
       </c>
       <c r="AH22" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI22" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="AI22" s="27" t="inlineStr">
+      <c r="AJ22" s="27" t="inlineStr">
         <is>
           <t>실제 사고 확인</t>
         </is>
       </c>
-      <c r="AJ22" s="9" t="inlineStr">
+      <c r="AK22" s="9" t="inlineStr">
         <is>
           <t>ENI-012, ENI-013, ENI-015, ENI-016, ENI-017
 정부 경보: ENI-030</t>
         </is>
       </c>
-      <c r="AK22" s="9" t="inlineStr">
+      <c r="AL22" s="9" t="inlineStr">
         <is>
           <t>랜섬·암호화 4 · 데이터 유출 2 · 자격증명·비밀 탈취 2 · 내부 접근 확보 2</t>
         </is>
       </c>
-      <c r="AL22" s="9" t="inlineStr">
+      <c r="AM22" s="9" t="inlineStr">
         <is>
           <t>SI-4 System Monitoring
 SI-7 Software, Firmware, and Information Integrity
 CM-7 Least Functionality</t>
         </is>
       </c>
-      <c r="AM22" s="9" t="inlineStr">
+      <c r="AN22" s="9" t="inlineStr">
         <is>
           <t>■ 탐지
 - 보안 서비스 중지·드라이버 로드와 EDR 텔레메트리 단절을 행위·네트워크 기반으로 탐지(NIST SI-4·SI-7)
@@ -12374,7 +12502,7 @@
 - 참고: LOLDrivers 〈Project〉 · Hive Security 〈Modern Attack Techniques 2026〉</t>
         </is>
       </c>
-      <c r="AN22" s="9" t="inlineStr">
+      <c r="AO22" s="9" t="inlineStr">
         <is>
           <t>LOLDrivers 〈Project〉
 Hive Security 〈Modern Attack Techniques 2026〉</t>
@@ -12484,54 +12612,59 @@
           <t>매우 높음</t>
         </is>
       </c>
-      <c r="AB23" s="8" t="n">
+      <c r="AB23" s="9" t="inlineStr">
+        <is>
+          <t>경계</t>
+        </is>
+      </c>
+      <c r="AC23" s="8" t="n">
         <v>14</v>
       </c>
-      <c r="AC23" s="9" t="inlineStr">
-        <is>
-          <t>실제 사고 2건(최근 1) · ATT&amp;CK 주체 4 · KEV - · 정부 경보 0 · 위협인텔 0 · 실증 0</t>
-        </is>
-      </c>
       <c r="AD23" s="9" t="inlineStr">
         <is>
+          <t>실제 사고 2건(최근 1, 서로 다른 행위자·캠페인 2) · ATT&amp;CK 주체 4 · KEV - · 정부 경보 0 · 위협인텔 0 · 실증 0</t>
+        </is>
+      </c>
+      <c r="AE23" s="9" t="inlineStr">
+        <is>
           <t>커널 계층에 드라이버를 올려 은닉·무력화의 토대를 만듦 — 상위 보안 제품이 보지 못하는 하위 계층</t>
         </is>
       </c>
-      <c r="AE23" s="9" t="n">
+      <c r="AF23" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="AF23" s="9" t="n">
+      <c r="AG23" s="9" t="n">
         <v>1</v>
-      </c>
-      <c r="AG23" s="9" t="n">
-        <v>0</v>
       </c>
       <c r="AH23" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="AI23" s="27" t="inlineStr">
+      <c r="AI23" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ23" s="27" t="inlineStr">
         <is>
           <t>실제 사고 확인</t>
         </is>
       </c>
-      <c r="AJ23" s="9" t="inlineStr">
+      <c r="AK23" s="9" t="inlineStr">
         <is>
           <t>ENI-016, ENI-017</t>
         </is>
       </c>
-      <c r="AK23" s="9" t="inlineStr">
+      <c r="AL23" s="9" t="inlineStr">
         <is>
           <t>랜섬·암호화 1 · 자격증명·비밀 탈취 1 · 내부 접근 확보 1</t>
         </is>
       </c>
-      <c r="AL23" s="9" t="inlineStr">
+      <c r="AM23" s="9" t="inlineStr">
         <is>
           <t>SI-7 Software, Firmware, and Information Integrity
 CM-7 Least Functionality
 SI-4 System Monitoring</t>
         </is>
       </c>
-      <c r="AM23" s="9" t="inlineStr">
+      <c r="AN23" s="9" t="inlineStr">
         <is>
           <t>■ 탐지
 - 신규 커널 드라이버 로드와 취약 드라이버 서명·해시를 차단 목록과 대조(NIST SI-7·SI-4)
@@ -12540,7 +12673,7 @@
 - 참고: LOLDrivers 〈Project〉</t>
         </is>
       </c>
-      <c r="AN23" s="9" t="inlineStr">
+      <c r="AO23" s="9" t="inlineStr">
         <is>
           <t>LOLDrivers 〈Project〉</t>
         </is>
@@ -12647,24 +12780,26 @@
           <t>높음</t>
         </is>
       </c>
-      <c r="AB24" s="8" t="n">
+      <c r="AB24" s="9" t="inlineStr">
+        <is>
+          <t>경계</t>
+        </is>
+      </c>
+      <c r="AC24" s="8" t="n">
         <v>19</v>
       </c>
-      <c r="AC24" s="9" t="inlineStr">
-        <is>
-          <t>실제 사고 2건(최근 0) · ATT&amp;CK 주체 335 · KEV - · 정부 경보 0 · 위협인텔 0 · 실증 0</t>
-        </is>
-      </c>
       <c r="AD24" s="9" t="inlineStr">
         <is>
+          <t>실제 사고 2건(최근 0, 서로 다른 행위자·캠페인 2) · ATT&amp;CK 주체 335 · KEV - · 정부 경보 0 · 위협인텔 0 · 실증 0</t>
+        </is>
+      </c>
+      <c r="AE24" s="9" t="inlineStr">
+        <is>
           <t>이벤트 로그·파일을 지워 레거시 SIEM 탐지·사후 분석을 무력화 — 원격·불변 로그가 없으면 흔적이 사라짐</t>
         </is>
       </c>
-      <c r="AE24" s="9" t="n">
+      <c r="AF24" s="9" t="n">
         <v>2</v>
-      </c>
-      <c r="AF24" s="9" t="n">
-        <v>0</v>
       </c>
       <c r="AG24" s="9" t="n">
         <v>0</v>
@@ -12672,29 +12807,32 @@
       <c r="AH24" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="AI24" s="27" t="inlineStr">
+      <c r="AI24" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ24" s="27" t="inlineStr">
         <is>
           <t>실제 사고 확인</t>
         </is>
       </c>
-      <c r="AJ24" s="9" t="inlineStr">
+      <c r="AK24" s="9" t="inlineStr">
         <is>
           <t>ENI-001, ENI-033</t>
         </is>
       </c>
-      <c r="AK24" s="9" t="inlineStr">
+      <c r="AL24" s="9" t="inlineStr">
         <is>
           <t>내부 접근 확보 2 · 첩보·감시 1 · 측면 이동·확산 1</t>
         </is>
       </c>
-      <c r="AL24" s="9" t="inlineStr">
+      <c r="AM24" s="9" t="inlineStr">
         <is>
           <t>AU-9 Protection of Audit Information
 SI-4 System Monitoring
 AU-6 Audit Record Review, Analysis, and Reporting</t>
         </is>
       </c>
-      <c r="AM24" s="9" t="inlineStr">
+      <c r="AN24" s="9" t="inlineStr">
         <is>
           <t>■ 탐지
 - 로그 삭제·감사 정책 변경 이벤트와 원격 수집 로그의 공백을 모니터링(NIST AU-6·SI-4)
@@ -12702,7 +12840,7 @@
 - 원격·불변 로그 전송과 로그 삭제 방지·보존 정책을 적용(NIST AU-9·AU-6)</t>
         </is>
       </c>
-      <c r="AN24" s="9" t="inlineStr">
+      <c r="AO24" s="9" t="inlineStr">
         <is>
           <t>MITRE 〈ATT&amp;CK Enterprise v19.2〉</t>
         </is>
@@ -12807,24 +12945,22 @@
           <t>보통</t>
         </is>
       </c>
-      <c r="AB25" s="8" t="n">
+      <c r="AB25" s="9" t="inlineStr"/>
+      <c r="AC25" s="8" t="n">
         <v>42</v>
       </c>
-      <c r="AC25" s="9" t="inlineStr">
-        <is>
-          <t>실제 사고 1건(최근 0) · ATT&amp;CK 주체 60 · KEV - · 정부 경보 0 · 위협인텔 0 · 실증 0</t>
-        </is>
-      </c>
       <c r="AD25" s="9" t="inlineStr">
         <is>
+          <t>실제 사고 1건(최근 0, 서로 다른 행위자·캠페인 1) · ATT&amp;CK 주체 60 · KEV - · 정부 경보 0 · 위협인텔 0 · 실증 0</t>
+        </is>
+      </c>
+      <c r="AE25" s="9" t="inlineStr">
+        <is>
           <t>정상 프로세스·경로·서명으로 위장해 눈과 규칙 기반 탐지를 피하나 단독 피해는 제한적</t>
         </is>
       </c>
-      <c r="AE25" s="9" t="n">
+      <c r="AF25" s="9" t="n">
         <v>1</v>
-      </c>
-      <c r="AF25" s="9" t="n">
-        <v>0</v>
       </c>
       <c r="AG25" s="9" t="n">
         <v>0</v>
@@ -12832,28 +12968,31 @@
       <c r="AH25" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="AI25" s="27" t="inlineStr">
+      <c r="AI25" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ25" s="27" t="inlineStr">
         <is>
           <t>실제 사고 확인</t>
         </is>
       </c>
-      <c r="AJ25" s="9" t="inlineStr">
+      <c r="AK25" s="9" t="inlineStr">
         <is>
           <t>ENI-033</t>
         </is>
       </c>
-      <c r="AK25" s="9" t="inlineStr">
+      <c r="AL25" s="9" t="inlineStr">
         <is>
           <t>내부 접근 확보 1</t>
         </is>
       </c>
-      <c r="AL25" s="9" t="inlineStr">
+      <c r="AM25" s="9" t="inlineStr">
         <is>
           <t>SI-4 System Monitoring
 SI-7 Software, Firmware, and Information Integrity</t>
         </is>
       </c>
-      <c r="AM25" s="9" t="inlineStr">
+      <c r="AN25" s="9" t="inlineStr">
         <is>
           <t>■ 탐지
 - 정상 이름과 다른 경로·서명·해시 불일치를 무결성·행위 기반으로 탐지(NIST SI-4·SI-7)
@@ -12861,7 +13000,7 @@
 - 바이너리 무결성·서명 검증과 정상 경로 기준선 대조를 적용(NIST SI-7·SI-4)</t>
         </is>
       </c>
-      <c r="AN25" s="9" t="inlineStr">
+      <c r="AO25" s="9" t="inlineStr">
         <is>
           <t>MITRE 〈ATT&amp;CK Enterprise v19.2〉</t>
         </is>
@@ -12966,24 +13105,22 @@
           <t>보통</t>
         </is>
       </c>
-      <c r="AB26" s="8" t="n">
+      <c r="AB26" s="9" t="inlineStr"/>
+      <c r="AC26" s="8" t="n">
         <v>36</v>
       </c>
-      <c r="AC26" s="9" t="inlineStr">
-        <is>
-          <t>실제 사고 1건(최근 0) · ATT&amp;CK 주체 160 · KEV - · 정부 경보 0 · 위협인텔 0 · 실증 0</t>
-        </is>
-      </c>
       <c r="AD26" s="9" t="inlineStr">
         <is>
+          <t>실제 사고 1건(최근 0, 서로 다른 행위자·캠페인 1) · ATT&amp;CK 주체 160 · KEV - · 정부 경보 0 · 위협인텔 0 · 실증 0</t>
+        </is>
+      </c>
+      <c r="AE26" s="9" t="inlineStr">
+        <is>
           <t>패킹·인코딩·암호화로 시그니처·정적 분석을 회피 — 변종 양산으로 레거시 AV를 지속 우회</t>
         </is>
       </c>
-      <c r="AE26" s="9" t="n">
+      <c r="AF26" s="9" t="n">
         <v>1</v>
-      </c>
-      <c r="AF26" s="9" t="n">
-        <v>0</v>
       </c>
       <c r="AG26" s="9" t="n">
         <v>0</v>
@@ -12991,28 +13128,31 @@
       <c r="AH26" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="AI26" s="27" t="inlineStr">
+      <c r="AI26" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ26" s="27" t="inlineStr">
         <is>
           <t>실제 사고 확인</t>
         </is>
       </c>
-      <c r="AJ26" s="9" t="inlineStr">
+      <c r="AK26" s="9" t="inlineStr">
         <is>
           <t>ENI-033</t>
         </is>
       </c>
-      <c r="AK26" s="9" t="inlineStr">
+      <c r="AL26" s="9" t="inlineStr">
         <is>
           <t>내부 접근 확보 1</t>
         </is>
       </c>
-      <c r="AL26" s="9" t="inlineStr">
+      <c r="AM26" s="9" t="inlineStr">
         <is>
           <t>SI-3 Malicious Code Protection
 SI-4 System Monitoring</t>
         </is>
       </c>
-      <c r="AM26" s="9" t="inlineStr">
+      <c r="AN26" s="9" t="inlineStr">
         <is>
           <t>■ 탐지
 - 실행 시점 행위·언패킹과 비정상 인코딩·엔트로피를 행위 기반으로 탐지(NIST SI-3·SI-4)
@@ -13020,7 +13160,7 @@
 - 시그니처 의존을 줄이고 행위 기반·샌드박스 분석을 병행(NIST SI-3·SI-4)</t>
         </is>
       </c>
-      <c r="AN26" s="9" t="inlineStr">
+      <c r="AO26" s="9" t="inlineStr">
         <is>
           <t>MITRE 〈ATT&amp;CK Enterprise v19.2〉</t>
         </is>
@@ -13125,24 +13265,22 @@
           <t>높음</t>
         </is>
       </c>
-      <c r="AB27" s="8" t="n">
+      <c r="AB27" s="9" t="inlineStr"/>
+      <c r="AC27" s="8" t="n">
         <v>25</v>
       </c>
-      <c r="AC27" s="9" t="inlineStr">
-        <is>
-          <t>실제 사고 1건(최근 0) · ATT&amp;CK 주체 32 · KEV - · 정부 경보 0 · 위협인텔 0 · 실증 0</t>
-        </is>
-      </c>
       <c r="AD27" s="9" t="inlineStr">
         <is>
+          <t>실제 사고 1건(최근 0, 서로 다른 행위자·캠페인 1) · ATT&amp;CK 주체 32 · KEV - · 정부 경보 0 · 위협인텔 0 · 실증 0</t>
+        </is>
+      </c>
+      <c r="AE27" s="9" t="inlineStr">
+        <is>
           <t>디스크를 거치지 않고 메모리에서 페이로드를 로드·실행 — 파일 기반 AV·시그니처가 원천적으로 보지 못함</t>
         </is>
       </c>
-      <c r="AE27" s="9" t="n">
+      <c r="AF27" s="9" t="n">
         <v>1</v>
-      </c>
-      <c r="AF27" s="9" t="n">
-        <v>0</v>
       </c>
       <c r="AG27" s="9" t="n">
         <v>0</v>
@@ -13150,28 +13288,31 @@
       <c r="AH27" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="AI27" s="27" t="inlineStr">
+      <c r="AI27" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ27" s="27" t="inlineStr">
         <is>
           <t>실제 사고 확인</t>
         </is>
       </c>
-      <c r="AJ27" s="9" t="inlineStr">
+      <c r="AK27" s="9" t="inlineStr">
         <is>
           <t>ENI-020</t>
         </is>
       </c>
-      <c r="AK27" s="9" t="inlineStr">
+      <c r="AL27" s="9" t="inlineStr">
         <is>
           <t>내부 접근 확보 1</t>
         </is>
       </c>
-      <c r="AL27" s="9" t="inlineStr">
+      <c r="AM27" s="9" t="inlineStr">
         <is>
           <t>SI-3 Malicious Code Protection
 SI-4 System Monitoring</t>
         </is>
       </c>
-      <c r="AM27" s="9" t="inlineStr">
+      <c r="AN27" s="9" t="inlineStr">
         <is>
           <t>■ 탐지
 - 메모리 영역 할당·실행과 비정상 로딩을 EDR 메모리 스캔으로 탐지(NIST SI-3·SI-4)
@@ -13179,7 +13320,7 @@
 - 메모리 가시성(EDR)·공격 표면 축소와 스크립트 실행 통제를 적용(NIST SI-3·SI-4)</t>
         </is>
       </c>
-      <c r="AN27" s="9" t="inlineStr">
+      <c r="AO27" s="9" t="inlineStr">
         <is>
           <t>MITRE 〈ATT&amp;CK Enterprise v19.2〉</t>
         </is>
@@ -13284,24 +13425,22 @@
           <t>높음</t>
         </is>
       </c>
-      <c r="AB28" s="8" t="n">
+      <c r="AB28" s="9" t="inlineStr"/>
+      <c r="AC28" s="8" t="n">
         <v>26</v>
       </c>
-      <c r="AC28" s="9" t="inlineStr">
-        <is>
-          <t>실제 사고 1건(최근 0) · ATT&amp;CK 주체 32 · KEV - · 정부 경보 0 · 위협인텔 0 · 실증 0</t>
-        </is>
-      </c>
       <c r="AD28" s="9" t="inlineStr">
         <is>
+          <t>실제 사고 1건(최근 0, 서로 다른 행위자·캠페인 1) · ATT&amp;CK 주체 32 · KEV - · 정부 경보 0 · 위협인텔 0 · 실증 0</t>
+        </is>
+      </c>
+      <c r="AE28" s="9" t="inlineStr">
+        <is>
           <t>프로세스·파일·연결을 하위 계층에서 숨겨 탐지·분석을 근본적으로 방해 — 레거시로는 존재 자체를 알기 어려움</t>
         </is>
       </c>
-      <c r="AE28" s="9" t="n">
+      <c r="AF28" s="9" t="n">
         <v>1</v>
-      </c>
-      <c r="AF28" s="9" t="n">
-        <v>0</v>
       </c>
       <c r="AG28" s="9" t="n">
         <v>0</v>
@@ -13309,28 +13448,31 @@
       <c r="AH28" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="AI28" s="27" t="inlineStr">
+      <c r="AI28" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ28" s="27" t="inlineStr">
         <is>
           <t>실제 사고 확인</t>
         </is>
       </c>
-      <c r="AJ28" s="9" t="inlineStr">
+      <c r="AK28" s="9" t="inlineStr">
         <is>
           <t>ENI-025</t>
         </is>
       </c>
-      <c r="AK28" s="9" t="inlineStr">
+      <c r="AL28" s="9" t="inlineStr">
         <is>
           <t>첩보·감시 1 · 내부 접근 확보 1</t>
         </is>
       </c>
-      <c r="AL28" s="9" t="inlineStr">
+      <c r="AM28" s="9" t="inlineStr">
         <is>
           <t>SI-7 Software, Firmware, and Information Integrity
 SI-4 System Monitoring</t>
         </is>
       </c>
-      <c r="AM28" s="9" t="inlineStr">
+      <c r="AN28" s="9" t="inlineStr">
         <is>
           <t>■ 탐지
 - 커널 무결성·드라이버 서명과 메모리·부트 무결성 검증으로 은폐를 탐지(NIST SI-7·SI-4)
@@ -13338,7 +13480,7 @@
 - 커널 무결성 보호(HVCI)·보안 부팅과 하위 계층 텔레메트리를 확보(NIST SI-7·SI-4)</t>
         </is>
       </c>
-      <c r="AN28" s="9" t="inlineStr">
+      <c r="AO28" s="9" t="inlineStr">
         <is>
           <t>MITRE 〈ATT&amp;CK Enterprise v19.2〉</t>
         </is>
@@ -13443,21 +13585,19 @@
           <t>높음</t>
         </is>
       </c>
-      <c r="AB29" s="8" t="n">
+      <c r="AB29" s="9" t="inlineStr"/>
+      <c r="AC29" s="8" t="n">
         <v>29</v>
       </c>
-      <c r="AC29" s="9" t="inlineStr">
-        <is>
-          <t>실제 사고 0건(최근 0) · ATT&amp;CK 주체 0 · KEV - · 정부 경보 0 · 위협인텔 0 · 실증 2</t>
-        </is>
-      </c>
       <c r="AD29" s="9" t="inlineStr">
         <is>
+          <t>실제 사고 0건(최근 0, 서로 다른 행위자·캠페인 0) · ATT&amp;CK 주체 0 · KEV - · 정부 경보 0 · 위협인텔 0 · 실증 2</t>
+        </is>
+      </c>
+      <c r="AE29" s="9" t="inlineStr">
+        <is>
           <t>OS 아래 펌웨어·부트 단계에 심어져 재설치·디스크 교체에도 살아남고 OS 보안 제품이 보지 못함 — 사실상 레거시·EDR 모두 공백</t>
         </is>
-      </c>
-      <c r="AE29" s="9" t="n">
-        <v>0</v>
       </c>
       <c r="AF29" s="9" t="n">
         <v>0</v>
@@ -13468,25 +13608,28 @@
       <c r="AH29" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="AI29" s="30" t="inlineStr">
+      <c r="AI29" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ29" s="30" t="inlineStr">
         <is>
           <t>이론·연구</t>
         </is>
       </c>
-      <c r="AJ29" s="9" t="inlineStr">
+      <c r="AK29" s="9" t="inlineStr">
         <is>
           <t xml:space="preserve">
 실증: ENI-024, ENI-026</t>
         </is>
       </c>
-      <c r="AK29" s="9" t="inlineStr"/>
-      <c r="AL29" s="9" t="inlineStr">
+      <c r="AL29" s="9" t="inlineStr"/>
+      <c r="AM29" s="9" t="inlineStr">
         <is>
           <t>SI-7 Software, Firmware, and Information Integrity
 CM-7 Least Functionality</t>
         </is>
       </c>
-      <c r="AM29" s="9" t="inlineStr">
+      <c r="AN29" s="9" t="inlineStr">
         <is>
           <t>■ 탐지
 - 펌웨어·부트 무결성 측정(보안 부팅·측정 부팅)과 펌웨어 버전·해시 변화를 점검(NIST SI-7)
@@ -13494,7 +13637,7 @@
 - 보안 부팅·펌웨어 무결성 검증·업데이트와 펌웨어 공급 신뢰를 관리(NIST SI-7·CM-7)</t>
         </is>
       </c>
-      <c r="AN29" s="9" t="inlineStr">
+      <c r="AO29" s="9" t="inlineStr">
         <is>
           <t>MITRE 〈ATT&amp;CK Enterprise v19.2〉</t>
         </is>
@@ -13599,55 +13742,56 @@
           <t>매우 높음</t>
         </is>
       </c>
-      <c r="AB30" s="8" t="n">
+      <c r="AB30" s="9" t="inlineStr"/>
+      <c r="AC30" s="8" t="n">
         <v>6</v>
       </c>
-      <c r="AC30" s="9" t="inlineStr">
-        <is>
-          <t>실제 사고 4건(최근 0) · ATT&amp;CK 주체 79 · KEV - · 정부 경보 1 · 위협인텔 0 · 실증 0</t>
-        </is>
-      </c>
       <c r="AD30" s="9" t="inlineStr">
         <is>
+          <t>실제 사고 4건(최근 0, 서로 다른 행위자·캠페인 4) · ATT&amp;CK 주체 79 · KEV - · 정부 경보 1 · 위협인텔 0 · 실증 0</t>
+        </is>
+      </c>
+      <c r="AE30" s="9" t="inlineStr">
+        <is>
           <t>LSASS 메모리에서 평문·해시 자격증명을 추출해 도메인 확산의 발판을 마련 — 정상 프로세스 접근이라 레거시가 구분하지 못함</t>
         </is>
       </c>
-      <c r="AE30" s="9" t="n">
+      <c r="AF30" s="9" t="n">
         <v>4</v>
       </c>
-      <c r="AF30" s="9" t="n">
+      <c r="AG30" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="AG30" s="9" t="n">
+      <c r="AH30" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="AH30" s="9" t="n">
+      <c r="AI30" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="AI30" s="27" t="inlineStr">
+      <c r="AJ30" s="27" t="inlineStr">
         <is>
           <t>실제 사고 확인</t>
         </is>
       </c>
-      <c r="AJ30" s="9" t="inlineStr">
+      <c r="AK30" s="9" t="inlineStr">
         <is>
           <t>ENI-001, ENI-012, ENI-014, ENI-021
 정부 경보: ENI-030</t>
         </is>
       </c>
-      <c r="AK30" s="9" t="inlineStr">
+      <c r="AL30" s="9" t="inlineStr">
         <is>
           <t>측면 이동·확산 2 · 랜섬·암호화 2 · 데이터 유출 2 · 내부 접근 확보 1</t>
         </is>
       </c>
-      <c r="AL30" s="9" t="inlineStr">
+      <c r="AM30" s="9" t="inlineStr">
         <is>
           <t>SI-4 System Monitoring
 AC-6 Least Privilege
 IA-5 Authenticator Management</t>
         </is>
       </c>
-      <c r="AM30" s="9" t="inlineStr">
+      <c r="AN30" s="9" t="inlineStr">
         <is>
           <t>■ 탐지
 - LSASS 비정상 접근·핸들 열기와 자격증명 덤프 도구 행위를 EDR 기반으로 탐지(NIST SI-4·AC-6)
@@ -13655,7 +13799,7 @@
 - LSASS 보호(PPL)·자격증명 가드와 최소 권한·특권 분리를 적용(NIST AC-6·IA-5)</t>
         </is>
       </c>
-      <c r="AN30" s="9" t="inlineStr">
+      <c r="AO30" s="9" t="inlineStr">
         <is>
           <t>MITRE 〈ATT&amp;CK Enterprise v19.2〉</t>
         </is>
@@ -13760,21 +13904,19 @@
           <t>보통</t>
         </is>
       </c>
-      <c r="AB31" s="8" t="n">
+      <c r="AB31" s="9" t="inlineStr"/>
+      <c r="AC31" s="8" t="n">
         <v>50</v>
       </c>
-      <c r="AC31" s="9" t="inlineStr">
-        <is>
-          <t>실제 사고 0건(최근 0) · ATT&amp;CK 주체 8 · KEV - · 정부 경보 0 · 위협인텔 0 · 실증 0</t>
-        </is>
-      </c>
       <c r="AD31" s="9" t="inlineStr">
         <is>
+          <t>실제 사고 0건(최근 0, 서로 다른 행위자·캠페인 0) · ATT&amp;CK 주체 8 · KEV - · 정부 경보 0 · 위협인텔 0 · 실증 0</t>
+        </is>
+      </c>
+      <c r="AE31" s="9" t="inlineStr">
+        <is>
           <t>오프라인으로 캐시 자격증명을 깨 추가 계정을 확보하나 피해는 확산 단계에서 커짐</t>
         </is>
-      </c>
-      <c r="AE31" s="9" t="n">
-        <v>0</v>
       </c>
       <c r="AF31" s="9" t="n">
         <v>0</v>
@@ -13785,20 +13927,23 @@
       <c r="AH31" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="AI31" s="29" t="inlineStr">
+      <c r="AI31" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ31" s="29" t="inlineStr">
         <is>
           <t>ATT&amp;CK 사례·KEV 일부</t>
         </is>
       </c>
-      <c r="AJ31" s="9" t="inlineStr"/>
       <c r="AK31" s="9" t="inlineStr"/>
-      <c r="AL31" s="9" t="inlineStr">
+      <c r="AL31" s="9" t="inlineStr"/>
+      <c r="AM31" s="9" t="inlineStr">
         <is>
           <t>SI-4 System Monitoring
 AC-6 Least Privilege</t>
         </is>
       </c>
-      <c r="AM31" s="9" t="inlineStr">
+      <c r="AN31" s="9" t="inlineStr">
         <is>
           <t>■ 탐지
 - 캐시 자격증명 저장소 접근과 비정상 레지스트리·메모리 읽기를 EDR 기반으로 탐지(NIST SI-4·AC-6)
@@ -13806,7 +13951,7 @@
 - 캐시 자격증명 수 제한·특권 분리와 강한 암호 정책을 적용(NIST AC-6·SI-4)</t>
         </is>
       </c>
-      <c r="AN31" s="9" t="inlineStr">
+      <c r="AO31" s="9" t="inlineStr">
         <is>
           <t>MITRE 〈ATT&amp;CK Enterprise v19.2〉</t>
         </is>
@@ -13915,24 +14060,26 @@
           <t>매우 높음</t>
         </is>
       </c>
-      <c r="AB32" s="8" t="n">
+      <c r="AB32" s="9" t="inlineStr">
+        <is>
+          <t>경계</t>
+        </is>
+      </c>
+      <c r="AC32" s="8" t="n">
         <v>13</v>
       </c>
-      <c r="AC32" s="9" t="inlineStr">
-        <is>
-          <t>실제 사고 2건(최근 0) · ATT&amp;CK 주체 12 · KEV - · 정부 경보 0 · 위협인텔 0 · 실증 0</t>
-        </is>
-      </c>
       <c r="AD32" s="9" t="inlineStr">
         <is>
+          <t>실제 사고 2건(최근 0, 서로 다른 행위자·캠페인 2) · ATT&amp;CK 주체 12 · KEV - · 정부 경보 0 · 위협인텔 0 · 실증 0</t>
+        </is>
+      </c>
+      <c r="AE32" s="9" t="inlineStr">
+        <is>
           <t>정상 Kerberos 요청으로 서비스 계정 해시를 받아 오프라인에서 크랙 — 정상 인증 트래픽이라 레거시가 탐지하지 못하고 도메인 권한 계정으로 직결</t>
         </is>
       </c>
-      <c r="AE32" s="9" t="n">
+      <c r="AF32" s="9" t="n">
         <v>2</v>
-      </c>
-      <c r="AF32" s="9" t="n">
-        <v>0</v>
       </c>
       <c r="AG32" s="9" t="n">
         <v>0</v>
@@ -13940,29 +14087,32 @@
       <c r="AH32" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="AI32" s="27" t="inlineStr">
+      <c r="AI32" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ32" s="27" t="inlineStr">
         <is>
           <t>실제 사고 확인</t>
         </is>
       </c>
-      <c r="AJ32" s="9" t="inlineStr">
+      <c r="AK32" s="9" t="inlineStr">
         <is>
           <t>ENI-002, ENI-023</t>
         </is>
       </c>
-      <c r="AK32" s="9" t="inlineStr">
+      <c r="AL32" s="9" t="inlineStr">
         <is>
           <t>내부 접근 확보 1 · 첩보·감시 1 · 자격증명·비밀 탈취 1 · 측면 이동·확산 1</t>
         </is>
       </c>
-      <c r="AL32" s="9" t="inlineStr">
+      <c r="AM32" s="9" t="inlineStr">
         <is>
           <t>SI-4 System Monitoring
 AC-6 Least Privilege
 IA-5 Authenticator Management</t>
         </is>
       </c>
-      <c r="AM32" s="9" t="inlineStr">
+      <c r="AN32" s="9" t="inlineStr">
         <is>
           <t>■ 탐지
 - 비정상적으로 많은 서비스 티켓 요청·약한 암호화 요청을 아이덴티티 기반으로 탐지(NIST SI-4·AC-6)
@@ -13970,7 +14120,7 @@
 - 서비스 계정에 길고 무작위한 암호·gMSA·강한 암호화를 적용하고 요청을 감사(NIST IA-5·AC-6)</t>
         </is>
       </c>
-      <c r="AN32" s="9" t="inlineStr">
+      <c r="AO32" s="9" t="inlineStr">
         <is>
           <t>MITRE 〈ATT&amp;CK Enterprise v19.2〉</t>
         </is>
@@ -14075,24 +14225,22 @@
           <t>보통</t>
         </is>
       </c>
-      <c r="AB33" s="8" t="n">
+      <c r="AB33" s="9" t="inlineStr"/>
+      <c r="AC33" s="8" t="n">
         <v>37</v>
       </c>
-      <c r="AC33" s="9" t="inlineStr">
-        <is>
-          <t>실제 사고 1건(최근 0) · ATT&amp;CK 주체 155 · KEV - · 정부 경보 0 · 위협인텔 0 · 실증 0</t>
-        </is>
-      </c>
       <c r="AD33" s="9" t="inlineStr">
         <is>
+          <t>실제 사고 1건(최근 0, 서로 다른 행위자·캠페인 1) · ATT&amp;CK 주체 155 · KEV - · 정부 경보 0 · 위협인텔 0 · 실증 0</t>
+        </is>
+      </c>
+      <c r="AE33" s="9" t="inlineStr">
+        <is>
           <t>키 입력·자격증명을 가로채나 수집 속도·범위가 제한적</t>
         </is>
       </c>
-      <c r="AE33" s="9" t="n">
+      <c r="AF33" s="9" t="n">
         <v>1</v>
-      </c>
-      <c r="AF33" s="9" t="n">
-        <v>0</v>
       </c>
       <c r="AG33" s="9" t="n">
         <v>0</v>
@@ -14100,28 +14248,31 @@
       <c r="AH33" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="AI33" s="27" t="inlineStr">
+      <c r="AI33" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ33" s="27" t="inlineStr">
         <is>
           <t>실제 사고 확인</t>
         </is>
       </c>
-      <c r="AJ33" s="9" t="inlineStr">
+      <c r="AK33" s="9" t="inlineStr">
         <is>
           <t>ENI-033</t>
         </is>
       </c>
-      <c r="AK33" s="9" t="inlineStr">
+      <c r="AL33" s="9" t="inlineStr">
         <is>
           <t>내부 접근 확보 1</t>
         </is>
       </c>
-      <c r="AL33" s="9" t="inlineStr">
+      <c r="AM33" s="9" t="inlineStr">
         <is>
           <t>SI-4 System Monitoring
 AC-6 Least Privilege</t>
         </is>
       </c>
-      <c r="AM33" s="9" t="inlineStr">
+      <c r="AN33" s="9" t="inlineStr">
         <is>
           <t>■ 탐지
 - 키보드 후킹·입력 가로채기 API와 비정상 입력 캡처를 EDR 기반으로 탐지(NIST SI-4·AC-6)
@@ -14129,7 +14280,7 @@
 - 엔드포인트 행위 탐지·피싱 내성 MFA로 자격증명 탈취 가치를 낮춤(NIST SI-4·AC-6)</t>
         </is>
       </c>
-      <c r="AN33" s="9" t="inlineStr">
+      <c r="AO33" s="9" t="inlineStr">
         <is>
           <t>MITRE 〈ATT&amp;CK Enterprise v19.2〉</t>
         </is>
@@ -14236,24 +14387,22 @@
           <t>보통</t>
         </is>
       </c>
-      <c r="AB34" s="8" t="n">
+      <c r="AB34" s="9" t="inlineStr"/>
+      <c r="AC34" s="8" t="n">
         <v>33</v>
       </c>
-      <c r="AC34" s="9" t="inlineStr">
-        <is>
-          <t>실제 사고 1건(최근 0) · ATT&amp;CK 주체 525 · KEV - · 정부 경보 0 · 위협인텔 0 · 실증 0</t>
-        </is>
-      </c>
       <c r="AD34" s="9" t="inlineStr">
         <is>
+          <t>실제 사고 1건(최근 0, 서로 다른 행위자·캠페인 1) · ATT&amp;CK 주체 525 · KEV - · 정부 경보 0 · 위협인텔 0 · 실증 0</t>
+        </is>
+      </c>
+      <c r="AE34" s="9" t="inlineStr">
+        <is>
           <t>정상 명령으로 환경을 파악해 확산·영향 계획의 토대가 되나 단독 피해는 없음</t>
         </is>
       </c>
-      <c r="AE34" s="9" t="n">
+      <c r="AF34" s="9" t="n">
         <v>1</v>
-      </c>
-      <c r="AF34" s="9" t="n">
-        <v>0</v>
       </c>
       <c r="AG34" s="9" t="n">
         <v>0</v>
@@ -14261,28 +14410,31 @@
       <c r="AH34" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="AI34" s="27" t="inlineStr">
+      <c r="AI34" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ34" s="27" t="inlineStr">
         <is>
           <t>실제 사고 확인</t>
         </is>
       </c>
-      <c r="AJ34" s="9" t="inlineStr">
+      <c r="AK34" s="9" t="inlineStr">
         <is>
           <t>ENI-001</t>
         </is>
       </c>
-      <c r="AK34" s="9" t="inlineStr">
+      <c r="AL34" s="9" t="inlineStr">
         <is>
           <t>내부 접근 확보 1 · 첩보·감시 1 · 측면 이동·확산 1</t>
         </is>
       </c>
-      <c r="AL34" s="9" t="inlineStr">
+      <c r="AM34" s="9" t="inlineStr">
         <is>
           <t>SI-4 System Monitoring
 AU-6 Audit Record Review, Analysis, and Reporting</t>
         </is>
       </c>
-      <c r="AM34" s="9" t="inlineStr">
+      <c r="AN34" s="9" t="inlineStr">
         <is>
           <t>■ 탐지
 - 짧은 시간의 연쇄 탐색 명령과 비정상 열거 패턴을 행위 기반으로 탐지(NIST SI-4·AU-6)
@@ -14290,7 +14442,7 @@
 - 탐색 명령 사용을 기준선과 대조·감사하고 최소 기능을 적용(NIST SI-4·AU-6)</t>
         </is>
       </c>
-      <c r="AN34" s="9" t="inlineStr">
+      <c r="AO34" s="9" t="inlineStr">
         <is>
           <t>MITRE 〈ATT&amp;CK Enterprise v19.2〉</t>
         </is>
@@ -14397,55 +14549,56 @@
           <t>높음</t>
         </is>
       </c>
-      <c r="AB35" s="8" t="n">
+      <c r="AB35" s="9" t="inlineStr"/>
+      <c r="AC35" s="8" t="n">
         <v>18</v>
       </c>
-      <c r="AC35" s="9" t="inlineStr">
-        <is>
-          <t>실제 사고 3건(최근 0) · ATT&amp;CK 주체 135 · KEV - · 정부 경보 1 · 위협인텔 0 · 실증 0</t>
-        </is>
-      </c>
       <c r="AD35" s="9" t="inlineStr">
         <is>
+          <t>실제 사고 3건(최근 0, 서로 다른 행위자·캠페인 3) · ATT&amp;CK 주체 135 · KEV - · 정부 경보 1 · 위협인텔 0 · 실증 0</t>
+        </is>
+      </c>
+      <c r="AE35" s="9" t="inlineStr">
+        <is>
           <t>정상 LDAP·AD 질의로 공격 경로(관리자·신뢰·공유)를 지도화 — 정상 트래픽이라 탐지가 어렵고 사람 운영 랜섬웨어의 핵심 정찰</t>
         </is>
       </c>
-      <c r="AE35" s="9" t="n">
+      <c r="AF35" s="9" t="n">
         <v>3</v>
       </c>
-      <c r="AF35" s="9" t="n">
+      <c r="AG35" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="AG35" s="9" t="n">
+      <c r="AH35" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="AH35" s="9" t="n">
+      <c r="AI35" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="AI35" s="27" t="inlineStr">
+      <c r="AJ35" s="27" t="inlineStr">
         <is>
           <t>실제 사고 확인</t>
         </is>
       </c>
-      <c r="AJ35" s="9" t="inlineStr">
+      <c r="AK35" s="9" t="inlineStr">
         <is>
           <t>ENI-001, ENI-012, ENI-023
 정부 경보: ENI-030</t>
         </is>
       </c>
-      <c r="AK35" s="9" t="inlineStr">
+      <c r="AL35" s="9" t="inlineStr">
         <is>
           <t>측면 이동·확산 2 · 자격증명·비밀 탈취 2 · 내부 접근 확보 1 · 첩보·감시 1</t>
         </is>
       </c>
-      <c r="AL35" s="9" t="inlineStr">
+      <c r="AM35" s="9" t="inlineStr">
         <is>
           <t>SI-4 System Monitoring
 AC-6 Least Privilege
 AU-6 Audit Record Review, Analysis, and Reporting</t>
         </is>
       </c>
-      <c r="AM35" s="9" t="inlineStr">
+      <c r="AN35" s="9" t="inlineStr">
         <is>
           <t>■ 탐지
 - 비정상 LDAP·AD 질의량과 공격 경로 지도화 도구 행위를 아이덴티티 기반으로 탐지(NIST SI-4·AC-6)
@@ -14453,7 +14606,7 @@
 - AD 질의·열거를 감사하고 공격 경로(관리자·신뢰)를 정리·최소화(NIST AC-6·AU-6)</t>
         </is>
       </c>
-      <c r="AN35" s="9" t="inlineStr">
+      <c r="AO35" s="9" t="inlineStr">
         <is>
           <t>MITRE 〈ATT&amp;CK Enterprise v19.2〉</t>
         </is>
@@ -14558,21 +14711,19 @@
           <t>낮음</t>
         </is>
       </c>
-      <c r="AB36" s="8" t="n">
+      <c r="AB36" s="9" t="inlineStr"/>
+      <c r="AC36" s="8" t="n">
         <v>51</v>
       </c>
-      <c r="AC36" s="9" t="inlineStr">
-        <is>
-          <t>실제 사고 0건(최근 0) · ATT&amp;CK 주체 141 · KEV - · 정부 경보 0 · 위협인텔 0 · 실증 0</t>
-        </is>
-      </c>
       <c r="AD36" s="9" t="inlineStr">
         <is>
+          <t>실제 사고 0건(최근 0, 서로 다른 행위자·캠페인 0) · ATT&amp;CK 주체 141 · KEV - · 정부 경보 0 · 위협인텔 0 · 실증 0</t>
+        </is>
+      </c>
+      <c r="AE36" s="9" t="inlineStr">
+        <is>
           <t>설치된 보안 제품을 확인해 회피·무력화를 준비하는 사전 단계로 직접 피해는 없음</t>
         </is>
-      </c>
-      <c r="AE36" s="9" t="n">
-        <v>0</v>
       </c>
       <c r="AF36" s="9" t="n">
         <v>0</v>
@@ -14583,19 +14734,22 @@
       <c r="AH36" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="AI36" s="28" t="inlineStr">
+      <c r="AI36" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ36" s="28" t="inlineStr">
         <is>
           <t>ATT&amp;CK 사례·KEV 다수</t>
         </is>
       </c>
-      <c r="AJ36" s="9" t="inlineStr"/>
       <c r="AK36" s="9" t="inlineStr"/>
-      <c r="AL36" s="9" t="inlineStr">
+      <c r="AL36" s="9" t="inlineStr"/>
+      <c r="AM36" s="9" t="inlineStr">
         <is>
           <t>SI-4 System Monitoring</t>
         </is>
       </c>
-      <c r="AM36" s="9" t="inlineStr">
+      <c r="AN36" s="9" t="inlineStr">
         <is>
           <t>■ 탐지
 - 보안 제품·서비스 열거 명령과 비정상 조회를 행위 기반으로 탐지(NIST SI-4)
@@ -14603,7 +14757,7 @@
 - 보안 제품 상태 변조 방지와 탐지 규칙·텔레메트리 중앙 감시를 적용(NIST SI-4)</t>
         </is>
       </c>
-      <c r="AN36" s="9" t="inlineStr">
+      <c r="AO36" s="9" t="inlineStr">
         <is>
           <t>MITRE 〈ATT&amp;CK Enterprise v19.2〉</t>
         </is>
@@ -14710,24 +14864,22 @@
           <t>매우 높음</t>
         </is>
       </c>
-      <c r="AB37" s="8" t="n">
+      <c r="AB37" s="9" t="inlineStr"/>
+      <c r="AC37" s="8" t="n">
         <v>4</v>
       </c>
-      <c r="AC37" s="9" t="inlineStr">
-        <is>
-          <t>실제 사고 5건(최근 0) · ATT&amp;CK 주체 111 · KEV - · 정부 경보 0 · 위협인텔 0 · 실증 0</t>
-        </is>
-      </c>
       <c r="AD37" s="9" t="inlineStr">
         <is>
+          <t>실제 사고 5건(최근 0, 서로 다른 행위자·캠페인 5) · ATT&amp;CK 주체 111 · KEV - · 정부 경보 0 · 위협인텔 0 · 실증 0</t>
+        </is>
+      </c>
+      <c r="AE37" s="9" t="inlineStr">
+        <is>
           <t>정상 원격 관리 프로토콜로 자격증명을 써 호스트 간 확산 — 정상 인증·세션이라 레거시가 악용과 구분하지 못하고 랜섬웨어 전개의 주 경로</t>
         </is>
       </c>
-      <c r="AE37" s="9" t="n">
+      <c r="AF37" s="9" t="n">
         <v>5</v>
-      </c>
-      <c r="AF37" s="9" t="n">
-        <v>0</v>
       </c>
       <c r="AG37" s="9" t="n">
         <v>0</v>
@@ -14735,29 +14887,32 @@
       <c r="AH37" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="AI37" s="27" t="inlineStr">
+      <c r="AI37" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ37" s="27" t="inlineStr">
         <is>
           <t>실제 사고 확인</t>
         </is>
       </c>
-      <c r="AJ37" s="9" t="inlineStr">
+      <c r="AK37" s="9" t="inlineStr">
         <is>
           <t>ENI-001, ENI-002, ENI-012, ENI-013, ENI-014</t>
         </is>
       </c>
-      <c r="AK37" s="9" t="inlineStr">
+      <c r="AL37" s="9" t="inlineStr">
         <is>
           <t>내부 접근 확보 3 · 랜섬·암호화 3 · 데이터 유출 3 · 첩보·감시 2</t>
         </is>
       </c>
-      <c r="AL37" s="9" t="inlineStr">
+      <c r="AM37" s="9" t="inlineStr">
         <is>
           <t>AC-17 Remote Access
 SI-4 System Monitoring
 SC-7 Boundary Protection</t>
         </is>
       </c>
-      <c r="AM37" s="9" t="inlineStr">
+      <c r="AN37" s="9" t="inlineStr">
         <is>
           <t>■ 탐지
 - 비정상 원격 세션(출발지·시간·계정)과 내부 RDP·SMB 급증을 네트워크·아이덴티티 기반으로 탐지(NIST SI-4·SC-7)
@@ -14766,7 +14921,7 @@
 - 참고: Mandiant 〈M-Trends〉</t>
         </is>
       </c>
-      <c r="AN37" s="9" t="inlineStr">
+      <c r="AO37" s="9" t="inlineStr">
         <is>
           <t>MITRE 〈ATT&amp;CK Enterprise v19.2〉
 Mandiant 〈M-Trends〉</t>
@@ -14877,24 +15032,26 @@
           <t>매우 높음</t>
         </is>
       </c>
-      <c r="AB38" s="8" t="n">
+      <c r="AB38" s="9" t="inlineStr">
+        <is>
+          <t>경계</t>
+        </is>
+      </c>
+      <c r="AC38" s="8" t="n">
         <v>11</v>
       </c>
-      <c r="AC38" s="9" t="inlineStr">
-        <is>
-          <t>실제 사고 2건(최근 0) · ATT&amp;CK 주체 26 · KEV - · 정부 경보 0 · 위협인텔 0 · 실증 0</t>
-        </is>
-      </c>
       <c r="AD38" s="9" t="inlineStr">
         <is>
+          <t>실제 사고 2건(최근 0, 서로 다른 행위자·캠페인 2) · ATT&amp;CK 주체 26 · KEV - · 정부 경보 0 · 위협인텔 0 · 실증 0</t>
+        </is>
+      </c>
+      <c r="AE38" s="9" t="inlineStr">
+        <is>
           <t>평문 암호 없이 해시·티켓으로 인증해 확산 — 정상 인증으로 보여 레거시가 탐지하지 못하고 도메인 장악으로 직결</t>
         </is>
       </c>
-      <c r="AE38" s="9" t="n">
+      <c r="AF38" s="9" t="n">
         <v>2</v>
-      </c>
-      <c r="AF38" s="9" t="n">
-        <v>0</v>
       </c>
       <c r="AG38" s="9" t="n">
         <v>0</v>
@@ -14902,29 +15059,32 @@
       <c r="AH38" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="AI38" s="27" t="inlineStr">
+      <c r="AI38" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ38" s="27" t="inlineStr">
         <is>
           <t>실제 사고 확인</t>
         </is>
       </c>
-      <c r="AJ38" s="9" t="inlineStr">
+      <c r="AK38" s="9" t="inlineStr">
         <is>
           <t>ENI-002, ENI-021</t>
         </is>
       </c>
-      <c r="AK38" s="9" t="inlineStr">
+      <c r="AL38" s="9" t="inlineStr">
         <is>
           <t>내부 접근 확보 1 · 첩보·감시 1 · 데이터 파괴 1 · 서비스 중단 1</t>
         </is>
       </c>
-      <c r="AL38" s="9" t="inlineStr">
+      <c r="AM38" s="9" t="inlineStr">
         <is>
           <t>IA-2 Identification and Authentication (Organizational Users)
 AC-6 Least Privilege
 SI-4 System Monitoring</t>
         </is>
       </c>
-      <c r="AM38" s="9" t="inlineStr">
+      <c r="AN38" s="9" t="inlineStr">
         <is>
           <t>■ 탐지
 - 비정상 티켓·해시 사용과 로그온 유형·계정 불일치를 아이덴티티 기반으로 탐지(NIST SI-4·AC-6)
@@ -14932,7 +15092,7 @@
 - 특권 분리·로컬 관리자 암호 고유화(LAPS)·티켓 수명 축소와 재사용 탐지를 적용(NIST IA-2·AC-6)</t>
         </is>
       </c>
-      <c r="AN38" s="9" t="inlineStr">
+      <c r="AO38" s="9" t="inlineStr">
         <is>
           <t>MITRE 〈ATT&amp;CK Enterprise v19.2〉</t>
         </is>
@@ -15037,24 +15197,22 @@
           <t>보통</t>
         </is>
       </c>
-      <c r="AB39" s="8" t="n">
+      <c r="AB39" s="9" t="inlineStr"/>
+      <c r="AC39" s="8" t="n">
         <v>43</v>
       </c>
-      <c r="AC39" s="9" t="inlineStr">
-        <is>
-          <t>실제 사고 1건(최근 0) · ATT&amp;CK 주체 55 · KEV - · 정부 경보 0 · 위협인텔 0 · 실증 0</t>
-        </is>
-      </c>
       <c r="AD39" s="9" t="inlineStr">
         <is>
+          <t>실제 사고 1건(최근 0, 서로 다른 행위자·캠페인 1) · ATT&amp;CK 주체 55 · KEV - · 정부 경보 0 · 위협인텔 0 · 실증 0</t>
+        </is>
+      </c>
+      <c r="AE39" s="9" t="inlineStr">
+        <is>
           <t>내부 공유·세션으로 도구를 퍼뜨리나 피해는 실행·영향 단계에서 발생</t>
         </is>
       </c>
-      <c r="AE39" s="9" t="n">
+      <c r="AF39" s="9" t="n">
         <v>1</v>
-      </c>
-      <c r="AF39" s="9" t="n">
-        <v>0</v>
       </c>
       <c r="AG39" s="9" t="n">
         <v>0</v>
@@ -15062,28 +15220,31 @@
       <c r="AH39" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="AI39" s="27" t="inlineStr">
+      <c r="AI39" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ39" s="27" t="inlineStr">
         <is>
           <t>실제 사고 확인</t>
         </is>
       </c>
-      <c r="AJ39" s="9" t="inlineStr">
+      <c r="AK39" s="9" t="inlineStr">
         <is>
           <t>ENI-013</t>
         </is>
       </c>
-      <c r="AK39" s="9" t="inlineStr">
+      <c r="AL39" s="9" t="inlineStr">
         <is>
           <t>내부 접근 확보 1 · 랜섬·암호화 1 · 데이터 유출 1</t>
         </is>
       </c>
-      <c r="AL39" s="9" t="inlineStr">
+      <c r="AM39" s="9" t="inlineStr">
         <is>
           <t>SI-4 System Monitoring
 SC-7 Boundary Protection</t>
         </is>
       </c>
-      <c r="AM39" s="9" t="inlineStr">
+      <c r="AN39" s="9" t="inlineStr">
         <is>
           <t>■ 탐지
 - 내부 호스트 간 비정상 파일 전송·공유 쓰기를 네트워크·엔드포인트 기반으로 탐지(NIST SI-4·SC-7)
@@ -15091,7 +15252,7 @@
 - 내부 분할·공유 권한 최소화와 측면 전송 모니터링을 적용(NIST SC-7·SI-4)</t>
         </is>
       </c>
-      <c r="AN39" s="9" t="inlineStr">
+      <c r="AO39" s="9" t="inlineStr">
         <is>
           <t>MITRE 〈ATT&amp;CK Enterprise v19.2〉</t>
         </is>
@@ -15204,24 +15365,26 @@
           <t>매우 높음</t>
         </is>
       </c>
-      <c r="AB40" s="8" t="n">
+      <c r="AB40" s="9" t="inlineStr">
+        <is>
+          <t>경계</t>
+        </is>
+      </c>
+      <c r="AC40" s="8" t="n">
         <v>17</v>
       </c>
-      <c r="AC40" s="9" t="inlineStr">
-        <is>
-          <t>실제 사고 2건(최근 0) · ATT&amp;CK 주체 25 · KEV O · 정부 경보 0 · 위협인텔 0 · 실증 0</t>
-        </is>
-      </c>
       <c r="AD40" s="9" t="inlineStr">
         <is>
+          <t>실제 사고 2건(최근 0, 서로 다른 행위자·캠페인 2) · ATT&amp;CK 주체 25 · KEV O · 정부 경보 0 · 위협인텔 0 · 실증 0</t>
+        </is>
+      </c>
+      <c r="AE40" s="9" t="inlineStr">
+        <is>
           <t>인증 없이 원격 서비스 취약점으로 자동 확산(웜) — 패치 전 대규모 전파로 조직 전반이 빠르게 침해됨</t>
         </is>
       </c>
-      <c r="AE40" s="9" t="n">
+      <c r="AF40" s="9" t="n">
         <v>2</v>
-      </c>
-      <c r="AF40" s="9" t="n">
-        <v>0</v>
       </c>
       <c r="AG40" s="9" t="n">
         <v>0</v>
@@ -15229,29 +15392,32 @@
       <c r="AH40" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="AI40" s="27" t="inlineStr">
+      <c r="AI40" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ40" s="27" t="inlineStr">
         <is>
           <t>실제 사고 확인</t>
         </is>
       </c>
-      <c r="AJ40" s="9" t="inlineStr">
+      <c r="AK40" s="9" t="inlineStr">
         <is>
           <t>ENI-021, ENI-022</t>
         </is>
       </c>
-      <c r="AK40" s="9" t="inlineStr">
+      <c r="AL40" s="9" t="inlineStr">
         <is>
           <t>서비스 중단 2 · 측면 이동·확산 2 · 데이터 파괴 1 · 랜섬·암호화 1</t>
         </is>
       </c>
-      <c r="AL40" s="9" t="inlineStr">
+      <c r="AM40" s="9" t="inlineStr">
         <is>
           <t>RA-5 Vulnerability Monitoring and Scanning
 SI-2 Flaw Remediation
 SC-7 Boundary Protection</t>
         </is>
       </c>
-      <c r="AM40" s="9" t="inlineStr">
+      <c r="AN40" s="9" t="inlineStr">
         <is>
           <t>■ 탐지
 - 내부 취약 서비스 대상 악용 시도와 급격한 횡적 전파를 네트워크 기반으로 탐지(NIST SC-7·RA-5)
@@ -15260,7 +15426,7 @@
 - 참고: CISA 〈KEV Catalog〉</t>
         </is>
       </c>
-      <c r="AN40" s="9" t="inlineStr">
+      <c r="AO40" s="9" t="inlineStr">
         <is>
           <t>CISA 〈KEV Catalog〉
 MITRE 〈ATT&amp;CK Enterprise v19.2〉</t>
@@ -15367,24 +15533,22 @@
           <t>보통</t>
         </is>
       </c>
-      <c r="AB41" s="8" t="n">
+      <c r="AB41" s="9" t="inlineStr"/>
+      <c r="AC41" s="8" t="n">
         <v>34</v>
       </c>
-      <c r="AC41" s="9" t="inlineStr">
-        <is>
-          <t>실제 사고 1건(최근 0) · ATT&amp;CK 주체 233 · KEV - · 정부 경보 0 · 위협인텔 0 · 실증 0</t>
-        </is>
-      </c>
       <c r="AD41" s="9" t="inlineStr">
         <is>
+          <t>실제 사고 1건(최근 0, 서로 다른 행위자·캠페인 1) · ATT&amp;CK 주체 233 · KEV - · 정부 경보 0 · 위협인텔 0 · 실증 0</t>
+        </is>
+      </c>
+      <c r="AE41" s="9" t="inlineStr">
+        <is>
           <t>반출 대상 데이터를 모으나 피해는 반출·영향 단계에서 실현</t>
         </is>
       </c>
-      <c r="AE41" s="9" t="n">
+      <c r="AF41" s="9" t="n">
         <v>1</v>
-      </c>
-      <c r="AF41" s="9" t="n">
-        <v>0</v>
       </c>
       <c r="AG41" s="9" t="n">
         <v>0</v>
@@ -15392,28 +15556,31 @@
       <c r="AH41" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="AI41" s="27" t="inlineStr">
+      <c r="AI41" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ41" s="27" t="inlineStr">
         <is>
           <t>실제 사고 확인</t>
         </is>
       </c>
-      <c r="AJ41" s="9" t="inlineStr">
+      <c r="AK41" s="9" t="inlineStr">
         <is>
           <t>ENI-031</t>
         </is>
       </c>
-      <c r="AK41" s="9" t="inlineStr">
+      <c r="AL41" s="9" t="inlineStr">
         <is>
           <t>데이터 유출 1 · 금전 피해 1</t>
         </is>
       </c>
-      <c r="AL41" s="9" t="inlineStr">
+      <c r="AM41" s="9" t="inlineStr">
         <is>
           <t>SI-4 System Monitoring
 AC-6 Least Privilege</t>
         </is>
       </c>
-      <c r="AM41" s="9" t="inlineStr">
+      <c r="AN41" s="9" t="inlineStr">
         <is>
           <t>■ 탐지
 - 대량 파일 열람·공유 접근과 비정상 수집 패턴을 행위 기반으로 탐지(NIST SI-4·AC-6)
@@ -15421,7 +15588,7 @@
 - 데이터 접근 최소화·민감 데이터 분류와 접근 감사를 적용(NIST AC-6·SI-4)</t>
         </is>
       </c>
-      <c r="AN41" s="9" t="inlineStr">
+      <c r="AO41" s="9" t="inlineStr">
         <is>
           <t>MITRE 〈ATT&amp;CK Enterprise v19.2〉</t>
         </is>
@@ -15527,24 +15694,22 @@
           <t>보통</t>
         </is>
       </c>
-      <c r="AB42" s="8" t="n">
+      <c r="AB42" s="9" t="inlineStr"/>
+      <c r="AC42" s="8" t="n">
         <v>40</v>
       </c>
-      <c r="AC42" s="9" t="inlineStr">
-        <is>
-          <t>실제 사고 1건(최근 0) · ATT&amp;CK 주체 66 · KEV - · 정부 경보 0 · 위협인텔 0 · 실증 0</t>
-        </is>
-      </c>
       <c r="AD42" s="9" t="inlineStr">
         <is>
+          <t>실제 사고 1건(최근 0, 서로 다른 행위자·캠페인 1) · ATT&amp;CK 주체 66 · KEV - · 정부 경보 0 · 위협인텔 0 · 실증 0</t>
+        </is>
+      </c>
+      <c r="AE42" s="9" t="inlineStr">
+        <is>
           <t>반출 전 압축·암호화로 내용 검사를 피하나 단독 피해는 제한적</t>
         </is>
       </c>
-      <c r="AE42" s="9" t="n">
+      <c r="AF42" s="9" t="n">
         <v>1</v>
-      </c>
-      <c r="AF42" s="9" t="n">
-        <v>0</v>
       </c>
       <c r="AG42" s="9" t="n">
         <v>0</v>
@@ -15552,28 +15717,31 @@
       <c r="AH42" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="AI42" s="27" t="inlineStr">
+      <c r="AI42" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ42" s="27" t="inlineStr">
         <is>
           <t>실제 사고 확인</t>
         </is>
       </c>
-      <c r="AJ42" s="9" t="inlineStr">
+      <c r="AK42" s="9" t="inlineStr">
         <is>
           <t>ENI-031</t>
         </is>
       </c>
-      <c r="AK42" s="9" t="inlineStr">
+      <c r="AL42" s="9" t="inlineStr">
         <is>
           <t>데이터 유출 1 · 금전 피해 1</t>
         </is>
       </c>
-      <c r="AL42" s="9" t="inlineStr">
+      <c r="AM42" s="9" t="inlineStr">
         <is>
           <t>SI-4 System Monitoring
 SC-7 Boundary Protection</t>
         </is>
       </c>
-      <c r="AM42" s="9" t="inlineStr">
+      <c r="AN42" s="9" t="inlineStr">
         <is>
           <t>■ 탐지
 - 대용량 압축·암호화 산출물 생성과 스테이징 디렉터리 집중을 행위 기반으로 탐지(NIST SI-4·SC-7)
@@ -15581,7 +15749,7 @@
 - 비정상 압축·스테이징 탐지와 반출 경로 통제를 병행(NIST SC-7·SI-4)</t>
         </is>
       </c>
-      <c r="AN42" s="9" t="inlineStr">
+      <c r="AO42" s="9" t="inlineStr">
         <is>
           <t>MITRE 〈ATT&amp;CK Enterprise v19.2〉</t>
         </is>
@@ -15687,24 +15855,22 @@
           <t>높음</t>
         </is>
       </c>
-      <c r="AB43" s="8" t="n">
+      <c r="AB43" s="9" t="inlineStr"/>
+      <c r="AC43" s="8" t="n">
         <v>22</v>
       </c>
-      <c r="AC43" s="9" t="inlineStr">
-        <is>
-          <t>실제 사고 1건(최근 0) · ATT&amp;CK 주체 79 · KEV - · 정부 경보 0 · 위협인텔 0 · 실증 0</t>
-        </is>
-      </c>
       <c r="AD43" s="9" t="inlineStr">
         <is>
+          <t>실제 사고 1건(최근 0, 서로 다른 행위자·캠페인 1) · ATT&amp;CK 주체 79 · KEV - · 정부 경보 0 · 위협인텔 0 · 실증 0</t>
+        </is>
+      </c>
+      <c r="AE43" s="9" t="inlineStr">
+        <is>
           <t>TLS 등으로 암호화해 정상 트래픽에 섞임 — 레거시 IDS·방화벽이 내용을 보지 못해 C2 식별이 사실상 불가</t>
         </is>
       </c>
-      <c r="AE43" s="9" t="n">
+      <c r="AF43" s="9" t="n">
         <v>1</v>
-      </c>
-      <c r="AF43" s="9" t="n">
-        <v>0</v>
       </c>
       <c r="AG43" s="9" t="n">
         <v>0</v>
@@ -15712,29 +15878,32 @@
       <c r="AH43" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="AI43" s="27" t="inlineStr">
+      <c r="AI43" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ43" s="27" t="inlineStr">
         <is>
           <t>실제 사고 확인</t>
         </is>
       </c>
-      <c r="AJ43" s="9" t="inlineStr">
+      <c r="AK43" s="9" t="inlineStr">
         <is>
           <t>ENI-018</t>
         </is>
       </c>
-      <c r="AK43" s="9" t="inlineStr">
+      <c r="AL43" s="9" t="inlineStr">
         <is>
           <t>내부 접근 확보 1 · 측면 이동·확산 1</t>
         </is>
       </c>
-      <c r="AL43" s="9" t="inlineStr">
+      <c r="AM43" s="9" t="inlineStr">
         <is>
           <t>SC-7 Boundary Protection
 SI-4 System Monitoring
 AU-6 Audit Record Review, Analysis, and Reporting</t>
         </is>
       </c>
-      <c r="AM43" s="9" t="inlineStr">
+      <c r="AN43" s="9" t="inlineStr">
         <is>
           <t>■ 탐지
 - TLS 메타데이터·JA3/비컨 주기·목적지 평판을 네트워크 기반으로 탐지(NIST SC-7·SI-4)
@@ -15742,7 +15911,7 @@
 - egress 통제·TLS 가시성·목적지 평판 차단과 비컨 탐지를 적용(NIST SC-7·AU-6)</t>
         </is>
       </c>
-      <c r="AN43" s="9" t="inlineStr">
+      <c r="AO43" s="9" t="inlineStr">
         <is>
           <t>MITRE 〈ATT&amp;CK Enterprise v19.2〉</t>
         </is>
@@ -15847,24 +16016,22 @@
           <t>높음</t>
         </is>
       </c>
-      <c r="AB44" s="8" t="n">
+      <c r="AB44" s="9" t="inlineStr"/>
+      <c r="AC44" s="8" t="n">
         <v>21</v>
       </c>
-      <c r="AC44" s="9" t="inlineStr">
-        <is>
-          <t>실제 사고 1건(최근 0) · ATT&amp;CK 주체 422 · KEV - · 정부 경보 0 · 위협인텔 0 · 실증 0</t>
-        </is>
-      </c>
       <c r="AD44" s="9" t="inlineStr">
         <is>
+          <t>실제 사고 1건(최근 0, 서로 다른 행위자·캠페인 1) · ATT&amp;CK 주체 422 · KEV - · 정부 경보 0 · 위협인텔 0 · 실증 0</t>
+        </is>
+      </c>
+      <c r="AE44" s="9" t="inlineStr">
+        <is>
           <t>정상 웹 트래픽처럼 보이는 HTTPS로 통제돼 포트·프로토콜 기반 통제를 통과 — 행위·네트워크 분석 없이는 구분 불가</t>
         </is>
       </c>
-      <c r="AE44" s="9" t="n">
+      <c r="AF44" s="9" t="n">
         <v>1</v>
-      </c>
-      <c r="AF44" s="9" t="n">
-        <v>0</v>
       </c>
       <c r="AG44" s="9" t="n">
         <v>0</v>
@@ -15872,29 +16039,32 @@
       <c r="AH44" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="AI44" s="27" t="inlineStr">
+      <c r="AI44" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ44" s="27" t="inlineStr">
         <is>
           <t>실제 사고 확인</t>
         </is>
       </c>
-      <c r="AJ44" s="9" t="inlineStr">
+      <c r="AK44" s="9" t="inlineStr">
         <is>
           <t>ENI-018</t>
         </is>
       </c>
-      <c r="AK44" s="9" t="inlineStr">
+      <c r="AL44" s="9" t="inlineStr">
         <is>
           <t>내부 접근 확보 1 · 측면 이동·확산 1</t>
         </is>
       </c>
-      <c r="AL44" s="9" t="inlineStr">
+      <c r="AM44" s="9" t="inlineStr">
         <is>
           <t>SC-7 Boundary Protection
 SI-4 System Monitoring
 AU-6 Audit Record Review, Analysis, and Reporting</t>
         </is>
       </c>
-      <c r="AM44" s="9" t="inlineStr">
+      <c r="AN44" s="9" t="inlineStr">
         <is>
           <t>■ 탐지
 - HTTP(S) 비컨 주기·사용자 에이전트·목적지 이상을 네트워크 기반으로 탐지(NIST SC-7·SI-4)
@@ -15902,7 +16072,7 @@
 - 웹 프록시·egress 통제·목적지 평판과 비컨 탐지를 적용(NIST SC-7·AU-6)</t>
         </is>
       </c>
-      <c r="AN44" s="9" t="inlineStr">
+      <c r="AO44" s="9" t="inlineStr">
         <is>
           <t>MITRE 〈ATT&amp;CK Enterprise v19.2〉</t>
         </is>
@@ -16015,24 +16185,22 @@
           <t>높음</t>
         </is>
       </c>
-      <c r="AB45" s="8" t="n">
+      <c r="AB45" s="9" t="inlineStr"/>
+      <c r="AC45" s="8" t="n">
         <v>23</v>
       </c>
-      <c r="AC45" s="9" t="inlineStr">
-        <is>
-          <t>실제 사고 1건(최근 0) · ATT&amp;CK 주체 50 · KEV - · 정부 경보 0 · 위협인텔 0 · 실증 0</t>
-        </is>
-      </c>
       <c r="AD45" s="9" t="inlineStr">
         <is>
+          <t>실제 사고 1건(최근 0, 서로 다른 행위자·캠페인 1) · ATT&amp;CK 주체 50 · KEV - · 정부 경보 0 · 위협인텔 0 · 실증 0</t>
+        </is>
+      </c>
+      <c r="AE45" s="9" t="inlineStr">
+        <is>
           <t>GitHub·클라우드·협업 SaaS 등 신뢰 도메인을 C2 중계로 악용 — 차단하면 업무가 끊겨 레거시 차단·탐지가 어려움</t>
         </is>
       </c>
-      <c r="AE45" s="9" t="n">
+      <c r="AF45" s="9" t="n">
         <v>1</v>
-      </c>
-      <c r="AF45" s="9" t="n">
-        <v>0</v>
       </c>
       <c r="AG45" s="9" t="n">
         <v>0</v>
@@ -16040,28 +16208,31 @@
       <c r="AH45" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="AI45" s="27" t="inlineStr">
+      <c r="AI45" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ45" s="27" t="inlineStr">
         <is>
           <t>실제 사고 확인</t>
         </is>
       </c>
-      <c r="AJ45" s="9" t="inlineStr">
+      <c r="AK45" s="9" t="inlineStr">
         <is>
           <t>ENI-028</t>
         </is>
       </c>
-      <c r="AK45" s="9" t="inlineStr">
+      <c r="AL45" s="9" t="inlineStr">
         <is>
           <t>내부 접근 확보 1 · 데이터 유출 1</t>
         </is>
       </c>
-      <c r="AL45" s="9" t="inlineStr">
+      <c r="AM45" s="9" t="inlineStr">
         <is>
           <t>SC-7 Boundary Protection
 SI-4 System Monitoring</t>
         </is>
       </c>
-      <c r="AM45" s="9" t="inlineStr">
+      <c r="AN45" s="9" t="inlineStr">
         <is>
           <t>■ 탐지
 - 신뢰 SaaS로의 비정상 API 호출·데이터량·주기를 네트워크 기반으로 탐지(NIST SC-7·SI-4)
@@ -16069,7 +16240,7 @@
 - 허용 SaaS·테넌트 제한과 egress 가시성·이상 사용 탐지를 적용(NIST SC-7·SI-4)</t>
         </is>
       </c>
-      <c r="AN45" s="9" t="inlineStr">
+      <c r="AO45" s="9" t="inlineStr">
         <is>
           <t>MITRE 〈ATT&amp;CK Enterprise v19.2〉</t>
         </is>
@@ -16175,24 +16346,22 @@
           <t>보통</t>
         </is>
       </c>
-      <c r="AB46" s="8" t="n">
+      <c r="AB46" s="9" t="inlineStr"/>
+      <c r="AC46" s="8" t="n">
         <v>31</v>
       </c>
-      <c r="AC46" s="9" t="inlineStr">
-        <is>
-          <t>실제 사고 1건(최근 0) · ATT&amp;CK 주체 81 · KEV - · 정부 경보 0 · 위협인텔 0 · 실증 0</t>
-        </is>
-      </c>
       <c r="AD46" s="9" t="inlineStr">
         <is>
+          <t>실제 사고 1건(최근 0, 서로 다른 행위자·캠페인 1) · ATT&amp;CK 주체 81 · KEV - · 정부 경보 0 · 위협인텔 0 · 실증 0</t>
+        </is>
+      </c>
+      <c r="AE46" s="9" t="inlineStr">
+        <is>
           <t>신뢰 CDN·프록시 뒤로 실제 C2를 숨겨 도메인·IP 기반 차단을 우회하나 탐지·차단 수단이 일부 존재</t>
         </is>
       </c>
-      <c r="AE46" s="9" t="n">
+      <c r="AF46" s="9" t="n">
         <v>1</v>
-      </c>
-      <c r="AF46" s="9" t="n">
-        <v>0</v>
       </c>
       <c r="AG46" s="9" t="n">
         <v>0</v>
@@ -16200,28 +16369,31 @@
       <c r="AH46" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="AI46" s="27" t="inlineStr">
+      <c r="AI46" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ46" s="27" t="inlineStr">
         <is>
           <t>실제 사고 확인</t>
         </is>
       </c>
-      <c r="AJ46" s="9" t="inlineStr">
+      <c r="AK46" s="9" t="inlineStr">
         <is>
           <t>ENI-018</t>
         </is>
       </c>
-      <c r="AK46" s="9" t="inlineStr">
+      <c r="AL46" s="9" t="inlineStr">
         <is>
           <t>내부 접근 확보 1 · 측면 이동·확산 1</t>
         </is>
       </c>
-      <c r="AL46" s="9" t="inlineStr">
+      <c r="AM46" s="9" t="inlineStr">
         <is>
           <t>SC-7 Boundary Protection
 SI-4 System Monitoring</t>
         </is>
       </c>
-      <c r="AM46" s="9" t="inlineStr">
+      <c r="AN46" s="9" t="inlineStr">
         <is>
           <t>■ 탐지
 - SNI와 실제 목적지 불일치·비정상 CDN 사용을 네트워크 기반으로 탐지(NIST SC-7·SI-4)
@@ -16229,7 +16401,7 @@
 - TLS 검사·SNI 정책과 프록시 경유 egress 통제를 적용(NIST SC-7·SI-4)</t>
         </is>
       </c>
-      <c r="AN46" s="9" t="inlineStr">
+      <c r="AO46" s="9" t="inlineStr">
         <is>
           <t>MITRE 〈ATT&amp;CK Enterprise v19.2〉</t>
         </is>
@@ -16338,24 +16510,26 @@
           <t>높음</t>
         </is>
       </c>
-      <c r="AB47" s="8" t="n">
+      <c r="AB47" s="9" t="inlineStr">
+        <is>
+          <t>경계</t>
+        </is>
+      </c>
+      <c r="AC47" s="8" t="n">
         <v>20</v>
       </c>
-      <c r="AC47" s="9" t="inlineStr">
-        <is>
-          <t>실제 사고 2건(최근 0) · ATT&amp;CK 주체 520 · KEV - · 정부 경보 0 · 위협인텔 0 · 실증 0</t>
-        </is>
-      </c>
       <c r="AD47" s="9" t="inlineStr">
         <is>
+          <t>실제 사고 2건(최근 0, 서로 다른 행위자·캠페인 2) · ATT&amp;CK 주체 520 · KEV - · 정부 경보 0 · 위협인텔 0 · 실증 0</t>
+        </is>
+      </c>
+      <c r="AE47" s="9" t="inlineStr">
+        <is>
           <t>정상 도구(certutil·curl 등)로 추가 페이로드를 내려받아 반입하나 피해는 후속 단계에서 발생</t>
         </is>
       </c>
-      <c r="AE47" s="9" t="n">
+      <c r="AF47" s="9" t="n">
         <v>2</v>
-      </c>
-      <c r="AF47" s="9" t="n">
-        <v>0</v>
       </c>
       <c r="AG47" s="9" t="n">
         <v>0</v>
@@ -16363,29 +16537,32 @@
       <c r="AH47" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="AI47" s="27" t="inlineStr">
+      <c r="AI47" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ47" s="27" t="inlineStr">
         <is>
           <t>실제 사고 확인</t>
         </is>
       </c>
-      <c r="AJ47" s="9" t="inlineStr">
+      <c r="AK47" s="9" t="inlineStr">
         <is>
           <t>ENI-018, ENI-019</t>
         </is>
       </c>
-      <c r="AK47" s="9" t="inlineStr">
+      <c r="AL47" s="9" t="inlineStr">
         <is>
           <t>내부 접근 확보 2 · 측면 이동·확산 1</t>
         </is>
       </c>
-      <c r="AL47" s="9" t="inlineStr">
+      <c r="AM47" s="9" t="inlineStr">
         <is>
           <t>SC-7 Boundary Protection
 SI-3 Malicious Code Protection
 SI-4 System Monitoring</t>
         </is>
       </c>
-      <c r="AM47" s="9" t="inlineStr">
+      <c r="AN47" s="9" t="inlineStr">
         <is>
           <t>■ 탐지
 - 정상 다운로드 도구의 비정상 사용·외부 다운로드를 행위·네트워크 기반으로 탐지(NIST SI-4·SC-7)
@@ -16394,7 +16571,7 @@
 - 참고: LOLBAS 〈Project〉</t>
         </is>
       </c>
-      <c r="AN47" s="9" t="inlineStr">
+      <c r="AO47" s="9" t="inlineStr">
         <is>
           <t>MITRE 〈ATT&amp;CK Enterprise v19.2〉
 LOLBAS 〈Project〉</t>
@@ -16500,24 +16677,22 @@
           <t>보통</t>
         </is>
       </c>
-      <c r="AB48" s="8" t="n">
+      <c r="AB48" s="9" t="inlineStr"/>
+      <c r="AC48" s="8" t="n">
         <v>32</v>
       </c>
-      <c r="AC48" s="9" t="inlineStr">
-        <is>
-          <t>실제 사고 1건(최근 0) · ATT&amp;CK 주체 55 · KEV - · 정부 경보 0 · 위협인텔 0 · 실증 0</t>
-        </is>
-      </c>
       <c r="AD48" s="9" t="inlineStr">
         <is>
+          <t>실제 사고 1건(최근 0, 서로 다른 행위자·캠페인 1) · ATT&amp;CK 주체 55 · KEV - · 정부 경보 0 · 위협인텔 0 · 실증 0</t>
+        </is>
+      </c>
+      <c r="AE48" s="9" t="inlineStr">
+        <is>
           <t>거의 항상 허용되는 DNS에 통제·데이터를 실어 방화벽을 우회하나 질의 이상 탐지로 일부 포착 가능</t>
         </is>
       </c>
-      <c r="AE48" s="9" t="n">
+      <c r="AF48" s="9" t="n">
         <v>1</v>
-      </c>
-      <c r="AF48" s="9" t="n">
-        <v>0</v>
       </c>
       <c r="AG48" s="9" t="n">
         <v>0</v>
@@ -16525,29 +16700,32 @@
       <c r="AH48" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="AI48" s="27" t="inlineStr">
+      <c r="AI48" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ48" s="27" t="inlineStr">
         <is>
           <t>실제 사고 확인</t>
         </is>
       </c>
-      <c r="AJ48" s="9" t="inlineStr">
+      <c r="AK48" s="9" t="inlineStr">
         <is>
           <t>ENI-027</t>
         </is>
       </c>
-      <c r="AK48" s="9" t="inlineStr">
+      <c r="AL48" s="9" t="inlineStr">
         <is>
           <t>데이터 유출 1 · 내부 접근 확보 1</t>
         </is>
       </c>
-      <c r="AL48" s="9" t="inlineStr">
+      <c r="AM48" s="9" t="inlineStr">
         <is>
           <t>SC-7 Boundary Protection
 SI-4 System Monitoring
 AU-6 Audit Record Review, Analysis, and Reporting</t>
         </is>
       </c>
-      <c r="AM48" s="9" t="inlineStr">
+      <c r="AN48" s="9" t="inlineStr">
         <is>
           <t>■ 탐지
 - 비정상 DNS 질의량·엔트로피·긴 서브도메인을 네트워크 기반으로 탐지(NIST SC-7·SI-4)
@@ -16555,7 +16733,7 @@
 - DNS 로깅·필터링·내부 리졸버 강제와 이상 질의 차단을 적용(NIST SC-7·AU-6)</t>
         </is>
       </c>
-      <c r="AN48" s="9" t="inlineStr">
+      <c r="AO48" s="9" t="inlineStr">
         <is>
           <t>MITRE 〈ATT&amp;CK Enterprise v19.2〉</t>
         </is>
@@ -16660,24 +16838,26 @@
           <t>매우 높음</t>
         </is>
       </c>
-      <c r="AB49" s="8" t="n">
+      <c r="AB49" s="9" t="inlineStr">
+        <is>
+          <t>경계</t>
+        </is>
+      </c>
+      <c r="AC49" s="8" t="n">
         <v>10</v>
       </c>
-      <c r="AC49" s="9" t="inlineStr">
-        <is>
-          <t>실제 사고 2건(최근 0) · ATT&amp;CK 주체 203 · KEV - · 정부 경보 0 · 위협인텔 0 · 실증 0</t>
-        </is>
-      </c>
       <c r="AD49" s="9" t="inlineStr">
         <is>
+          <t>실제 사고 2건(최근 0, 서로 다른 행위자·캠페인 2) · ATT&amp;CK 주체 203 · KEV - · 정부 경보 0 · 위협인텔 0 · 실증 0</t>
+        </is>
+      </c>
+      <c r="AE49" s="9" t="inlineStr">
+        <is>
           <t>기존 암호화 C2에 데이터를 실어 반출 — 별도 채널이 없어 레거시 DLP가 탐지하기 어렵고 이중협박 랜섬웨어의 유출 단계</t>
         </is>
       </c>
-      <c r="AE49" s="9" t="n">
+      <c r="AF49" s="9" t="n">
         <v>2</v>
-      </c>
-      <c r="AF49" s="9" t="n">
-        <v>0</v>
       </c>
       <c r="AG49" s="9" t="n">
         <v>0</v>
@@ -16685,29 +16865,32 @@
       <c r="AH49" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="AI49" s="27" t="inlineStr">
+      <c r="AI49" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ49" s="27" t="inlineStr">
         <is>
           <t>실제 사고 확인</t>
         </is>
       </c>
-      <c r="AJ49" s="9" t="inlineStr">
+      <c r="AK49" s="9" t="inlineStr">
         <is>
           <t>ENI-027, ENI-031</t>
         </is>
       </c>
-      <c r="AK49" s="9" t="inlineStr">
+      <c r="AL49" s="9" t="inlineStr">
         <is>
           <t>데이터 유출 2 · 내부 접근 확보 1 · 금전 피해 1</t>
         </is>
       </c>
-      <c r="AL49" s="9" t="inlineStr">
+      <c r="AM49" s="9" t="inlineStr">
         <is>
           <t>SC-7 Boundary Protection
 SI-4 System Monitoring
 AU-6 Audit Record Review, Analysis, and Reporting</t>
         </is>
       </c>
-      <c r="AM49" s="9" t="inlineStr">
+      <c r="AN49" s="9" t="inlineStr">
         <is>
           <t>■ 탐지
 - C2 세션의 비정상 업로드량·방향성과 비컨-대용량 전환을 네트워크 기반으로 탐지(NIST SC-7·SI-4)
@@ -16715,7 +16898,7 @@
 - egress 통제·데이터 유출 탐지와 C2 차단으로 반출을 막음(NIST SC-7·AU-6)</t>
         </is>
       </c>
-      <c r="AN49" s="9" t="inlineStr">
+      <c r="AO49" s="9" t="inlineStr">
         <is>
           <t>MITRE 〈ATT&amp;CK Enterprise v19.2〉</t>
         </is>
@@ -16825,24 +17008,22 @@
           <t>매우 높음</t>
         </is>
       </c>
-      <c r="AB50" s="8" t="n">
+      <c r="AB50" s="9" t="inlineStr"/>
+      <c r="AC50" s="8" t="n">
         <v>9</v>
       </c>
-      <c r="AC50" s="9" t="inlineStr">
-        <is>
-          <t>실제 사고 3건(최근 0) · ATT&amp;CK 주체 25 · KEV - · 정부 경보 0 · 위협인텔 0 · 실증 0</t>
-        </is>
-      </c>
       <c r="AD50" s="9" t="inlineStr">
         <is>
+          <t>실제 사고 3건(최근 0, 서로 다른 행위자·캠페인 3) · ATT&amp;CK 주체 25 · KEV - · 정부 경보 0 · 위협인텔 0 · 실증 0</t>
+        </is>
+      </c>
+      <c r="AE50" s="9" t="inlineStr">
+        <is>
           <t>클라우드 스토리지·정상 SaaS로 대량 반출 — 신뢰 도메인이라 차단·탐지가 어렵고 유출 규모가 큼</t>
         </is>
       </c>
-      <c r="AE50" s="9" t="n">
+      <c r="AF50" s="9" t="n">
         <v>3</v>
-      </c>
-      <c r="AF50" s="9" t="n">
-        <v>0</v>
       </c>
       <c r="AG50" s="9" t="n">
         <v>0</v>
@@ -16850,28 +17031,31 @@
       <c r="AH50" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="AI50" s="27" t="inlineStr">
+      <c r="AI50" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ50" s="27" t="inlineStr">
         <is>
           <t>실제 사고 확인</t>
         </is>
       </c>
-      <c r="AJ50" s="9" t="inlineStr">
+      <c r="AK50" s="9" t="inlineStr">
         <is>
           <t>ENI-004, ENI-010, ENI-028</t>
         </is>
       </c>
-      <c r="AK50" s="9" t="inlineStr">
+      <c r="AL50" s="9" t="inlineStr">
         <is>
           <t>데이터 유출 3 · 금전 피해 2 · 내부 접근 확보 1</t>
         </is>
       </c>
-      <c r="AL50" s="9" t="inlineStr">
+      <c r="AM50" s="9" t="inlineStr">
         <is>
           <t>SC-7 Boundary Protection
 SI-4 System Monitoring</t>
         </is>
       </c>
-      <c r="AM50" s="9" t="inlineStr">
+      <c r="AN50" s="9" t="inlineStr">
         <is>
           <t>■ 탐지
 - 신뢰 SaaS·외부 저장소로의 비정상 대량 업로드를 네트워크·DLP 기반으로 탐지(NIST SC-7·SI-4)
@@ -16879,7 +17063,7 @@
 - 허용 SaaS 제한·egress 통제·DLP와 대용량 업로드 경보를 적용(NIST SC-7·SI-4)</t>
         </is>
       </c>
-      <c r="AN50" s="9" t="inlineStr">
+      <c r="AO50" s="9" t="inlineStr">
         <is>
           <t>MITRE 〈ATT&amp;CK Enterprise v19.2〉</t>
         </is>
@@ -16992,24 +17176,22 @@
           <t>매우 높음</t>
         </is>
       </c>
-      <c r="AB51" s="8" t="n">
+      <c r="AB51" s="9" t="inlineStr"/>
+      <c r="AC51" s="8" t="n">
         <v>2</v>
       </c>
-      <c r="AC51" s="9" t="inlineStr">
-        <is>
-          <t>실제 사고 7건(최근 0) · ATT&amp;CK 주체 85 · KEV - · 정부 경보 0 · 위협인텔 0 · 실증 0</t>
-        </is>
-      </c>
       <c r="AD51" s="9" t="inlineStr">
         <is>
+          <t>실제 사고 7건(최근 0, 서로 다른 행위자·캠페인 7) · ATT&amp;CK 주체 85 · KEV - · 정부 경보 0 · 위협인텔 0 · 실증 0</t>
+        </is>
+      </c>
+      <c r="AE51" s="9" t="inlineStr">
+        <is>
           <t>사람 운영 랜섬웨어가 도메인 장악 후 전사 암호화 — 앞 단계가 레거시로 탐지되지 않아 암호화 시점에야 드러나 피해가 전면적</t>
         </is>
       </c>
-      <c r="AE51" s="9" t="n">
+      <c r="AF51" s="9" t="n">
         <v>7</v>
-      </c>
-      <c r="AF51" s="9" t="n">
-        <v>0</v>
       </c>
       <c r="AG51" s="9" t="n">
         <v>0</v>
@@ -17017,29 +17199,32 @@
       <c r="AH51" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="AI51" s="27" t="inlineStr">
+      <c r="AI51" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ51" s="27" t="inlineStr">
         <is>
           <t>실제 사고 확인</t>
         </is>
       </c>
-      <c r="AJ51" s="9" t="inlineStr">
+      <c r="AK51" s="9" t="inlineStr">
         <is>
           <t>ENI-009, ENI-011, ENI-012, ENI-013, ENI-014, ENI-015, ENI-022</t>
         </is>
       </c>
-      <c r="AK51" s="9" t="inlineStr">
+      <c r="AL51" s="9" t="inlineStr">
         <is>
           <t>랜섬·암호화 7 · 내부 접근 확보 3 · 데이터 유출 3 · 서비스 중단 2</t>
         </is>
       </c>
-      <c r="AL51" s="9" t="inlineStr">
+      <c r="AM51" s="9" t="inlineStr">
         <is>
           <t>SI-4 System Monitoring
 CP-9 System Backup
 CP-10 System Recovery and Reconstitution</t>
         </is>
       </c>
-      <c r="AM51" s="9" t="inlineStr">
+      <c r="AN51" s="9" t="inlineStr">
         <is>
           <t>■ 탐지
 - 대량 파일 변경·암호화 행위와 선행 단계(자격증명·확산) 상관 이벤트를 행위 기반으로 탐지(NIST SI-4)
@@ -17048,7 +17233,7 @@
 - 참고: Securelist 〈State of Ransomware 2026〉</t>
         </is>
       </c>
-      <c r="AN51" s="9" t="inlineStr">
+      <c r="AO51" s="9" t="inlineStr">
         <is>
           <t>MITRE 〈ATT&amp;CK Enterprise v19.2〉
 Securelist 〈State of Ransomware 2026〉</t>
@@ -17154,54 +17339,59 @@
           <t>매우 높음</t>
         </is>
       </c>
-      <c r="AB52" s="8" t="n">
+      <c r="AB52" s="9" t="inlineStr">
+        <is>
+          <t>경계</t>
+        </is>
+      </c>
+      <c r="AC52" s="8" t="n">
         <v>16</v>
       </c>
-      <c r="AC52" s="9" t="inlineStr">
-        <is>
-          <t>실제 사고 2건(최근 0) · ATT&amp;CK 주체 56 · KEV - · 정부 경보 1 · 위협인텔 0 · 실증 0</t>
-        </is>
-      </c>
       <c r="AD52" s="9" t="inlineStr">
         <is>
+          <t>실제 사고 2건(최근 0, 서로 다른 행위자·캠페인 2) · ATT&amp;CK 주체 56 · KEV - · 정부 경보 1 · 위협인텔 0 · 실증 0</t>
+        </is>
+      </c>
+      <c r="AE52" s="9" t="inlineStr">
+        <is>
           <t>정상 도구로 섀도 카피·백업을 지워 복구를 막음 — 랜섬웨어 피해를 돌이킬 수 없게 만드는 결정적 단계</t>
         </is>
       </c>
-      <c r="AE52" s="9" t="n">
+      <c r="AF52" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="AF52" s="9" t="n">
+      <c r="AG52" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="AG52" s="9" t="n">
+      <c r="AH52" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="AH52" s="9" t="n">
+      <c r="AI52" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="AI52" s="27" t="inlineStr">
+      <c r="AJ52" s="27" t="inlineStr">
         <is>
           <t>실제 사고 확인</t>
         </is>
       </c>
-      <c r="AJ52" s="9" t="inlineStr">
+      <c r="AK52" s="9" t="inlineStr">
         <is>
           <t>ENI-012, ENI-015
 정부 경보: ENI-030</t>
         </is>
       </c>
-      <c r="AK52" s="9" t="inlineStr">
+      <c r="AL52" s="9" t="inlineStr">
         <is>
           <t>랜섬·암호화 2 · 데이터 유출 1 · 자격증명·비밀 탈취 1 · 서비스 중단 1</t>
         </is>
       </c>
-      <c r="AL52" s="9" t="inlineStr">
+      <c r="AM52" s="9" t="inlineStr">
         <is>
           <t>CP-9 System Backup
 SI-4 System Monitoring</t>
         </is>
       </c>
-      <c r="AM52" s="9" t="inlineStr">
+      <c r="AN52" s="9" t="inlineStr">
         <is>
           <t>■ 탐지
 - 섀도 카피 삭제·백업 서비스 중지 명령을 행위 기반으로 탐지(NIST SI-4·CP-9)
@@ -17209,7 +17399,7 @@
 - 오프라인·불변 백업과 백업 삭제 방지·권한 분리를 적용(NIST CP-9·SI-4)</t>
         </is>
       </c>
-      <c r="AN52" s="9" t="inlineStr">
+      <c r="AO52" s="9" t="inlineStr">
         <is>
           <t>MITRE 〈ATT&amp;CK Enterprise v19.2〉</t>
         </is>
@@ -17319,24 +17509,22 @@
           <t>높음</t>
         </is>
       </c>
-      <c r="AB53" s="8" t="n">
+      <c r="AB53" s="9" t="inlineStr"/>
+      <c r="AC53" s="8" t="n">
         <v>24</v>
       </c>
-      <c r="AC53" s="9" t="inlineStr">
-        <is>
-          <t>실제 사고 1건(최근 0) · ATT&amp;CK 주체 40 · KEV - · 정부 경보 0 · 위협인텔 0 · 실증 0</t>
-        </is>
-      </c>
       <c r="AD53" s="9" t="inlineStr">
         <is>
+          <t>실제 사고 1건(최근 0, 서로 다른 행위자·캠페인 1) · ATT&amp;CK 주체 40 · KEV - · 정부 경보 0 · 위협인텔 0 · 실증 0</t>
+        </is>
+      </c>
+      <c r="AE53" s="9" t="inlineStr">
+        <is>
           <t>디스크·데이터를 파괴해 운영을 중단시킴 — 국가배후·핵티비스트의 파괴 작전으로 복구가 어렵고 피해가 전면적</t>
         </is>
       </c>
-      <c r="AE53" s="9" t="n">
+      <c r="AF53" s="9" t="n">
         <v>1</v>
-      </c>
-      <c r="AF53" s="9" t="n">
-        <v>0</v>
       </c>
       <c r="AG53" s="9" t="n">
         <v>0</v>
@@ -17344,29 +17532,32 @@
       <c r="AH53" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="AI53" s="27" t="inlineStr">
+      <c r="AI53" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ53" s="27" t="inlineStr">
         <is>
           <t>실제 사고 확인</t>
         </is>
       </c>
-      <c r="AJ53" s="9" t="inlineStr">
+      <c r="AK53" s="9" t="inlineStr">
         <is>
           <t>ENI-021</t>
         </is>
       </c>
-      <c r="AK53" s="9" t="inlineStr">
+      <c r="AL53" s="9" t="inlineStr">
         <is>
           <t>데이터 파괴 1 · 서비스 중단 1 · 측면 이동·확산 1</t>
         </is>
       </c>
-      <c r="AL53" s="9" t="inlineStr">
+      <c r="AM53" s="9" t="inlineStr">
         <is>
           <t>SI-7 Software, Firmware, and Information Integrity
 CP-9 System Backup
 SI-4 System Monitoring</t>
         </is>
       </c>
-      <c r="AM53" s="9" t="inlineStr">
+      <c r="AN53" s="9" t="inlineStr">
         <is>
           <t>■ 탐지
 - 대량 삭제·디스크 와이프·MBR 변조 행위를 행위 기반으로 탐지(NIST SI-4·SI-7)
@@ -17374,7 +17565,7 @@
 - 오프라인·불변 백업과 무결성 보호·분할로 파괴 범위를 제한(NIST CP-9·SI-7)</t>
         </is>
       </c>
-      <c r="AN53" s="9" t="inlineStr">
+      <c r="AO53" s="9" t="inlineStr">
         <is>
           <t>MITRE 〈ATT&amp;CK Enterprise v19.2〉</t>
         </is>
@@ -17480,24 +17671,22 @@
           <t>보통</t>
         </is>
       </c>
-      <c r="AB54" s="8" t="n">
+      <c r="AB54" s="9" t="inlineStr"/>
+      <c r="AC54" s="8" t="n">
         <v>39</v>
       </c>
-      <c r="AC54" s="9" t="inlineStr">
-        <is>
-          <t>실제 사고 1건(최근 0) · ATT&amp;CK 주체 76 · KEV - · 정부 경보 0 · 위협인텔 0 · 실증 0</t>
-        </is>
-      </c>
       <c r="AD54" s="9" t="inlineStr">
         <is>
+          <t>실제 사고 1건(최근 0, 서로 다른 행위자·캠페인 1) · ATT&amp;CK 주체 76 · KEV - · 정부 경보 0 · 위협인텔 0 · 실증 0</t>
+        </is>
+      </c>
+      <c r="AE54" s="9" t="inlineStr">
+        <is>
           <t>보안·백업·DB 서비스를 멈춰 암호화·파괴를 돕거나 가용성을 해치나 단독 피해는 복구 가능</t>
         </is>
       </c>
-      <c r="AE54" s="9" t="n">
+      <c r="AF54" s="9" t="n">
         <v>1</v>
-      </c>
-      <c r="AF54" s="9" t="n">
-        <v>0</v>
       </c>
       <c r="AG54" s="9" t="n">
         <v>0</v>
@@ -17505,28 +17694,31 @@
       <c r="AH54" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="AI54" s="27" t="inlineStr">
+      <c r="AI54" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ54" s="27" t="inlineStr">
         <is>
           <t>실제 사고 확인</t>
         </is>
       </c>
-      <c r="AJ54" s="9" t="inlineStr">
+      <c r="AK54" s="9" t="inlineStr">
         <is>
           <t>ENI-015</t>
         </is>
       </c>
-      <c r="AK54" s="9" t="inlineStr">
+      <c r="AL54" s="9" t="inlineStr">
         <is>
           <t>랜섬·암호화 1 · 서비스 중단 1</t>
         </is>
       </c>
-      <c r="AL54" s="9" t="inlineStr">
+      <c r="AM54" s="9" t="inlineStr">
         <is>
           <t>SI-4 System Monitoring
 CP-10 System Recovery and Reconstitution</t>
         </is>
       </c>
-      <c r="AM54" s="9" t="inlineStr">
+      <c r="AN54" s="9" t="inlineStr">
         <is>
           <t>■ 탐지
 - 보안·백업·DB 서비스의 비정상 중지와 대량 종료 명령을 행위 기반으로 탐지(NIST SI-4·CP-10)
@@ -17534,7 +17726,7 @@
 - 중요 서비스 변조 방지·권한 분리와 신속 복구 체계를 적용(NIST CP-10·SI-4)</t>
         </is>
       </c>
-      <c r="AN54" s="9" t="inlineStr">
+      <c r="AO54" s="9" t="inlineStr">
         <is>
           <t>MITRE 〈ATT&amp;CK Enterprise v19.2〉</t>
         </is>
@@ -17647,54 +17839,55 @@
           <t>매우 높음</t>
         </is>
       </c>
-      <c r="AB55" s="8" t="n">
+      <c r="AB55" s="9" t="inlineStr"/>
+      <c r="AC55" s="8" t="n">
         <v>8</v>
       </c>
-      <c r="AC55" s="9" t="inlineStr">
-        <is>
-          <t>실제 사고 3건(최근 0) · ATT&amp;CK 주체 26 · KEV - · 정부 경보 1 · 위협인텔 0 · 실증 0</t>
-        </is>
-      </c>
       <c r="AD55" s="9" t="inlineStr">
         <is>
+          <t>실제 사고 3건(최근 0, 서로 다른 행위자·캠페인 3) · ATT&amp;CK 주체 26 · KEV - · 정부 경보 1 · 위협인텔 0 · 실증 0</t>
+        </is>
+      </c>
+      <c r="AE55" s="9" t="inlineStr">
+        <is>
           <t>반출 데이터 공개 협박·부정 이체로 금전 피해를 실현 — 이중 협박은 백업 복구로도 막지 못하고 대규모 금전·평판 피해로 직결</t>
         </is>
       </c>
-      <c r="AE55" s="9" t="n">
+      <c r="AF55" s="9" t="n">
         <v>3</v>
       </c>
-      <c r="AF55" s="9" t="n">
+      <c r="AG55" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="AG55" s="9" t="n">
+      <c r="AH55" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="AH55" s="9" t="n">
+      <c r="AI55" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="AI55" s="27" t="inlineStr">
+      <c r="AJ55" s="27" t="inlineStr">
         <is>
           <t>실제 사고 확인</t>
         </is>
       </c>
-      <c r="AJ55" s="9" t="inlineStr">
+      <c r="AK55" s="9" t="inlineStr">
         <is>
           <t>ENI-004, ENI-010, ENI-031
 정부 경보: ENI-030</t>
         </is>
       </c>
-      <c r="AK55" s="9" t="inlineStr">
+      <c r="AL55" s="9" t="inlineStr">
         <is>
           <t>데이터 유출 3 · 금전 피해 3</t>
         </is>
       </c>
-      <c r="AL55" s="9" t="inlineStr">
+      <c r="AM55" s="9" t="inlineStr">
         <is>
           <t>SI-4 System Monitoring
 IR-4 Incident Handling</t>
         </is>
       </c>
-      <c r="AM55" s="9" t="inlineStr">
+      <c r="AN55" s="9" t="inlineStr">
         <is>
           <t>■ 탐지
 - 대량 반출 선행 징후와 갈취·부정 이체 정황을 통합 모니터링(NIST SI-4·IR-4)
@@ -17702,23 +17895,23 @@
 - 데이터 반출 차단·사고 대응·법집행 연계와 백업·복구를 병행(NIST IR-4·SI-4)</t>
         </is>
       </c>
-      <c r="AN55" s="9" t="inlineStr">
+      <c r="AO55" s="9" t="inlineStr">
         <is>
           <t>MITRE 〈ATT&amp;CK Enterprise v19.2〉</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A4:AN55"/>
+  <autoFilter ref="A4:AO55"/>
   <mergeCells count="8">
-    <mergeCell ref="Y3:AD3"/>
     <mergeCell ref="A3:H3"/>
+    <mergeCell ref="A2:AO2"/>
     <mergeCell ref="I3:L3"/>
-    <mergeCell ref="A2:AN2"/>
-    <mergeCell ref="AE3:AK3"/>
+    <mergeCell ref="A1:AO1"/>
+    <mergeCell ref="AF3:AL3"/>
     <mergeCell ref="M3:X3"/>
-    <mergeCell ref="AL3:AN3"/>
-    <mergeCell ref="A1:AN1"/>
+    <mergeCell ref="Y3:AE3"/>
+    <mergeCell ref="AM3:AO3"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/enterprise/output/통합_고도화엔터프라이즈_보안위협_매트릭스_v2.xlsx
+++ b/enterprise/output/통합_고도화엔터프라이즈_보안위협_매트릭스_v2.xlsx
@@ -681,7 +681,7 @@
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
     </row>
@@ -1185,7 +1185,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G69"/>
+  <dimension ref="A1:G68"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -2728,14 +2728,18 @@
         <v>140</v>
       </c>
       <c r="E52" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F52" s="9" t="inlineStr">
         <is>
-          <t>ENT-PE-01</t>
-        </is>
-      </c>
-      <c r="G52" s="9" t="inlineStr"/>
+          <t>ENT-PE-01, ENT-DE-01.2</t>
+        </is>
+      </c>
+      <c r="G52" s="9" t="inlineStr">
+        <is>
+          <t>BYOVD</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" s="9" t="inlineStr">
@@ -2769,61 +2773,57 @@
     <row r="54">
       <c r="A54" s="9" t="inlineStr">
         <is>
-          <t>T1547.006</t>
+          <t>T1548.002</t>
         </is>
       </c>
       <c r="B54" s="9" t="inlineStr">
         <is>
-          <t>Boot or Logon Autostart Execution: Kernel Modules and Extensions</t>
+          <t>Abuse Elevation Control Mechanism: Bypass User Account Control</t>
         </is>
       </c>
       <c r="C54" s="9" t="inlineStr">
         <is>
-          <t>Persistence, Privilege Escalation</t>
+          <t>Privilege Escalation</t>
         </is>
       </c>
       <c r="D54" s="9" t="n">
-        <v>4</v>
+        <v>63</v>
       </c>
       <c r="E54" s="9" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F54" s="9" t="inlineStr">
         <is>
-          <t>ENT-DE-01.1, ENT-DE-01.2</t>
-        </is>
-      </c>
-      <c r="G54" s="9" t="inlineStr">
-        <is>
-          <t>BYOVD</t>
-        </is>
-      </c>
+          <t>ENT-PV-03</t>
+        </is>
+      </c>
+      <c r="G54" s="9" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" s="9" t="inlineStr">
         <is>
-          <t>T1548.002</t>
+          <t>T1550.002</t>
         </is>
       </c>
       <c r="B55" s="9" t="inlineStr">
         <is>
-          <t>Abuse Elevation Control Mechanism: Bypass User Account Control</t>
+          <t>Use Alternate Authentication Material: Pass the Hash</t>
         </is>
       </c>
       <c r="C55" s="9" t="inlineStr">
         <is>
-          <t>Privilege Escalation</t>
+          <t>Lateral Movement</t>
         </is>
       </c>
       <c r="D55" s="9" t="n">
-        <v>63</v>
+        <v>22</v>
       </c>
       <c r="E55" s="9" t="n">
         <v>1</v>
       </c>
       <c r="F55" s="9" t="inlineStr">
         <is>
-          <t>ENT-PV-03</t>
+          <t>ENT-LM-02</t>
         </is>
       </c>
       <c r="G55" s="9" t="inlineStr"/>
@@ -2831,12 +2831,12 @@
     <row r="56">
       <c r="A56" s="9" t="inlineStr">
         <is>
-          <t>T1550.002</t>
+          <t>T1550.003</t>
         </is>
       </c>
       <c r="B56" s="9" t="inlineStr">
         <is>
-          <t>Use Alternate Authentication Material: Pass the Hash</t>
+          <t>Use Alternate Authentication Material: Pass the Ticket</t>
         </is>
       </c>
       <c r="C56" s="9" t="inlineStr">
@@ -2845,7 +2845,7 @@
         </is>
       </c>
       <c r="D56" s="9" t="n">
-        <v>22</v>
+        <v>6</v>
       </c>
       <c r="E56" s="9" t="n">
         <v>1</v>
@@ -2860,28 +2860,28 @@
     <row r="57">
       <c r="A57" s="9" t="inlineStr">
         <is>
-          <t>T1550.003</t>
+          <t>T1558.003</t>
         </is>
       </c>
       <c r="B57" s="9" t="inlineStr">
         <is>
-          <t>Use Alternate Authentication Material: Pass the Ticket</t>
+          <t>Steal or Forge Kerberos Tickets: Kerberoasting</t>
         </is>
       </c>
       <c r="C57" s="9" t="inlineStr">
         <is>
-          <t>Lateral Movement</t>
+          <t>Credential Access</t>
         </is>
       </c>
       <c r="D57" s="9" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="E57" s="9" t="n">
         <v>1</v>
       </c>
       <c r="F57" s="9" t="inlineStr">
         <is>
-          <t>ENT-LM-02</t>
+          <t>ENT-CA-03</t>
         </is>
       </c>
       <c r="G57" s="9" t="inlineStr"/>
@@ -2889,28 +2889,28 @@
     <row r="58">
       <c r="A58" s="9" t="inlineStr">
         <is>
-          <t>T1558.003</t>
+          <t>T1560</t>
         </is>
       </c>
       <c r="B58" s="9" t="inlineStr">
         <is>
-          <t>Steal or Forge Kerberos Tickets: Kerberoasting</t>
+          <t>Archive Collected Data</t>
         </is>
       </c>
       <c r="C58" s="9" t="inlineStr">
         <is>
-          <t>Credential Access</t>
+          <t>Collection</t>
         </is>
       </c>
       <c r="D58" s="9" t="n">
-        <v>12</v>
+        <v>57</v>
       </c>
       <c r="E58" s="9" t="n">
         <v>1</v>
       </c>
       <c r="F58" s="9" t="inlineStr">
         <is>
-          <t>ENT-CA-03</t>
+          <t>ENT-CO-02</t>
         </is>
       </c>
       <c r="G58" s="9" t="inlineStr"/>
@@ -2918,28 +2918,28 @@
     <row r="59">
       <c r="A59" s="9" t="inlineStr">
         <is>
-          <t>T1560</t>
+          <t>T1561</t>
         </is>
       </c>
       <c r="B59" s="9" t="inlineStr">
         <is>
-          <t>Archive Collected Data</t>
+          <t>Disk Wipe</t>
         </is>
       </c>
       <c r="C59" s="9" t="inlineStr">
         <is>
-          <t>Collection</t>
+          <t>Impact</t>
         </is>
       </c>
       <c r="D59" s="9" t="n">
-        <v>57</v>
+        <v>0</v>
       </c>
       <c r="E59" s="9" t="n">
         <v>1</v>
       </c>
       <c r="F59" s="9" t="inlineStr">
         <is>
-          <t>ENT-CO-02</t>
+          <t>ENT-IM-03</t>
         </is>
       </c>
       <c r="G59" s="9" t="inlineStr"/>
@@ -2947,28 +2947,28 @@
     <row r="60">
       <c r="A60" s="9" t="inlineStr">
         <is>
-          <t>T1561</t>
+          <t>T1567</t>
         </is>
       </c>
       <c r="B60" s="9" t="inlineStr">
         <is>
-          <t>Disk Wipe</t>
+          <t>Exfiltration Over Web Service</t>
         </is>
       </c>
       <c r="C60" s="9" t="inlineStr">
         <is>
-          <t>Impact</t>
+          <t>Exfiltration</t>
         </is>
       </c>
       <c r="D60" s="9" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="E60" s="9" t="n">
         <v>1</v>
       </c>
       <c r="F60" s="9" t="inlineStr">
         <is>
-          <t>ENT-IM-03</t>
+          <t>ENT-EF-02</t>
         </is>
       </c>
       <c r="G60" s="9" t="inlineStr"/>
@@ -2976,28 +2976,28 @@
     <row r="61">
       <c r="A61" s="9" t="inlineStr">
         <is>
-          <t>T1567</t>
+          <t>T1569.002</t>
         </is>
       </c>
       <c r="B61" s="9" t="inlineStr">
         <is>
-          <t>Exfiltration Over Web Service</t>
+          <t>System Services: Service Execution</t>
         </is>
       </c>
       <c r="C61" s="9" t="inlineStr">
         <is>
-          <t>Exfiltration</t>
+          <t>Execution</t>
         </is>
       </c>
       <c r="D61" s="9" t="n">
-        <v>16</v>
+        <v>72</v>
       </c>
       <c r="E61" s="9" t="n">
         <v>1</v>
       </c>
       <c r="F61" s="9" t="inlineStr">
         <is>
-          <t>ENT-EF-02</t>
+          <t>ENT-EX-04</t>
         </is>
       </c>
       <c r="G61" s="9" t="inlineStr"/>
@@ -3005,28 +3005,28 @@
     <row r="62">
       <c r="A62" s="9" t="inlineStr">
         <is>
-          <t>T1569.002</t>
+          <t>T1570</t>
         </is>
       </c>
       <c r="B62" s="9" t="inlineStr">
         <is>
-          <t>System Services: Service Execution</t>
+          <t>Lateral Tool Transfer</t>
         </is>
       </c>
       <c r="C62" s="9" t="inlineStr">
         <is>
-          <t>Execution</t>
+          <t>Lateral Movement</t>
         </is>
       </c>
       <c r="D62" s="9" t="n">
-        <v>72</v>
+        <v>55</v>
       </c>
       <c r="E62" s="9" t="n">
         <v>1</v>
       </c>
       <c r="F62" s="9" t="inlineStr">
         <is>
-          <t>ENT-EX-04</t>
+          <t>ENT-LM-03</t>
         </is>
       </c>
       <c r="G62" s="9" t="inlineStr"/>
@@ -3034,28 +3034,28 @@
     <row r="63">
       <c r="A63" s="9" t="inlineStr">
         <is>
-          <t>T1570</t>
+          <t>T1571</t>
         </is>
       </c>
       <c r="B63" s="9" t="inlineStr">
         <is>
-          <t>Lateral Tool Transfer</t>
+          <t>Non-Standard Port</t>
         </is>
       </c>
       <c r="C63" s="9" t="inlineStr">
         <is>
-          <t>Lateral Movement</t>
+          <t>Command and Control</t>
         </is>
       </c>
       <c r="D63" s="9" t="n">
-        <v>55</v>
+        <v>66</v>
       </c>
       <c r="E63" s="9" t="n">
         <v>1</v>
       </c>
       <c r="F63" s="9" t="inlineStr">
         <is>
-          <t>ENT-LM-03</t>
+          <t>ENT-C2-01.1</t>
         </is>
       </c>
       <c r="G63" s="9" t="inlineStr"/>
@@ -3063,12 +3063,12 @@
     <row r="64">
       <c r="A64" s="9" t="inlineStr">
         <is>
-          <t>T1571</t>
+          <t>T1573</t>
         </is>
       </c>
       <c r="B64" s="9" t="inlineStr">
         <is>
-          <t>Non-Standard Port</t>
+          <t>Encrypted Channel</t>
         </is>
       </c>
       <c r="C64" s="9" t="inlineStr">
@@ -3077,7 +3077,7 @@
         </is>
       </c>
       <c r="D64" s="9" t="n">
-        <v>66</v>
+        <v>17</v>
       </c>
       <c r="E64" s="9" t="n">
         <v>1</v>
@@ -3092,28 +3092,28 @@
     <row r="65">
       <c r="A65" s="9" t="inlineStr">
         <is>
-          <t>T1573</t>
+          <t>T1620</t>
         </is>
       </c>
       <c r="B65" s="9" t="inlineStr">
         <is>
-          <t>Encrypted Channel</t>
+          <t>Reflective Code Loading</t>
         </is>
       </c>
       <c r="C65" s="9" t="inlineStr">
         <is>
-          <t>Command and Control</t>
+          <t>Stealth</t>
         </is>
       </c>
       <c r="D65" s="9" t="n">
-        <v>17</v>
+        <v>32</v>
       </c>
       <c r="E65" s="9" t="n">
         <v>1</v>
       </c>
       <c r="F65" s="9" t="inlineStr">
         <is>
-          <t>ENT-C2-01.1</t>
+          <t>ENT-DE-06</t>
         </is>
       </c>
       <c r="G65" s="9" t="inlineStr"/>
@@ -3121,28 +3121,28 @@
     <row r="66">
       <c r="A66" s="9" t="inlineStr">
         <is>
-          <t>T1620</t>
+          <t>T1657</t>
         </is>
       </c>
       <c r="B66" s="9" t="inlineStr">
         <is>
-          <t>Reflective Code Loading</t>
+          <t>Financial Theft</t>
         </is>
       </c>
       <c r="C66" s="9" t="inlineStr">
         <is>
-          <t>Stealth</t>
+          <t>Impact</t>
         </is>
       </c>
       <c r="D66" s="9" t="n">
-        <v>32</v>
+        <v>26</v>
       </c>
       <c r="E66" s="9" t="n">
         <v>1</v>
       </c>
       <c r="F66" s="9" t="inlineStr">
         <is>
-          <t>ENT-DE-06</t>
+          <t>ENT-IM-05</t>
         </is>
       </c>
       <c r="G66" s="9" t="inlineStr"/>
@@ -3150,41 +3150,45 @@
     <row r="67">
       <c r="A67" s="9" t="inlineStr">
         <is>
-          <t>T1657</t>
+          <t>T1685</t>
         </is>
       </c>
       <c r="B67" s="9" t="inlineStr">
         <is>
-          <t>Financial Theft</t>
+          <t>Disable or Modify Tools</t>
         </is>
       </c>
       <c r="C67" s="9" t="inlineStr">
         <is>
-          <t>Impact</t>
+          <t>Defense Impairment</t>
         </is>
       </c>
       <c r="D67" s="9" t="n">
-        <v>26</v>
+        <v>128</v>
       </c>
       <c r="E67" s="9" t="n">
         <v>1</v>
       </c>
       <c r="F67" s="9" t="inlineStr">
         <is>
-          <t>ENT-IM-05</t>
-        </is>
-      </c>
-      <c r="G67" s="9" t="inlineStr"/>
+          <t>ENT-DE-01.1</t>
+        </is>
+      </c>
+      <c r="G67" s="9" t="inlineStr">
+        <is>
+          <t>BYOVD</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" s="9" t="inlineStr">
         <is>
-          <t>T1685</t>
+          <t>T1685.005</t>
         </is>
       </c>
       <c r="B68" s="9" t="inlineStr">
         <is>
-          <t>Disable or Modify Tools</t>
+          <t>Disable or Modify Tools: Clear Windows Event Logs</t>
         </is>
       </c>
       <c r="C68" s="9" t="inlineStr">
@@ -3193,50 +3197,17 @@
         </is>
       </c>
       <c r="D68" s="9" t="n">
-        <v>128</v>
+        <v>42</v>
       </c>
       <c r="E68" s="9" t="n">
         <v>1</v>
       </c>
       <c r="F68" s="9" t="inlineStr">
         <is>
-          <t>ENT-DE-01.1</t>
-        </is>
-      </c>
-      <c r="G68" s="9" t="inlineStr">
-        <is>
-          <t>BYOVD</t>
-        </is>
-      </c>
-    </row>
-    <row r="69">
-      <c r="A69" s="9" t="inlineStr">
-        <is>
-          <t>T1685.005</t>
-        </is>
-      </c>
-      <c r="B69" s="9" t="inlineStr">
-        <is>
-          <t>Disable or Modify Tools: Clear Windows Event Logs</t>
-        </is>
-      </c>
-      <c r="C69" s="9" t="inlineStr">
-        <is>
-          <t>Defense Impairment</t>
-        </is>
-      </c>
-      <c r="D69" s="9" t="n">
-        <v>42</v>
-      </c>
-      <c r="E69" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="F69" s="9" t="inlineStr">
-        <is>
           <t>ENT-DE-03</t>
         </is>
       </c>
-      <c r="G69" s="9" t="inlineStr"/>
+      <c r="G68" s="9" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -3742,7 +3713,7 @@
       </c>
       <c r="E21" s="9" t="inlineStr">
         <is>
-          <t>ENT-IA-01, ENT-IM-01, ENT-DE-01.1, ENT-LM-01, ENT-IA-02, ENT-CA-01.1, ENT-EX-01.1, ENT-IM-05, ENT-EF-02, ENT-EF-01, ENT-LM-02, ENT-IA-05, ENT-CA-03, ENT-DE-01.2, ENT-EX-03, ENT-IM-02, ENT-DI-02, ENT-DE-03, ENT-C2-05, ENT-C2-01.2, ENT-C2-01.1, ENT-C2-03, ENT-IM-03, ENT-DE-06, ENT-DE-07, ENT-PV-01.1, ENT-PV-04, ENT-EX-01.2, ENT-C2-04, ENT-C2-06, ENT-DI-01, ENT-CO-01, ENT-PE-03, ENT-DE-05, ENT-CA-04, ENT-PE-01, ENT-IM-04, ENT-CO-02, ENT-PV-03, ENT-DE-04, ENT-LM-03, ENT-PV-01.2, ENT-PE-02, ENT-EX-04, ENT-IA-03, ENT-CA-01.2, ENT-DI-03</t>
+          <t>ENT-IA-01, ENT-IM-01, ENT-DE-01.1, ENT-LM-01, ENT-IA-02, ENT-CA-01.1, ENT-EX-01.1, ENT-IM-05, ENT-EF-02, ENT-EF-01, ENT-DE-01.2, ENT-LM-02, ENT-IA-05, ENT-CA-03, ENT-EX-03, ENT-IM-02, ENT-DI-02, ENT-DE-03, ENT-C2-05, ENT-C2-01.2, ENT-C2-01.1, ENT-C2-03, ENT-IM-03, ENT-DE-06, ENT-DE-07, ENT-PV-01.1, ENT-PV-04, ENT-EX-01.2, ENT-C2-04, ENT-C2-06, ENT-DI-01, ENT-CO-01, ENT-PE-03, ENT-DE-05, ENT-CA-04, ENT-PE-01, ENT-IM-04, ENT-CO-02, ENT-PV-03, ENT-DE-04, ENT-LM-03, ENT-PV-01.2, ENT-PE-02, ENT-EX-04, ENT-IA-03, ENT-CA-01.2, ENT-DI-03</t>
         </is>
       </c>
     </row>
@@ -5473,7 +5444,7 @@
     <row r="2">
       <c r="A2" s="6" t="inlineStr">
         <is>
-          <t>순위 = 위험도 → 실제 사고 → 방어 난이도 → ATT&amp;CK 주체 수 | 2026-10-26</t>
+          <t>순위 = 위험도 → 실제 사고 → 방어 난이도 → ATT&amp;CK 주체 수 | 2026-10-27</t>
         </is>
       </c>
     </row>
@@ -6199,22 +6170,22 @@
       </c>
       <c r="B15" s="9" t="inlineStr">
         <is>
-          <t>[LM] 측면 이동</t>
+          <t>[DE] 방어 회피</t>
         </is>
       </c>
       <c r="C15" s="10" t="inlineStr">
         <is>
-          <t>ENT-LM-02</t>
+          <t>ENT-DE-01.2</t>
         </is>
       </c>
       <c r="D15" s="10" t="inlineStr">
         <is>
-          <t>대체 인증 자료 사용(Pass-the-Hash·Pass-the-Ticket)</t>
+          <t>취약·악성 드라이버 로드(커널)</t>
         </is>
       </c>
       <c r="E15" s="9" t="inlineStr">
         <is>
-          <t>대체 인증 자료(PtH·PtT)로 평문 없이 인증해 확산</t>
+          <t>취약·악성 드라이버 로드로 커널 은닉·무력화 토대 마련</t>
         </is>
       </c>
       <c r="F15" s="11" t="inlineStr">
@@ -6244,7 +6215,7 @@
       </c>
       <c r="K15" s="8" t="inlineStr">
         <is>
-          <t>정상 인증 위장</t>
+          <t>커널·펌웨어 하위 계층</t>
         </is>
       </c>
       <c r="L15" s="9" t="n">
@@ -6252,12 +6223,12 @@
       </c>
       <c r="M15" s="9" t="inlineStr">
         <is>
-          <t>[실제 사고] APT28 인접 네트워크(Nearest Neighbor) 무선 경유 침투(2024-11) (ENI-002)</t>
+          <t>[실제 사고] 서명된 취약 드라이버 대량 변종 캠페인(TrueSight 등)(2025-01) (ENI-017)</t>
         </is>
       </c>
       <c r="N15" s="9" t="inlineStr">
         <is>
-          <t>특권 분리·로컬 관리자 암호 고유화(LAPS)·티켓 수명 축소와 재사용 탐지를 적용(NIST IA-2·AC-6)</t>
+          <t>HVCI·드라이버 블록리스트로 취약 드라이버 로드를 차단(NIST SI-7·CM-7)</t>
         </is>
       </c>
     </row>
@@ -6267,22 +6238,22 @@
       </c>
       <c r="B16" s="9" t="inlineStr">
         <is>
-          <t>[IA] 초기 침투</t>
+          <t>[LM] 측면 이동</t>
         </is>
       </c>
       <c r="C16" s="10" t="inlineStr">
         <is>
-          <t>ENT-IA-05</t>
+          <t>ENT-LM-02</t>
         </is>
       </c>
       <c r="D16" s="10" t="inlineStr">
         <is>
-          <t>신뢰 관계(MSP·협력사·연동) 악용</t>
+          <t>대체 인증 자료 사용(Pass-the-Hash·Pass-the-Ticket)</t>
         </is>
       </c>
       <c r="E16" s="9" t="inlineStr">
         <is>
-          <t>MSP·협력사·연동 신뢰 경로 악용으로 다수 하위 고객 침해</t>
+          <t>대체 인증 자료(PtH·PtT)로 평문 없이 인증해 확산</t>
         </is>
       </c>
       <c r="F16" s="11" t="inlineStr">
@@ -6312,7 +6283,7 @@
       </c>
       <c r="K16" s="8" t="inlineStr">
         <is>
-          <t>신뢰·공급 관계 경유 · 정상 인증 위장</t>
+          <t>정상 인증 위장</t>
         </is>
       </c>
       <c r="L16" s="9" t="n">
@@ -6320,12 +6291,12 @@
       </c>
       <c r="M16" s="9" t="inlineStr">
         <is>
-          <t>[실제 사고] ConnectWise ScreenConnect 취약점 경유 랜섬웨어(2024-02) (ENI-009)</t>
+          <t>[실제 사고] APT28 인접 네트워크(Nearest Neighbor) 무선 경유 침투(2024-11) (ENI-002)</t>
         </is>
       </c>
       <c r="N16" s="9" t="inlineStr">
         <is>
-          <t>공급·관리 관계에 최소 권한·분리·계약상 보안 요구를 적용하고 연동 토큰을 단기화·감사(NIST SR-3·CA-3·AC-20)</t>
+          <t>특권 분리·로컬 관리자 암호 고유화(LAPS)·티켓 수명 축소와 재사용 탐지를 적용(NIST IA-2·AC-6)</t>
         </is>
       </c>
     </row>
@@ -6335,22 +6306,22 @@
       </c>
       <c r="B17" s="9" t="inlineStr">
         <is>
-          <t>[CA] 자격증명 접근</t>
+          <t>[IA] 초기 침투</t>
         </is>
       </c>
       <c r="C17" s="10" t="inlineStr">
         <is>
-          <t>ENT-CA-03</t>
+          <t>ENT-IA-05</t>
         </is>
       </c>
       <c r="D17" s="10" t="inlineStr">
         <is>
-          <t>Kerberoasting·AS-REP 로스팅</t>
+          <t>신뢰 관계(MSP·협력사·연동) 악용</t>
         </is>
       </c>
       <c r="E17" s="9" t="inlineStr">
         <is>
-          <t>Kerberoasting·AS-REP 로스팅으로 도메인 권한 계정 탈취</t>
+          <t>MSP·협력사·연동 신뢰 경로 악용으로 다수 하위 고객 침해</t>
         </is>
       </c>
       <c r="F17" s="11" t="inlineStr">
@@ -6380,7 +6351,7 @@
       </c>
       <c r="K17" s="8" t="inlineStr">
         <is>
-          <t>정상 인증 위장</t>
+          <t>신뢰·공급 관계 경유 · 정상 인증 위장</t>
         </is>
       </c>
       <c r="L17" s="9" t="n">
@@ -6388,12 +6359,12 @@
       </c>
       <c r="M17" s="9" t="inlineStr">
         <is>
-          <t>[실제 사고] APT28 인접 네트워크(Nearest Neighbor) 무선 경유 침투(2024-11) (ENI-002)</t>
+          <t>[실제 사고] ConnectWise ScreenConnect 취약점 경유 랜섬웨어(2024-02) (ENI-009)</t>
         </is>
       </c>
       <c r="N17" s="9" t="inlineStr">
         <is>
-          <t>서비스 계정에 길고 무작위한 암호·gMSA·강한 암호화를 적용하고 요청을 감사(NIST IA-5·AC-6)</t>
+          <t>공급·관리 관계에 최소 권한·분리·계약상 보안 요구를 적용하고 연동 토큰을 단기화·감사(NIST SR-3·CA-3·AC-20)</t>
         </is>
       </c>
     </row>
@@ -6403,22 +6374,22 @@
       </c>
       <c r="B18" s="9" t="inlineStr">
         <is>
-          <t>[DE] 방어 회피</t>
+          <t>[CA] 자격증명 접근</t>
         </is>
       </c>
       <c r="C18" s="10" t="inlineStr">
         <is>
-          <t>ENT-DE-01.2</t>
+          <t>ENT-CA-03</t>
         </is>
       </c>
       <c r="D18" s="10" t="inlineStr">
         <is>
-          <t>취약·악성 드라이버 로드(커널)</t>
+          <t>Kerberoasting·AS-REP 로스팅</t>
         </is>
       </c>
       <c r="E18" s="9" t="inlineStr">
         <is>
-          <t>취약·악성 드라이버 로드로 커널 은닉·무력화 토대 마련</t>
+          <t>Kerberoasting·AS-REP 로스팅으로 도메인 권한 계정 탈취</t>
         </is>
       </c>
       <c r="F18" s="11" t="inlineStr">
@@ -6448,7 +6419,7 @@
       </c>
       <c r="K18" s="8" t="inlineStr">
         <is>
-          <t>커널·펌웨어 하위 계층</t>
+          <t>정상 인증 위장</t>
         </is>
       </c>
       <c r="L18" s="9" t="n">
@@ -6456,12 +6427,12 @@
       </c>
       <c r="M18" s="9" t="inlineStr">
         <is>
-          <t>[실제 사고] 서명된 취약 드라이버 대량 변종 캠페인(TrueSight 등)(2025-01) (ENI-017)</t>
+          <t>[실제 사고] APT28 인접 네트워크(Nearest Neighbor) 무선 경유 침투(2024-11) (ENI-002)</t>
         </is>
       </c>
       <c r="N18" s="9" t="inlineStr">
         <is>
-          <t>HVCI·드라이버 블록리스트로 취약 드라이버 로드를 차단(NIST SI-7·CM-7)</t>
+          <t>서비스 계정에 길고 무작위한 암호·gMSA·강한 암호화를 적용하고 요청을 감사(NIST IA-5·AC-6)</t>
         </is>
       </c>
     </row>
@@ -9313,7 +9284,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>사고 DB 33건 + ATT&amp;CK v19.2 + CISA KEV + LOLBAS·LOLDrivers | 2026-10-26</t>
+          <t>사고 DB 33건 + ATT&amp;CK v19.2 + CISA KEV + LOLBAS·LOLDrivers | 2026-10-27</t>
         </is>
       </c>
     </row>
@@ -10332,7 +10303,7 @@
         </is>
       </c>
       <c r="AC9" s="8" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AD9" s="9" t="inlineStr">
         <is>
@@ -11282,7 +11253,7 @@
         </is>
       </c>
       <c r="O15" s="8" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="P15" s="8" t="inlineStr"/>
       <c r="Q15" s="8" t="inlineStr"/>
@@ -11314,7 +11285,7 @@
       </c>
       <c r="AD15" s="9" t="inlineStr">
         <is>
-          <t>실제 사고 1건(최근 0, 서로 다른 행위자·캠페인 1) · ATT&amp;CK 주체 6 · KEV - · 정부 경보 0 · 위협인텔 0 · 실증 0</t>
+          <t>실제 사고 1건(최근 0, 서로 다른 행위자·캠페인 1) · ATT&amp;CK 주체 10 · KEV - · 정부 경보 0 · 위협인텔 0 · 실증 0</t>
         </is>
       </c>
       <c r="AE15" s="9" t="inlineStr">
@@ -12404,17 +12375,16 @@
       </c>
       <c r="M22" s="9" t="inlineStr">
         <is>
-          <t>T1685, T1547.006</t>
+          <t>T1685</t>
         </is>
       </c>
       <c r="N22" s="9" t="inlineStr">
         <is>
-          <t>T1685 Disable or Modify Tools
-T1547.006 Boot or Logon Autostart Execution: Kernel Modules and Extensions</t>
+          <t>T1685 Disable or Modify Tools</t>
         </is>
       </c>
       <c r="O22" s="8" t="n">
-        <v>131</v>
+        <v>155</v>
       </c>
       <c r="P22" s="8" t="inlineStr"/>
       <c r="Q22" s="8" t="inlineStr"/>
@@ -12450,7 +12420,7 @@
       </c>
       <c r="AD22" s="9" t="inlineStr">
         <is>
-          <t>실제 사고 5건(최근 1, 서로 다른 행위자·캠페인 5) · ATT&amp;CK 주체 131 · KEV - · 정부 경보 1 · 위협인텔 0 · 실증 0</t>
+          <t>실제 사고 5건(최근 1, 서로 다른 행위자·캠페인 5) · ATT&amp;CK 주체 155 · KEV - · 정부 경보 1 · 위협인텔 0 · 실증 0</t>
         </is>
       </c>
       <c r="AE22" s="9" t="inlineStr">
@@ -12573,16 +12543,16 @@
       </c>
       <c r="M23" s="9" t="inlineStr">
         <is>
-          <t>T1547.006</t>
+          <t>T1543.003</t>
         </is>
       </c>
       <c r="N23" s="9" t="inlineStr">
         <is>
-          <t>T1547.006 Boot or Logon Autostart Execution: Kernel Modules and Extensions</t>
+          <t>T1543.003 Create or Modify System Process: Windows Service</t>
         </is>
       </c>
       <c r="O23" s="8" t="n">
-        <v>4</v>
+        <v>140</v>
       </c>
       <c r="P23" s="8" t="inlineStr"/>
       <c r="Q23" s="8" t="inlineStr"/>
@@ -12618,11 +12588,11 @@
         </is>
       </c>
       <c r="AC23" s="8" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="AD23" s="9" t="inlineStr">
         <is>
-          <t>실제 사고 2건(최근 1, 서로 다른 행위자·캠페인 2) · ATT&amp;CK 주체 4 · KEV - · 정부 경보 0 · 위협인텔 0 · 실증 0</t>
+          <t>실제 사고 2건(최근 1, 서로 다른 행위자·캠페인 2) · ATT&amp;CK 주체 140 · KEV - · 정부 경보 0 · 위협인텔 0 · 실증 0</t>
         </is>
       </c>
       <c r="AE23" s="9" t="inlineStr">
@@ -14066,7 +14036,7 @@
         </is>
       </c>
       <c r="AC32" s="8" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AD32" s="9" t="inlineStr">
         <is>
@@ -15038,7 +15008,7 @@
         </is>
       </c>
       <c r="AC38" s="8" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AD38" s="9" t="inlineStr">
         <is>
@@ -18462,7 +18432,7 @@
         </is>
       </c>
       <c r="M7" s="8" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="N7" s="27" t="inlineStr">
         <is>
@@ -18992,7 +18962,7 @@
         <v>1</v>
       </c>
       <c r="P13" s="8" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="Q13" s="8" t="inlineStr"/>
       <c r="R13" s="9" t="inlineStr">
@@ -19599,7 +19569,7 @@
         <v>5</v>
       </c>
       <c r="P20" s="8" t="n">
-        <v>131</v>
+        <v>155</v>
       </c>
       <c r="Q20" s="8" t="inlineStr"/>
       <c r="R20" s="9" t="inlineStr">
@@ -19675,7 +19645,7 @@
         </is>
       </c>
       <c r="M21" s="8" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="N21" s="27" t="inlineStr">
         <is>
@@ -19686,7 +19656,7 @@
         <v>2</v>
       </c>
       <c r="P21" s="8" t="n">
-        <v>4</v>
+        <v>140</v>
       </c>
       <c r="Q21" s="8" t="inlineStr"/>
       <c r="R21" s="9" t="inlineStr">
@@ -20450,7 +20420,7 @@
         </is>
       </c>
       <c r="M30" s="8" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="N30" s="27" t="inlineStr">
         <is>
@@ -20967,7 +20937,7 @@
         </is>
       </c>
       <c r="M36" s="8" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="N36" s="27" t="inlineStr">
         <is>

--- a/enterprise/output/통합_고도화엔터프라이즈_보안위협_매트릭스_v2.xlsx
+++ b/enterprise/output/통합_고도화엔터프라이즈_보안위협_매트릭스_v2.xlsx
@@ -27,7 +27,7 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'보고서용 간략 매트릭스'!$A$4:$N$55</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'통합 매트릭스'!$A$4:$AO$55</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'통합매트릭스_LITE'!$A$2:$R$53</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">'역매핑_사고사례'!$A$1:$N$25</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">'역매핑_사고사례'!$A$1:$N$29</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -698,7 +698,7 @@
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>24건(2017~2025) — 실제 사고 22 · 정부 경보 1 · 위협인텔 0 · 실증·연구 1. 실제 사고가 매핑된 세부위협 30/51</t>
+          <t>28건(2017~2026) — 실제 사고 26 · 정부 경보 1 · 위협인텔 0 · 실증·연구 1. 실제 사고가 매핑된 세부위협 30/51</t>
         </is>
       </c>
     </row>
@@ -914,7 +914,7 @@
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>사고 DB 24건과 매핑 세부위협·CVE·출처</t>
+          <t>사고 DB 28건과 매핑 세부위협·CVE·출처</t>
         </is>
       </c>
     </row>
@@ -1082,7 +1082,7 @@
       </c>
       <c r="B41" s="2" t="inlineStr">
         <is>
-          <t>51/51개 작성 — 전 항목 완료 | validate.py 세부위협 51개(문구 51) · 사고 24건 · 시나리오 8개 · 실제 사고 매핑 행 30개 · 인용 사례 59건</t>
+          <t>51/51개 작성 — 전 항목 완료 | validate.py 세부위협 51개(문구 51) · 사고 28건 · 시나리오 8개 · 실제 사고 매핑 행 30개 · 인용 사례 63건</t>
         </is>
       </c>
     </row>
@@ -1094,14 +1094,14 @@
       </c>
       <c r="B42" s="2" t="inlineStr">
         <is>
-          <t>1. ENT-IM-01 데이터 암호화(사람 운영 랜섬웨어) — 매우 높음, 실제 사고 7건(행위·네트워크·아이덴티티)
+          <t>1. ENT-IM-01 데이터 암호화(사람 운영 랜섬웨어) — 매우 높음, 실제 사고 8건(행위·네트워크·아이덴티티)
 2. ENT-IM-05 금전 탈취·이중 협박 갈취 — 매우 높음, 실제 사고 2건(행위·네트워크·아이덴티티)
 3. ENT-EF-02 정상 웹 서비스·대체 프로토콜 경유 반출 — 매우 높음, 실제 사고 2건(행위·네트워크·아이덴티티)
 4. ENT-IA-05 신뢰 관계(MSP·협력사·연동) 악용 — 매우 높음, 실제 사고 2건(행위·네트워크·아이덴티티)
 5. ENT-IM-02 복구 방해(섀도 카피·백업 삭제) — 매우 높음, 실제 사고 2건(EDR·XDR)
 6. ENT-LM-04 원격 서비스 취약점 악용(웜 확산) — 매우 높음, 실제 사고 2건(EDR·XDR)
-7. ENT-IA-01 인터넷 노출 경계·엣지 장비 취약점 악용(빠른 n-day·0-day) — 높음, 실제 사고 8건(행위·네트워크·아이덴티티)
-8. ENT-DE-01.1 보안 도구 무력화(EDR 변조·BYOVD EDR 킬러) — 높음, 실제 사고 5건(행위·네트워크·아이덴티티)
+7. ENT-IA-01 인터넷 노출 경계·엣지 장비 취약점 악용(빠른 n-day·0-day) — 높음, 실제 사고 10건(행위·네트워크·아이덴티티)
+8. ENT-DE-01.1 보안 도구 무력화(EDR 변조·BYOVD EDR 킬러) — 높음, 실제 사고 7건(행위·네트워크·아이덴티티)
 9. ENT-LM-01 원격 서비스 악용(RDP·SMB·WinRM) — 높음, 실제 사고 5건(행위·네트워크·아이덴티티)
 10. ENT-IA-02 외부 원격 서비스 악용(VPN·RDP·원격 관리) — 높음, 실제 사고 4건(행위·네트워크·아이덴티티)</t>
         </is>
@@ -3361,7 +3361,7 @@
       </c>
       <c r="E6" s="9" t="inlineStr">
         <is>
-          <t>ENT-DI-02, ENT-C2-01.2, ENT-DE-03, ENT-DI-01, ENT-EF-01, ENT-C2-01.1, ENT-EX-01.2, ENT-C2-06, ENT-PE-03, ENT-PE-01, ENT-PE-04</t>
+          <t>ENT-DE-03, ENT-DI-02, ENT-C2-01.2, ENT-DI-01, ENT-EF-01, ENT-C2-01.1, ENT-EX-01.2, ENT-C2-06, ENT-PE-03, ENT-PE-01, ENT-PE-04</t>
         </is>
       </c>
     </row>
@@ -3430,7 +3430,7 @@
       </c>
       <c r="E9" s="9" t="inlineStr">
         <is>
-          <t>ENT-DE-01.1, ENT-EX-01.1, ENT-DE-01.2, ENT-EX-03, ENT-DE-08, ENT-EX-01.2, ENT-EX-04, ENT-PE-03, ENT-PE-01, ENT-PV-03, ENT-PE-02</t>
+          <t>ENT-DE-01.1, ENT-DE-01.2, ENT-EX-01.1, ENT-EX-03, ENT-DE-08, ENT-EX-01.2, ENT-EX-04, ENT-PE-03, ENT-PE-01, ENT-PV-03, ENT-PE-02</t>
         </is>
       </c>
     </row>
@@ -3706,7 +3706,7 @@
       </c>
       <c r="E21" s="9" t="inlineStr">
         <is>
-          <t>ENT-IM-01, ENT-IM-05, ENT-EF-02, ENT-IA-05, ENT-IM-02, ENT-IA-01, ENT-DE-01.1, ENT-LM-01, ENT-IA-02, ENT-CA-01.1, ENT-EX-01.1, ENT-DE-01.2, ENT-DI-02, ENT-LM-02, ENT-C2-01.2, ENT-DE-03, ENT-IM-03, ENT-DI-01, ENT-C2-05, ENT-EF-01, ENT-C2-04, ENT-C2-01.1, ENT-CA-03, ENT-EX-03, ENT-PV-01.1, ENT-IM-04, ENT-LM-03, ENT-PV-04, ENT-EX-01.2, ENT-C2-06, ENT-C2-03, ENT-DE-06, ENT-DE-07, ENT-EX-04, ENT-CO-01, ENT-PE-03, ENT-DE-05, ENT-CA-04, ENT-PE-01, ENT-CO-02, ENT-PV-03, ENT-DE-04, ENT-IA-03, ENT-DI-03, ENT-PV-01.2, ENT-PE-02, ENT-CA-01.2</t>
+          <t>ENT-IM-01, ENT-IM-05, ENT-EF-02, ENT-IA-05, ENT-IM-02, ENT-IA-01, ENT-DE-01.1, ENT-LM-01, ENT-IA-02, ENT-CA-01.1, ENT-DE-01.2, ENT-DE-03, ENT-EX-01.1, ENT-DI-02, ENT-LM-02, ENT-C2-01.2, ENT-IM-03, ENT-DI-01, ENT-C2-05, ENT-EF-01, ENT-C2-04, ENT-C2-01.1, ENT-CA-03, ENT-EX-03, ENT-PV-01.1, ENT-IM-04, ENT-LM-03, ENT-PV-04, ENT-EX-01.2, ENT-C2-06, ENT-C2-03, ENT-DE-06, ENT-DE-07, ENT-EX-04, ENT-CO-01, ENT-PE-03, ENT-DE-05, ENT-CA-04, ENT-PE-01, ENT-CO-02, ENT-PV-03, ENT-DE-04, ENT-IA-03, ENT-DI-03, ENT-PV-01.2, ENT-PE-02, ENT-CA-01.2</t>
         </is>
       </c>
     </row>
@@ -5596,11 +5596,11 @@
         </is>
       </c>
       <c r="L5" s="9" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="M5" s="9" t="inlineStr">
         <is>
-          <t>[실제 사고] Black Basta 사람 운영 랜섬웨어(LotL·BYOVD·AD 확산)(2024-05) (ENI-012)</t>
+          <t>[실제 사고] Akira 랜섬웨어의 무방비 웹캠 경유 암호화(EDR 우회)(2025-03) (ENI-037)</t>
         </is>
       </c>
       <c r="N5" s="9" t="inlineStr">
@@ -6000,11 +6000,11 @@
         </is>
       </c>
       <c r="L11" s="9" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="M11" s="9" t="inlineStr">
         <is>
-          <t>[실제 사고] Cl0p의 Cleo 파일전송 취약점 대량 악용(2024-12) (ENI-010)</t>
+          <t>[실제 사고] 롯데카드 결제 서버 웹셸 침해·고객정보 유출(국내)(2025-08) (ENI-035)</t>
         </is>
       </c>
       <c r="N11" s="9" t="inlineStr">
@@ -6064,11 +6064,11 @@
         </is>
       </c>
       <c r="L12" s="9" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="M12" s="9" t="inlineStr">
         <is>
-          <t>[실제 사고] 서명된 취약 드라이버 대량 변종 캠페인(TrueSight 등)(2025-01) (ENI-017)</t>
+          <t>[실제 사고] Reynolds 랜섬웨어의 취약 드라이버 번들(BYOVD)(2026-02) (ENI-036)</t>
         </is>
       </c>
       <c r="N12" s="9" t="inlineStr">
@@ -6275,22 +6275,22 @@
       </c>
       <c r="B16" s="9" t="inlineStr">
         <is>
-          <t>[EX] 실행</t>
+          <t>[DE] 방어 회피</t>
         </is>
       </c>
       <c r="C16" s="10" t="inlineStr">
         <is>
-          <t>ENT-EX-01.1</t>
+          <t>ENT-DE-01.2</t>
         </is>
       </c>
       <c r="D16" s="10" t="inlineStr">
         <is>
-          <t>PowerShell 악용(파일리스 실행)</t>
+          <t>취약·악성 드라이버 로드(커널)</t>
         </is>
       </c>
       <c r="E16" s="9" t="inlineStr">
         <is>
-          <t>PowerShell 파일리스 실행으로 시그니처 AV 무력화</t>
+          <t>취약·악성 드라이버 로드로 커널 은닉·무력화 토대 마련</t>
         </is>
       </c>
       <c r="F16" s="12" t="inlineStr">
@@ -6316,20 +6316,20 @@
       </c>
       <c r="K16" s="8" t="inlineStr">
         <is>
-          <t>파일리스·인메모리 · 서명된 정상 도구 악용</t>
+          <t>커널·펌웨어 하위 계층</t>
         </is>
       </c>
       <c r="L16" s="9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="M16" s="9" t="inlineStr">
         <is>
-          <t>[실제 사고] Black Basta 사람 운영 랜섬웨어(LotL·BYOVD·AD 확산)(2024-05) (ENI-012)</t>
+          <t>[실제 사고] Reynolds 랜섬웨어의 취약 드라이버 번들(BYOVD)(2026-02) (ENI-036)</t>
         </is>
       </c>
       <c r="N16" s="9" t="inlineStr">
         <is>
-          <t>스크립트 로깅·제약 언어 모드·서명 정책과 최소 기능 원칙을 적용(NIST CM-7·SI-4)</t>
+          <t>HVCI·드라이버 블록리스트로 취약 드라이버 로드를 차단(NIST SI-7·CM-7)</t>
         </is>
       </c>
     </row>
@@ -6344,17 +6344,17 @@
       </c>
       <c r="C17" s="10" t="inlineStr">
         <is>
-          <t>ENT-DE-01.2</t>
+          <t>ENT-DE-03</t>
         </is>
       </c>
       <c r="D17" s="10" t="inlineStr">
         <is>
-          <t>취약·악성 드라이버 로드(커널)</t>
+          <t>지표 삭제(이벤트 로그·파일 삭제)</t>
         </is>
       </c>
       <c r="E17" s="9" t="inlineStr">
         <is>
-          <t>취약·악성 드라이버 로드로 커널 은닉·무력화 토대 마련</t>
+          <t>이벤트 로그·파일 삭제로 레거시 SIEM 탐지·분석 무력화</t>
         </is>
       </c>
       <c r="F17" s="12" t="inlineStr">
@@ -6380,7 +6380,7 @@
       </c>
       <c r="K17" s="8" t="inlineStr">
         <is>
-          <t>커널·펌웨어 하위 계층</t>
+          <t>시그니처 회피</t>
         </is>
       </c>
       <c r="L17" s="9" t="n">
@@ -6388,12 +6388,12 @@
       </c>
       <c r="M17" s="9" t="inlineStr">
         <is>
-          <t>[실제 사고] 서명된 취약 드라이버 대량 변종 캠페인(TrueSight 등)(2025-01) (ENI-017)</t>
+          <t>[실제 사고] SK텔레콤 핵심 서버 침해(BPFDoor·장기 잠복, 국내)(2025-04) (ENI-034)</t>
         </is>
       </c>
       <c r="N17" s="9" t="inlineStr">
         <is>
-          <t>HVCI·드라이버 블록리스트로 취약 드라이버 로드를 차단(NIST SI-7·CM-7)</t>
+          <t>원격·불변 로그 전송과 로그 삭제 방지·보존 정책을 적용(NIST AU-9·AU-6)</t>
         </is>
       </c>
     </row>
@@ -6403,22 +6403,22 @@
       </c>
       <c r="B18" s="9" t="inlineStr">
         <is>
-          <t>[DI] 탐색</t>
+          <t>[EX] 실행</t>
         </is>
       </c>
       <c r="C18" s="10" t="inlineStr">
         <is>
-          <t>ENT-DI-02</t>
+          <t>ENT-EX-01.1</t>
         </is>
       </c>
       <c r="D18" s="10" t="inlineStr">
         <is>
-          <t>도메인·AD 열거(계정·신뢰·공유)</t>
+          <t>PowerShell 악용(파일리스 실행)</t>
         </is>
       </c>
       <c r="E18" s="9" t="inlineStr">
         <is>
-          <t>정상 LDAP·AD 질의로 공격 경로(관리자·신뢰·공유) 지도화</t>
+          <t>PowerShell 파일리스 실행으로 시그니처 AV 무력화</t>
         </is>
       </c>
       <c r="F18" s="12" t="inlineStr">
@@ -6444,7 +6444,7 @@
       </c>
       <c r="K18" s="8" t="inlineStr">
         <is>
-          <t>정상 인증 위장 · 서명된 정상 도구 악용</t>
+          <t>파일리스·인메모리 · 서명된 정상 도구 악용</t>
         </is>
       </c>
       <c r="L18" s="9" t="n">
@@ -6457,7 +6457,7 @@
       </c>
       <c r="N18" s="9" t="inlineStr">
         <is>
-          <t>AD 질의·열거를 감사하고 공격 경로(관리자·신뢰)를 정리·최소화(NIST AC-6·AU-6)</t>
+          <t>스크립트 로깅·제약 언어 모드·서명 정책과 최소 기능 원칙을 적용(NIST CM-7·SI-4)</t>
         </is>
       </c>
     </row>
@@ -6467,22 +6467,22 @@
       </c>
       <c r="B19" s="9" t="inlineStr">
         <is>
-          <t>[LM] 측면 이동</t>
+          <t>[DI] 탐색</t>
         </is>
       </c>
       <c r="C19" s="10" t="inlineStr">
         <is>
-          <t>ENT-LM-02</t>
+          <t>ENT-DI-02</t>
         </is>
       </c>
       <c r="D19" s="10" t="inlineStr">
         <is>
-          <t>대체 인증 자료 사용(Pass-the-Hash·Pass-the-Ticket)</t>
+          <t>도메인·AD 열거(계정·신뢰·공유)</t>
         </is>
       </c>
       <c r="E19" s="9" t="inlineStr">
         <is>
-          <t>대체 인증 자료(PtH·PtT)로 평문 없이 인증해 확산</t>
+          <t>정상 LDAP·AD 질의로 공격 경로(관리자·신뢰·공유) 지도화</t>
         </is>
       </c>
       <c r="F19" s="12" t="inlineStr">
@@ -6490,11 +6490,7 @@
           <t>높음</t>
         </is>
       </c>
-      <c r="G19" s="8" t="inlineStr">
-        <is>
-          <t>경계</t>
-        </is>
-      </c>
+      <c r="G19" s="8" t="inlineStr"/>
       <c r="H19" s="8" t="inlineStr">
         <is>
           <t>상</t>
@@ -6512,7 +6508,7 @@
       </c>
       <c r="K19" s="8" t="inlineStr">
         <is>
-          <t>정상 인증 위장</t>
+          <t>정상 인증 위장 · 서명된 정상 도구 악용</t>
         </is>
       </c>
       <c r="L19" s="9" t="n">
@@ -6520,12 +6516,12 @@
       </c>
       <c r="M19" s="9" t="inlineStr">
         <is>
-          <t>[실제 사고] APT28 인접 네트워크(Nearest Neighbor) 무선 경유 침투(2024-11) (ENI-002)</t>
+          <t>[실제 사고] Black Basta 사람 운영 랜섬웨어(LotL·BYOVD·AD 확산)(2024-05) (ENI-012)</t>
         </is>
       </c>
       <c r="N19" s="9" t="inlineStr">
         <is>
-          <t>특권 분리·로컬 관리자 암호 고유화(LAPS)·티켓 수명 축소와 재사용 탐지를 적용(NIST IA-2·AC-6)</t>
+          <t>AD 질의·열거를 감사하고 공격 경로(관리자·신뢰)를 정리·최소화(NIST AC-6·AU-6)</t>
         </is>
       </c>
     </row>
@@ -6535,22 +6531,22 @@
       </c>
       <c r="B20" s="9" t="inlineStr">
         <is>
-          <t>[C2] 명령·제어</t>
+          <t>[LM] 측면 이동</t>
         </is>
       </c>
       <c r="C20" s="10" t="inlineStr">
         <is>
-          <t>ENT-C2-01.2</t>
+          <t>ENT-LM-02</t>
         </is>
       </c>
       <c r="D20" s="10" t="inlineStr">
         <is>
-          <t>응용 계층 프로토콜(HTTPS) C2</t>
+          <t>대체 인증 자료 사용(Pass-the-Hash·Pass-the-Ticket)</t>
         </is>
       </c>
       <c r="E20" s="9" t="inlineStr">
         <is>
-          <t>응용 계층 프로토콜(HTTPS) C2로 포트·프로토콜 통제 통과</t>
+          <t>대체 인증 자료(PtH·PtT)로 평문 없이 인증해 확산</t>
         </is>
       </c>
       <c r="F20" s="12" t="inlineStr">
@@ -6580,20 +6576,20 @@
       </c>
       <c r="K20" s="8" t="inlineStr">
         <is>
-          <t>암호화·정상 채널 은닉</t>
+          <t>정상 인증 위장</t>
         </is>
       </c>
       <c r="L20" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M20" s="9" t="inlineStr">
         <is>
-          <t>[실제 사고] Operation MORPHEUS — 불법 복제 Cobalt Strike 인프라 국제 단속(2024-07) (ENI-018)</t>
+          <t>[실제 사고] APT28 인접 네트워크(Nearest Neighbor) 무선 경유 침투(2024-11) (ENI-002)</t>
         </is>
       </c>
       <c r="N20" s="9" t="inlineStr">
         <is>
-          <t>웹 프록시·egress 통제·목적지 평판과 비컨 탐지를 적용(NIST SC-7·AU-6)</t>
+          <t>특권 분리·로컬 관리자 암호 고유화(LAPS)·티켓 수명 축소와 재사용 탐지를 적용(NIST IA-2·AC-6)</t>
         </is>
       </c>
     </row>
@@ -6603,22 +6599,22 @@
       </c>
       <c r="B21" s="9" t="inlineStr">
         <is>
-          <t>[DE] 방어 회피</t>
+          <t>[C2] 명령·제어</t>
         </is>
       </c>
       <c r="C21" s="10" t="inlineStr">
         <is>
-          <t>ENT-DE-03</t>
+          <t>ENT-C2-01.2</t>
         </is>
       </c>
       <c r="D21" s="10" t="inlineStr">
         <is>
-          <t>지표 삭제(이벤트 로그·파일 삭제)</t>
+          <t>응용 계층 프로토콜(HTTPS) C2</t>
         </is>
       </c>
       <c r="E21" s="9" t="inlineStr">
         <is>
-          <t>이벤트 로그·파일 삭제로 레거시 SIEM 탐지·분석 무력화</t>
+          <t>응용 계층 프로토콜(HTTPS) C2로 포트·프로토콜 통제 통과</t>
         </is>
       </c>
       <c r="F21" s="12" t="inlineStr">
@@ -6648,7 +6644,7 @@
       </c>
       <c r="K21" s="8" t="inlineStr">
         <is>
-          <t>시그니처 회피</t>
+          <t>암호화·정상 채널 은닉</t>
         </is>
       </c>
       <c r="L21" s="9" t="n">
@@ -6656,12 +6652,12 @@
       </c>
       <c r="M21" s="9" t="inlineStr">
         <is>
-          <t>[실제 사고] Volt Typhoon의 LotL 기반 핵심 기반시설 장기 침투(2024-02) (ENI-001)</t>
+          <t>[실제 사고] Operation MORPHEUS — 불법 복제 Cobalt Strike 인프라 국제 단속(2024-07) (ENI-018)</t>
         </is>
       </c>
       <c r="N21" s="9" t="inlineStr">
         <is>
-          <t>원격·불변 로그 전송과 로그 삭제 방지·보존 정책을 적용(NIST AU-9·AU-6)</t>
+          <t>웹 프록시·egress 통제·목적지 평판과 비컨 탐지를 적용(NIST SC-7·AU-6)</t>
         </is>
       </c>
     </row>
@@ -9002,7 +8998,7 @@
       </c>
       <c r="E3" s="17" t="inlineStr">
         <is>
-          <t>ENT-DE-01.1 보안 도구 무력화(EDR 변조·BYOVD EDR 킬러) [5]</t>
+          <t>ENT-DE-01.1 보안 도구 무력화(EDR 변조·BYOVD EDR 킬러) [7]</t>
         </is>
       </c>
       <c r="F3" s="17" t="inlineStr">
@@ -9037,14 +9033,14 @@
       </c>
       <c r="L3" s="16" t="inlineStr">
         <is>
-          <t>ENT-IM-01 데이터 암호화(사람 운영 랜섬웨어) [7]</t>
+          <t>ENT-IM-01 데이터 암호화(사람 운영 랜섬웨어) [8]</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="17" t="inlineStr">
         <is>
-          <t>ENT-IA-01 인터넷 노출 경계·엣지 장비 취약점 악용(빠른 n-day·0-day) [8]</t>
+          <t>ENT-IA-01 인터넷 노출 경계·엣지 장비 취약점 악용(빠른 n-day·0-day) [10]</t>
         </is>
       </c>
       <c r="B4" s="18" t="inlineStr">
@@ -9064,7 +9060,7 @@
       </c>
       <c r="E4" s="17" t="inlineStr">
         <is>
-          <t>ENT-DE-01.2 취약·악성 드라이버 로드(커널) [2]</t>
+          <t>ENT-DE-01.2 취약·악성 드라이버 로드(커널) [3]</t>
         </is>
       </c>
       <c r="F4" s="18" t="inlineStr">
@@ -9126,7 +9122,7 @@
       </c>
       <c r="E5" s="17" t="inlineStr">
         <is>
-          <t>ENT-DE-03 지표 삭제(이벤트 로그·파일 삭제) [1]</t>
+          <t>ENT-DE-03 지표 삭제(이벤트 로그·파일 삭제) [2]</t>
         </is>
       </c>
       <c r="F5" s="18" t="inlineStr">
@@ -9317,7 +9313,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>사고 DB 24건 + ATT&amp;CK v19.2 + CISA KEV + LOLBAS·LOLDrivers | 2026-10-27</t>
+          <t>사고 DB 28건 + ATT&amp;CK v19.2 + CISA KEV + LOLBAS·LOLDrivers | 2026-10-27</t>
         </is>
       </c>
     </row>
@@ -9673,7 +9669,7 @@
       </c>
       <c r="AD5" s="9" t="inlineStr">
         <is>
-          <t>실제 사고 8건(최근 0, 서로 다른 행위자·캠페인 8) · 빈발 지수 중(ATT&amp;CK 주체 75) · KEV O · 정부 경보 0 · 위협인텔 0 · 실증 0</t>
+          <t>실제 사고 10건(최근 2, 서로 다른 행위자·캠페인 9) · 빈발 지수 중(ATT&amp;CK 주체 75) · KEV O · 정부 경보 0 · 위협인텔 0 · 실증 0</t>
         </is>
       </c>
       <c r="AE5" s="9" t="inlineStr">
@@ -9682,10 +9678,10 @@
         </is>
       </c>
       <c r="AF5" s="9" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="AG5" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AH5" s="9" t="n">
         <v>0</v>
@@ -9700,12 +9696,12 @@
       </c>
       <c r="AK5" s="9" t="inlineStr">
         <is>
-          <t>ENI-001, ENI-003, ENI-004, ENI-005, ENI-006, ENI-007, ENI-008, ENI-010</t>
+          <t>ENI-001, ENI-003, ENI-004, ENI-005, ENI-006, ENI-007, ENI-008, ENI-010, ENI-034, ENI-035</t>
         </is>
       </c>
       <c r="AL5" s="9" t="inlineStr">
         <is>
-          <t>내부 접근 확보 6 · 측면 이동·확산 2 · 데이터 유출 2 · 금전 피해 2</t>
+          <t>내부 접근 확보 7 · 데이터 유출 4 · 측면 이동·확산 2 · 금전 피해 2</t>
         </is>
       </c>
       <c r="AM5" s="9" t="inlineStr">
@@ -10508,7 +10504,7 @@
       </c>
       <c r="AB10" s="9" t="inlineStr"/>
       <c r="AC10" s="8" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="AD10" s="9" t="inlineStr">
         <is>
@@ -12405,7 +12401,7 @@
       </c>
       <c r="AD22" s="9" t="inlineStr">
         <is>
-          <t>실제 사고 5건(최근 1, 서로 다른 행위자·캠페인 5) · 빈발 지수 상(ATT&amp;CK 주체 155) · KEV - · 정부 경보 1 · 위협인텔 0 · 실증 0</t>
+          <t>실제 사고 7건(최근 3, 서로 다른 행위자·캠페인 7) · 빈발 지수 상(ATT&amp;CK 주체 155) · KEV - · 정부 경보 1 · 위협인텔 0 · 실증 0</t>
         </is>
       </c>
       <c r="AE22" s="9" t="inlineStr">
@@ -12414,10 +12410,10 @@
         </is>
       </c>
       <c r="AF22" s="9" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="AG22" s="9" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AH22" s="9" t="n">
         <v>1</v>
@@ -12432,13 +12428,13 @@
       </c>
       <c r="AK22" s="9" t="inlineStr">
         <is>
-          <t>ENI-012, ENI-013, ENI-015, ENI-016, ENI-017
+          <t>ENI-012, ENI-013, ENI-015, ENI-016, ENI-017, ENI-036, ENI-037
 정부 경보: ENI-030</t>
         </is>
       </c>
       <c r="AL22" s="9" t="inlineStr">
         <is>
-          <t>랜섬·암호화 4 · 데이터 유출 2 · 자격증명·비밀 탈취 2 · 내부 접근 확보 2</t>
+          <t>랜섬·암호화 6 · 데이터 유출 2 · 자격증명·비밀 탈취 2 · 내부 접근 확보 2</t>
         </is>
       </c>
       <c r="AM22" s="9" t="inlineStr">
@@ -12569,11 +12565,11 @@
       </c>
       <c r="AB23" s="9" t="inlineStr"/>
       <c r="AC23" s="8" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AD23" s="9" t="inlineStr">
         <is>
-          <t>실제 사고 2건(최근 1, 서로 다른 행위자·캠페인 2) · 빈발 지수 상(ATT&amp;CK 주체 140) · KEV - · 정부 경보 0 · 위협인텔 0 · 실증 0</t>
+          <t>실제 사고 3건(최근 2, 서로 다른 행위자·캠페인 3) · 빈발 지수 상(ATT&amp;CK 주체 140) · KEV - · 정부 경보 0 · 위협인텔 0 · 실증 0</t>
         </is>
       </c>
       <c r="AE23" s="9" t="inlineStr">
@@ -12582,10 +12578,10 @@
         </is>
       </c>
       <c r="AF23" s="9" t="n">
+        <v>3</v>
+      </c>
+      <c r="AG23" s="9" t="n">
         <v>2</v>
-      </c>
-      <c r="AG23" s="9" t="n">
-        <v>1</v>
       </c>
       <c r="AH23" s="9" t="n">
         <v>0</v>
@@ -12600,12 +12596,12 @@
       </c>
       <c r="AK23" s="9" t="inlineStr">
         <is>
-          <t>ENI-016, ENI-017</t>
+          <t>ENI-016, ENI-017, ENI-036</t>
         </is>
       </c>
       <c r="AL23" s="9" t="inlineStr">
         <is>
-          <t>랜섬·암호화 1 · 자격증명·비밀 탈취 1 · 내부 접근 확보 1</t>
+          <t>랜섬·암호화 2 · 자격증명·비밀 탈취 1 · 내부 접근 확보 1</t>
         </is>
       </c>
       <c r="AM23" s="9" t="inlineStr">
@@ -12731,17 +12727,13 @@
           <t>높음</t>
         </is>
       </c>
-      <c r="AB24" s="9" t="inlineStr">
-        <is>
-          <t>경계</t>
-        </is>
-      </c>
+      <c r="AB24" s="9" t="inlineStr"/>
       <c r="AC24" s="8" t="n">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="AD24" s="9" t="inlineStr">
         <is>
-          <t>실제 사고 1건(최근 0, 서로 다른 행위자·캠페인 1) · 빈발 지수 상(ATT&amp;CK 주체 335) · KEV - · 정부 경보 0 · 위협인텔 0 · 실증 0</t>
+          <t>실제 사고 2건(최근 1, 서로 다른 행위자·캠페인 2) · 빈발 지수 상(ATT&amp;CK 주체 335) · KEV - · 정부 경보 0 · 위협인텔 0 · 실증 0</t>
         </is>
       </c>
       <c r="AE24" s="9" t="inlineStr">
@@ -12750,10 +12742,10 @@
         </is>
       </c>
       <c r="AF24" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="AG24" s="9" t="n">
         <v>1</v>
-      </c>
-      <c r="AG24" s="9" t="n">
-        <v>0</v>
       </c>
       <c r="AH24" s="9" t="n">
         <v>0</v>
@@ -12768,12 +12760,12 @@
       </c>
       <c r="AK24" s="9" t="inlineStr">
         <is>
-          <t>ENI-001</t>
+          <t>ENI-001, ENI-034</t>
         </is>
       </c>
       <c r="AL24" s="9" t="inlineStr">
         <is>
-          <t>내부 접근 확보 1 · 첩보·감시 1 · 측면 이동·확산 1</t>
+          <t>내부 접근 확보 2 · 첩보·감시 1 · 측면 이동·확산 1 · 데이터 유출 1</t>
         </is>
       </c>
       <c r="AM24" s="9" t="inlineStr">
@@ -14470,7 +14462,7 @@
       </c>
       <c r="AB35" s="9" t="inlineStr"/>
       <c r="AC35" s="8" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AD35" s="9" t="inlineStr">
         <is>
@@ -14957,7 +14949,7 @@
         </is>
       </c>
       <c r="AC38" s="8" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AD38" s="9" t="inlineStr">
         <is>
@@ -15925,7 +15917,7 @@
         </is>
       </c>
       <c r="AC44" s="8" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AD44" s="9" t="inlineStr">
         <is>
@@ -17065,7 +17057,7 @@
       </c>
       <c r="AD51" s="9" t="inlineStr">
         <is>
-          <t>실제 사고 7건(최근 0, 서로 다른 행위자·캠페인 7) · 빈발 지수 중(ATT&amp;CK 주체 85) · KEV - · 정부 경보 0 · 위협인텔 0 · 실증 0</t>
+          <t>실제 사고 8건(최근 1, 서로 다른 행위자·캠페인 7) · 빈발 지수 중(ATT&amp;CK 주체 85) · KEV - · 정부 경보 0 · 위협인텔 0 · 실증 0</t>
         </is>
       </c>
       <c r="AE51" s="9" t="inlineStr">
@@ -17074,10 +17066,10 @@
         </is>
       </c>
       <c r="AF51" s="9" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AG51" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AH51" s="9" t="n">
         <v>0</v>
@@ -17092,12 +17084,12 @@
       </c>
       <c r="AK51" s="9" t="inlineStr">
         <is>
-          <t>ENI-009, ENI-011, ENI-012, ENI-013, ENI-014, ENI-015, ENI-022</t>
+          <t>ENI-009, ENI-011, ENI-012, ENI-013, ENI-014, ENI-015, ENI-022, ENI-037</t>
         </is>
       </c>
       <c r="AL51" s="9" t="inlineStr">
         <is>
-          <t>랜섬·암호화 7 · 내부 접근 확보 3 · 데이터 유출 3 · 서비스 중단 2</t>
+          <t>랜섬·암호화 8 · 내부 접근 확보 3 · 데이터 유출 3 · 서비스 중단 2</t>
         </is>
       </c>
       <c r="AM51" s="9" t="inlineStr">
@@ -18003,7 +17995,7 @@
         </is>
       </c>
       <c r="O3" s="8" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="P3" s="8" t="n">
         <v>75</v>
@@ -18436,7 +18428,7 @@
         </is>
       </c>
       <c r="M8" s="8" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="N8" s="27" t="inlineStr">
         <is>
@@ -19483,7 +19475,7 @@
         </is>
       </c>
       <c r="O20" s="8" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="P20" s="8" t="n">
         <v>155</v>
@@ -19562,7 +19554,7 @@
         </is>
       </c>
       <c r="M21" s="8" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="N21" s="27" t="inlineStr">
         <is>
@@ -19570,7 +19562,7 @@
         </is>
       </c>
       <c r="O21" s="8" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="P21" s="8" t="n">
         <v>140</v>
@@ -19649,7 +19641,7 @@
         </is>
       </c>
       <c r="M22" s="8" t="n">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="N22" s="27" t="inlineStr">
         <is>
@@ -19657,7 +19649,7 @@
         </is>
       </c>
       <c r="O22" s="8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="P22" s="8" t="n">
         <v>335</v>
@@ -20595,7 +20587,7 @@
         </is>
       </c>
       <c r="M33" s="8" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="N33" s="27" t="inlineStr">
         <is>
@@ -20854,7 +20846,7 @@
         </is>
       </c>
       <c r="M36" s="8" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="N36" s="27" t="inlineStr">
         <is>
@@ -21375,7 +21367,7 @@
         </is>
       </c>
       <c r="M42" s="8" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="N42" s="27" t="inlineStr">
         <is>
@@ -21986,7 +21978,7 @@
         </is>
       </c>
       <c r="O49" s="8" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="P49" s="8" t="n">
         <v>85</v>
@@ -22502,7 +22494,7 @@
         <v>0</v>
       </c>
       <c r="N2" s="9" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="O2" s="9" t="inlineStr">
         <is>
@@ -22730,7 +22722,7 @@
         <v>0</v>
       </c>
       <c r="N6" s="9" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="O6" s="9" t="inlineStr">
         <is>
@@ -23127,7 +23119,7 @@
         <v>0</v>
       </c>
       <c r="N13" s="9" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="O13" s="9" t="inlineStr">
         <is>
@@ -24223,7 +24215,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N25"/>
+  <dimension ref="A1:N29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
@@ -24317,27 +24309,27 @@
     <row r="2">
       <c r="A2" s="9" t="inlineStr">
         <is>
-          <t>ENI-030</t>
+          <t>ENI-036</t>
         </is>
       </c>
       <c r="B2" s="9" t="inlineStr">
         <is>
-          <t>정부 경보 — 사람 운영 랜섬웨어의 레거시 우회 공통 TTP</t>
+          <t>Reynolds 랜섬웨어의 취약 드라이버 번들(BYOVD)</t>
         </is>
       </c>
       <c r="C2" s="9" t="inlineStr">
         <is>
-          <t>2025-03</t>
+          <t>2026-02</t>
         </is>
       </c>
       <c r="D2" s="9" t="inlineStr">
         <is>
-          <t>정부 경보</t>
+          <t>캠페인</t>
         </is>
       </c>
       <c r="E2" s="9" t="inlineStr">
         <is>
-          <t>정부 경보</t>
+          <t>실제 사고</t>
         </is>
       </c>
       <c r="F2" s="9" t="inlineStr">
@@ -24352,7 +24344,7 @@
       </c>
       <c r="H2" s="9" t="inlineStr">
         <is>
-          <t>다수 랜섬웨어</t>
+          <t>Reynolds(신규 랜섬웨어)</t>
         </is>
       </c>
       <c r="I2" s="9" t="inlineStr">
@@ -24362,41 +24354,41 @@
       </c>
       <c r="J2" s="9" t="inlineStr">
         <is>
-          <t>랜섬·암호화 · 데이터 유출</t>
+          <t>랜섬·암호화</t>
         </is>
       </c>
       <c r="K2" s="9" t="inlineStr"/>
       <c r="L2" s="9" t="inlineStr">
         <is>
-          <t>ENT-IA-02, ENT-EX-03, ENT-CA-01.1, ENT-DI-02, ENT-DE-01.1, ENT-IM-02, ENT-IM-05</t>
+          <t>ENT-DE-01.1, ENT-DE-01.2</t>
         </is>
       </c>
       <c r="M2" s="9" t="inlineStr"/>
       <c r="N2" s="9" t="inlineStr">
         <is>
-          <t>CISA·FBI·MS-ISAC(2023) StopRansomware Guide(2023 개정) | https://www.cisa.gov/resources-tools/resources/stopransomware-guide</t>
+          <t>Symantec(2026) Reynolds — defense evasion embedded in ransomware payload | https://www.security.com/threat-intelligence/black-basta-ransomware-byovd</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="9" t="inlineStr">
         <is>
-          <t>ENI-017</t>
+          <t>ENI-035</t>
         </is>
       </c>
       <c r="B3" s="9" t="inlineStr">
         <is>
-          <t>서명된 취약 드라이버 대량 변종 캠페인(TrueSight 등)</t>
+          <t>롯데카드 결제 서버 웹셸 침해·고객정보 유출(국내)</t>
         </is>
       </c>
       <c r="C3" s="9" t="inlineStr">
         <is>
-          <t>2025-01</t>
+          <t>2025-08</t>
         </is>
       </c>
       <c r="D3" s="9" t="inlineStr">
         <is>
-          <t>캠페인</t>
+          <t>사고</t>
         </is>
       </c>
       <c r="E3" s="9" t="inlineStr">
@@ -24406,61 +24398,61 @@
       </c>
       <c r="F3" s="9" t="inlineStr">
         <is>
-          <t>글로벌</t>
+          <t>한국</t>
         </is>
       </c>
       <c r="G3" s="9" t="inlineStr">
         <is>
-          <t>다부문</t>
+          <t>금융·서비스</t>
         </is>
       </c>
       <c r="H3" s="9" t="inlineStr">
         <is>
-          <t>다수(랜섬웨어·국가배후)</t>
+          <t>미상</t>
         </is>
       </c>
       <c r="I3" s="9" t="inlineStr">
         <is>
-          <t>랜섬웨어 · 국가배후</t>
+          <t>사이버범죄</t>
         </is>
       </c>
       <c r="J3" s="9" t="inlineStr">
         <is>
-          <t>내부 접근 확보</t>
+          <t>데이터 유출 · 자격증명·비밀 탈취</t>
         </is>
       </c>
       <c r="K3" s="9" t="inlineStr"/>
       <c r="L3" s="9" t="inlineStr">
         <is>
-          <t>ENT-DE-01.2, ENT-DE-01.1</t>
+          <t>ENT-IA-01</t>
         </is>
       </c>
       <c r="M3" s="9" t="inlineStr"/>
       <c r="N3" s="9" t="inlineStr">
         <is>
-          <t>Check Point(2025) The TrueSight driver BYOVD campaign | https://research.checkpoint.com/2025/large-scale-exploitation-of-legacy-driver/</t>
+          <t>금융감독원(2025) 롯데카드 등 금융회사 제재 공시 | https://www.fss.or.kr/fss/bbs/B0000188/list.do?menuNo=200218</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="9" t="inlineStr">
         <is>
-          <t>ENI-010</t>
+          <t>ENI-034</t>
         </is>
       </c>
       <c r="B4" s="9" t="inlineStr">
         <is>
-          <t>Cl0p의 Cleo 파일전송 취약점 대량 악용</t>
+          <t>SK텔레콤 핵심 서버 침해(BPFDoor·장기 잠복, 국내)</t>
         </is>
       </c>
       <c r="C4" s="9" t="inlineStr">
         <is>
-          <t>2024-12</t>
+          <t>2025-04</t>
         </is>
       </c>
       <c r="D4" s="9" t="inlineStr">
         <is>
-          <t>캠페인</t>
+          <t>사고</t>
         </is>
       </c>
       <c r="E4" s="9" t="inlineStr">
@@ -24470,65 +24462,61 @@
       </c>
       <c r="F4" s="9" t="inlineStr">
         <is>
-          <t>글로벌</t>
+          <t>한국</t>
         </is>
       </c>
       <c r="G4" s="9" t="inlineStr">
         <is>
-          <t>다부문</t>
+          <t>통신·미디어</t>
         </is>
       </c>
       <c r="H4" s="9" t="inlineStr">
         <is>
-          <t>Cl0p</t>
+          <t>미상(국가배후 의심)</t>
         </is>
       </c>
       <c r="I4" s="9" t="inlineStr">
         <is>
-          <t>랜섬웨어 · 사이버범죄</t>
+          <t>국가배후</t>
         </is>
       </c>
       <c r="J4" s="9" t="inlineStr">
         <is>
-          <t>데이터 유출 · 금전 피해</t>
-        </is>
-      </c>
-      <c r="K4" s="9" t="inlineStr">
-        <is>
-          <t>CVE-2024-55956</t>
-        </is>
-      </c>
+          <t>데이터 유출 · 내부 접근 확보</t>
+        </is>
+      </c>
+      <c r="K4" s="9" t="inlineStr"/>
       <c r="L4" s="9" t="inlineStr">
         <is>
-          <t>ENT-IA-01, ENT-EF-02, ENT-IM-05</t>
+          <t>ENT-IA-01, ENT-DE-03</t>
         </is>
       </c>
       <c r="M4" s="9" t="inlineStr"/>
       <c r="N4" s="9" t="inlineStr">
         <is>
-          <t>Huntress(2024) Cleo mass exploitation | https://www.huntress.com/blog/threat-advisory-oh-no-cleo-cleo-software-actively-being-exploited-in-the-wild</t>
+          <t>과학기술정보통신부(2025) SKT 침해사고 민관합동조사단 조사결과 | https://www.msit.go.kr/bbs/view.do?sCode=user&amp;mId=113&amp;mPid=112&amp;bbsSeqNo=94&amp;nttSeqNo=3185685</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="9" t="inlineStr">
         <is>
-          <t>ENI-002</t>
+          <t>ENI-037</t>
         </is>
       </c>
       <c r="B5" s="9" t="inlineStr">
         <is>
-          <t>APT28 인접 네트워크(Nearest Neighbor) 무선 경유 침투</t>
+          <t>Akira 랜섬웨어의 무방비 웹캠 경유 암호화(EDR 우회)</t>
         </is>
       </c>
       <c r="C5" s="9" t="inlineStr">
         <is>
-          <t>2024-11</t>
+          <t>2025-03</t>
         </is>
       </c>
       <c r="D5" s="9" t="inlineStr">
         <is>
-          <t>캠페인</t>
+          <t>사고</t>
         </is>
       </c>
       <c r="E5" s="9" t="inlineStr">
@@ -24538,70 +24526,66 @@
       </c>
       <c r="F5" s="9" t="inlineStr">
         <is>
-          <t>미국</t>
+          <t>글로벌</t>
         </is>
       </c>
       <c r="G5" s="9" t="inlineStr">
         <is>
-          <t>정부·군</t>
+          <t>다부문</t>
         </is>
       </c>
       <c r="H5" s="9" t="inlineStr">
         <is>
-          <t>APT28(러시아 GRU 연계)</t>
+          <t>Akira</t>
         </is>
       </c>
       <c r="I5" s="9" t="inlineStr">
         <is>
-          <t>국가배후</t>
+          <t>랜섬웨어</t>
         </is>
       </c>
       <c r="J5" s="9" t="inlineStr">
         <is>
-          <t>내부 접근 확보 · 첩보·감시</t>
+          <t>랜섬·암호화</t>
         </is>
       </c>
       <c r="K5" s="9" t="inlineStr"/>
       <c r="L5" s="9" t="inlineStr">
         <is>
-          <t>ENT-IA-02, ENT-LM-01, ENT-LM-02, ENT-CA-03</t>
-        </is>
-      </c>
-      <c r="M5" s="9" t="inlineStr">
-        <is>
-          <t>C0051, G0007</t>
-        </is>
-      </c>
+          <t>ENT-IM-01, ENT-DE-01.1</t>
+        </is>
+      </c>
+      <c r="M5" s="9" t="inlineStr"/>
       <c r="N5" s="9" t="inlineStr">
         <is>
-          <t>Volexity(2024) The Nearest Neighbor Attack | https://www.volexity.com/blog/2024/11/22/the-nearest-neighbor-attack-how-a-russian-apt-weaponized-nearby-wi-fi-networks/</t>
+          <t>S-RM(2025) Camera off — Akira deploys ransomware via webcam | https://www.s-rminform.com/latest-thinking/camera-off-akira-deploys-ransomware-via-webcam</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="9" t="inlineStr">
         <is>
-          <t>ENI-016</t>
+          <t>ENI-030</t>
         </is>
       </c>
       <c r="B6" s="9" t="inlineStr">
         <is>
-          <t>RansomHub 제휴의 EDR 킬러(BYOVD) 사용</t>
+          <t>정부 경보 — 사람 운영 랜섬웨어의 레거시 우회 공통 TTP</t>
         </is>
       </c>
       <c r="C6" s="9" t="inlineStr">
         <is>
-          <t>2024-08</t>
+          <t>2025-03</t>
         </is>
       </c>
       <c r="D6" s="9" t="inlineStr">
         <is>
-          <t>캠페인</t>
+          <t>정부 경보</t>
         </is>
       </c>
       <c r="E6" s="9" t="inlineStr">
         <is>
-          <t>실제 사고</t>
+          <t>정부 경보</t>
         </is>
       </c>
       <c r="F6" s="9" t="inlineStr">
@@ -24616,7 +24600,7 @@
       </c>
       <c r="H6" s="9" t="inlineStr">
         <is>
-          <t>RansomHub 제휴(Scattered Spider 등 공유)</t>
+          <t>다수 랜섬웨어</t>
         </is>
       </c>
       <c r="I6" s="9" t="inlineStr">
@@ -24626,40 +24610,36 @@
       </c>
       <c r="J6" s="9" t="inlineStr">
         <is>
-          <t>랜섬·암호화 · 자격증명·비밀 탈취</t>
+          <t>랜섬·암호화 · 데이터 유출</t>
         </is>
       </c>
       <c r="K6" s="9" t="inlineStr"/>
       <c r="L6" s="9" t="inlineStr">
         <is>
-          <t>ENT-DE-01.1, ENT-DE-01.2, ENT-PV-04</t>
-        </is>
-      </c>
-      <c r="M6" s="9" t="inlineStr">
-        <is>
-          <t>S1212</t>
-        </is>
-      </c>
+          <t>ENT-IA-02, ENT-EX-03, ENT-CA-01.1, ENT-DI-02, ENT-DE-01.1, ENT-IM-02, ENT-IM-05</t>
+        </is>
+      </c>
+      <c r="M6" s="9" t="inlineStr"/>
       <c r="N6" s="9" t="inlineStr">
         <is>
-          <t>Sophos(2024) EDRKillShifter — RansomHub affiliate BYOVD tool | https://news.sophos.com/en-us/2024/08/14/edr-kill-shifter/</t>
+          <t>CISA·FBI·MS-ISAC(2023) StopRansomware Guide(2023 개정) | https://www.cisa.gov/resources-tools/resources/stopransomware-guide</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="9" t="inlineStr">
         <is>
-          <t>ENI-018</t>
+          <t>ENI-017</t>
         </is>
       </c>
       <c r="B7" s="9" t="inlineStr">
         <is>
-          <t>Operation MORPHEUS — 불법 복제 Cobalt Strike 인프라 국제 단속</t>
+          <t>서명된 취약 드라이버 대량 변종 캠페인(TrueSight 등)</t>
         </is>
       </c>
       <c r="C7" s="9" t="inlineStr">
         <is>
-          <t>2024-07</t>
+          <t>2025-01</t>
         </is>
       </c>
       <c r="D7" s="9" t="inlineStr">
@@ -24694,40 +24674,36 @@
       </c>
       <c r="J7" s="9" t="inlineStr">
         <is>
-          <t>내부 접근 확보 · 측면 이동·확산</t>
+          <t>내부 접근 확보</t>
         </is>
       </c>
       <c r="K7" s="9" t="inlineStr"/>
       <c r="L7" s="9" t="inlineStr">
         <is>
-          <t>ENT-PV-01.1, ENT-C2-01.1, ENT-C2-01.2, ENT-C2-04, ENT-C2-05</t>
-        </is>
-      </c>
-      <c r="M7" s="9" t="inlineStr">
-        <is>
-          <t>S0154</t>
-        </is>
-      </c>
+          <t>ENT-DE-01.2, ENT-DE-01.1</t>
+        </is>
+      </c>
+      <c r="M7" s="9" t="inlineStr"/>
       <c r="N7" s="9" t="inlineStr">
         <is>
-          <t>Europol(2024) Global operation targets Cobalt Strike (Operation MORPHEUS) | https://www.europol.europa.eu/media-press/newsroom/news/global-crackdown-tooling-abused-criminals</t>
+          <t>Check Point(2025) The TrueSight driver BYOVD campaign | https://research.checkpoint.com/2025/large-scale-exploitation-of-legacy-driver/</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="9" t="inlineStr">
         <is>
-          <t>ENI-012</t>
+          <t>ENI-010</t>
         </is>
       </c>
       <c r="B8" s="9" t="inlineStr">
         <is>
-          <t>Black Basta 사람 운영 랜섬웨어(LotL·BYOVD·AD 확산)</t>
+          <t>Cl0p의 Cleo 파일전송 취약점 대량 악용</t>
         </is>
       </c>
       <c r="C8" s="9" t="inlineStr">
         <is>
-          <t>2024-05</t>
+          <t>2024-12</t>
         </is>
       </c>
       <c r="D8" s="9" t="inlineStr">
@@ -24747,55 +24723,55 @@
       </c>
       <c r="G8" s="9" t="inlineStr">
         <is>
-          <t>다부문 · 의료·바이오</t>
+          <t>다부문</t>
         </is>
       </c>
       <c r="H8" s="9" t="inlineStr">
         <is>
-          <t>Black Basta</t>
+          <t>Cl0p</t>
         </is>
       </c>
       <c r="I8" s="9" t="inlineStr">
         <is>
-          <t>랜섬웨어</t>
+          <t>랜섬웨어 · 사이버범죄</t>
         </is>
       </c>
       <c r="J8" s="9" t="inlineStr">
         <is>
-          <t>랜섬·암호화 · 데이터 유출 · 자격증명·비밀 탈취</t>
-        </is>
-      </c>
-      <c r="K8" s="9" t="inlineStr"/>
+          <t>데이터 유출 · 금전 피해</t>
+        </is>
+      </c>
+      <c r="K8" s="9" t="inlineStr">
+        <is>
+          <t>CVE-2024-55956</t>
+        </is>
+      </c>
       <c r="L8" s="9" t="inlineStr">
         <is>
-          <t>ENT-EX-01.1, ENT-CA-01.1, ENT-DI-02, ENT-LM-01, ENT-DE-01.1, ENT-IM-01, ENT-IM-02</t>
-        </is>
-      </c>
-      <c r="M8" s="9" t="inlineStr">
-        <is>
-          <t>S1070</t>
-        </is>
-      </c>
+          <t>ENT-IA-01, ENT-EF-02, ENT-IM-05</t>
+        </is>
+      </c>
+      <c r="M8" s="9" t="inlineStr"/>
       <c r="N8" s="9" t="inlineStr">
         <is>
-          <t>CISA(2024) StopRansomware — Black Basta (AA24-131A) | https://www.cisa.gov/news-events/cybersecurity-advisories/aa24-131a</t>
+          <t>Huntress(2024) Cleo mass exploitation | https://www.huntress.com/blog/threat-advisory-oh-no-cleo-cleo-software-actively-being-exploited-in-the-wild</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="9" t="inlineStr">
         <is>
-          <t>ENI-014</t>
+          <t>ENI-002</t>
         </is>
       </c>
       <c r="B9" s="9" t="inlineStr">
         <is>
-          <t>Akira 랜섬웨어의 MFA 미적용 VPN 경유 침투</t>
+          <t>APT28 인접 네트워크(Nearest Neighbor) 무선 경유 침투</t>
         </is>
       </c>
       <c r="C9" s="9" t="inlineStr">
         <is>
-          <t>2024-04</t>
+          <t>2024-11</t>
         </is>
       </c>
       <c r="D9" s="9" t="inlineStr">
@@ -24810,60 +24786,60 @@
       </c>
       <c r="F9" s="9" t="inlineStr">
         <is>
-          <t>글로벌</t>
+          <t>미국</t>
         </is>
       </c>
       <c r="G9" s="9" t="inlineStr">
         <is>
-          <t>다부문</t>
+          <t>정부·군</t>
         </is>
       </c>
       <c r="H9" s="9" t="inlineStr">
         <is>
-          <t>Akira</t>
+          <t>APT28(러시아 GRU 연계)</t>
         </is>
       </c>
       <c r="I9" s="9" t="inlineStr">
         <is>
-          <t>랜섬웨어</t>
+          <t>국가배후</t>
         </is>
       </c>
       <c r="J9" s="9" t="inlineStr">
         <is>
-          <t>랜섬·암호화 · 데이터 유출</t>
+          <t>내부 접근 확보 · 첩보·감시</t>
         </is>
       </c>
       <c r="K9" s="9" t="inlineStr"/>
       <c r="L9" s="9" t="inlineStr">
         <is>
-          <t>ENT-IA-02, ENT-CA-01.1, ENT-LM-01, ENT-IM-01</t>
+          <t>ENT-IA-02, ENT-LM-01, ENT-LM-02, ENT-CA-03</t>
         </is>
       </c>
       <c r="M9" s="9" t="inlineStr">
         <is>
-          <t>G1024</t>
+          <t>C0051, G0007</t>
         </is>
       </c>
       <c r="N9" s="9" t="inlineStr">
         <is>
-          <t>CISA(2024) StopRansomware — Akira (AA24-109A) | https://www.cisa.gov/news-events/cybersecurity-advisories/aa24-109a</t>
+          <t>Volexity(2024) The Nearest Neighbor Attack | https://www.volexity.com/blog/2024/11/22/the-nearest-neighbor-attack-how-a-russian-apt-weaponized-nearby-wi-fi-networks/</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="9" t="inlineStr">
         <is>
-          <t>ENI-008</t>
+          <t>ENI-016</t>
         </is>
       </c>
       <c r="B10" s="9" t="inlineStr">
         <is>
-          <t>Palo Alto PAN-OS GlobalProtect 0-day 악용</t>
+          <t>RansomHub 제휴의 EDR 킬러(BYOVD) 사용</t>
         </is>
       </c>
       <c r="C10" s="9" t="inlineStr">
         <is>
-          <t>2024-04</t>
+          <t>2024-08</t>
         </is>
       </c>
       <c r="D10" s="9" t="inlineStr">
@@ -24888,50 +24864,50 @@
       </c>
       <c r="H10" s="9" t="inlineStr">
         <is>
-          <t>미상(국가배후 추정)</t>
+          <t>RansomHub 제휴(Scattered Spider 등 공유)</t>
         </is>
       </c>
       <c r="I10" s="9" t="inlineStr">
         <is>
-          <t>국가배후 · 접근 브로커</t>
+          <t>랜섬웨어</t>
         </is>
       </c>
       <c r="J10" s="9" t="inlineStr">
         <is>
-          <t>내부 접근 확보</t>
-        </is>
-      </c>
-      <c r="K10" s="9" t="inlineStr">
-        <is>
-          <t>CVE-2024-3400</t>
-        </is>
-      </c>
+          <t>랜섬·암호화 · 자격증명·비밀 탈취</t>
+        </is>
+      </c>
+      <c r="K10" s="9" t="inlineStr"/>
       <c r="L10" s="9" t="inlineStr">
         <is>
-          <t>ENT-IA-01</t>
-        </is>
-      </c>
-      <c r="M10" s="9" t="inlineStr"/>
+          <t>ENT-DE-01.1, ENT-DE-01.2, ENT-PV-04</t>
+        </is>
+      </c>
+      <c r="M10" s="9" t="inlineStr">
+        <is>
+          <t>S1212</t>
+        </is>
+      </c>
       <c r="N10" s="9" t="inlineStr">
         <is>
-          <t>Unit 42(2024) Operation MidnightEclipse — PAN-OS CVE-2024-3400 | https://unit42.paloaltonetworks.com/cve-2024-3400/</t>
+          <t>Sophos(2024) EDRKillShifter — RansomHub affiliate BYOVD tool | https://news.sophos.com/en-us/2024/08/14/edr-kill-shifter/</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="9" t="inlineStr">
         <is>
-          <t>ENI-009</t>
+          <t>ENI-018</t>
         </is>
       </c>
       <c r="B11" s="9" t="inlineStr">
         <is>
-          <t>ConnectWise ScreenConnect 취약점 경유 랜섬웨어</t>
+          <t>Operation MORPHEUS — 불법 복제 Cobalt Strike 인프라 국제 단속</t>
         </is>
       </c>
       <c r="C11" s="9" t="inlineStr">
         <is>
-          <t>2024-02</t>
+          <t>2024-07</t>
         </is>
       </c>
       <c r="D11" s="9" t="inlineStr">
@@ -24956,50 +24932,50 @@
       </c>
       <c r="H11" s="9" t="inlineStr">
         <is>
-          <t>다수 랜섬웨어·브로커</t>
+          <t>다수(랜섬웨어·국가배후)</t>
         </is>
       </c>
       <c r="I11" s="9" t="inlineStr">
         <is>
-          <t>랜섬웨어 · 접근 브로커</t>
+          <t>랜섬웨어 · 국가배후</t>
         </is>
       </c>
       <c r="J11" s="9" t="inlineStr">
         <is>
-          <t>내부 접근 확보 · 랜섬·암호화</t>
-        </is>
-      </c>
-      <c r="K11" s="9" t="inlineStr">
-        <is>
-          <t>CVE-2024-1709</t>
-        </is>
-      </c>
+          <t>내부 접근 확보 · 측면 이동·확산</t>
+        </is>
+      </c>
+      <c r="K11" s="9" t="inlineStr"/>
       <c r="L11" s="9" t="inlineStr">
         <is>
-          <t>ENT-IA-02, ENT-IA-05, ENT-IM-01</t>
-        </is>
-      </c>
-      <c r="M11" s="9" t="inlineStr"/>
+          <t>ENT-PV-01.1, ENT-C2-01.1, ENT-C2-01.2, ENT-C2-04, ENT-C2-05</t>
+        </is>
+      </c>
+      <c r="M11" s="9" t="inlineStr">
+        <is>
+          <t>S0154</t>
+        </is>
+      </c>
       <c r="N11" s="9" t="inlineStr">
         <is>
-          <t>CISA(2024) KEV — ConnectWise ScreenConnect Authentication Bypass | https://www.cisa.gov/known-exploited-vulnerabilities-catalog</t>
+          <t>Europol(2024) Global operation targets Cobalt Strike (Operation MORPHEUS) | https://www.europol.europa.eu/media-press/newsroom/news/global-crackdown-tooling-abused-criminals</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="9" t="inlineStr">
         <is>
-          <t>ENI-005</t>
+          <t>ENI-012</t>
         </is>
       </c>
       <c r="B12" s="9" t="inlineStr">
         <is>
-          <t>Fortinet FortiOS SSL-VPN 취약점 악용</t>
+          <t>Black Basta 사람 운영 랜섬웨어(LotL·BYOVD·AD 확산)</t>
         </is>
       </c>
       <c r="C12" s="9" t="inlineStr">
         <is>
-          <t>2024-02</t>
+          <t>2024-05</t>
         </is>
       </c>
       <c r="D12" s="9" t="inlineStr">
@@ -25019,55 +24995,55 @@
       </c>
       <c r="G12" s="9" t="inlineStr">
         <is>
-          <t>다부문</t>
+          <t>다부문 · 의료·바이오</t>
         </is>
       </c>
       <c r="H12" s="9" t="inlineStr">
         <is>
-          <t>다수(국가배후·랜섬웨어)</t>
+          <t>Black Basta</t>
         </is>
       </c>
       <c r="I12" s="9" t="inlineStr">
         <is>
-          <t>국가배후 · 랜섬웨어 · 접근 브로커</t>
+          <t>랜섬웨어</t>
         </is>
       </c>
       <c r="J12" s="9" t="inlineStr">
         <is>
-          <t>내부 접근 확보</t>
-        </is>
-      </c>
-      <c r="K12" s="9" t="inlineStr">
-        <is>
-          <t>CVE-2024-21762, CVE-2022-42475, CVE-2023-27997</t>
-        </is>
-      </c>
+          <t>랜섬·암호화 · 데이터 유출 · 자격증명·비밀 탈취</t>
+        </is>
+      </c>
+      <c r="K12" s="9" t="inlineStr"/>
       <c r="L12" s="9" t="inlineStr">
         <is>
-          <t>ENT-IA-01</t>
-        </is>
-      </c>
-      <c r="M12" s="9" t="inlineStr"/>
+          <t>ENT-EX-01.1, ENT-CA-01.1, ENT-DI-02, ENT-LM-01, ENT-DE-01.1, ENT-IM-01, ENT-IM-02</t>
+        </is>
+      </c>
+      <c r="M12" s="9" t="inlineStr">
+        <is>
+          <t>S1070</t>
+        </is>
+      </c>
       <c r="N12" s="9" t="inlineStr">
         <is>
-          <t>CISA(2024) KEV — Fortinet FortiOS Out-of-bound Write (CVE-2024-21762) | https://www.cisa.gov/known-exploited-vulnerabilities-catalog</t>
+          <t>CISA(2024) StopRansomware — Black Basta (AA24-131A) | https://www.cisa.gov/news-events/cybersecurity-advisories/aa24-131a</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="9" t="inlineStr">
         <is>
-          <t>ENI-001</t>
+          <t>ENI-014</t>
         </is>
       </c>
       <c r="B13" s="9" t="inlineStr">
         <is>
-          <t>Volt Typhoon의 LotL 기반 핵심 기반시설 장기 침투</t>
+          <t>Akira 랜섬웨어의 MFA 미적용 VPN 경유 침투</t>
         </is>
       </c>
       <c r="C13" s="9" t="inlineStr">
         <is>
-          <t>2024-02</t>
+          <t>2024-04</t>
         </is>
       </c>
       <c r="D13" s="9" t="inlineStr">
@@ -25082,60 +25058,60 @@
       </c>
       <c r="F13" s="9" t="inlineStr">
         <is>
-          <t>미국</t>
+          <t>글로벌</t>
         </is>
       </c>
       <c r="G13" s="9" t="inlineStr">
         <is>
-          <t>에너지·기반시설 · 통신·미디어</t>
+          <t>다부문</t>
         </is>
       </c>
       <c r="H13" s="9" t="inlineStr">
         <is>
-          <t>Volt Typhoon(중국 연계)</t>
+          <t>Akira</t>
         </is>
       </c>
       <c r="I13" s="9" t="inlineStr">
         <is>
-          <t>국가배후</t>
+          <t>랜섬웨어</t>
         </is>
       </c>
       <c r="J13" s="9" t="inlineStr">
         <is>
-          <t>내부 접근 확보 · 첩보·감시 · 측면 이동·확산</t>
+          <t>랜섬·암호화 · 데이터 유출</t>
         </is>
       </c>
       <c r="K13" s="9" t="inlineStr"/>
       <c r="L13" s="9" t="inlineStr">
         <is>
-          <t>ENT-IA-01, ENT-EX-01.1, ENT-EX-03, ENT-DI-01, ENT-DI-02, ENT-CA-01.1, ENT-LM-01, ENT-DE-03</t>
+          <t>ENT-IA-02, ENT-CA-01.1, ENT-LM-01, ENT-IM-01</t>
         </is>
       </c>
       <c r="M13" s="9" t="inlineStr">
         <is>
-          <t>G1017</t>
+          <t>G1024</t>
         </is>
       </c>
       <c r="N13" s="9" t="inlineStr">
         <is>
-          <t>CISA(2024) PRC State-Sponsored Actors Compromise and Maintain Persistent Access (AA24-038A) | https://www.cisa.gov/news-events/cybersecurity-advisories/aa24-038a</t>
+          <t>CISA(2024) StopRansomware — Akira (AA24-109A) | https://www.cisa.gov/news-events/cybersecurity-advisories/aa24-109a</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="9" t="inlineStr">
         <is>
-          <t>ENI-006</t>
+          <t>ENI-008</t>
         </is>
       </c>
       <c r="B14" s="9" t="inlineStr">
         <is>
-          <t>Ivanti Connect Secure VPN 연쇄 0-day 악용(2024)</t>
+          <t>Palo Alto PAN-OS GlobalProtect 0-day 악용</t>
         </is>
       </c>
       <c r="C14" s="9" t="inlineStr">
         <is>
-          <t>2024-01</t>
+          <t>2024-04</t>
         </is>
       </c>
       <c r="D14" s="9" t="inlineStr">
@@ -25160,7 +25136,7 @@
       </c>
       <c r="H14" s="9" t="inlineStr">
         <is>
-          <t>국가배후·다수 행위자</t>
+          <t>미상(국가배후 추정)</t>
         </is>
       </c>
       <c r="I14" s="9" t="inlineStr">
@@ -25170,12 +25146,12 @@
       </c>
       <c r="J14" s="9" t="inlineStr">
         <is>
-          <t>내부 접근 확보 · 측면 이동·확산</t>
+          <t>내부 접근 확보</t>
         </is>
       </c>
       <c r="K14" s="9" t="inlineStr">
         <is>
-          <t>CVE-2023-46805, CVE-2024-21887</t>
+          <t>CVE-2024-3400</t>
         </is>
       </c>
       <c r="L14" s="9" t="inlineStr">
@@ -25186,24 +25162,24 @@
       <c r="M14" s="9" t="inlineStr"/>
       <c r="N14" s="9" t="inlineStr">
         <is>
-          <t>CISA(2024) Threat Actors Exploit Multiple Vulnerabilities in Ivanti Connect Secure and Policy Secure (AA24-060B) | https://www.cisa.gov/news-events/cybersecurity-advisories/aa24-060b</t>
+          <t>Unit 42(2024) Operation MidnightEclipse — PAN-OS CVE-2024-3400 | https://unit42.paloaltonetworks.com/cve-2024-3400/</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="9" t="inlineStr">
         <is>
-          <t>ENI-013</t>
+          <t>ENI-009</t>
         </is>
       </c>
       <c r="B15" s="9" t="inlineStr">
         <is>
-          <t>Scattered Spider의 헬프데스크 사칭·EDR 회피 침투</t>
+          <t>ConnectWise ScreenConnect 취약점 경유 랜섬웨어</t>
         </is>
       </c>
       <c r="C15" s="9" t="inlineStr">
         <is>
-          <t>2023-11</t>
+          <t>2024-02</t>
         </is>
       </c>
       <c r="D15" s="9" t="inlineStr">
@@ -25218,60 +25194,60 @@
       </c>
       <c r="F15" s="9" t="inlineStr">
         <is>
-          <t>미국</t>
+          <t>글로벌</t>
         </is>
       </c>
       <c r="G15" s="9" t="inlineStr">
         <is>
-          <t>금융·서비스 · 통신·미디어 · 숙박·여행</t>
+          <t>다부문</t>
         </is>
       </c>
       <c r="H15" s="9" t="inlineStr">
         <is>
-          <t>Scattered Spider</t>
+          <t>다수 랜섬웨어·브로커</t>
         </is>
       </c>
       <c r="I15" s="9" t="inlineStr">
         <is>
-          <t>사이버범죄 · 랜섬웨어 · 접근 브로커</t>
+          <t>랜섬웨어 · 접근 브로커</t>
         </is>
       </c>
       <c r="J15" s="9" t="inlineStr">
         <is>
-          <t>내부 접근 확보 · 랜섬·암호화 · 데이터 유출</t>
-        </is>
-      </c>
-      <c r="K15" s="9" t="inlineStr"/>
+          <t>내부 접근 확보 · 랜섬·암호화</t>
+        </is>
+      </c>
+      <c r="K15" s="9" t="inlineStr">
+        <is>
+          <t>CVE-2024-1709</t>
+        </is>
+      </c>
       <c r="L15" s="9" t="inlineStr">
         <is>
-          <t>ENT-IA-02, ENT-DE-01.1, ENT-LM-01, ENT-LM-03, ENT-IM-01</t>
-        </is>
-      </c>
-      <c r="M15" s="9" t="inlineStr">
-        <is>
-          <t>G1015</t>
-        </is>
-      </c>
+          <t>ENT-IA-02, ENT-IA-05, ENT-IM-01</t>
+        </is>
+      </c>
+      <c r="M15" s="9" t="inlineStr"/>
       <c r="N15" s="9" t="inlineStr">
         <is>
-          <t>CISA(2023) Scattered Spider (AA23-320A) | https://www.cisa.gov/news-events/cybersecurity-advisories/aa23-320a</t>
+          <t>CISA(2024) KEV — ConnectWise ScreenConnect Authentication Bypass | https://www.cisa.gov/known-exploited-vulnerabilities-catalog</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="9" t="inlineStr">
         <is>
-          <t>ENI-007</t>
+          <t>ENI-005</t>
         </is>
       </c>
       <c r="B16" s="9" t="inlineStr">
         <is>
-          <t>Cisco IOS XE 웹 UI 취약점 대량 임플란트 설치</t>
+          <t>Fortinet FortiOS SSL-VPN 취약점 악용</t>
         </is>
       </c>
       <c r="C16" s="9" t="inlineStr">
         <is>
-          <t>2023-10</t>
+          <t>2024-02</t>
         </is>
       </c>
       <c r="D16" s="9" t="inlineStr">
@@ -25296,12 +25272,12 @@
       </c>
       <c r="H16" s="9" t="inlineStr">
         <is>
-          <t>미상</t>
+          <t>다수(국가배후·랜섬웨어)</t>
         </is>
       </c>
       <c r="I16" s="9" t="inlineStr">
         <is>
-          <t>국가배후 · 접근 브로커</t>
+          <t>국가배후 · 랜섬웨어 · 접근 브로커</t>
         </is>
       </c>
       <c r="J16" s="9" t="inlineStr">
@@ -25311,7 +25287,7 @@
       </c>
       <c r="K16" s="9" t="inlineStr">
         <is>
-          <t>CVE-2023-20198</t>
+          <t>CVE-2024-21762, CVE-2022-42475, CVE-2023-27997</t>
         </is>
       </c>
       <c r="L16" s="9" t="inlineStr">
@@ -25322,24 +25298,24 @@
       <c r="M16" s="9" t="inlineStr"/>
       <c r="N16" s="9" t="inlineStr">
         <is>
-          <t>Cisco Talos(2023) Active exploitation of Cisco IOS XE Web UI | https://blog.talosintelligence.com/active-exploitation-of-cisco-ios-xe-software-web-management-user-interface/</t>
+          <t>CISA(2024) KEV — Fortinet FortiOS Out-of-bound Write (CVE-2024-21762) | https://www.cisa.gov/known-exploited-vulnerabilities-catalog</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="9" t="inlineStr">
         <is>
-          <t>ENI-003</t>
+          <t>ENI-001</t>
         </is>
       </c>
       <c r="B17" s="9" t="inlineStr">
         <is>
-          <t>Citrix Bleed NetScaler 세션 토큰 탈취 대량 악용</t>
+          <t>Volt Typhoon의 LotL 기반 핵심 기반시설 장기 침투</t>
         </is>
       </c>
       <c r="C17" s="9" t="inlineStr">
         <is>
-          <t>2023-10</t>
+          <t>2024-02</t>
         </is>
       </c>
       <c r="D17" s="9" t="inlineStr">
@@ -25354,60 +25330,60 @@
       </c>
       <c r="F17" s="9" t="inlineStr">
         <is>
-          <t>글로벌</t>
+          <t>미국</t>
         </is>
       </c>
       <c r="G17" s="9" t="inlineStr">
         <is>
-          <t>다부문</t>
+          <t>에너지·기반시설 · 통신·미디어</t>
         </is>
       </c>
       <c r="H17" s="9" t="inlineStr">
         <is>
-          <t>LockBit 제휴·다수 행위자</t>
+          <t>Volt Typhoon(중국 연계)</t>
         </is>
       </c>
       <c r="I17" s="9" t="inlineStr">
         <is>
-          <t>랜섬웨어 · 접근 브로커</t>
+          <t>국가배후</t>
         </is>
       </c>
       <c r="J17" s="9" t="inlineStr">
         <is>
-          <t>내부 접근 확보 · 랜섬·암호화</t>
-        </is>
-      </c>
-      <c r="K17" s="9" t="inlineStr">
-        <is>
-          <t>CVE-2023-4966</t>
-        </is>
-      </c>
+          <t>내부 접근 확보 · 첩보·감시 · 측면 이동·확산</t>
+        </is>
+      </c>
+      <c r="K17" s="9" t="inlineStr"/>
       <c r="L17" s="9" t="inlineStr">
         <is>
-          <t>ENT-IA-01</t>
-        </is>
-      </c>
-      <c r="M17" s="9" t="inlineStr"/>
+          <t>ENT-IA-01, ENT-EX-01.1, ENT-EX-03, ENT-DI-01, ENT-DI-02, ENT-CA-01.1, ENT-LM-01, ENT-DE-03</t>
+        </is>
+      </c>
+      <c r="M17" s="9" t="inlineStr">
+        <is>
+          <t>G1017</t>
+        </is>
+      </c>
       <c r="N17" s="9" t="inlineStr">
         <is>
-          <t>CISA(2023) Threat Actors Exploiting Citrix CVE-2023-4966 (AA23-325A) | https://www.cisa.gov/news-events/cybersecurity-advisories/aa23-325a</t>
+          <t>CISA(2024) PRC State-Sponsored Actors Compromise and Maintain Persistent Access (AA24-038A) | https://www.cisa.gov/news-events/cybersecurity-advisories/aa24-038a</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="9" t="inlineStr">
         <is>
-          <t>ENI-029</t>
+          <t>ENI-006</t>
         </is>
       </c>
       <c r="B18" s="9" t="inlineStr">
         <is>
-          <t>이동식 매체(USB) 경유 격리망 침투·전파</t>
+          <t>Ivanti Connect Secure VPN 연쇄 0-day 악용(2024)</t>
         </is>
       </c>
       <c r="C18" s="9" t="inlineStr">
         <is>
-          <t>2023-06</t>
+          <t>2024-01</t>
         </is>
       </c>
       <c r="D18" s="9" t="inlineStr">
@@ -25422,22 +25398,22 @@
       </c>
       <c r="F18" s="9" t="inlineStr">
         <is>
-          <t>유럽</t>
+          <t>글로벌</t>
         </is>
       </c>
       <c r="G18" s="9" t="inlineStr">
         <is>
-          <t>정부·군 · 에너지·기반시설</t>
+          <t>다부문</t>
         </is>
       </c>
       <c r="H18" s="9" t="inlineStr">
         <is>
-          <t>Gamaredon 등(러시아 연계)</t>
+          <t>국가배후·다수 행위자</t>
         </is>
       </c>
       <c r="I18" s="9" t="inlineStr">
         <is>
-          <t>국가배후</t>
+          <t>국가배후 · 접근 브로커</t>
         </is>
       </c>
       <c r="J18" s="9" t="inlineStr">
@@ -25445,33 +25421,37 @@
           <t>내부 접근 확보 · 측면 이동·확산</t>
         </is>
       </c>
-      <c r="K18" s="9" t="inlineStr"/>
+      <c r="K18" s="9" t="inlineStr">
+        <is>
+          <t>CVE-2023-46805, CVE-2024-21887</t>
+        </is>
+      </c>
       <c r="L18" s="9" t="inlineStr">
         <is>
-          <t>ENT-IA-04</t>
+          <t>ENT-IA-01</t>
         </is>
       </c>
       <c r="M18" s="9" t="inlineStr"/>
       <c r="N18" s="9" t="inlineStr">
         <is>
-          <t>ESET(2023) Gamaredon's USB-spreading malware (GAMMASTEEL) | https://www.welivesecurity.com/en/eset-research/sneaky-gamaredon-usb-spreading/</t>
+          <t>CISA(2024) Threat Actors Exploit Multiple Vulnerabilities in Ivanti Connect Secure and Policy Secure (AA24-060B) | https://www.cisa.gov/news-events/cybersecurity-advisories/aa24-060b</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="9" t="inlineStr">
         <is>
-          <t>ENI-015</t>
+          <t>ENI-013</t>
         </is>
       </c>
       <c r="B19" s="9" t="inlineStr">
         <is>
-          <t>LockBit 제휴의 복구 방해·EDR 무력화 암호화(CISA 권고)</t>
+          <t>Scattered Spider의 헬프데스크 사칭·EDR 회피 침투</t>
         </is>
       </c>
       <c r="C19" s="9" t="inlineStr">
         <is>
-          <t>2023-06</t>
+          <t>2023-11</t>
         </is>
       </c>
       <c r="D19" s="9" t="inlineStr">
@@ -25486,454 +25466,722 @@
       </c>
       <c r="F19" s="9" t="inlineStr">
         <is>
-          <t>글로벌</t>
+          <t>미국</t>
         </is>
       </c>
       <c r="G19" s="9" t="inlineStr">
         <is>
-          <t>다부문</t>
+          <t>금융·서비스 · 통신·미디어 · 숙박·여행</t>
         </is>
       </c>
       <c r="H19" s="9" t="inlineStr">
         <is>
-          <t>LockBit(RaaS)</t>
+          <t>Scattered Spider</t>
         </is>
       </c>
       <c r="I19" s="9" t="inlineStr">
         <is>
-          <t>랜섬웨어</t>
+          <t>사이버범죄 · 랜섬웨어 · 접근 브로커</t>
         </is>
       </c>
       <c r="J19" s="9" t="inlineStr">
         <is>
-          <t>랜섬·암호화 · 서비스 중단</t>
+          <t>내부 접근 확보 · 랜섬·암호화 · 데이터 유출</t>
         </is>
       </c>
       <c r="K19" s="9" t="inlineStr"/>
       <c r="L19" s="9" t="inlineStr">
         <is>
+          <t>ENT-IA-02, ENT-DE-01.1, ENT-LM-01, ENT-LM-03, ENT-IM-01</t>
+        </is>
+      </c>
+      <c r="M19" s="9" t="inlineStr">
+        <is>
+          <t>G1015</t>
+        </is>
+      </c>
+      <c r="N19" s="9" t="inlineStr">
+        <is>
+          <t>CISA(2023) Scattered Spider (AA23-320A) | https://www.cisa.gov/news-events/cybersecurity-advisories/aa23-320a</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="9" t="inlineStr">
+        <is>
+          <t>ENI-007</t>
+        </is>
+      </c>
+      <c r="B20" s="9" t="inlineStr">
+        <is>
+          <t>Cisco IOS XE 웹 UI 취약점 대량 임플란트 설치</t>
+        </is>
+      </c>
+      <c r="C20" s="9" t="inlineStr">
+        <is>
+          <t>2023-10</t>
+        </is>
+      </c>
+      <c r="D20" s="9" t="inlineStr">
+        <is>
+          <t>캠페인</t>
+        </is>
+      </c>
+      <c r="E20" s="9" t="inlineStr">
+        <is>
+          <t>실제 사고</t>
+        </is>
+      </c>
+      <c r="F20" s="9" t="inlineStr">
+        <is>
+          <t>글로벌</t>
+        </is>
+      </c>
+      <c r="G20" s="9" t="inlineStr">
+        <is>
+          <t>다부문</t>
+        </is>
+      </c>
+      <c r="H20" s="9" t="inlineStr">
+        <is>
+          <t>미상</t>
+        </is>
+      </c>
+      <c r="I20" s="9" t="inlineStr">
+        <is>
+          <t>국가배후 · 접근 브로커</t>
+        </is>
+      </c>
+      <c r="J20" s="9" t="inlineStr">
+        <is>
+          <t>내부 접근 확보</t>
+        </is>
+      </c>
+      <c r="K20" s="9" t="inlineStr">
+        <is>
+          <t>CVE-2023-20198</t>
+        </is>
+      </c>
+      <c r="L20" s="9" t="inlineStr">
+        <is>
+          <t>ENT-IA-01</t>
+        </is>
+      </c>
+      <c r="M20" s="9" t="inlineStr"/>
+      <c r="N20" s="9" t="inlineStr">
+        <is>
+          <t>Cisco Talos(2023) Active exploitation of Cisco IOS XE Web UI | https://blog.talosintelligence.com/active-exploitation-of-cisco-ios-xe-software-web-management-user-interface/</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="9" t="inlineStr">
+        <is>
+          <t>ENI-003</t>
+        </is>
+      </c>
+      <c r="B21" s="9" t="inlineStr">
+        <is>
+          <t>Citrix Bleed NetScaler 세션 토큰 탈취 대량 악용</t>
+        </is>
+      </c>
+      <c r="C21" s="9" t="inlineStr">
+        <is>
+          <t>2023-10</t>
+        </is>
+      </c>
+      <c r="D21" s="9" t="inlineStr">
+        <is>
+          <t>캠페인</t>
+        </is>
+      </c>
+      <c r="E21" s="9" t="inlineStr">
+        <is>
+          <t>실제 사고</t>
+        </is>
+      </c>
+      <c r="F21" s="9" t="inlineStr">
+        <is>
+          <t>글로벌</t>
+        </is>
+      </c>
+      <c r="G21" s="9" t="inlineStr">
+        <is>
+          <t>다부문</t>
+        </is>
+      </c>
+      <c r="H21" s="9" t="inlineStr">
+        <is>
+          <t>LockBit 제휴·다수 행위자</t>
+        </is>
+      </c>
+      <c r="I21" s="9" t="inlineStr">
+        <is>
+          <t>랜섬웨어 · 접근 브로커</t>
+        </is>
+      </c>
+      <c r="J21" s="9" t="inlineStr">
+        <is>
+          <t>내부 접근 확보 · 랜섬·암호화</t>
+        </is>
+      </c>
+      <c r="K21" s="9" t="inlineStr">
+        <is>
+          <t>CVE-2023-4966</t>
+        </is>
+      </c>
+      <c r="L21" s="9" t="inlineStr">
+        <is>
+          <t>ENT-IA-01</t>
+        </is>
+      </c>
+      <c r="M21" s="9" t="inlineStr"/>
+      <c r="N21" s="9" t="inlineStr">
+        <is>
+          <t>CISA(2023) Threat Actors Exploiting Citrix CVE-2023-4966 (AA23-325A) | https://www.cisa.gov/news-events/cybersecurity-advisories/aa23-325a</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="9" t="inlineStr">
+        <is>
+          <t>ENI-029</t>
+        </is>
+      </c>
+      <c r="B22" s="9" t="inlineStr">
+        <is>
+          <t>이동식 매체(USB) 경유 격리망 침투·전파</t>
+        </is>
+      </c>
+      <c r="C22" s="9" t="inlineStr">
+        <is>
+          <t>2023-06</t>
+        </is>
+      </c>
+      <c r="D22" s="9" t="inlineStr">
+        <is>
+          <t>캠페인</t>
+        </is>
+      </c>
+      <c r="E22" s="9" t="inlineStr">
+        <is>
+          <t>실제 사고</t>
+        </is>
+      </c>
+      <c r="F22" s="9" t="inlineStr">
+        <is>
+          <t>유럽</t>
+        </is>
+      </c>
+      <c r="G22" s="9" t="inlineStr">
+        <is>
+          <t>정부·군 · 에너지·기반시설</t>
+        </is>
+      </c>
+      <c r="H22" s="9" t="inlineStr">
+        <is>
+          <t>Gamaredon 등(러시아 연계)</t>
+        </is>
+      </c>
+      <c r="I22" s="9" t="inlineStr">
+        <is>
+          <t>국가배후</t>
+        </is>
+      </c>
+      <c r="J22" s="9" t="inlineStr">
+        <is>
+          <t>내부 접근 확보 · 측면 이동·확산</t>
+        </is>
+      </c>
+      <c r="K22" s="9" t="inlineStr"/>
+      <c r="L22" s="9" t="inlineStr">
+        <is>
+          <t>ENT-IA-04</t>
+        </is>
+      </c>
+      <c r="M22" s="9" t="inlineStr"/>
+      <c r="N22" s="9" t="inlineStr">
+        <is>
+          <t>ESET(2023) Gamaredon's USB-spreading malware (GAMMASTEEL) | https://www.welivesecurity.com/en/eset-research/sneaky-gamaredon-usb-spreading/</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="9" t="inlineStr">
+        <is>
+          <t>ENI-015</t>
+        </is>
+      </c>
+      <c r="B23" s="9" t="inlineStr">
+        <is>
+          <t>LockBit 제휴의 복구 방해·EDR 무력화 암호화(CISA 권고)</t>
+        </is>
+      </c>
+      <c r="C23" s="9" t="inlineStr">
+        <is>
+          <t>2023-06</t>
+        </is>
+      </c>
+      <c r="D23" s="9" t="inlineStr">
+        <is>
+          <t>캠페인</t>
+        </is>
+      </c>
+      <c r="E23" s="9" t="inlineStr">
+        <is>
+          <t>실제 사고</t>
+        </is>
+      </c>
+      <c r="F23" s="9" t="inlineStr">
+        <is>
+          <t>글로벌</t>
+        </is>
+      </c>
+      <c r="G23" s="9" t="inlineStr">
+        <is>
+          <t>다부문</t>
+        </is>
+      </c>
+      <c r="H23" s="9" t="inlineStr">
+        <is>
+          <t>LockBit(RaaS)</t>
+        </is>
+      </c>
+      <c r="I23" s="9" t="inlineStr">
+        <is>
+          <t>랜섬웨어</t>
+        </is>
+      </c>
+      <c r="J23" s="9" t="inlineStr">
+        <is>
+          <t>랜섬·암호화 · 서비스 중단</t>
+        </is>
+      </c>
+      <c r="K23" s="9" t="inlineStr"/>
+      <c r="L23" s="9" t="inlineStr">
+        <is>
           <t>ENT-IM-01, ENT-IM-02, ENT-IM-04, ENT-DE-01.1</t>
         </is>
       </c>
-      <c r="M19" s="9" t="inlineStr"/>
-      <c r="N19" s="9" t="inlineStr">
+      <c r="M23" s="9" t="inlineStr"/>
+      <c r="N23" s="9" t="inlineStr">
         <is>
           <t>{'CISA(2023) Understanding Ransomware Threat Actors': 'LockBit (AA23-165A) | https://www.cisa.gov/news-events/cybersecurity-advisories/aa23-165a'}
 NCA(2024) Operation Cronos — international disruption of LockBit | https://www.nationalcrimeagency.gov.uk/news/nca-leads-international-investigation-targeting-lockbit</t>
         </is>
       </c>
     </row>
-    <row r="20">
-      <c r="A20" s="9" t="inlineStr">
+    <row r="24">
+      <c r="A24" s="9" t="inlineStr">
         <is>
           <t>ENI-004</t>
         </is>
       </c>
-      <c r="B20" s="9" t="inlineStr">
+      <c r="B24" s="9" t="inlineStr">
         <is>
           <t>Cl0p의 MOVEit Transfer 0-day 대량 데이터 탈취</t>
         </is>
       </c>
-      <c r="C20" s="9" t="inlineStr">
+      <c r="C24" s="9" t="inlineStr">
         <is>
           <t>2023-06</t>
         </is>
       </c>
-      <c r="D20" s="9" t="inlineStr">
+      <c r="D24" s="9" t="inlineStr">
         <is>
           <t>캠페인</t>
         </is>
       </c>
-      <c r="E20" s="9" t="inlineStr">
+      <c r="E24" s="9" t="inlineStr">
         <is>
           <t>실제 사고</t>
         </is>
       </c>
-      <c r="F20" s="9" t="inlineStr">
+      <c r="F24" s="9" t="inlineStr">
         <is>
           <t>글로벌</t>
         </is>
       </c>
-      <c r="G20" s="9" t="inlineStr">
+      <c r="G24" s="9" t="inlineStr">
         <is>
           <t>다부문</t>
         </is>
       </c>
-      <c r="H20" s="9" t="inlineStr">
+      <c r="H24" s="9" t="inlineStr">
         <is>
           <t>Cl0p(FIN11 연계)</t>
         </is>
       </c>
-      <c r="I20" s="9" t="inlineStr">
+      <c r="I24" s="9" t="inlineStr">
         <is>
           <t>랜섬웨어 · 사이버범죄</t>
         </is>
       </c>
-      <c r="J20" s="9" t="inlineStr">
+      <c r="J24" s="9" t="inlineStr">
         <is>
           <t>데이터 유출 · 금전 피해</t>
         </is>
       </c>
-      <c r="K20" s="9" t="inlineStr">
+      <c r="K24" s="9" t="inlineStr">
         <is>
           <t>CVE-2023-34362</t>
         </is>
       </c>
-      <c r="L20" s="9" t="inlineStr">
+      <c r="L24" s="9" t="inlineStr">
         <is>
           <t>ENT-IA-01, ENT-EF-02, ENT-IM-05</t>
         </is>
       </c>
-      <c r="M20" s="9" t="inlineStr"/>
-      <c r="N20" s="9" t="inlineStr">
+      <c r="M24" s="9" t="inlineStr"/>
+      <c r="N24" s="9" t="inlineStr">
         <is>
           <t>CISA(2023) CL0P Ransomware Gang Exploits MOVEit Vulnerability (AA23-158A) | https://www.cisa.gov/news-events/cybersecurity-advisories/aa23-158a</t>
         </is>
       </c>
     </row>
-    <row r="21">
-      <c r="A21" s="9" t="inlineStr">
+    <row r="25">
+      <c r="A25" s="9" t="inlineStr">
         <is>
           <t>ENI-024</t>
         </is>
       </c>
-      <c r="B21" s="9" t="inlineStr">
+      <c r="B25" s="9" t="inlineStr">
         <is>
           <t>BlackLotus UEFI 부트킷(보안 부팅 우회)</t>
         </is>
       </c>
-      <c r="C21" s="9" t="inlineStr">
+      <c r="C25" s="9" t="inlineStr">
         <is>
           <t>2023-03</t>
         </is>
       </c>
-      <c r="D21" s="9" t="inlineStr">
+      <c r="D25" s="9" t="inlineStr">
         <is>
           <t>연구·시연</t>
         </is>
       </c>
-      <c r="E21" s="9" t="inlineStr">
+      <c r="E25" s="9" t="inlineStr">
         <is>
           <t>실증·연구</t>
         </is>
       </c>
-      <c r="F21" s="9" t="inlineStr">
+      <c r="F25" s="9" t="inlineStr">
         <is>
           <t>글로벌</t>
         </is>
       </c>
-      <c r="G21" s="9" t="inlineStr">
+      <c r="G25" s="9" t="inlineStr">
         <is>
           <t>다부문</t>
         </is>
       </c>
-      <c r="H21" s="9" t="inlineStr">
+      <c r="H25" s="9" t="inlineStr">
         <is>
           <t>미상(지하 판매)</t>
         </is>
       </c>
-      <c r="I21" s="9" t="inlineStr">
+      <c r="I25" s="9" t="inlineStr">
         <is>
           <t>사이버범죄 · 국가배후</t>
         </is>
       </c>
-      <c r="J21" s="9" t="inlineStr">
+      <c r="J25" s="9" t="inlineStr">
         <is>
           <t>내부 접근 확보</t>
         </is>
       </c>
-      <c r="K21" s="9" t="inlineStr"/>
-      <c r="L21" s="9" t="inlineStr">
+      <c r="K25" s="9" t="inlineStr"/>
+      <c r="L25" s="9" t="inlineStr">
         <is>
           <t>ENT-DE-08</t>
         </is>
       </c>
-      <c r="M21" s="9" t="inlineStr"/>
-      <c r="N21" s="9" t="inlineStr">
+      <c r="M25" s="9" t="inlineStr"/>
+      <c r="N25" s="9" t="inlineStr">
         <is>
           <t>ESET(2023) BlackLotus UEFI bootkit | https://www.welivesecurity.com/2023/03/01/blacklotus-uefi-bootkit-myth-confirmed/</t>
         </is>
       </c>
     </row>
-    <row r="22">
-      <c r="A22" s="9" t="inlineStr">
+    <row r="26">
+      <c r="A26" s="9" t="inlineStr">
         <is>
           <t>ENI-026</t>
         </is>
       </c>
-      <c r="B22" s="9" t="inlineStr">
+      <c r="B26" s="9" t="inlineStr">
         <is>
           <t>UEFI 펌웨어 임플란트(LoJax·APT28 / MoonBounce·APT41)</t>
         </is>
       </c>
-      <c r="C22" s="9" t="inlineStr">
+      <c r="C26" s="9" t="inlineStr">
         <is>
           <t>2022-01</t>
         </is>
       </c>
-      <c r="D22" s="9" t="inlineStr">
+      <c r="D26" s="9" t="inlineStr">
         <is>
           <t>캠페인</t>
         </is>
       </c>
-      <c r="E22" s="9" t="inlineStr">
+      <c r="E26" s="9" t="inlineStr">
         <is>
           <t>실제 사고</t>
         </is>
       </c>
-      <c r="F22" s="9" t="inlineStr">
+      <c r="F26" s="9" t="inlineStr">
         <is>
           <t>글로벌</t>
         </is>
       </c>
-      <c r="G22" s="9" t="inlineStr">
+      <c r="G26" s="9" t="inlineStr">
         <is>
           <t>정부·군 · 다부문</t>
         </is>
       </c>
-      <c r="H22" s="9" t="inlineStr">
+      <c r="H26" s="9" t="inlineStr">
         <is>
           <t>APT28(LoJax)·APT41(MoonBounce)</t>
         </is>
       </c>
-      <c r="I22" s="9" t="inlineStr">
+      <c r="I26" s="9" t="inlineStr">
         <is>
           <t>국가배후</t>
         </is>
       </c>
-      <c r="J22" s="9" t="inlineStr">
+      <c r="J26" s="9" t="inlineStr">
         <is>
           <t>내부 접근 확보 · 첩보·감시</t>
         </is>
       </c>
-      <c r="K22" s="9" t="inlineStr"/>
-      <c r="L22" s="9" t="inlineStr">
+      <c r="K26" s="9" t="inlineStr"/>
+      <c r="L26" s="9" t="inlineStr">
         <is>
           <t>ENT-DE-08</t>
         </is>
       </c>
-      <c r="M22" s="9" t="inlineStr">
+      <c r="M26" s="9" t="inlineStr">
         <is>
           <t>G0007, G0096</t>
         </is>
       </c>
-      <c r="N22" s="9" t="inlineStr">
+      <c r="N26" s="9" t="inlineStr">
         <is>
           <t>Kaspersky(2022) MoonBounce — the dark side of UEFI firmware | https://securelist.com/moonbounce-the-dark-side-of-uefi-firmware/105468/
 ESET(2018) LoJax — first UEFI rootkit found in the wild | https://www.welivesecurity.com/2018/09/27/lojax-first-uefi-rootkit-found-wild-courtesy-sednit-group/</t>
         </is>
       </c>
     </row>
-    <row r="23">
-      <c r="A23" s="9" t="inlineStr">
+    <row r="27">
+      <c r="A27" s="9" t="inlineStr">
         <is>
           <t>ENI-011</t>
         </is>
       </c>
-      <c r="B23" s="9" t="inlineStr">
+      <c r="B27" s="9" t="inlineStr">
         <is>
           <t>Kaseya VSA 공급·관리 도구 경유 대규모 랜섬웨어</t>
         </is>
       </c>
-      <c r="C23" s="9" t="inlineStr">
+      <c r="C27" s="9" t="inlineStr">
         <is>
           <t>2021-07</t>
         </is>
       </c>
-      <c r="D23" s="9" t="inlineStr">
+      <c r="D27" s="9" t="inlineStr">
         <is>
           <t>사고</t>
         </is>
       </c>
-      <c r="E23" s="9" t="inlineStr">
+      <c r="E27" s="9" t="inlineStr">
         <is>
           <t>실제 사고</t>
         </is>
       </c>
-      <c r="F23" s="9" t="inlineStr">
+      <c r="F27" s="9" t="inlineStr">
         <is>
           <t>글로벌</t>
         </is>
       </c>
-      <c r="G23" s="9" t="inlineStr">
+      <c r="G27" s="9" t="inlineStr">
         <is>
           <t>다부문</t>
         </is>
       </c>
-      <c r="H23" s="9" t="inlineStr">
+      <c r="H27" s="9" t="inlineStr">
         <is>
           <t>REvil</t>
         </is>
       </c>
-      <c r="I23" s="9" t="inlineStr">
+      <c r="I27" s="9" t="inlineStr">
         <is>
           <t>랜섬웨어</t>
         </is>
       </c>
-      <c r="J23" s="9" t="inlineStr">
+      <c r="J27" s="9" t="inlineStr">
         <is>
           <t>랜섬·암호화 · 내부 접근 확보</t>
         </is>
       </c>
-      <c r="K23" s="9" t="inlineStr">
+      <c r="K27" s="9" t="inlineStr">
         <is>
           <t>CVE-2021-30116</t>
         </is>
       </c>
-      <c r="L23" s="9" t="inlineStr">
+      <c r="L27" s="9" t="inlineStr">
         <is>
           <t>ENT-IA-05, ENT-IM-01</t>
         </is>
       </c>
-      <c r="M23" s="9" t="inlineStr"/>
-      <c r="N23" s="9" t="inlineStr">
+      <c r="M27" s="9" t="inlineStr"/>
+      <c r="N27" s="9" t="inlineStr">
         <is>
           <t>CISA(2021) Kaseya VSA Supply-Chain Ransomware Attack | https://www.cisa.gov/news-events/alerts/2021/07/04/kaseya-vsa-supply-chain-ransomware-attack</t>
         </is>
       </c>
     </row>
-    <row r="24">
-      <c r="A24" s="9" t="inlineStr">
+    <row r="28">
+      <c r="A28" s="9" t="inlineStr">
         <is>
           <t>ENI-021</t>
         </is>
       </c>
-      <c r="B24" s="9" t="inlineStr">
+      <c r="B28" s="9" t="inlineStr">
         <is>
           <t>NotPetya의 자격증명 탈취·원격 취약점 웜 확산·파괴</t>
         </is>
       </c>
-      <c r="C24" s="9" t="inlineStr">
+      <c r="C28" s="9" t="inlineStr">
         <is>
           <t>2017-06</t>
         </is>
       </c>
-      <c r="D24" s="9" t="inlineStr">
+      <c r="D28" s="9" t="inlineStr">
         <is>
           <t>사고</t>
         </is>
       </c>
-      <c r="E24" s="9" t="inlineStr">
+      <c r="E28" s="9" t="inlineStr">
         <is>
           <t>실제 사고</t>
         </is>
       </c>
-      <c r="F24" s="9" t="inlineStr">
+      <c r="F28" s="9" t="inlineStr">
         <is>
           <t>유럽</t>
         </is>
       </c>
-      <c r="G24" s="9" t="inlineStr">
+      <c r="G28" s="9" t="inlineStr">
         <is>
           <t>다부문 · 에너지·기반시설</t>
         </is>
       </c>
-      <c r="H24" s="9" t="inlineStr">
+      <c r="H28" s="9" t="inlineStr">
         <is>
           <t>Sandworm(러시아 GRU)</t>
         </is>
       </c>
-      <c r="I24" s="9" t="inlineStr">
+      <c r="I28" s="9" t="inlineStr">
         <is>
           <t>국가배후</t>
         </is>
       </c>
-      <c r="J24" s="9" t="inlineStr">
+      <c r="J28" s="9" t="inlineStr">
         <is>
           <t>데이터 파괴 · 서비스 중단 · 측면 이동·확산</t>
         </is>
       </c>
-      <c r="K24" s="9" t="inlineStr"/>
-      <c r="L24" s="9" t="inlineStr">
+      <c r="K28" s="9" t="inlineStr"/>
+      <c r="L28" s="9" t="inlineStr">
         <is>
           <t>ENT-CA-01.1, ENT-LM-02, ENT-LM-04, ENT-IM-03</t>
         </is>
       </c>
-      <c r="M24" s="9" t="inlineStr">
+      <c r="M28" s="9" t="inlineStr">
         <is>
           <t>S0368, G0034</t>
         </is>
       </c>
-      <c r="N24" s="9" t="inlineStr">
+      <c r="N28" s="9" t="inlineStr">
         <is>
           <t>US-CERT(2017) Petya Ransomware (TA17-181A; 2018-02 미·영 정부의 러시아군 귀속 반영) | https://www.cisa.gov/news-events/alerts/2017/07/01/petya-ransomware</t>
         </is>
       </c>
     </row>
-    <row r="25">
-      <c r="A25" s="9" t="inlineStr">
+    <row r="29">
+      <c r="A29" s="9" t="inlineStr">
         <is>
           <t>ENI-022</t>
         </is>
       </c>
-      <c r="B25" s="9" t="inlineStr">
+      <c r="B29" s="9" t="inlineStr">
         <is>
           <t>WannaCry의 원격 취약점 웜 확산 랜섬웨어</t>
         </is>
       </c>
-      <c r="C25" s="9" t="inlineStr">
+      <c r="C29" s="9" t="inlineStr">
         <is>
           <t>2017-05</t>
         </is>
       </c>
-      <c r="D25" s="9" t="inlineStr">
+      <c r="D29" s="9" t="inlineStr">
         <is>
           <t>사고</t>
         </is>
       </c>
-      <c r="E25" s="9" t="inlineStr">
+      <c r="E29" s="9" t="inlineStr">
         <is>
           <t>실제 사고</t>
         </is>
       </c>
-      <c r="F25" s="9" t="inlineStr">
+      <c r="F29" s="9" t="inlineStr">
         <is>
           <t>글로벌</t>
         </is>
       </c>
-      <c r="G25" s="9" t="inlineStr">
+      <c r="G29" s="9" t="inlineStr">
         <is>
           <t>의료·바이오 · 다부문</t>
         </is>
       </c>
-      <c r="H25" s="9" t="inlineStr">
+      <c r="H29" s="9" t="inlineStr">
         <is>
           <t>Lazarus(북한 연계)</t>
         </is>
       </c>
-      <c r="I25" s="9" t="inlineStr">
+      <c r="I29" s="9" t="inlineStr">
         <is>
           <t>국가배후</t>
         </is>
       </c>
-      <c r="J25" s="9" t="inlineStr">
+      <c r="J29" s="9" t="inlineStr">
         <is>
           <t>랜섬·암호화 · 서비스 중단 · 측면 이동·확산</t>
         </is>
       </c>
-      <c r="K25" s="9" t="inlineStr">
+      <c r="K29" s="9" t="inlineStr">
         <is>
           <t>CVE-2017-0144</t>
         </is>
       </c>
-      <c r="L25" s="9" t="inlineStr">
+      <c r="L29" s="9" t="inlineStr">
         <is>
           <t>ENT-LM-04, ENT-IM-01</t>
         </is>
       </c>
-      <c r="M25" s="9" t="inlineStr">
+      <c r="M29" s="9" t="inlineStr">
         <is>
           <t>S0366</t>
         </is>
       </c>
-      <c r="N25" s="9" t="inlineStr">
+      <c r="N29" s="9" t="inlineStr">
         <is>
           <t>CISA(2017) Indicators Associated With WannaCry Ransomware (TA17-132A) | https://www.cisa.gov/news-events/alerts/2017/05/12/indicators-associated-wannacry-ransomware</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:N25"/>
+  <autoFilter ref="A1:N29"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/enterprise/output/통합_고도화엔터프라이즈_보안위협_매트릭스_v2.xlsx
+++ b/enterprise/output/통합_고도화엔터프라이즈_보안위협_매트릭스_v2.xlsx
@@ -782,7 +782,7 @@
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>ATT&amp;CK Enterprise 침투~영향 12개 — [IA]초기 침투 → [EX]실행 → [PE]지속 → [PV]권한 상승 → [DE]방어 회피 → [CA]자격증명 접근 → [DI]탐색 → [LM]측면 이동 → [CO]수집 → [C2]명령·제어 → [EF]반출 → [IM]영향</t>
+          <t>ATT&amp;CK Enterprise 침투~영향 13개(v19 방어 회피 분리) — [IA]초기 침투 → [EX]실행 → [PE]지속 → [PV]권한 상승 → [ST]은닉 → [DM]방어 무력화 → [CA]자격증명 접근 → [DI]탐색 → [LM]측면 이동 → [CO]수집 → [C2]명령·제어 → [EF]반출 → [IM]영향</t>
         </is>
       </c>
     </row>
@@ -1010,7 +1010,7 @@
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>51개 / 위협분류 46 / 전술 12</t>
+          <t>51개 / 위협분류 46 / 전술 13</t>
         </is>
       </c>
     </row>
@@ -1101,7 +1101,7 @@
 5. ENT-IM-02 복구 방해(섀도 카피·백업 삭제) — 매우 높음, 실제 사고 2건(EDR·XDR)
 6. ENT-LM-04 원격 서비스 취약점 악용(웜 확산) — 매우 높음, 실제 사고 2건(EDR·XDR)
 7. ENT-IA-01 인터넷 노출 경계·엣지 장비 취약점 악용(빠른 n-day·0-day) — 높음, 실제 사고 10건(행위·네트워크·아이덴티티)
-8. ENT-DE-01.1 보안 도구 무력화(EDR 변조·BYOVD EDR 킬러) — 높음, 실제 사고 7건(행위·네트워크·아이덴티티)
+8. ENT-DM-01.1 보안 도구 무력화(EDR 변조·BYOVD EDR 킬러) — 높음, 실제 사고 7건(행위·네트워크·아이덴티티)
 9. ENT-LM-01 원격 서비스 악용(RDP·SMB·WinRM) — 높음, 실제 사고 5건(행위·네트워크·아이덴티티)
 10. ENT-IA-02 외부 원격 서비스 악용(VPN·RDP·원격 관리) — 높음, 실제 사고 4건(행위·네트워크·아이덴티티)</t>
         </is>
@@ -1338,7 +1338,7 @@
       </c>
       <c r="F5" s="9" t="inlineStr">
         <is>
-          <t>ENT-DE-07</t>
+          <t>ENT-ST-05</t>
         </is>
       </c>
       <c r="G5" s="9" t="inlineStr"/>
@@ -1512,7 +1512,7 @@
       </c>
       <c r="F11" s="9" t="inlineStr">
         <is>
-          <t>ENT-DE-05</t>
+          <t>ENT-ST-03</t>
         </is>
       </c>
       <c r="G11" s="9" t="inlineStr"/>
@@ -1570,7 +1570,7 @@
       </c>
       <c r="F13" s="9" t="inlineStr">
         <is>
-          <t>ENT-DE-04</t>
+          <t>ENT-ST-02</t>
         </is>
       </c>
       <c r="G13" s="9" t="inlineStr"/>
@@ -1868,7 +1868,7 @@
       </c>
       <c r="F23" s="9" t="inlineStr">
         <is>
-          <t>ENT-DE-03</t>
+          <t>ENT-ST-01</t>
         </is>
       </c>
       <c r="G23" s="9" t="inlineStr"/>
@@ -1897,7 +1897,7 @@
       </c>
       <c r="F24" s="9" t="inlineStr">
         <is>
-          <t>ENT-DE-03</t>
+          <t>ENT-ST-01</t>
         </is>
       </c>
       <c r="G24" s="9" t="inlineStr"/>
@@ -2696,7 +2696,7 @@
       </c>
       <c r="F51" s="9" t="inlineStr">
         <is>
-          <t>ENT-DE-08</t>
+          <t>ENT-ST-06</t>
         </is>
       </c>
       <c r="G51" s="9" t="inlineStr"/>
@@ -2725,7 +2725,7 @@
       </c>
       <c r="F52" s="9" t="inlineStr">
         <is>
-          <t>ENT-PE-01, ENT-DE-01.2</t>
+          <t>ENT-PE-01, ENT-DM-01.2</t>
         </is>
       </c>
       <c r="G52" s="9" t="inlineStr">
@@ -3106,7 +3106,7 @@
       </c>
       <c r="F65" s="9" t="inlineStr">
         <is>
-          <t>ENT-DE-06</t>
+          <t>ENT-ST-04</t>
         </is>
       </c>
       <c r="G65" s="9" t="inlineStr"/>
@@ -3164,7 +3164,7 @@
       </c>
       <c r="F67" s="9" t="inlineStr">
         <is>
-          <t>ENT-DE-01.1</t>
+          <t>ENT-DM-01.1</t>
         </is>
       </c>
       <c r="G67" s="9" t="inlineStr">
@@ -3197,7 +3197,7 @@
       </c>
       <c r="F68" s="9" t="inlineStr">
         <is>
-          <t>ENT-DE-03</t>
+          <t>ENT-ST-01</t>
         </is>
       </c>
       <c r="G68" s="9" t="inlineStr"/>
@@ -3361,7 +3361,7 @@
       </c>
       <c r="E6" s="9" t="inlineStr">
         <is>
-          <t>ENT-DE-03, ENT-DI-02, ENT-C2-01.2, ENT-DI-01, ENT-EF-01, ENT-C2-01.1, ENT-EX-01.2, ENT-C2-06, ENT-PE-03, ENT-PE-01, ENT-PE-04</t>
+          <t>ENT-ST-01, ENT-DI-02, ENT-C2-01.2, ENT-DI-01, ENT-EF-01, ENT-C2-01.1, ENT-EX-01.2, ENT-C2-06, ENT-PE-03, ENT-PE-01, ENT-PE-04</t>
         </is>
       </c>
     </row>
@@ -3384,7 +3384,7 @@
       </c>
       <c r="E7" s="9" t="inlineStr">
         <is>
-          <t>ENT-DE-03</t>
+          <t>ENT-ST-01</t>
         </is>
       </c>
     </row>
@@ -3430,7 +3430,7 @@
       </c>
       <c r="E9" s="9" t="inlineStr">
         <is>
-          <t>ENT-DE-01.1, ENT-DE-01.2, ENT-EX-01.1, ENT-EX-03, ENT-DE-08, ENT-EX-01.2, ENT-EX-04, ENT-PE-03, ENT-PE-01, ENT-PV-03, ENT-PE-02</t>
+          <t>ENT-DM-01.1, ENT-DM-01.2, ENT-EX-01.1, ENT-EX-03, ENT-ST-06, ENT-EX-01.2, ENT-EX-04, ENT-PE-03, ENT-PE-01, ENT-PV-03, ENT-PE-02</t>
         </is>
       </c>
     </row>
@@ -3683,7 +3683,7 @@
       </c>
       <c r="E20" s="9" t="inlineStr">
         <is>
-          <t>ENT-EX-01.1, ENT-C2-05, ENT-PV-01.1, ENT-IA-04, ENT-DE-06, ENT-DE-05, ENT-IA-03</t>
+          <t>ENT-EX-01.1, ENT-C2-05, ENT-PV-01.1, ENT-IA-04, ENT-ST-04, ENT-ST-03, ENT-IA-03</t>
         </is>
       </c>
     </row>
@@ -3706,7 +3706,7 @@
       </c>
       <c r="E21" s="9" t="inlineStr">
         <is>
-          <t>ENT-IM-01, ENT-IM-05, ENT-EF-02, ENT-IA-05, ENT-IM-02, ENT-IA-01, ENT-DE-01.1, ENT-LM-01, ENT-IA-02, ENT-CA-01.1, ENT-DE-01.2, ENT-DE-03, ENT-EX-01.1, ENT-DI-02, ENT-LM-02, ENT-C2-01.2, ENT-IM-03, ENT-DI-01, ENT-C2-05, ENT-EF-01, ENT-C2-04, ENT-C2-01.1, ENT-CA-03, ENT-EX-03, ENT-PV-01.1, ENT-IM-04, ENT-LM-03, ENT-PV-04, ENT-EX-01.2, ENT-C2-06, ENT-C2-03, ENT-DE-06, ENT-DE-07, ENT-EX-04, ENT-CO-01, ENT-PE-03, ENT-DE-05, ENT-CA-04, ENT-PE-01, ENT-CO-02, ENT-PV-03, ENT-DE-04, ENT-IA-03, ENT-DI-03, ENT-PV-01.2, ENT-PE-02, ENT-CA-01.2</t>
+          <t>ENT-IM-01, ENT-IM-05, ENT-EF-02, ENT-IA-05, ENT-IM-02, ENT-IA-01, ENT-DM-01.1, ENT-LM-01, ENT-IA-02, ENT-CA-01.1, ENT-DM-01.2, ENT-ST-01, ENT-EX-01.1, ENT-DI-02, ENT-LM-02, ENT-C2-01.2, ENT-IM-03, ENT-DI-01, ENT-C2-05, ENT-EF-01, ENT-C2-04, ENT-C2-01.1, ENT-CA-03, ENT-EX-03, ENT-PV-01.1, ENT-IM-04, ENT-LM-03, ENT-PV-04, ENT-EX-01.2, ENT-C2-06, ENT-C2-03, ENT-ST-04, ENT-ST-05, ENT-EX-04, ENT-CO-01, ENT-PE-03, ENT-ST-03, ENT-CA-04, ENT-PE-01, ENT-CO-02, ENT-PV-03, ENT-ST-02, ENT-IA-03, ENT-DI-03, ENT-PV-01.2, ENT-PE-02, ENT-CA-01.2</t>
         </is>
       </c>
     </row>
@@ -3729,7 +3729,7 @@
       </c>
       <c r="E22" s="9" t="inlineStr">
         <is>
-          <t>ENT-DE-01.1, ENT-DE-01.2, ENT-IM-03, ENT-EX-03, ENT-DE-08, ENT-DE-07, ENT-DE-04, ENT-PE-02</t>
+          <t>ENT-DM-01.1, ENT-DM-01.2, ENT-IM-03, ENT-EX-03, ENT-ST-06, ENT-ST-05, ENT-ST-02, ENT-PE-02</t>
         </is>
       </c>
     </row>
@@ -3879,12 +3879,12 @@
       </c>
       <c r="G2" s="9" t="inlineStr">
         <is>
-          <t>IA · EX · PE · PV · DE · CA · DI · LM · CO · C2 · EF · IM</t>
+          <t>IA · EX · PE · PV · ST · DM · CA · DI · LM · CO · C2 · EF · IM</t>
         </is>
       </c>
       <c r="H2" s="9" t="inlineStr">
         <is>
-          <t>ENT-IA-02, ENT-IA-03, ENT-IA-04, ENT-IA-05, ENT-EX-01.1, ENT-EX-01.2, ENT-EX-03, ENT-EX-04, ENT-PE-01, ENT-PE-02, ENT-PE-03, ENT-PE-04, ENT-PV-01.1, ENT-PV-01.2, ENT-PV-03, ENT-DE-03, ENT-DE-04, ENT-DE-05, ENT-DE-06, ENT-DE-07, ENT-DE-08, ENT-CA-01.1, ENT-CA-01.2, ENT-CA-03, ENT-CA-04, ENT-DI-01, ENT-DI-02, ENT-DI-03, ENT-LM-01, ENT-LM-02, ENT-LM-03, ENT-LM-04, ENT-CO-01, ENT-CO-02, ENT-C2-01.1, ENT-C2-01.2, ENT-C2-03, ENT-C2-04, ENT-C2-05, ENT-C2-06, ENT-EF-01, ENT-EF-02, ENT-IM-01, ENT-IM-02, ENT-IM-03, ENT-IM-04, ENT-IM-05</t>
+          <t>ENT-IA-02, ENT-IA-03, ENT-IA-04, ENT-IA-05, ENT-EX-01.1, ENT-EX-01.2, ENT-EX-03, ENT-EX-04, ENT-PE-01, ENT-PE-02, ENT-PE-03, ENT-PE-04, ENT-PV-01.1, ENT-PV-01.2, ENT-PV-03, ENT-ST-01, ENT-ST-02, ENT-ST-03, ENT-ST-04, ENT-ST-05, ENT-ST-06, ENT-CA-01.1, ENT-CA-01.2, ENT-CA-03, ENT-CA-04, ENT-DI-01, ENT-DI-02, ENT-DI-03, ENT-LM-01, ENT-LM-02, ENT-LM-03, ENT-LM-04, ENT-CO-01, ENT-CO-02, ENT-C2-01.1, ENT-C2-01.2, ENT-C2-03, ENT-C2-04, ENT-C2-05, ENT-C2-06, ENT-EF-01, ENT-EF-02, ENT-IM-01, ENT-IM-02, ENT-IM-03, ENT-IM-04, ENT-IM-05</t>
         </is>
       </c>
       <c r="I2" s="9" t="inlineStr">
@@ -4003,12 +4003,12 @@
       </c>
       <c r="G4" s="9" t="inlineStr">
         <is>
-          <t>DE</t>
+          <t>DM</t>
         </is>
       </c>
       <c r="H4" s="9" t="inlineStr">
         <is>
-          <t>ENT-DE-01.1</t>
+          <t>ENT-DM-01.1</t>
         </is>
       </c>
       <c r="I4" s="9" t="inlineStr">
@@ -4189,12 +4189,12 @@
       </c>
       <c r="G7" s="9" t="inlineStr">
         <is>
-          <t>PV · DE</t>
+          <t>PV · DM</t>
         </is>
       </c>
       <c r="H7" s="9" t="inlineStr">
         <is>
-          <t>ENT-PV-04, ENT-DE-01.1, ENT-DE-01.2</t>
+          <t>ENT-PV-04, ENT-DM-01.1, ENT-DM-01.2</t>
         </is>
       </c>
       <c r="I7" s="9" t="inlineStr">
@@ -5008,7 +5008,7 @@
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>호스트·엔드포인트·네트워크·C2·방어 회피·온프레미스 AD 인접 기법만. 클라우드·신원·OT·AI·공급망 특화는 통합 v4.1 요약 ID로 연계만</t>
+          <t>호스트·엔드포인트·네트워크·C2·은닉·방어 무력화·온프레미스 AD 인접 기법만. 클라우드·신원·OT·AI·공급망 특화는 통합 v4.1 요약 ID로 연계만</t>
         </is>
       </c>
     </row>
@@ -5035,7 +5035,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F12"/>
+  <dimension ref="A1:F13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -5091,61 +5091,61 @@
       </c>
       <c r="C2" s="9" t="inlineStr">
         <is>
-          <t>평가</t>
+          <t>구조</t>
         </is>
       </c>
       <c r="D2" s="9" t="inlineStr">
         <is>
-          <t>빈발 지수·심각도 영향만·사고 정리(P1b·P2·P3)</t>
+          <t>v19 전술 분리 — 은닉·방어 무력화(P1)</t>
         </is>
       </c>
       <c r="E2" s="9" t="inlineStr">
         <is>
-          <t>편재 기법(LOLBin·WMI·Kerberoasting·UAC·지표 삭제·DNS/웹 C2·스테이징 등) 기법 일반 서술 9건을 사고 DB에서 제거하고 ATT&amp;CK 절차 수 기반 '빈발 지수'(≥100 상·≥30 중)로 발생가능성에 반영. Cobalt Strike(Operation MORPHEUS)·UEFI 임플란트(LoJax·MoonBounce)·Gamaredon USB·CISA #StopRansomware 4건은 실제 사례로 재구성. ATT&amp;CK 주체 수 하위 기법 롤업 버그 수정, BYOVD 매핑 정정(T1547.006 Linux 전용 제거→T1685·T1543.003). 심각도는 영향만으로 재판정(엔에이블러 상 26→8). 발생가능성 상에 서로 다른 행위자·캠페인 2개 요건, 경계 플래그 신설. 사고 33→24, 위험도 매우 높음 6·높음 15·보통 25·낮음 5</t>
+          <t>ATT&amp;CK v19(2026-04)의 방어 회피 분리를 반영(D15) — 구 방어 회피(DE) 8행을 은닉(ST, TA0005 유지) 6행·방어 무력화(DM, 신설 TA0112) 2행으로 재코딩. ENT-DE-* → ENT-ST-*(지표 삭제·위장·난독화·인메모리·루트킷·펌웨어)·ENT-DM-*(EDR 무력화 BYOVD·취약 드라이버 로드). 전술 12→13, DOMAIN_ORDER·TACTICS·frameworks 어휘·text(ST.yaml·DM.yaml 신설, DE.yaml 제거)·사고 매핑·시나리오 전술 라벨 일괄 갱신. 저장소 ATT&amp;CK v19.2 추출본 전술 배정과 대조(이벤트 로그 삭제 T1685.005만 v19 DM이나 흔적 제거 목적이라 ST 행에 함께 매핑). 세부위협 51행·검증 오류·경고 0 유지</t>
         </is>
       </c>
       <c r="F2" s="9" t="inlineStr">
         <is>
-          <t>검토 5.1~5.4·6.1 — 근거 무결성·렌즈 변별력 교정</t>
+          <t>검토 D15 — ATT&amp;CK v19.2 전술 체계 반영</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="9" t="inlineStr">
         <is>
-          <t>v1</t>
+          <t>v3</t>
         </is>
       </c>
       <c r="B3" s="9" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="C3" s="9" t="inlineStr">
         <is>
-          <t>구조</t>
+          <t>평가</t>
         </is>
       </c>
       <c r="D3" s="9" t="inlineStr">
         <is>
-          <t>워크북·CSV(scripts/build_enterprise_threat_matrix.py)</t>
+          <t>빈발 지수·심각도 영향만·사고 정리(P1b·P2·P3)</t>
         </is>
       </c>
       <c r="E3" s="9" t="inlineStr">
         <is>
-          <t>15시트 워크북·CSV 생성(세부위협 51행). aiattack 빌드를 이식하되 레거시 공백·요구 방어 수준 고유 축 시트와 ATT&amp;CK·KEV 교차 시트를 둠. 위험도 매우 높음 17·높음 12·보통 21·낮음 1, 근거 수준 실제 사고 45·ATT&amp;CK/KEV 다수 3·일부 2·이론 1. 우선순위에 요구 방어 수준(방어 난이도)·ATT&amp;CK 주체 수 보조(D5). 빌드 전 검증기 자동 실행</t>
+          <t>편재 기법(LOLBin·WMI·Kerberoasting·UAC·지표 삭제·DNS/웹 C2·스테이징 등) 기법 일반 서술 9건을 사고 DB에서 제거하고 ATT&amp;CK 절차 수 기반 '빈발 지수'(≥100 상·≥30 중)로 발생가능성에 반영. Cobalt Strike(Operation MORPHEUS)·UEFI 임플란트(LoJax·MoonBounce)·Gamaredon USB·CISA #StopRansomware 4건은 실제 사례로 재구성. ATT&amp;CK 주체 수 하위 기법 롤업 버그 수정, BYOVD 매핑 정정(T1547.006 Linux 전용 제거→T1685·T1543.003). 심각도는 영향만으로 재판정(엔에이블러 상 26→8). 발생가능성 상에 서로 다른 행위자·캠페인 2개 요건, 경계 플래그 신설. 사고 33→24, 위험도 매우 높음 6·높음 15·보통 25·낮음 5</t>
         </is>
       </c>
       <c r="F3" s="9" t="inlineStr">
         <is>
-          <t>②단계(v1) — 분류·근거·평가를 한 워크북에서 검토</t>
+          <t>검토 5.1~5.4·6.1 — 근거 무결성·렌즈 변별력 교정</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="9" t="inlineStr">
         <is>
-          <t>v2</t>
+          <t>v1</t>
         </is>
       </c>
       <c r="B4" s="9" t="inlineStr">
@@ -5155,22 +5155,22 @@
       </c>
       <c r="C4" s="9" t="inlineStr">
         <is>
-          <t>문구</t>
+          <t>구조</t>
         </is>
       </c>
       <c r="D4" s="9" t="inlineStr">
         <is>
-          <t>관점 문구(data/text/*.yaml)</t>
+          <t>워크북·CSV(scripts/build_enterprise_threat_matrix.py)</t>
         </is>
       </c>
       <c r="E4" s="9" t="inlineStr">
         <is>
-          <t>51개 행 전부에 핵심 요약·요약설명·참조(■ 관점·■ 실제 사례)·탐지·대응 작성. 인용 사례 83건([실제 사고]·[정부 경보]·[실증]), 실제 사고가 없는 5개 행(드라이브바이·네이티브 API·계정 조작·캐시 자격증명·보안 SW 탐색)은 '공개 사고 미확인 — 사유'로 표기. 가드레일 D11(공세 제작법 미기재, 탐지·대응 중심) 적용</t>
+          <t>15시트 워크북·CSV 생성(세부위협 51행). aiattack 빌드를 이식하되 레거시 공백·요구 방어 수준 고유 축 시트와 ATT&amp;CK·KEV 교차 시트를 둠. 위험도 매우 높음 17·높음 12·보통 21·낮음 1, 근거 수준 실제 사고 45·ATT&amp;CK/KEV 다수 3·일부 2·이론 1. 우선순위에 요구 방어 수준(방어 난이도)·ATT&amp;CK 주체 수 보조(D5). 빌드 전 검증기 자동 실행</t>
         </is>
       </c>
       <c r="F4" s="9" t="inlineStr">
         <is>
-          <t>③단계(v2) — 방어 관점으로 행마다 근거·통제를 연결</t>
+          <t>②단계(v1) — 분류·근거·평가를 한 워크북에서 검토</t>
         </is>
       </c>
     </row>
@@ -5187,22 +5187,22 @@
       </c>
       <c r="C5" s="9" t="inlineStr">
         <is>
-          <t>시나리오</t>
+          <t>문구</t>
         </is>
       </c>
       <c r="D5" s="9" t="inlineStr">
         <is>
-          <t>공격 체인 시나리오(data/scenarios.yaml)</t>
+          <t>관점 문구(data/text/*.yaml)</t>
         </is>
       </c>
       <c r="E5" s="9" t="inlineStr">
         <is>
-          <t>실제 사고를 침해 흐름 8개로 재구성(ESN-01~08) — 엣지 0-day→LotL→확산, 사람 운영 랜섬웨어(BYOVD·복구 방해), 파일전송 0-day 갈취(Cl0p), 웜 확산→파괴, 비콘 C2, MSP 신뢰 관계, 지표 삭제 은닉, 커널·펌웨어 하위 계층. 21개 단계·초크 포인트 16개</t>
+          <t>51개 행 전부에 핵심 요약·요약설명·참조(■ 관점·■ 실제 사례)·탐지·대응 작성. 인용 사례 83건([실제 사고]·[정부 경보]·[실증]), 실제 사고가 없는 5개 행(드라이브바이·네이티브 API·계정 조작·캐시 자격증명·보안 SW 탐색)은 '공개 사고 미확인 — 사유'로 표기. 가드레일 D11(공세 제작법 미기재, 탐지·대응 중심) 적용</t>
         </is>
       </c>
       <c r="F5" s="9" t="inlineStr">
         <is>
-          <t>한 행=한 행위로 나눈 세부위협을 흐름 안에서 보고 차단 지점을 드러냄</t>
+          <t>③단계(v2) — 방어 관점으로 행마다 근거·통제를 연결</t>
         </is>
       </c>
     </row>
@@ -5219,29 +5219,29 @@
       </c>
       <c r="C6" s="9" t="inlineStr">
         <is>
-          <t>검증</t>
+          <t>시나리오</t>
         </is>
       </c>
       <c r="D6" s="9" t="inlineStr">
         <is>
-          <t>scripts/validate.py</t>
+          <t>공격 체인 시나리오(data/scenarios.yaml)</t>
         </is>
       </c>
       <c r="E6" s="9" t="inlineStr">
         <is>
-          <t>문구·시나리오 검사 이식 — 형식, 사례 라벨↔집계 상태·시점·수치 대조, 참조 ID(ATT&amp;CK·CVE↔KEV·NIST·연계) 존재·행 매핑, 가드레일. 문구 51·시나리오 8을 --strict로 검증해 오류·경고 0</t>
+          <t>실제 사고를 침해 흐름 8개로 재구성(ESN-01~08) — 엣지 0-day→LotL→확산, 사람 운영 랜섬웨어(BYOVD·복구 방해), 파일전송 0-day 갈취(Cl0p), 웜 확산→파괴, 비콘 C2, MSP 신뢰 관계, 지표 삭제 은닉, 커널·펌웨어 하위 계층. 21개 단계·초크 포인트 16개</t>
         </is>
       </c>
       <c r="F6" s="9" t="inlineStr">
         <is>
-          <t>문구·시나리오를 사고 DB·카탈로그와 기계적으로 대조</t>
+          <t>한 행=한 행위로 나눈 세부위협을 흐름 안에서 보고 차단 지점을 드러냄</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="9" t="inlineStr">
         <is>
-          <t>v0</t>
+          <t>v2</t>
         </is>
       </c>
       <c r="B7" s="9" t="inlineStr">
@@ -5251,22 +5251,22 @@
       </c>
       <c r="C7" s="9" t="inlineStr">
         <is>
-          <t>결정</t>
+          <t>검증</t>
         </is>
       </c>
       <c r="D7" s="9" t="inlineStr">
         <is>
-          <t>작업방향 D5~D7·D9·D11·D12</t>
+          <t>scripts/validate.py</t>
         </is>
       </c>
       <c r="E7" s="9" t="inlineStr">
         <is>
-          <t>영역 2(고도화 엔터프라이즈 침해) 착수 결정 확정 — D5(ATT&amp;CK Enterprise에서 고도화·최근빈발·레거시난제 점수로 ~50행 선별, 자산 특화는 연계)·D6(Lv1 ATT&amp;CK 전술 + 레거시 공백 유형·요구 방어 수준 축)·D7(호스트·엔드포인트·네트워크·C2·회피·온프레미스 AD 인접, 클라우드·신원·OT·AI·공급망은 연계)·D9(통합본 뷰 Lv0)·D11(방어 자료 가드레일)·D12(v4.1 베이스라인)</t>
+          <t>문구·시나리오 검사 이식 — 형식, 사례 라벨↔집계 상태·시점·수치 대조, 참조 ID(ATT&amp;CK·CVE↔KEV·NIST·연계) 존재·행 매핑, 가드레일. 문구 51·시나리오 8을 --strict로 검증해 오류·경고 0</t>
         </is>
       </c>
       <c r="F7" s="9" t="inlineStr">
         <is>
-          <t>emerging/작업방향 10장 권장안을 영역 2 착수 결정으로 확정</t>
+          <t>문구·시나리오를 사고 DB·카탈로그와 기계적으로 대조</t>
         </is>
       </c>
     </row>
@@ -5283,22 +5283,22 @@
       </c>
       <c r="C8" s="9" t="inlineStr">
         <is>
-          <t>구조</t>
+          <t>결정</t>
         </is>
       </c>
       <c r="D8" s="9" t="inlineStr">
         <is>
-          <t>분류 체계(data/taxonomy.yaml)</t>
+          <t>작업방향 D5~D7·D9·D11·D12</t>
         </is>
       </c>
       <c r="E8" s="9" t="inlineStr">
         <is>
-          <t>ATT&amp;CK Enterprise 침투~영향 12개 전술 도메인(IA·EX·PE·PV·DE·CA·DI·LM·CO·C2·EF·IM) → 위협분류 → 세부위협 51개 ID 대장(ENT-&lt;전술&gt;-NN). 전술 14개 중 정찰·자원 개발은 영역 1·정찰이 다뤄 제외·연계(D7). 행마다 레거시 방어 공백 유형·요구 방어 수준·주체·플랫폼·ATT&amp;CK·KEV·LOLBin·BYOVD 드라이버·대응 기준·연계·심각도. 심각도 상 26·중 24·하 1, 요구 방어 수준 '행위·네트워크·아이덴티티' 27·'EDR·XDR' 24</t>
+          <t>영역 2(고도화 엔터프라이즈 침해) 착수 결정 확정 — D5(ATT&amp;CK Enterprise에서 고도화·최근빈발·레거시난제 점수로 ~50행 선별, 자산 특화는 연계)·D6(Lv1 ATT&amp;CK 전술 + 레거시 공백 유형·요구 방어 수준 축)·D7(호스트·엔드포인트·네트워크·C2·회피·온프레미스 AD 인접, 클라우드·신원·OT·AI·공급망은 연계)·D9(통합본 뷰 Lv0)·D11(방어 자료 가드레일)·D12(v4.1 베이스라인)</t>
         </is>
       </c>
       <c r="F8" s="9" t="inlineStr">
         <is>
-          <t>D5·D6 확정안을 행 단위로 구현 — ①단계</t>
+          <t>emerging/작업방향 10장 권장안을 영역 2 착수 결정으로 확정</t>
         </is>
       </c>
     </row>
@@ -5315,22 +5315,22 @@
       </c>
       <c r="C9" s="9" t="inlineStr">
         <is>
-          <t>근거</t>
+          <t>구조</t>
         </is>
       </c>
       <c r="D9" s="9" t="inlineStr">
         <is>
-          <t>사고 DB(data/incidents.yaml)</t>
+          <t>분류 체계(data/taxonomy.yaml)</t>
         </is>
       </c>
       <c r="E9" s="9" t="inlineStr">
         <is>
-          <t>고도화·레거시 우회 침해 사고 33건 구축 — 경계·엣지 0-day(Citrix Bleed·MOVEit·Fortinet·Ivanti·Cisco IOS XE·PAN-OS·ScreenConnect·Cleo), 국가배후 LotL(Volt Typhoon·APT28 Nearest Neighbor), 사람 운영 랜섬웨어(Black Basta·Scattered Spider·Akira·LockBit·RansomHub), BYOVD EDR 킬러, 웜 확산(NotPetya·WannaCry), 커널·펌웨어(BlackLotus·루트킷·펌웨어 임플란트), C2·DNS·이동식 매체. 실제 사고가 매핑된 세부위협 45/51. CVE는 KEV 목록과 대조</t>
+          <t>ATT&amp;CK Enterprise 침투~영향 12개 전술 도메인(IA·EX·PE·PV·DE·CA·DI·LM·CO·C2·EF·IM) → 위협분류 → 세부위협 51개 ID 대장(ENT-&lt;전술&gt;-NN). 전술 14개 중 정찰·자원 개발은 영역 1·정찰이 다뤄 제외·연계(D7). 행마다 레거시 방어 공백 유형·요구 방어 수준·주체·플랫폼·ATT&amp;CK·KEV·LOLBin·BYOVD 드라이버·대응 기준·연계·심각도. 심각도 상 26·중 24·하 1, 요구 방어 수준 '행위·네트워크·아이덴티티' 27·'EDR·XDR' 24</t>
         </is>
       </c>
       <c r="F9" s="9" t="inlineStr">
         <is>
-          <t>D8 — 호스트·엔드포인트·네트워크·랜섬웨어·엣지 0-day 사례로 근거 구축</t>
+          <t>D5·D6 확정안을 행 단위로 구현 — ①단계</t>
         </is>
       </c>
     </row>
@@ -5347,22 +5347,22 @@
       </c>
       <c r="C10" s="9" t="inlineStr">
         <is>
-          <t>교차 매핑</t>
+          <t>근거</t>
         </is>
       </c>
       <c r="D10" s="9" t="inlineStr">
         <is>
-          <t>프레임워크·참고 문헌(data/frameworks.yaml)</t>
+          <t>사고 DB(data/incidents.yaml)</t>
         </is>
       </c>
       <c r="E10" s="9" t="inlineStr">
         <is>
-          <t>ATT&amp;CK Enterprise v19.2(1차 분류·근거), CISA KEV 2026.10.02(1,733건), LOLBAS 245·LOLDrivers 706, NIST SP 800-53 Rev.5, 참고 문헌 카탈로그 8종(ATT&amp;CK·KEV·CISA·Mandiant·LOLBAS·LOLDrivers·Hive·Securelist)</t>
+          <t>고도화·레거시 우회 침해 사고 33건 구축 — 경계·엣지 0-day(Citrix Bleed·MOVEit·Fortinet·Ivanti·Cisco IOS XE·PAN-OS·ScreenConnect·Cleo), 국가배후 LotL(Volt Typhoon·APT28 Nearest Neighbor), 사람 운영 랜섬웨어(Black Basta·Scattered Spider·Akira·LockBit·RansomHub), BYOVD EDR 킬러, 웜 확산(NotPetya·WannaCry), 커널·펌웨어(BlackLotus·루트킷·펌웨어 임플란트), C2·DNS·이동식 매체. 실제 사고가 매핑된 세부위협 45/51. CVE는 KEV 목록과 대조</t>
         </is>
       </c>
       <c r="F10" s="9" t="inlineStr">
         <is>
-          <t>역할별 교차 매핑·근거 출처와 이용 조건을 행 매핑 전에 고정</t>
+          <t>D8 — 호스트·엔드포인트·네트워크·랜섬웨어·엣지 0-day 사례로 근거 구축</t>
         </is>
       </c>
     </row>
@@ -5379,22 +5379,22 @@
       </c>
       <c r="C11" s="9" t="inlineStr">
         <is>
-          <t>근거</t>
+          <t>교차 매핑</t>
         </is>
       </c>
       <c r="D11" s="9" t="inlineStr">
         <is>
-          <t>참조 추출본(reference/)</t>
+          <t>프레임워크·참고 문헌(data/frameworks.yaml)</t>
         </is>
       </c>
       <c r="E11" s="9" t="inlineStr">
         <is>
-          <t>ATT&amp;CK 추출본(prepare_attack.py — 기법 68·주체 977·절차 6,087, 절차 수는 최근빈발 신호), KEV 추출본(prepare_kev.py — 연도별 등재·경계/엣지 장비 비중 14~21%·같은 해 악용 비중), LOLBAS·LOLDrivers 추출본(prepare_lolbas.py), NIST·통합 v4.1 연계 ID 237개(prepare_refs.py)</t>
+          <t>ATT&amp;CK Enterprise v19.2(1차 분류·근거), CISA KEV 2026.10.02(1,733건), LOLBAS 245·LOLDrivers 706, NIST SP 800-53 Rev.5, 참고 문헌 카탈로그 8종(ATT&amp;CK·KEV·CISA·Mandiant·LOLBAS·LOLDrivers·Hive·Securelist)</t>
         </is>
       </c>
       <c r="F11" s="9" t="inlineStr">
         <is>
-          <t>빌드·검증을 저장소 안에서 재현. 겹치는 위협은 통합 v4.1 요약 ID로 연계만(D9)</t>
+          <t>역할별 교차 매핑·근거 출처와 이용 조건을 행 매핑 전에 고정</t>
         </is>
       </c>
     </row>
@@ -5411,20 +5411,52 @@
       </c>
       <c r="C12" s="9" t="inlineStr">
         <is>
+          <t>근거</t>
+        </is>
+      </c>
+      <c r="D12" s="9" t="inlineStr">
+        <is>
+          <t>참조 추출본(reference/)</t>
+        </is>
+      </c>
+      <c r="E12" s="9" t="inlineStr">
+        <is>
+          <t>ATT&amp;CK 추출본(prepare_attack.py — 기법 68·주체 977·절차 6,087, 절차 수는 최근빈발 신호), KEV 추출본(prepare_kev.py — 연도별 등재·경계/엣지 장비 비중 14~21%·같은 해 악용 비중), LOLBAS·LOLDrivers 추출본(prepare_lolbas.py), NIST·통합 v4.1 연계 ID 237개(prepare_refs.py)</t>
+        </is>
+      </c>
+      <c r="F12" s="9" t="inlineStr">
+        <is>
+          <t>빌드·검증을 저장소 안에서 재현. 겹치는 위협은 통합 v4.1 요약 ID로 연계만(D9)</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="9" t="inlineStr">
+        <is>
+          <t>v0</t>
+        </is>
+      </c>
+      <c r="B13" s="9" t="inlineStr">
+        <is>
+          <t>2026-10-26</t>
+        </is>
+      </c>
+      <c r="C13" s="9" t="inlineStr">
+        <is>
           <t>검증</t>
         </is>
       </c>
-      <c r="D12" s="9" t="inlineStr">
+      <c r="D13" s="9" t="inlineStr">
         <is>
           <t>scripts/validate.py · taxonomy_rules.py</t>
         </is>
       </c>
-      <c r="E12" s="9" t="inlineStr">
+      <c r="E13" s="9" t="inlineStr">
         <is>
           <t>검증기를 aiattack·물리 매트릭스 기준으로 이식 — 분류 체계 필드·어휘·ID 체계, ATT&amp;CK·KEV·NIST·연계·참고 문헌 키 존재, CVE↔KEV 대조, 레거시 공백·요구 방어 수준·주체·플랫폼 어휘, 사고 DB 필드·매핑·출처. 데이터 검증 오류·경고 0</t>
         </is>
       </c>
-      <c r="F12" s="9" t="inlineStr">
+      <c r="F13" s="9" t="inlineStr">
         <is>
           <t>①단계 완료 기준(매핑·참조 ID 전부 카탈로그에 존재, 검증 데이터 통과) 자동 확인</t>
         </is>
@@ -6019,12 +6051,12 @@
       </c>
       <c r="B12" s="9" t="inlineStr">
         <is>
-          <t>[DE] 방어 회피</t>
+          <t>[DM] 방어 무력화</t>
         </is>
       </c>
       <c r="C12" s="10" t="inlineStr">
         <is>
-          <t>ENT-DE-01.1</t>
+          <t>ENT-DM-01.1</t>
         </is>
       </c>
       <c r="D12" s="10" t="inlineStr">
@@ -6275,12 +6307,12 @@
       </c>
       <c r="B16" s="9" t="inlineStr">
         <is>
-          <t>[DE] 방어 회피</t>
+          <t>[DM] 방어 무력화</t>
         </is>
       </c>
       <c r="C16" s="10" t="inlineStr">
         <is>
-          <t>ENT-DE-01.2</t>
+          <t>ENT-DM-01.2</t>
         </is>
       </c>
       <c r="D16" s="10" t="inlineStr">
@@ -6339,12 +6371,12 @@
       </c>
       <c r="B17" s="9" t="inlineStr">
         <is>
-          <t>[DE] 방어 회피</t>
+          <t>[ST] 은닉</t>
         </is>
       </c>
       <c r="C17" s="10" t="inlineStr">
         <is>
-          <t>ENT-DE-03</t>
+          <t>ENT-ST-01</t>
         </is>
       </c>
       <c r="D17" s="10" t="inlineStr">
@@ -7191,12 +7223,12 @@
       </c>
       <c r="B30" s="9" t="inlineStr">
         <is>
-          <t>[DE] 방어 회피</t>
+          <t>[ST] 은닉</t>
         </is>
       </c>
       <c r="C30" s="10" t="inlineStr">
         <is>
-          <t>ENT-DE-08</t>
+          <t>ENT-ST-06</t>
         </is>
       </c>
       <c r="D30" s="10" t="inlineStr">
@@ -7771,12 +7803,12 @@
       </c>
       <c r="B39" s="9" t="inlineStr">
         <is>
-          <t>[DE] 방어 회피</t>
+          <t>[ST] 은닉</t>
         </is>
       </c>
       <c r="C39" s="10" t="inlineStr">
         <is>
-          <t>ENT-DE-06</t>
+          <t>ENT-ST-04</t>
         </is>
       </c>
       <c r="D39" s="10" t="inlineStr">
@@ -7835,12 +7867,12 @@
       </c>
       <c r="B40" s="9" t="inlineStr">
         <is>
-          <t>[DE] 방어 회피</t>
+          <t>[ST] 은닉</t>
         </is>
       </c>
       <c r="C40" s="10" t="inlineStr">
         <is>
-          <t>ENT-DE-07</t>
+          <t>ENT-ST-05</t>
         </is>
       </c>
       <c r="D40" s="10" t="inlineStr">
@@ -8091,12 +8123,12 @@
       </c>
       <c r="B44" s="9" t="inlineStr">
         <is>
-          <t>[DE] 방어 회피</t>
+          <t>[ST] 은닉</t>
         </is>
       </c>
       <c r="C44" s="10" t="inlineStr">
         <is>
-          <t>ENT-DE-05</t>
+          <t>ENT-ST-03</t>
         </is>
       </c>
       <c r="D44" s="10" t="inlineStr">
@@ -8411,12 +8443,12 @@
       </c>
       <c r="B49" s="9" t="inlineStr">
         <is>
-          <t>[DE] 방어 회피</t>
+          <t>[ST] 은닉</t>
         </is>
       </c>
       <c r="C49" s="10" t="inlineStr">
         <is>
-          <t>ENT-DE-04</t>
+          <t>ENT-ST-02</t>
         </is>
       </c>
       <c r="D49" s="10" t="inlineStr">
@@ -8865,7 +8897,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L10"/>
+  <dimension ref="A1:M8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -8880,6 +8912,7 @@
     <col width="22" customWidth="1" min="10" max="10"/>
     <col width="22" customWidth="1" min="11" max="11"/>
     <col width="22" customWidth="1" min="12" max="12"/>
+    <col width="22" customWidth="1" min="13" max="13"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -8920,54 +8953,61 @@
       </c>
       <c r="E2" s="15" t="inlineStr">
         <is>
-          <t>[DE] 방어 회피
-Defense Evasion
-(8)</t>
+          <t>[ST] 은닉
+Stealth
+(6)</t>
         </is>
       </c>
       <c r="F2" s="15" t="inlineStr">
+        <is>
+          <t>[DM] 방어 무력화
+Defense Impairment
+(2)</t>
+        </is>
+      </c>
+      <c r="G2" s="15" t="inlineStr">
         <is>
           <t>[CA] 자격증명 접근
 Credential Access
 (4)</t>
         </is>
       </c>
-      <c r="G2" s="15" t="inlineStr">
+      <c r="H2" s="15" t="inlineStr">
         <is>
           <t>[DI] 탐색
 Discovery
 (3)</t>
         </is>
       </c>
-      <c r="H2" s="15" t="inlineStr">
+      <c r="I2" s="15" t="inlineStr">
         <is>
           <t>[LM] 측면 이동
 Lateral Movement
 (4)</t>
         </is>
       </c>
-      <c r="I2" s="15" t="inlineStr">
+      <c r="J2" s="15" t="inlineStr">
         <is>
           <t>[CO] 수집
 Collection
 (2)</t>
         </is>
       </c>
-      <c r="J2" s="15" t="inlineStr">
+      <c r="K2" s="15" t="inlineStr">
         <is>
           <t>[C2] 명령·제어
 Command and Control
 (6)</t>
         </is>
       </c>
-      <c r="K2" s="15" t="inlineStr">
+      <c r="L2" s="15" t="inlineStr">
         <is>
           <t>[EF] 반출
 Exfiltration
 (2)</t>
         </is>
       </c>
-      <c r="L2" s="15" t="inlineStr">
+      <c r="M2" s="15" t="inlineStr">
         <is>
           <t>[IM] 영향
 Impact
@@ -8998,40 +9038,45 @@
       </c>
       <c r="E3" s="17" t="inlineStr">
         <is>
-          <t>ENT-DE-01.1 보안 도구 무력화(EDR 변조·BYOVD EDR 킬러) [7]</t>
+          <t>ENT-ST-01 지표 삭제(이벤트 로그·파일 삭제) [2]</t>
         </is>
       </c>
       <c r="F3" s="17" t="inlineStr">
         <is>
+          <t>ENT-DM-01.1 보안 도구 무력화(EDR 변조·BYOVD EDR 킬러) [7]</t>
+        </is>
+      </c>
+      <c r="G3" s="17" t="inlineStr">
+        <is>
           <t>ENT-CA-01.1 OS 자격증명 덤프(LSASS 메모리) [4]</t>
         </is>
       </c>
-      <c r="G3" s="17" t="inlineStr">
+      <c r="H3" s="17" t="inlineStr">
         <is>
           <t>ENT-DI-02 도메인·AD 열거(계정·신뢰·공유) [2]</t>
         </is>
       </c>
-      <c r="H3" s="16" t="inlineStr">
+      <c r="I3" s="16" t="inlineStr">
         <is>
           <t>ENT-LM-04 원격 서비스 취약점 악용(웜 확산) [2]</t>
         </is>
       </c>
-      <c r="I3" s="18" t="inlineStr">
+      <c r="J3" s="18" t="inlineStr">
         <is>
           <t>ENT-CO-01 로컬·네트워크 공유 데이터 수집</t>
         </is>
       </c>
-      <c r="J3" s="17" t="inlineStr">
+      <c r="K3" s="17" t="inlineStr">
         <is>
           <t>ENT-C2-01.2 응용 계층 프로토콜(HTTPS) C2 [1]</t>
         </is>
       </c>
-      <c r="K3" s="16" t="inlineStr">
+      <c r="L3" s="16" t="inlineStr">
         <is>
           <t>ENT-EF-02 정상 웹 서비스·대체 프로토콜 경유 반출 [2]</t>
         </is>
       </c>
-      <c r="L3" s="16" t="inlineStr">
+      <c r="M3" s="16" t="inlineStr">
         <is>
           <t>ENT-IM-01 데이터 암호화(사람 운영 랜섬웨어) [8]</t>
         </is>
@@ -9058,42 +9103,47 @@
           <t>ENT-PV-04 권한 상승 취약점 악용(로컬·커널) [1]</t>
         </is>
       </c>
-      <c r="E4" s="17" t="inlineStr">
-        <is>
-          <t>ENT-DE-01.2 취약·악성 드라이버 로드(커널) [3]</t>
-        </is>
-      </c>
-      <c r="F4" s="18" t="inlineStr">
+      <c r="E4" s="18" t="inlineStr">
+        <is>
+          <t>ENT-ST-06 펌웨어·부트킷(UEFI) 지속·은닉 [1]</t>
+        </is>
+      </c>
+      <c r="F4" s="17" t="inlineStr">
+        <is>
+          <t>ENT-DM-01.2 취약·악성 드라이버 로드(커널) [3]</t>
+        </is>
+      </c>
+      <c r="G4" s="18" t="inlineStr">
         <is>
           <t>ENT-CA-03 Kerberoasting·AS-REP 로스팅 [1]</t>
         </is>
       </c>
-      <c r="G4" s="17" t="inlineStr">
+      <c r="H4" s="17" t="inlineStr">
         <is>
           <t>ENT-DI-01 호스트·시스템·네트워크 구성 탐색 [1]</t>
         </is>
       </c>
-      <c r="H4" s="17" t="inlineStr">
+      <c r="I4" s="17" t="inlineStr">
         <is>
           <t>ENT-LM-01 원격 서비스 악용(RDP·SMB·WinRM) [5]</t>
         </is>
       </c>
-      <c r="I4" s="18" t="inlineStr">
+      <c r="J4" s="18" t="inlineStr">
         <is>
           <t>ENT-CO-02 수집 데이터 압축·암호화 스테이징</t>
         </is>
       </c>
-      <c r="J4" s="17" t="inlineStr">
+      <c r="K4" s="17" t="inlineStr">
         <is>
           <t>ENT-C2-05 인그레스 도구 전송(페이로드 반입) [1]</t>
         </is>
       </c>
-      <c r="K4" s="17" t="inlineStr">
+      <c r="L4" s="17" t="inlineStr">
         <is>
           <t>ENT-EF-01 C2 채널 경유 반출</t>
         </is>
       </c>
-      <c r="L4" s="16" t="inlineStr">
+      <c r="M4" s="16" t="inlineStr">
         <is>
           <t>ENT-IM-02 복구 방해(섀도 카피·백업 삭제) [2]</t>
         </is>
@@ -9120,32 +9170,32 @@
           <t>ENT-PV-03 사용자 계정 컨트롤(UAC) 우회</t>
         </is>
       </c>
-      <c r="E5" s="17" t="inlineStr">
-        <is>
-          <t>ENT-DE-03 지표 삭제(이벤트 로그·파일 삭제) [2]</t>
-        </is>
-      </c>
-      <c r="F5" s="18" t="inlineStr">
+      <c r="E5" s="18" t="inlineStr">
+        <is>
+          <t>ENT-ST-02 위장(정상 이름·경로·서명 가장)</t>
+        </is>
+      </c>
+      <c r="G5" s="18" t="inlineStr">
         <is>
           <t>ENT-CA-04 입력 캡처·키로깅</t>
         </is>
       </c>
-      <c r="G5" s="19" t="inlineStr">
+      <c r="H5" s="19" t="inlineStr">
         <is>
           <t>ENT-DI-03 보안 소프트웨어·방어 환경 탐색</t>
         </is>
       </c>
-      <c r="H5" s="17" t="inlineStr">
+      <c r="I5" s="17" t="inlineStr">
         <is>
           <t>ENT-LM-02 대체 인증 자료 사용(Pass-the-Hash·Pass-the-Ticket) [2]</t>
         </is>
       </c>
-      <c r="J5" s="18" t="inlineStr">
+      <c r="K5" s="18" t="inlineStr">
         <is>
           <t>ENT-C2-01.1 암호화 채널·비표준/정상 포트 위장 C2 [1]</t>
         </is>
       </c>
-      <c r="L5" s="16" t="inlineStr">
+      <c r="M5" s="16" t="inlineStr">
         <is>
           <t>ENT-IM-05 금전 탈취·이중 협박 갈취 [2]</t>
         </is>
@@ -9174,25 +9224,25 @@
       </c>
       <c r="E6" s="18" t="inlineStr">
         <is>
-          <t>ENT-DE-08 펌웨어·부트킷(UEFI) 지속·은닉 [1]</t>
-        </is>
-      </c>
-      <c r="F6" s="19" t="inlineStr">
+          <t>ENT-ST-03 파일·정보 난독화·암호화</t>
+        </is>
+      </c>
+      <c r="G6" s="19" t="inlineStr">
         <is>
           <t>ENT-CA-01.2 캐시된 도메인 자격증명 추출</t>
         </is>
       </c>
-      <c r="H6" s="18" t="inlineStr">
+      <c r="I6" s="18" t="inlineStr">
         <is>
           <t>ENT-LM-03 측면 도구 전송 [1]</t>
         </is>
       </c>
-      <c r="J6" s="18" t="inlineStr">
+      <c r="K6" s="18" t="inlineStr">
         <is>
           <t>ENT-C2-04 도메인 프런팅·다단계 프록시 [1]</t>
         </is>
       </c>
-      <c r="L6" s="17" t="inlineStr">
+      <c r="M6" s="17" t="inlineStr">
         <is>
           <t>ENT-IM-03 데이터 파괴·와이퍼 [1]</t>
         </is>
@@ -9206,15 +9256,15 @@
       </c>
       <c r="E7" s="18" t="inlineStr">
         <is>
-          <t>ENT-DE-04 위장(정상 이름·경로·서명 가장)</t>
-        </is>
-      </c>
-      <c r="J7" s="18" t="inlineStr">
+          <t>ENT-ST-04 인메모리·반사 코드 로딩</t>
+        </is>
+      </c>
+      <c r="K7" s="18" t="inlineStr">
         <is>
           <t>ENT-C2-03 정상 웹 서비스·클라우드 플랫폼 경유 C2</t>
         </is>
       </c>
-      <c r="L7" s="18" t="inlineStr">
+      <c r="M7" s="18" t="inlineStr">
         <is>
           <t>ENT-IM-04 서비스 중지·시스템 종료/재시작 [1]</t>
         </is>
@@ -9223,26 +9273,12 @@
     <row r="8">
       <c r="E8" s="18" t="inlineStr">
         <is>
-          <t>ENT-DE-05 파일·정보 난독화·암호화</t>
-        </is>
-      </c>
-      <c r="J8" s="18" t="inlineStr">
+          <t>ENT-ST-05 루트킷(사용자·커널 은폐)</t>
+        </is>
+      </c>
+      <c r="K8" s="18" t="inlineStr">
         <is>
           <t>ENT-C2-06 DNS 경유 C2·터널링</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="E9" s="18" t="inlineStr">
-        <is>
-          <t>ENT-DE-06 인메모리·반사 코드 로딩</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="E10" s="18" t="inlineStr">
-        <is>
-          <t>ENT-DE-07 루트킷(사용자·커널 은폐)</t>
         </is>
       </c>
     </row>
@@ -12295,38 +12331,38 @@
     <row r="22">
       <c r="A22" s="9" t="inlineStr">
         <is>
-          <t>[DE] 방어 회피</t>
+          <t>[ST] 은닉</t>
         </is>
       </c>
       <c r="B22" s="9" t="inlineStr">
         <is>
-          <t>ENT-DE-01.1</t>
+          <t>ENT-ST-01</t>
         </is>
       </c>
       <c r="C22" s="9" t="inlineStr">
         <is>
-          <t>보안 도구 무력화·드라이버 로드</t>
+          <t>지표 삭제</t>
         </is>
       </c>
       <c r="D22" s="9" t="inlineStr">
         <is>
-          <t>보안 도구 무력화(EDR 변조·BYOVD EDR 킬러)</t>
+          <t>지표 삭제(이벤트 로그·파일 삭제)</t>
         </is>
       </c>
       <c r="E22" s="9" t="inlineStr">
         <is>
-          <t>서명된 취약 드라이버로 EDR·백신을 커널에서 무력화(BYOVD)</t>
+          <t>이벤트 로그·파일 삭제로 레거시 SIEM 탐지·분석 무력화</t>
         </is>
       </c>
       <c r="F22" s="9" t="inlineStr">
         <is>
-          <t>- 공격자는 서명된 취약 드라이버를 올려 EDR·백신을 커널에서 무력화할 수 있음
-- 보안 도구 자체가 꺼지므로 이후 단계가 전부 가려지고, 여러 랜섬웨어·국가배후가 EDR 킬러를 공유함</t>
+          <t>- 공격자는 이벤트 로그·파일을 지워 레거시 SIEM 탐지와 사후 분석을 무력화할 수 있음
+- 원격·불변 로그가 없으면 흔적이 사라져 추적이 어려워짐</t>
         </is>
       </c>
       <c r="G22" s="9" t="inlineStr">
         <is>
-          <t>Impair/disable security tools (EDR tampering, BYOVD killers)</t>
+          <t>Indicator removal (clear event logs, file deletion)</t>
         </is>
       </c>
       <c r="H22" s="9" t="inlineStr">
@@ -12336,7 +12372,7 @@
       </c>
       <c r="I22" s="9" t="inlineStr">
         <is>
-          <t>커널·펌웨어 하위 계층 · 서명된 정상 도구 악용</t>
+          <t>시그니처 회피</t>
         </is>
       </c>
       <c r="J22" s="8" t="inlineStr">
@@ -12346,34 +12382,32 @@
       </c>
       <c r="K22" s="9" t="inlineStr">
         <is>
-          <t>랜섬웨어 · 국가배후</t>
+          <t>국가배후 · 랜섬웨어</t>
         </is>
       </c>
       <c r="L22" s="9" t="inlineStr">
         <is>
-          <t>Windows</t>
+          <t>Windows · Linux</t>
         </is>
       </c>
       <c r="M22" s="9" t="inlineStr">
         <is>
-          <t>T1685</t>
+          <t>T1070, T1070.004, T1685.005</t>
         </is>
       </c>
       <c r="N22" s="9" t="inlineStr">
         <is>
-          <t>T1685 Disable or Modify Tools</t>
+          <t>T1070 Indicator Removal
+T1070.004 Indicator Removal: File Deletion
+T1685.005 Disable or Modify Tools: Clear Windows Event Logs</t>
         </is>
       </c>
       <c r="O22" s="8" t="n">
-        <v>155</v>
+        <v>335</v>
       </c>
       <c r="P22" s="8" t="inlineStr"/>
       <c r="Q22" s="8" t="inlineStr"/>
-      <c r="R22" s="8" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
+      <c r="R22" s="8" t="inlineStr"/>
       <c r="S22" s="9" t="inlineStr"/>
       <c r="T22" s="9" t="inlineStr"/>
       <c r="U22" s="9" t="inlineStr"/>
@@ -12397,26 +12431,26 @@
       </c>
       <c r="AB22" s="9" t="inlineStr"/>
       <c r="AC22" s="8" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="AD22" s="9" t="inlineStr">
         <is>
-          <t>실제 사고 7건(최근 3, 서로 다른 행위자·캠페인 7) · 빈발 지수 상(ATT&amp;CK 주체 155) · KEV - · 정부 경보 1 · 위협인텔 0 · 실증 0</t>
+          <t>실제 사고 2건(최근 1, 서로 다른 행위자·캠페인 2) · 빈발 지수 상(ATT&amp;CK 주체 335) · KEV - · 정부 경보 0 · 위협인텔 0 · 실증 0</t>
         </is>
       </c>
       <c r="AE22" s="9" t="inlineStr">
         <is>
-          <t>EDR·백신을 무력화해 이후 단계를 가리는 방어 무력화 수단 — 단독 피해보다 공격 성공률을 높이는 조건</t>
+          <t>이벤트 로그·파일을 지워 레거시 SIEM 탐지·사후 분석을 무력화 — 원격·불변 로그가 없으면 흔적이 사라짐(로그 삭제 T1685.005는 v19 방어 무력화로 재배치됐으나 공격 목적이 흔적 제거라 은닉 행으로 둠)</t>
         </is>
       </c>
       <c r="AF22" s="9" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="AG22" s="9" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AH22" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AI22" s="9" t="n">
         <v>0</v>
@@ -12428,73 +12462,70 @@
       </c>
       <c r="AK22" s="9" t="inlineStr">
         <is>
-          <t>ENI-012, ENI-013, ENI-015, ENI-016, ENI-017, ENI-036, ENI-037
-정부 경보: ENI-030</t>
+          <t>ENI-001, ENI-034</t>
         </is>
       </c>
       <c r="AL22" s="9" t="inlineStr">
         <is>
-          <t>랜섬·암호화 6 · 데이터 유출 2 · 자격증명·비밀 탈취 2 · 내부 접근 확보 2</t>
+          <t>내부 접근 확보 2 · 첩보·감시 1 · 측면 이동·확산 1 · 데이터 유출 1</t>
         </is>
       </c>
       <c r="AM22" s="9" t="inlineStr">
         <is>
-          <t>SI-4 System Monitoring
-SI-7 Software, Firmware, and Information Integrity
-CM-7 Least Functionality</t>
+          <t>AU-9 Protection of Audit Information
+SI-4 System Monitoring
+AU-6 Audit Record Review, Analysis, and Reporting</t>
         </is>
       </c>
       <c r="AN22" s="9" t="inlineStr">
         <is>
           <t>■ 탐지
-- 보안 서비스 중지·드라이버 로드와 EDR 텔레메트리 단절을 행위·네트워크 기반으로 탐지(NIST SI-4·SI-7)
+- 로그 삭제·감사 정책 변경 이벤트와 원격 수집 로그의 공백을 모니터링(NIST AU-6·SI-4)
 ■ 대응
-- 취약 드라이버 차단 목록(HVCI·블록리스트)·변조 방지와 보안 도구 상태를 중앙 감시(NIST SI-7·CM-7)
-- 참고: LOLDrivers 〈Project〉 · Hive Security 〈Modern Attack Techniques 2026〉</t>
+- 원격·불변 로그 전송과 로그 삭제 방지·보존 정책을 적용(NIST AU-9·AU-6)</t>
         </is>
       </c>
       <c r="AO22" s="9" t="inlineStr">
         <is>
-          <t>LOLDrivers 〈Project〉
-Hive Security 〈Modern Attack Techniques 2026〉</t>
+          <t>MITRE 〈ATT&amp;CK Enterprise v19.2〉</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="9" t="inlineStr">
         <is>
-          <t>[DE] 방어 회피</t>
+          <t>[ST] 은닉</t>
         </is>
       </c>
       <c r="B23" s="9" t="inlineStr">
         <is>
-          <t>ENT-DE-01.2</t>
+          <t>ENT-ST-02</t>
         </is>
       </c>
       <c r="C23" s="9" t="inlineStr">
         <is>
-          <t>보안 도구 무력화·드라이버 로드</t>
+          <t>위장(정상 이름·서명)</t>
         </is>
       </c>
       <c r="D23" s="9" t="inlineStr">
         <is>
-          <t>취약·악성 드라이버 로드(커널)</t>
+          <t>위장(정상 이름·경로·서명 가장)</t>
         </is>
       </c>
       <c r="E23" s="9" t="inlineStr">
         <is>
-          <t>취약·악성 드라이버 로드로 커널 은닉·무력화 토대 마련</t>
+          <t>정상 이름·경로·서명 가장(위장)으로 눈·규칙 탐지 회피</t>
         </is>
       </c>
       <c r="F23" s="9" t="inlineStr">
         <is>
-          <t>- 공격자는 취약·악성 드라이버를 커널에 올려 은닉·무력화의 토대를 만들 수 있음
-- 커널 계층이라 상위 보안 제품이 보지 못함</t>
+          <t>- 공격자는 정상 프로세스·경로·서명으로 위장해 사람 눈과 규칙 기반 탐지를 피할 수 있음
+- 정상처럼 보여 레거시가 구분하기 어려우나 단독 피해는 제한적임</t>
         </is>
       </c>
       <c r="G23" s="9" t="inlineStr">
         <is>
-          <t>Load vulnerable/malicious kernel driver</t>
+          <t>Masquerading</t>
         </is>
       </c>
       <c r="H23" s="9" t="inlineStr">
@@ -12504,44 +12535,40 @@
       </c>
       <c r="I23" s="9" t="inlineStr">
         <is>
-          <t>커널·펌웨어 하위 계층</t>
+          <t>서명된 정상 도구 악용 · 시그니처 회피</t>
         </is>
       </c>
       <c r="J23" s="8" t="inlineStr">
         <is>
-          <t>행위·네트워크·아이덴티티</t>
+          <t>EDR·XDR</t>
         </is>
       </c>
       <c r="K23" s="9" t="inlineStr">
         <is>
-          <t>국가배후 · 랜섬웨어</t>
+          <t>국가배후 · 랜섬웨어 · 사이버범죄</t>
         </is>
       </c>
       <c r="L23" s="9" t="inlineStr">
         <is>
-          <t>Windows</t>
+          <t>Windows · Linux · macOS</t>
         </is>
       </c>
       <c r="M23" s="9" t="inlineStr">
         <is>
-          <t>T1543.003</t>
+          <t>T1036</t>
         </is>
       </c>
       <c r="N23" s="9" t="inlineStr">
         <is>
-          <t>T1543.003 Create or Modify System Process: Windows Service</t>
+          <t>T1036 Masquerading</t>
         </is>
       </c>
       <c r="O23" s="8" t="n">
-        <v>140</v>
+        <v>60</v>
       </c>
       <c r="P23" s="8" t="inlineStr"/>
       <c r="Q23" s="8" t="inlineStr"/>
-      <c r="R23" s="8" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
+      <c r="R23" s="8" t="inlineStr"/>
       <c r="S23" s="9" t="inlineStr"/>
       <c r="T23" s="9" t="inlineStr"/>
       <c r="U23" s="9" t="inlineStr"/>
@@ -12550,7 +12577,7 @@
       <c r="X23" s="9" t="inlineStr"/>
       <c r="Y23" s="8" t="inlineStr">
         <is>
-          <t>상</t>
+          <t>중</t>
         </is>
       </c>
       <c r="Z23" s="8" t="inlineStr">
@@ -12558,30 +12585,30 @@
           <t>중</t>
         </is>
       </c>
-      <c r="AA23" s="12" t="inlineStr">
-        <is>
-          <t>높음</t>
+      <c r="AA23" s="13" t="inlineStr">
+        <is>
+          <t>보통</t>
         </is>
       </c>
       <c r="AB23" s="9" t="inlineStr"/>
       <c r="AC23" s="8" t="n">
-        <v>12</v>
+        <v>45</v>
       </c>
       <c r="AD23" s="9" t="inlineStr">
         <is>
-          <t>실제 사고 3건(최근 2, 서로 다른 행위자·캠페인 3) · 빈발 지수 상(ATT&amp;CK 주체 140) · KEV - · 정부 경보 0 · 위협인텔 0 · 실증 0</t>
+          <t>실제 사고 0건(최근 0, 서로 다른 행위자·캠페인 0) · 빈발 지수 중(ATT&amp;CK 주체 60) · KEV - · 정부 경보 0 · 위협인텔 0 · 실증 0</t>
         </is>
       </c>
       <c r="AE23" s="9" t="inlineStr">
         <is>
-          <t>커널에 취약 드라이버를 올려 무력화·은닉의 토대를 만드는 단계 — 단독 피해는 없음</t>
+          <t>정상 프로세스·경로·서명으로 위장해 눈과 규칙 기반 탐지를 피하나 단독 피해는 제한적</t>
         </is>
       </c>
       <c r="AF23" s="9" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AG23" s="9" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AH23" s="9" t="n">
         <v>0</v>
@@ -12589,78 +12616,68 @@
       <c r="AI23" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="AJ23" s="27" t="inlineStr">
-        <is>
-          <t>실제 사고 확인</t>
-        </is>
-      </c>
-      <c r="AK23" s="9" t="inlineStr">
-        <is>
-          <t>ENI-016, ENI-017, ENI-036</t>
-        </is>
-      </c>
-      <c r="AL23" s="9" t="inlineStr">
-        <is>
-          <t>랜섬·암호화 2 · 자격증명·비밀 탈취 1 · 내부 접근 확보 1</t>
-        </is>
-      </c>
+      <c r="AJ23" s="28" t="inlineStr">
+        <is>
+          <t>ATT&amp;CK 사례·KEV 다수</t>
+        </is>
+      </c>
+      <c r="AK23" s="9" t="inlineStr"/>
+      <c r="AL23" s="9" t="inlineStr"/>
       <c r="AM23" s="9" t="inlineStr">
         <is>
-          <t>SI-7 Software, Firmware, and Information Integrity
-CM-7 Least Functionality
-SI-4 System Monitoring</t>
+          <t>SI-4 System Monitoring
+SI-7 Software, Firmware, and Information Integrity</t>
         </is>
       </c>
       <c r="AN23" s="9" t="inlineStr">
         <is>
           <t>■ 탐지
-- 신규 커널 드라이버 로드와 취약 드라이버 서명·해시를 차단 목록과 대조(NIST SI-7·SI-4)
+- 정상 이름과 다른 경로·서명·해시 불일치를 무결성·행위 기반으로 탐지(NIST SI-4·SI-7)
 ■ 대응
-- HVCI·드라이버 블록리스트로 취약 드라이버 로드를 차단(NIST SI-7·CM-7)
-- 참고: LOLDrivers 〈Project〉</t>
+- 바이너리 무결성·서명 검증과 정상 경로 기준선 대조를 적용(NIST SI-7·SI-4)</t>
         </is>
       </c>
       <c r="AO23" s="9" t="inlineStr">
         <is>
-          <t>LOLDrivers 〈Project〉</t>
+          <t>MITRE 〈ATT&amp;CK Enterprise v19.2〉</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="9" t="inlineStr">
         <is>
-          <t>[DE] 방어 회피</t>
+          <t>[ST] 은닉</t>
         </is>
       </c>
       <c r="B24" s="9" t="inlineStr">
         <is>
-          <t>ENT-DE-03</t>
+          <t>ENT-ST-03</t>
         </is>
       </c>
       <c r="C24" s="9" t="inlineStr">
         <is>
-          <t>지표 삭제</t>
+          <t>파일·정보 난독화</t>
         </is>
       </c>
       <c r="D24" s="9" t="inlineStr">
         <is>
-          <t>지표 삭제(이벤트 로그·파일 삭제)</t>
+          <t>파일·정보 난독화·암호화</t>
         </is>
       </c>
       <c r="E24" s="9" t="inlineStr">
         <is>
-          <t>이벤트 로그·파일 삭제로 레거시 SIEM 탐지·분석 무력화</t>
+          <t>패킹·인코딩·암호화 난독화로 시그니처·정적 분석 회피</t>
         </is>
       </c>
       <c r="F24" s="9" t="inlineStr">
         <is>
-          <t>- 공격자는 이벤트 로그·파일을 지워 레거시 SIEM 탐지와 사후 분석을 무력화할 수 있음
-- 원격·불변 로그가 없으면 흔적이 사라져 추적이 어려워짐</t>
+          <t>- 공격자는 페이로드를 패킹·인코딩·암호화해 시그니처·정적 분석을 회피할 수 있음
+- 변종 양산으로 레거시 AV를 지속 우회하나 단독 피해는 제한적임</t>
         </is>
       </c>
       <c r="G24" s="9" t="inlineStr">
         <is>
-          <t>Indicator removal (clear event logs, file deletion)</t>
+          <t>Obfuscated files or information</t>
         </is>
       </c>
       <c r="H24" s="9" t="inlineStr">
@@ -12670,38 +12687,36 @@
       </c>
       <c r="I24" s="9" t="inlineStr">
         <is>
-          <t>시그니처 회피</t>
+          <t>시그니처 회피 · 파일리스·인메모리</t>
         </is>
       </c>
       <c r="J24" s="8" t="inlineStr">
         <is>
-          <t>행위·네트워크·아이덴티티</t>
+          <t>EDR·XDR</t>
         </is>
       </c>
       <c r="K24" s="9" t="inlineStr">
         <is>
-          <t>국가배후 · 랜섬웨어</t>
+          <t>사이버범죄 · 랜섬웨어 · 국가배후</t>
         </is>
       </c>
       <c r="L24" s="9" t="inlineStr">
         <is>
-          <t>Windows · Linux</t>
+          <t>Windows · Linux · macOS</t>
         </is>
       </c>
       <c r="M24" s="9" t="inlineStr">
         <is>
-          <t>T1070, T1070.004, T1685.005</t>
+          <t>T1027</t>
         </is>
       </c>
       <c r="N24" s="9" t="inlineStr">
         <is>
-          <t>T1070 Indicator Removal
-T1070.004 Indicator Removal: File Deletion
-T1685.005 Disable or Modify Tools: Clear Windows Event Logs</t>
+          <t>T1027 Obfuscated Files or Information</t>
         </is>
       </c>
       <c r="O24" s="8" t="n">
-        <v>335</v>
+        <v>160</v>
       </c>
       <c r="P24" s="8" t="inlineStr"/>
       <c r="Q24" s="8" t="inlineStr"/>
@@ -12714,7 +12729,7 @@
       <c r="X24" s="9" t="inlineStr"/>
       <c r="Y24" s="8" t="inlineStr">
         <is>
-          <t>상</t>
+          <t>중</t>
         </is>
       </c>
       <c r="Z24" s="8" t="inlineStr">
@@ -12722,30 +12737,30 @@
           <t>중</t>
         </is>
       </c>
-      <c r="AA24" s="12" t="inlineStr">
-        <is>
-          <t>높음</t>
+      <c r="AA24" s="13" t="inlineStr">
+        <is>
+          <t>보통</t>
         </is>
       </c>
       <c r="AB24" s="9" t="inlineStr"/>
       <c r="AC24" s="8" t="n">
-        <v>13</v>
+        <v>40</v>
       </c>
       <c r="AD24" s="9" t="inlineStr">
         <is>
-          <t>실제 사고 2건(최근 1, 서로 다른 행위자·캠페인 2) · 빈발 지수 상(ATT&amp;CK 주체 335) · KEV - · 정부 경보 0 · 위협인텔 0 · 실증 0</t>
+          <t>실제 사고 0건(최근 0, 서로 다른 행위자·캠페인 0) · 빈발 지수 상(ATT&amp;CK 주체 160) · KEV - · 정부 경보 0 · 위협인텔 0 · 실증 0</t>
         </is>
       </c>
       <c r="AE24" s="9" t="inlineStr">
         <is>
-          <t>이벤트 로그·파일을 지워 레거시 SIEM 탐지·사후 분석을 무력화 — 원격·불변 로그가 없으면 흔적이 사라짐</t>
+          <t>패킹·인코딩·암호화로 시그니처·정적 분석을 회피 — 변종 양산으로 레거시 AV를 지속 우회</t>
         </is>
       </c>
       <c r="AF24" s="9" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AG24" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AH24" s="9" t="n">
         <v>0</v>
@@ -12753,34 +12768,25 @@
       <c r="AI24" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="AJ24" s="27" t="inlineStr">
-        <is>
-          <t>실제 사고 확인</t>
-        </is>
-      </c>
-      <c r="AK24" s="9" t="inlineStr">
-        <is>
-          <t>ENI-001, ENI-034</t>
-        </is>
-      </c>
-      <c r="AL24" s="9" t="inlineStr">
-        <is>
-          <t>내부 접근 확보 2 · 첩보·감시 1 · 측면 이동·확산 1 · 데이터 유출 1</t>
-        </is>
-      </c>
+      <c r="AJ24" s="28" t="inlineStr">
+        <is>
+          <t>ATT&amp;CK 사례·KEV 다수</t>
+        </is>
+      </c>
+      <c r="AK24" s="9" t="inlineStr"/>
+      <c r="AL24" s="9" t="inlineStr"/>
       <c r="AM24" s="9" t="inlineStr">
         <is>
-          <t>AU-9 Protection of Audit Information
-SI-4 System Monitoring
-AU-6 Audit Record Review, Analysis, and Reporting</t>
+          <t>SI-3 Malicious Code Protection
+SI-4 System Monitoring</t>
         </is>
       </c>
       <c r="AN24" s="9" t="inlineStr">
         <is>
           <t>■ 탐지
-- 로그 삭제·감사 정책 변경 이벤트와 원격 수집 로그의 공백을 모니터링(NIST AU-6·SI-4)
+- 실행 시점 행위·언패킹과 비정상 인코딩·엔트로피를 행위 기반으로 탐지(NIST SI-3·SI-4)
 ■ 대응
-- 원격·불변 로그 전송과 로그 삭제 방지·보존 정책을 적용(NIST AU-9·AU-6)</t>
+- 시그니처 의존을 줄이고 행위 기반·샌드박스 분석을 병행(NIST SI-3·SI-4)</t>
         </is>
       </c>
       <c r="AO24" s="9" t="inlineStr">
@@ -12792,38 +12798,38 @@
     <row r="25">
       <c r="A25" s="9" t="inlineStr">
         <is>
-          <t>[DE] 방어 회피</t>
+          <t>[ST] 은닉</t>
         </is>
       </c>
       <c r="B25" s="9" t="inlineStr">
         <is>
-          <t>ENT-DE-04</t>
+          <t>ENT-ST-04</t>
         </is>
       </c>
       <c r="C25" s="9" t="inlineStr">
         <is>
-          <t>위장(정상 이름·서명)</t>
+          <t>인메모리·반사 로딩</t>
         </is>
       </c>
       <c r="D25" s="9" t="inlineStr">
         <is>
-          <t>위장(정상 이름·경로·서명 가장)</t>
+          <t>인메모리·반사 코드 로딩</t>
         </is>
       </c>
       <c r="E25" s="9" t="inlineStr">
         <is>
-          <t>정상 이름·경로·서명 가장(위장)으로 눈·규칙 탐지 회피</t>
+          <t>인메모리·반사 코드 로딩으로 파일 기반 AV 원천 회피</t>
         </is>
       </c>
       <c r="F25" s="9" t="inlineStr">
         <is>
-          <t>- 공격자는 정상 프로세스·경로·서명으로 위장해 사람 눈과 규칙 기반 탐지를 피할 수 있음
-- 정상처럼 보여 레거시가 구분하기 어려우나 단독 피해는 제한적임</t>
+          <t>- 공격자는 디스크를 거치지 않고 메모리에서 페이로드를 로드·실행할 수 있음
+- 파일 기반 AV·시그니처가 원천적으로 보지 못해 행위·메모리 기반 탐지가 필요함</t>
         </is>
       </c>
       <c r="G25" s="9" t="inlineStr">
         <is>
-          <t>Masquerading</t>
+          <t>In-memory / reflective code loading</t>
         </is>
       </c>
       <c r="H25" s="9" t="inlineStr">
@@ -12833,36 +12839,36 @@
       </c>
       <c r="I25" s="9" t="inlineStr">
         <is>
-          <t>서명된 정상 도구 악용 · 시그니처 회피</t>
+          <t>파일리스·인메모리 · 시그니처 회피</t>
         </is>
       </c>
       <c r="J25" s="8" t="inlineStr">
         <is>
-          <t>EDR·XDR</t>
+          <t>행위·네트워크·아이덴티티</t>
         </is>
       </c>
       <c r="K25" s="9" t="inlineStr">
         <is>
-          <t>국가배후 · 랜섬웨어 · 사이버범죄</t>
+          <t>국가배후 · 랜섬웨어</t>
         </is>
       </c>
       <c r="L25" s="9" t="inlineStr">
         <is>
-          <t>Windows · Linux · macOS</t>
+          <t>Windows</t>
         </is>
       </c>
       <c r="M25" s="9" t="inlineStr">
         <is>
-          <t>T1036</t>
+          <t>T1620</t>
         </is>
       </c>
       <c r="N25" s="9" t="inlineStr">
         <is>
-          <t>T1036 Masquerading</t>
+          <t>T1620 Reflective Code Loading</t>
         </is>
       </c>
       <c r="O25" s="8" t="n">
-        <v>60</v>
+        <v>32</v>
       </c>
       <c r="P25" s="8" t="inlineStr"/>
       <c r="Q25" s="8" t="inlineStr"/>
@@ -12890,16 +12896,16 @@
       </c>
       <c r="AB25" s="9" t="inlineStr"/>
       <c r="AC25" s="8" t="n">
-        <v>45</v>
+        <v>35</v>
       </c>
       <c r="AD25" s="9" t="inlineStr">
         <is>
-          <t>실제 사고 0건(최근 0, 서로 다른 행위자·캠페인 0) · 빈발 지수 중(ATT&amp;CK 주체 60) · KEV - · 정부 경보 0 · 위협인텔 0 · 실증 0</t>
+          <t>실제 사고 0건(최근 0, 서로 다른 행위자·캠페인 0) · 빈발 지수 중(ATT&amp;CK 주체 32) · KEV - · 정부 경보 0 · 위협인텔 0 · 실증 0</t>
         </is>
       </c>
       <c r="AE25" s="9" t="inlineStr">
         <is>
-          <t>정상 프로세스·경로·서명으로 위장해 눈과 규칙 기반 탐지를 피하나 단독 피해는 제한적</t>
+          <t>메모리 로딩으로 탐지를 회피하는 은닉 수단 — 단독 피해 없음</t>
         </is>
       </c>
       <c r="AF25" s="9" t="n">
@@ -12923,16 +12929,16 @@
       <c r="AL25" s="9" t="inlineStr"/>
       <c r="AM25" s="9" t="inlineStr">
         <is>
-          <t>SI-4 System Monitoring
-SI-7 Software, Firmware, and Information Integrity</t>
+          <t>SI-3 Malicious Code Protection
+SI-4 System Monitoring</t>
         </is>
       </c>
       <c r="AN25" s="9" t="inlineStr">
         <is>
           <t>■ 탐지
-- 정상 이름과 다른 경로·서명·해시 불일치를 무결성·행위 기반으로 탐지(NIST SI-4·SI-7)
+- 메모리 영역 할당·실행과 비정상 로딩을 EDR 메모리 스캔으로 탐지(NIST SI-3·SI-4)
 ■ 대응
-- 바이너리 무결성·서명 검증과 정상 경로 기준선 대조를 적용(NIST SI-7·SI-4)</t>
+- 메모리 가시성(EDR)·공격 표면 축소와 스크립트 실행 통제를 적용(NIST SI-3·SI-4)</t>
         </is>
       </c>
       <c r="AO25" s="9" t="inlineStr">
@@ -12944,38 +12950,38 @@
     <row r="26">
       <c r="A26" s="9" t="inlineStr">
         <is>
-          <t>[DE] 방어 회피</t>
+          <t>[ST] 은닉</t>
         </is>
       </c>
       <c r="B26" s="9" t="inlineStr">
         <is>
-          <t>ENT-DE-05</t>
+          <t>ENT-ST-05</t>
         </is>
       </c>
       <c r="C26" s="9" t="inlineStr">
         <is>
-          <t>파일·정보 난독화</t>
+          <t>루트킷</t>
         </is>
       </c>
       <c r="D26" s="9" t="inlineStr">
         <is>
-          <t>파일·정보 난독화·암호화</t>
+          <t>루트킷(사용자·커널 은폐)</t>
         </is>
       </c>
       <c r="E26" s="9" t="inlineStr">
         <is>
-          <t>패킹·인코딩·암호화 난독화로 시그니처·정적 분석 회피</t>
+          <t>루트킷으로 프로세스·파일·연결을 하위 계층에서 은폐</t>
         </is>
       </c>
       <c r="F26" s="9" t="inlineStr">
         <is>
-          <t>- 공격자는 페이로드를 패킹·인코딩·암호화해 시그니처·정적 분석을 회피할 수 있음
-- 변종 양산으로 레거시 AV를 지속 우회하나 단독 피해는 제한적임</t>
+          <t>- 공격자는 루트킷으로 프로세스·파일·연결을 하위 계층에서 숨겨 탐지·분석을 방해할 수 있음
+- 레거시로는 존재 자체를 알기 어려워 장기 잠복에 쓰임</t>
         </is>
       </c>
       <c r="G26" s="9" t="inlineStr">
         <is>
-          <t>Obfuscated files or information</t>
+          <t>Rootkit</t>
         </is>
       </c>
       <c r="H26" s="9" t="inlineStr">
@@ -12985,36 +12991,36 @@
       </c>
       <c r="I26" s="9" t="inlineStr">
         <is>
-          <t>시그니처 회피 · 파일리스·인메모리</t>
+          <t>커널·펌웨어 하위 계층 · 파일리스·인메모리</t>
         </is>
       </c>
       <c r="J26" s="8" t="inlineStr">
         <is>
-          <t>EDR·XDR</t>
+          <t>행위·네트워크·아이덴티티</t>
         </is>
       </c>
       <c r="K26" s="9" t="inlineStr">
         <is>
-          <t>사이버범죄 · 랜섬웨어 · 국가배후</t>
+          <t>국가배후</t>
         </is>
       </c>
       <c r="L26" s="9" t="inlineStr">
         <is>
-          <t>Windows · Linux · macOS</t>
+          <t>Windows · Linux</t>
         </is>
       </c>
       <c r="M26" s="9" t="inlineStr">
         <is>
-          <t>T1027</t>
+          <t>T1014</t>
         </is>
       </c>
       <c r="N26" s="9" t="inlineStr">
         <is>
-          <t>T1027 Obfuscated Files or Information</t>
+          <t>T1014 Rootkit</t>
         </is>
       </c>
       <c r="O26" s="8" t="n">
-        <v>160</v>
+        <v>32</v>
       </c>
       <c r="P26" s="8" t="inlineStr"/>
       <c r="Q26" s="8" t="inlineStr"/>
@@ -13042,16 +13048,16 @@
       </c>
       <c r="AB26" s="9" t="inlineStr"/>
       <c r="AC26" s="8" t="n">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="AD26" s="9" t="inlineStr">
         <is>
-          <t>실제 사고 0건(최근 0, 서로 다른 행위자·캠페인 0) · 빈발 지수 상(ATT&amp;CK 주체 160) · KEV - · 정부 경보 0 · 위협인텔 0 · 실증 0</t>
+          <t>실제 사고 0건(최근 0, 서로 다른 행위자·캠페인 0) · 빈발 지수 중(ATT&amp;CK 주체 32) · KEV - · 정부 경보 0 · 위협인텔 0 · 실증 0</t>
         </is>
       </c>
       <c r="AE26" s="9" t="inlineStr">
         <is>
-          <t>패킹·인코딩·암호화로 시그니처·정적 분석을 회피 — 변종 양산으로 레거시 AV를 지속 우회</t>
+          <t>루트킷으로 존재를 은폐해 장기 잠복하는 은닉 수단 — 직접 피해보다 지속·은닉 조건</t>
         </is>
       </c>
       <c r="AF26" s="9" t="n">
@@ -13075,16 +13081,16 @@
       <c r="AL26" s="9" t="inlineStr"/>
       <c r="AM26" s="9" t="inlineStr">
         <is>
-          <t>SI-3 Malicious Code Protection
+          <t>SI-7 Software, Firmware, and Information Integrity
 SI-4 System Monitoring</t>
         </is>
       </c>
       <c r="AN26" s="9" t="inlineStr">
         <is>
           <t>■ 탐지
-- 실행 시점 행위·언패킹과 비정상 인코딩·엔트로피를 행위 기반으로 탐지(NIST SI-3·SI-4)
+- 커널 무결성·드라이버 서명과 메모리·부트 무결성 검증으로 은폐를 탐지(NIST SI-7·SI-4)
 ■ 대응
-- 시그니처 의존을 줄이고 행위 기반·샌드박스 분석을 병행(NIST SI-3·SI-4)</t>
+- 커널 무결성 보호(HVCI)·보안 부팅과 하위 계층 텔레메트리를 확보(NIST SI-7·SI-4)</t>
         </is>
       </c>
       <c r="AO26" s="9" t="inlineStr">
@@ -13096,38 +13102,38 @@
     <row r="27">
       <c r="A27" s="9" t="inlineStr">
         <is>
-          <t>[DE] 방어 회피</t>
+          <t>[ST] 은닉</t>
         </is>
       </c>
       <c r="B27" s="9" t="inlineStr">
         <is>
-          <t>ENT-DE-06</t>
+          <t>ENT-ST-06</t>
         </is>
       </c>
       <c r="C27" s="9" t="inlineStr">
         <is>
-          <t>인메모리·반사 로딩</t>
+          <t>펌웨어·부트 수준 은닉</t>
         </is>
       </c>
       <c r="D27" s="9" t="inlineStr">
         <is>
-          <t>인메모리·반사 코드 로딩</t>
+          <t>펌웨어·부트킷(UEFI) 지속·은닉</t>
         </is>
       </c>
       <c r="E27" s="9" t="inlineStr">
         <is>
-          <t>인메모리·반사 코드 로딩으로 파일 기반 AV 원천 회피</t>
+          <t>펌웨어·부트킷(UEFI)으로 OS 아래 지속·은닉</t>
         </is>
       </c>
       <c r="F27" s="9" t="inlineStr">
         <is>
-          <t>- 공격자는 디스크를 거치지 않고 메모리에서 페이로드를 로드·실행할 수 있음
-- 파일 기반 AV·시그니처가 원천적으로 보지 못해 행위·메모리 기반 탐지가 필요함</t>
+          <t>- 공격자는 OS 아래 펌웨어·부트 단계에 임플란트를 심어 재설치·디스크 교체에도 지속할 수 있음
+- OS 보안 제품의 가시성 밖이라 레거시·EDR 모두 사실상 공백임</t>
         </is>
       </c>
       <c r="G27" s="9" t="inlineStr">
         <is>
-          <t>In-memory / reflective code loading</t>
+          <t>Pre-OS boot / firmware implant (bootkit)</t>
         </is>
       </c>
       <c r="H27" s="9" t="inlineStr">
@@ -13137,7 +13143,7 @@
       </c>
       <c r="I27" s="9" t="inlineStr">
         <is>
-          <t>파일리스·인메모리 · 시그니처 회피</t>
+          <t>커널·펌웨어 하위 계층</t>
         </is>
       </c>
       <c r="J27" s="8" t="inlineStr">
@@ -13147,26 +13153,26 @@
       </c>
       <c r="K27" s="9" t="inlineStr">
         <is>
-          <t>국가배후 · 랜섬웨어</t>
+          <t>국가배후</t>
         </is>
       </c>
       <c r="L27" s="9" t="inlineStr">
         <is>
-          <t>Windows</t>
+          <t>펌웨어 · Windows</t>
         </is>
       </c>
       <c r="M27" s="9" t="inlineStr">
         <is>
-          <t>T1620</t>
+          <t>T1542</t>
         </is>
       </c>
       <c r="N27" s="9" t="inlineStr">
         <is>
-          <t>T1620 Reflective Code Loading</t>
+          <t>T1542 Pre-OS Boot</t>
         </is>
       </c>
       <c r="O27" s="8" t="n">
-        <v>32</v>
+        <v>0</v>
       </c>
       <c r="P27" s="8" t="inlineStr"/>
       <c r="Q27" s="8" t="inlineStr"/>
@@ -13194,20 +13200,20 @@
       </c>
       <c r="AB27" s="9" t="inlineStr"/>
       <c r="AC27" s="8" t="n">
-        <v>35</v>
+        <v>26</v>
       </c>
       <c r="AD27" s="9" t="inlineStr">
         <is>
-          <t>실제 사고 0건(최근 0, 서로 다른 행위자·캠페인 0) · 빈발 지수 중(ATT&amp;CK 주체 32) · KEV - · 정부 경보 0 · 위협인텔 0 · 실증 0</t>
+          <t>실제 사고 1건(최근 0, 서로 다른 행위자·캠페인 1) · 빈발 지수 하(ATT&amp;CK 주체 0) · KEV - · 정부 경보 0 · 위협인텔 0 · 실증 1</t>
         </is>
       </c>
       <c r="AE27" s="9" t="inlineStr">
         <is>
-          <t>메모리 로딩으로 탐지를 회피하는 은닉 수단 — 단독 피해 없음</t>
+          <t>펌웨어·부트킷으로 재설치에도 지속하는 하위 계층 지속성 — 직접 피해보다 장기 지속 조건</t>
         </is>
       </c>
       <c r="AF27" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG27" s="9" t="n">
         <v>0</v>
@@ -13218,25 +13224,34 @@
       <c r="AI27" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="AJ27" s="28" t="inlineStr">
-        <is>
-          <t>ATT&amp;CK 사례·KEV 다수</t>
-        </is>
-      </c>
-      <c r="AK27" s="9" t="inlineStr"/>
-      <c r="AL27" s="9" t="inlineStr"/>
+      <c r="AJ27" s="27" t="inlineStr">
+        <is>
+          <t>실제 사고 확인</t>
+        </is>
+      </c>
+      <c r="AK27" s="9" t="inlineStr">
+        <is>
+          <t>ENI-026
+실증: ENI-024</t>
+        </is>
+      </c>
+      <c r="AL27" s="9" t="inlineStr">
+        <is>
+          <t>내부 접근 확보 1 · 첩보·감시 1</t>
+        </is>
+      </c>
       <c r="AM27" s="9" t="inlineStr">
         <is>
-          <t>SI-3 Malicious Code Protection
-SI-4 System Monitoring</t>
+          <t>SI-7 Software, Firmware, and Information Integrity
+CM-7 Least Functionality</t>
         </is>
       </c>
       <c r="AN27" s="9" t="inlineStr">
         <is>
           <t>■ 탐지
-- 메모리 영역 할당·실행과 비정상 로딩을 EDR 메모리 스캔으로 탐지(NIST SI-3·SI-4)
+- 펌웨어·부트 무결성 측정(보안 부팅·측정 부팅)과 펌웨어 버전·해시 변화를 점검(NIST SI-7)
 ■ 대응
-- 메모리 가시성(EDR)·공격 표면 축소와 스크립트 실행 통제를 적용(NIST SI-3·SI-4)</t>
+- 보안 부팅·펌웨어 무결성 검증·업데이트와 펌웨어 공급 신뢰를 관리(NIST SI-7·CM-7)</t>
         </is>
       </c>
       <c r="AO27" s="9" t="inlineStr">
@@ -13248,38 +13263,38 @@
     <row r="28">
       <c r="A28" s="9" t="inlineStr">
         <is>
-          <t>[DE] 방어 회피</t>
+          <t>[DM] 방어 무력화</t>
         </is>
       </c>
       <c r="B28" s="9" t="inlineStr">
         <is>
-          <t>ENT-DE-07</t>
+          <t>ENT-DM-01.1</t>
         </is>
       </c>
       <c r="C28" s="9" t="inlineStr">
         <is>
-          <t>루트킷</t>
+          <t>보안 도구 무력화·드라이버 로드</t>
         </is>
       </c>
       <c r="D28" s="9" t="inlineStr">
         <is>
-          <t>루트킷(사용자·커널 은폐)</t>
+          <t>보안 도구 무력화(EDR 변조·BYOVD EDR 킬러)</t>
         </is>
       </c>
       <c r="E28" s="9" t="inlineStr">
         <is>
-          <t>루트킷으로 프로세스·파일·연결을 하위 계층에서 은폐</t>
+          <t>서명된 취약 드라이버로 EDR·백신을 커널에서 무력화(BYOVD)</t>
         </is>
       </c>
       <c r="F28" s="9" t="inlineStr">
         <is>
-          <t>- 공격자는 루트킷으로 프로세스·파일·연결을 하위 계층에서 숨겨 탐지·분석을 방해할 수 있음
-- 레거시로는 존재 자체를 알기 어려워 장기 잠복에 쓰임</t>
+          <t>- 공격자는 서명된 취약 드라이버를 올려 EDR·백신을 커널에서 무력화할 수 있음
+- 보안 도구 자체가 꺼지므로 이후 단계가 전부 가려지고, 여러 랜섬웨어·국가배후가 EDR 킬러를 공유함</t>
         </is>
       </c>
       <c r="G28" s="9" t="inlineStr">
         <is>
-          <t>Rootkit</t>
+          <t>Impair/disable security tools (EDR tampering, BYOVD killers)</t>
         </is>
       </c>
       <c r="H28" s="9" t="inlineStr">
@@ -13289,7 +13304,7 @@
       </c>
       <c r="I28" s="9" t="inlineStr">
         <is>
-          <t>커널·펌웨어 하위 계층 · 파일리스·인메모리</t>
+          <t>커널·펌웨어 하위 계층 · 서명된 정상 도구 악용</t>
         </is>
       </c>
       <c r="J28" s="8" t="inlineStr">
@@ -13299,30 +13314,34 @@
       </c>
       <c r="K28" s="9" t="inlineStr">
         <is>
-          <t>국가배후</t>
+          <t>랜섬웨어 · 국가배후</t>
         </is>
       </c>
       <c r="L28" s="9" t="inlineStr">
         <is>
-          <t>Windows · Linux</t>
+          <t>Windows</t>
         </is>
       </c>
       <c r="M28" s="9" t="inlineStr">
         <is>
-          <t>T1014</t>
+          <t>T1685</t>
         </is>
       </c>
       <c r="N28" s="9" t="inlineStr">
         <is>
-          <t>T1014 Rootkit</t>
+          <t>T1685 Disable or Modify Tools</t>
         </is>
       </c>
       <c r="O28" s="8" t="n">
-        <v>32</v>
+        <v>155</v>
       </c>
       <c r="P28" s="8" t="inlineStr"/>
       <c r="Q28" s="8" t="inlineStr"/>
-      <c r="R28" s="8" t="inlineStr"/>
+      <c r="R28" s="8" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
       <c r="S28" s="9" t="inlineStr"/>
       <c r="T28" s="9" t="inlineStr"/>
       <c r="U28" s="9" t="inlineStr"/>
@@ -13331,107 +13350,119 @@
       <c r="X28" s="9" t="inlineStr"/>
       <c r="Y28" s="8" t="inlineStr">
         <is>
+          <t>상</t>
+        </is>
+      </c>
+      <c r="Z28" s="8" t="inlineStr">
+        <is>
           <t>중</t>
         </is>
       </c>
-      <c r="Z28" s="8" t="inlineStr">
-        <is>
-          <t>중</t>
-        </is>
-      </c>
-      <c r="AA28" s="13" t="inlineStr">
-        <is>
-          <t>보통</t>
+      <c r="AA28" s="12" t="inlineStr">
+        <is>
+          <t>높음</t>
         </is>
       </c>
       <c r="AB28" s="9" t="inlineStr"/>
       <c r="AC28" s="8" t="n">
-        <v>36</v>
+        <v>8</v>
       </c>
       <c r="AD28" s="9" t="inlineStr">
         <is>
-          <t>실제 사고 0건(최근 0, 서로 다른 행위자·캠페인 0) · 빈발 지수 중(ATT&amp;CK 주체 32) · KEV - · 정부 경보 0 · 위협인텔 0 · 실증 0</t>
+          <t>실제 사고 7건(최근 3, 서로 다른 행위자·캠페인 7) · 빈발 지수 상(ATT&amp;CK 주체 155) · KEV - · 정부 경보 1 · 위협인텔 0 · 실증 0</t>
         </is>
       </c>
       <c r="AE28" s="9" t="inlineStr">
         <is>
-          <t>루트킷으로 존재를 은폐해 장기 잠복하는 은닉 수단 — 직접 피해보다 지속·은닉 조건</t>
+          <t>EDR·백신을 무력화해 이후 단계를 가리는 방어 무력화 수단 — 단독 피해보다 공격 성공률을 높이는 조건</t>
         </is>
       </c>
       <c r="AF28" s="9" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="AG28" s="9" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AH28" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AI28" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="AJ28" s="28" t="inlineStr">
-        <is>
-          <t>ATT&amp;CK 사례·KEV 다수</t>
-        </is>
-      </c>
-      <c r="AK28" s="9" t="inlineStr"/>
-      <c r="AL28" s="9" t="inlineStr"/>
+      <c r="AJ28" s="27" t="inlineStr">
+        <is>
+          <t>실제 사고 확인</t>
+        </is>
+      </c>
+      <c r="AK28" s="9" t="inlineStr">
+        <is>
+          <t>ENI-012, ENI-013, ENI-015, ENI-016, ENI-017, ENI-036, ENI-037
+정부 경보: ENI-030</t>
+        </is>
+      </c>
+      <c r="AL28" s="9" t="inlineStr">
+        <is>
+          <t>랜섬·암호화 6 · 데이터 유출 2 · 자격증명·비밀 탈취 2 · 내부 접근 확보 2</t>
+        </is>
+      </c>
       <c r="AM28" s="9" t="inlineStr">
         <is>
-          <t>SI-7 Software, Firmware, and Information Integrity
-SI-4 System Monitoring</t>
+          <t>SI-4 System Monitoring
+SI-7 Software, Firmware, and Information Integrity
+CM-7 Least Functionality</t>
         </is>
       </c>
       <c r="AN28" s="9" t="inlineStr">
         <is>
           <t>■ 탐지
-- 커널 무결성·드라이버 서명과 메모리·부트 무결성 검증으로 은폐를 탐지(NIST SI-7·SI-4)
+- 보안 서비스 중지·드라이버 로드와 EDR 텔레메트리 단절을 행위·네트워크 기반으로 탐지(NIST SI-4·SI-7)
 ■ 대응
-- 커널 무결성 보호(HVCI)·보안 부팅과 하위 계층 텔레메트리를 확보(NIST SI-7·SI-4)</t>
+- 취약 드라이버 차단 목록(HVCI·블록리스트)·변조 방지와 보안 도구 상태를 중앙 감시(NIST SI-7·CM-7)
+- 참고: LOLDrivers 〈Project〉 · Hive Security 〈Modern Attack Techniques 2026〉</t>
         </is>
       </c>
       <c r="AO28" s="9" t="inlineStr">
         <is>
-          <t>MITRE 〈ATT&amp;CK Enterprise v19.2〉</t>
+          <t>LOLDrivers 〈Project〉
+Hive Security 〈Modern Attack Techniques 2026〉</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="9" t="inlineStr">
         <is>
-          <t>[DE] 방어 회피</t>
+          <t>[DM] 방어 무력화</t>
         </is>
       </c>
       <c r="B29" s="9" t="inlineStr">
         <is>
-          <t>ENT-DE-08</t>
+          <t>ENT-DM-01.2</t>
         </is>
       </c>
       <c r="C29" s="9" t="inlineStr">
         <is>
-          <t>펌웨어·부트 수준 은닉</t>
+          <t>보안 도구 무력화·드라이버 로드</t>
         </is>
       </c>
       <c r="D29" s="9" t="inlineStr">
         <is>
-          <t>펌웨어·부트킷(UEFI) 지속·은닉</t>
+          <t>취약·악성 드라이버 로드(커널)</t>
         </is>
       </c>
       <c r="E29" s="9" t="inlineStr">
         <is>
-          <t>펌웨어·부트킷(UEFI)으로 OS 아래 지속·은닉</t>
+          <t>취약·악성 드라이버 로드로 커널 은닉·무력화 토대 마련</t>
         </is>
       </c>
       <c r="F29" s="9" t="inlineStr">
         <is>
-          <t>- 공격자는 OS 아래 펌웨어·부트 단계에 임플란트를 심어 재설치·디스크 교체에도 지속할 수 있음
-- OS 보안 제품의 가시성 밖이라 레거시·EDR 모두 사실상 공백임</t>
+          <t>- 공격자는 취약·악성 드라이버를 커널에 올려 은닉·무력화의 토대를 만들 수 있음
+- 커널 계층이라 상위 보안 제품이 보지 못함</t>
         </is>
       </c>
       <c r="G29" s="9" t="inlineStr">
         <is>
-          <t>Pre-OS boot / firmware implant (bootkit)</t>
+          <t>Load vulnerable/malicious kernel driver</t>
         </is>
       </c>
       <c r="H29" s="9" t="inlineStr">
@@ -13451,30 +13482,34 @@
       </c>
       <c r="K29" s="9" t="inlineStr">
         <is>
-          <t>국가배후</t>
+          <t>국가배후 · 랜섬웨어</t>
         </is>
       </c>
       <c r="L29" s="9" t="inlineStr">
         <is>
-          <t>펌웨어 · Windows</t>
+          <t>Windows</t>
         </is>
       </c>
       <c r="M29" s="9" t="inlineStr">
         <is>
-          <t>T1542</t>
+          <t>T1543.003</t>
         </is>
       </c>
       <c r="N29" s="9" t="inlineStr">
         <is>
-          <t>T1542 Pre-OS Boot</t>
+          <t>T1543.003 Create or Modify System Process: Windows Service</t>
         </is>
       </c>
       <c r="O29" s="8" t="n">
-        <v>0</v>
+        <v>140</v>
       </c>
       <c r="P29" s="8" t="inlineStr"/>
       <c r="Q29" s="8" t="inlineStr"/>
-      <c r="R29" s="8" t="inlineStr"/>
+      <c r="R29" s="8" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
       <c r="S29" s="9" t="inlineStr"/>
       <c r="T29" s="9" t="inlineStr"/>
       <c r="U29" s="9" t="inlineStr"/>
@@ -13483,38 +13518,38 @@
       <c r="X29" s="9" t="inlineStr"/>
       <c r="Y29" s="8" t="inlineStr">
         <is>
+          <t>상</t>
+        </is>
+      </c>
+      <c r="Z29" s="8" t="inlineStr">
+        <is>
           <t>중</t>
         </is>
       </c>
-      <c r="Z29" s="8" t="inlineStr">
-        <is>
-          <t>중</t>
-        </is>
-      </c>
-      <c r="AA29" s="13" t="inlineStr">
-        <is>
-          <t>보통</t>
+      <c r="AA29" s="12" t="inlineStr">
+        <is>
+          <t>높음</t>
         </is>
       </c>
       <c r="AB29" s="9" t="inlineStr"/>
       <c r="AC29" s="8" t="n">
-        <v>26</v>
+        <v>12</v>
       </c>
       <c r="AD29" s="9" t="inlineStr">
         <is>
-          <t>실제 사고 1건(최근 0, 서로 다른 행위자·캠페인 1) · 빈발 지수 하(ATT&amp;CK 주체 0) · KEV - · 정부 경보 0 · 위협인텔 0 · 실증 1</t>
+          <t>실제 사고 3건(최근 2, 서로 다른 행위자·캠페인 3) · 빈발 지수 상(ATT&amp;CK 주체 140) · KEV - · 정부 경보 0 · 위협인텔 0 · 실증 0</t>
         </is>
       </c>
       <c r="AE29" s="9" t="inlineStr">
         <is>
-          <t>펌웨어·부트킷으로 재설치에도 지속하는 하위 계층 지속성 — 직접 피해보다 장기 지속 조건</t>
+          <t>커널에 취약 드라이버를 올려 무력화·은닉의 토대를 만드는 단계 — 단독 피해는 없음</t>
         </is>
       </c>
       <c r="AF29" s="9" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AG29" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AH29" s="9" t="n">
         <v>0</v>
@@ -13529,32 +13564,33 @@
       </c>
       <c r="AK29" s="9" t="inlineStr">
         <is>
-          <t>ENI-026
-실증: ENI-024</t>
+          <t>ENI-016, ENI-017, ENI-036</t>
         </is>
       </c>
       <c r="AL29" s="9" t="inlineStr">
         <is>
-          <t>내부 접근 확보 1 · 첩보·감시 1</t>
+          <t>랜섬·암호화 2 · 자격증명·비밀 탈취 1 · 내부 접근 확보 1</t>
         </is>
       </c>
       <c r="AM29" s="9" t="inlineStr">
         <is>
           <t>SI-7 Software, Firmware, and Information Integrity
-CM-7 Least Functionality</t>
+CM-7 Least Functionality
+SI-4 System Monitoring</t>
         </is>
       </c>
       <c r="AN29" s="9" t="inlineStr">
         <is>
           <t>■ 탐지
-- 펌웨어·부트 무결성 측정(보안 부팅·측정 부팅)과 펌웨어 버전·해시 변화를 점검(NIST SI-7)
+- 신규 커널 드라이버 로드와 취약 드라이버 서명·해시를 차단 목록과 대조(NIST SI-7·SI-4)
 ■ 대응
-- 보안 부팅·펌웨어 무결성 검증·업데이트와 펌웨어 공급 신뢰를 관리(NIST SI-7·CM-7)</t>
+- HVCI·드라이버 블록리스트로 취약 드라이버 로드를 차단(NIST SI-7·CM-7)
+- 참고: LOLDrivers 〈Project〉</t>
         </is>
       </c>
       <c r="AO29" s="9" t="inlineStr">
         <is>
-          <t>MITRE 〈ATT&amp;CK Enterprise v19.2〉</t>
+          <t>LOLDrivers 〈Project〉</t>
         </is>
       </c>
     </row>
@@ -14552,7 +14588,7 @@
       <c r="F36" s="9" t="inlineStr">
         <is>
           <t>- 공격자는 설치된 보안 제품을 확인해 회피·무력화를 준비할 수 있음
-- 사전 단계라 직접 피해는 없으나 이후 방어 회피로 이어짐</t>
+- 사전 단계라 직접 피해는 없으나 이후 은닉·방어 무력화로 이어짐</t>
         </is>
       </c>
       <c r="G36" s="9" t="inlineStr">
@@ -19407,81 +19443,597 @@
     <row r="20">
       <c r="A20" s="9" t="inlineStr">
         <is>
-          <t>[DE] 방어 회피</t>
+          <t>[ST] 은닉</t>
         </is>
       </c>
       <c r="B20" s="9" t="inlineStr">
         <is>
-          <t>ENT-DE-01.1</t>
+          <t>ENT-ST-01</t>
         </is>
       </c>
       <c r="C20" s="9" t="inlineStr">
         <is>
+          <t>지표 삭제</t>
+        </is>
+      </c>
+      <c r="D20" s="9" t="inlineStr">
+        <is>
+          <t>지표 삭제(이벤트 로그·파일 삭제)</t>
+        </is>
+      </c>
+      <c r="E20" s="9" t="inlineStr">
+        <is>
+          <t>이벤트 로그·파일 삭제로 레거시 SIEM 탐지·분석 무력화</t>
+        </is>
+      </c>
+      <c r="F20" s="9" t="inlineStr">
+        <is>
+          <t>- 공격자는 이벤트 로그·파일을 지워 레거시 SIEM 탐지와 사후 분석을 무력화할 수 있음
+- 원격·불변 로그가 없으면 흔적이 사라져 추적이 어려워짐</t>
+        </is>
+      </c>
+      <c r="G20" s="9" t="inlineStr">
+        <is>
+          <t>시그니처 회피</t>
+        </is>
+      </c>
+      <c r="H20" s="8" t="inlineStr">
+        <is>
+          <t>행위·네트워크·아이덴티티</t>
+        </is>
+      </c>
+      <c r="I20" s="9" t="inlineStr">
+        <is>
+          <t>Windows · Linux</t>
+        </is>
+      </c>
+      <c r="J20" s="8" t="inlineStr">
+        <is>
+          <t>상</t>
+        </is>
+      </c>
+      <c r="K20" s="8" t="inlineStr">
+        <is>
+          <t>중</t>
+        </is>
+      </c>
+      <c r="L20" s="12" t="inlineStr">
+        <is>
+          <t>높음</t>
+        </is>
+      </c>
+      <c r="M20" s="8" t="n">
+        <v>13</v>
+      </c>
+      <c r="N20" s="27" t="inlineStr">
+        <is>
+          <t>실제 사고 확인</t>
+        </is>
+      </c>
+      <c r="O20" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="P20" s="8" t="n">
+        <v>335</v>
+      </c>
+      <c r="Q20" s="8" t="inlineStr"/>
+      <c r="R20" s="9" t="inlineStr">
+        <is>
+          <t>■ 탐지
+- 로그 삭제·감사 정책 변경 이벤트와 원격 수집 로그의 공백을 모니터링(NIST AU-6·SI-4)
+■ 대응
+- 원격·불변 로그 전송과 로그 삭제 방지·보존 정책을 적용(NIST AU-9·AU-6)</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="9" t="inlineStr">
+        <is>
+          <t>[ST] 은닉</t>
+        </is>
+      </c>
+      <c r="B21" s="9" t="inlineStr">
+        <is>
+          <t>ENT-ST-02</t>
+        </is>
+      </c>
+      <c r="C21" s="9" t="inlineStr">
+        <is>
+          <t>위장(정상 이름·서명)</t>
+        </is>
+      </c>
+      <c r="D21" s="9" t="inlineStr">
+        <is>
+          <t>위장(정상 이름·경로·서명 가장)</t>
+        </is>
+      </c>
+      <c r="E21" s="9" t="inlineStr">
+        <is>
+          <t>정상 이름·경로·서명 가장(위장)으로 눈·규칙 탐지 회피</t>
+        </is>
+      </c>
+      <c r="F21" s="9" t="inlineStr">
+        <is>
+          <t>- 공격자는 정상 프로세스·경로·서명으로 위장해 사람 눈과 규칙 기반 탐지를 피할 수 있음
+- 정상처럼 보여 레거시가 구분하기 어려우나 단독 피해는 제한적임</t>
+        </is>
+      </c>
+      <c r="G21" s="9" t="inlineStr">
+        <is>
+          <t>서명된 정상 도구 악용 · 시그니처 회피</t>
+        </is>
+      </c>
+      <c r="H21" s="8" t="inlineStr">
+        <is>
+          <t>EDR·XDR</t>
+        </is>
+      </c>
+      <c r="I21" s="9" t="inlineStr">
+        <is>
+          <t>Windows · Linux · macOS</t>
+        </is>
+      </c>
+      <c r="J21" s="8" t="inlineStr">
+        <is>
+          <t>중</t>
+        </is>
+      </c>
+      <c r="K21" s="8" t="inlineStr">
+        <is>
+          <t>중</t>
+        </is>
+      </c>
+      <c r="L21" s="13" t="inlineStr">
+        <is>
+          <t>보통</t>
+        </is>
+      </c>
+      <c r="M21" s="8" t="n">
+        <v>45</v>
+      </c>
+      <c r="N21" s="28" t="inlineStr">
+        <is>
+          <t>ATT&amp;CK 사례·KEV 다수</t>
+        </is>
+      </c>
+      <c r="O21" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="P21" s="8" t="n">
+        <v>60</v>
+      </c>
+      <c r="Q21" s="8" t="inlineStr"/>
+      <c r="R21" s="9" t="inlineStr">
+        <is>
+          <t>■ 탐지
+- 정상 이름과 다른 경로·서명·해시 불일치를 무결성·행위 기반으로 탐지(NIST SI-4·SI-7)
+■ 대응
+- 바이너리 무결성·서명 검증과 정상 경로 기준선 대조를 적용(NIST SI-7·SI-4)</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="9" t="inlineStr">
+        <is>
+          <t>[ST] 은닉</t>
+        </is>
+      </c>
+      <c r="B22" s="9" t="inlineStr">
+        <is>
+          <t>ENT-ST-03</t>
+        </is>
+      </c>
+      <c r="C22" s="9" t="inlineStr">
+        <is>
+          <t>파일·정보 난독화</t>
+        </is>
+      </c>
+      <c r="D22" s="9" t="inlineStr">
+        <is>
+          <t>파일·정보 난독화·암호화</t>
+        </is>
+      </c>
+      <c r="E22" s="9" t="inlineStr">
+        <is>
+          <t>패킹·인코딩·암호화 난독화로 시그니처·정적 분석 회피</t>
+        </is>
+      </c>
+      <c r="F22" s="9" t="inlineStr">
+        <is>
+          <t>- 공격자는 페이로드를 패킹·인코딩·암호화해 시그니처·정적 분석을 회피할 수 있음
+- 변종 양산으로 레거시 AV를 지속 우회하나 단독 피해는 제한적임</t>
+        </is>
+      </c>
+      <c r="G22" s="9" t="inlineStr">
+        <is>
+          <t>시그니처 회피 · 파일리스·인메모리</t>
+        </is>
+      </c>
+      <c r="H22" s="8" t="inlineStr">
+        <is>
+          <t>EDR·XDR</t>
+        </is>
+      </c>
+      <c r="I22" s="9" t="inlineStr">
+        <is>
+          <t>Windows · Linux · macOS</t>
+        </is>
+      </c>
+      <c r="J22" s="8" t="inlineStr">
+        <is>
+          <t>중</t>
+        </is>
+      </c>
+      <c r="K22" s="8" t="inlineStr">
+        <is>
+          <t>중</t>
+        </is>
+      </c>
+      <c r="L22" s="13" t="inlineStr">
+        <is>
+          <t>보통</t>
+        </is>
+      </c>
+      <c r="M22" s="8" t="n">
+        <v>40</v>
+      </c>
+      <c r="N22" s="28" t="inlineStr">
+        <is>
+          <t>ATT&amp;CK 사례·KEV 다수</t>
+        </is>
+      </c>
+      <c r="O22" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="P22" s="8" t="n">
+        <v>160</v>
+      </c>
+      <c r="Q22" s="8" t="inlineStr"/>
+      <c r="R22" s="9" t="inlineStr">
+        <is>
+          <t>■ 탐지
+- 실행 시점 행위·언패킹과 비정상 인코딩·엔트로피를 행위 기반으로 탐지(NIST SI-3·SI-4)
+■ 대응
+- 시그니처 의존을 줄이고 행위 기반·샌드박스 분석을 병행(NIST SI-3·SI-4)</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="9" t="inlineStr">
+        <is>
+          <t>[ST] 은닉</t>
+        </is>
+      </c>
+      <c r="B23" s="9" t="inlineStr">
+        <is>
+          <t>ENT-ST-04</t>
+        </is>
+      </c>
+      <c r="C23" s="9" t="inlineStr">
+        <is>
+          <t>인메모리·반사 로딩</t>
+        </is>
+      </c>
+      <c r="D23" s="9" t="inlineStr">
+        <is>
+          <t>인메모리·반사 코드 로딩</t>
+        </is>
+      </c>
+      <c r="E23" s="9" t="inlineStr">
+        <is>
+          <t>인메모리·반사 코드 로딩으로 파일 기반 AV 원천 회피</t>
+        </is>
+      </c>
+      <c r="F23" s="9" t="inlineStr">
+        <is>
+          <t>- 공격자는 디스크를 거치지 않고 메모리에서 페이로드를 로드·실행할 수 있음
+- 파일 기반 AV·시그니처가 원천적으로 보지 못해 행위·메모리 기반 탐지가 필요함</t>
+        </is>
+      </c>
+      <c r="G23" s="9" t="inlineStr">
+        <is>
+          <t>파일리스·인메모리 · 시그니처 회피</t>
+        </is>
+      </c>
+      <c r="H23" s="8" t="inlineStr">
+        <is>
+          <t>행위·네트워크·아이덴티티</t>
+        </is>
+      </c>
+      <c r="I23" s="9" t="inlineStr">
+        <is>
+          <t>Windows</t>
+        </is>
+      </c>
+      <c r="J23" s="8" t="inlineStr">
+        <is>
+          <t>중</t>
+        </is>
+      </c>
+      <c r="K23" s="8" t="inlineStr">
+        <is>
+          <t>중</t>
+        </is>
+      </c>
+      <c r="L23" s="13" t="inlineStr">
+        <is>
+          <t>보통</t>
+        </is>
+      </c>
+      <c r="M23" s="8" t="n">
+        <v>35</v>
+      </c>
+      <c r="N23" s="28" t="inlineStr">
+        <is>
+          <t>ATT&amp;CK 사례·KEV 다수</t>
+        </is>
+      </c>
+      <c r="O23" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="P23" s="8" t="n">
+        <v>32</v>
+      </c>
+      <c r="Q23" s="8" t="inlineStr"/>
+      <c r="R23" s="9" t="inlineStr">
+        <is>
+          <t>■ 탐지
+- 메모리 영역 할당·실행과 비정상 로딩을 EDR 메모리 스캔으로 탐지(NIST SI-3·SI-4)
+■ 대응
+- 메모리 가시성(EDR)·공격 표면 축소와 스크립트 실행 통제를 적용(NIST SI-3·SI-4)</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="9" t="inlineStr">
+        <is>
+          <t>[ST] 은닉</t>
+        </is>
+      </c>
+      <c r="B24" s="9" t="inlineStr">
+        <is>
+          <t>ENT-ST-05</t>
+        </is>
+      </c>
+      <c r="C24" s="9" t="inlineStr">
+        <is>
+          <t>루트킷</t>
+        </is>
+      </c>
+      <c r="D24" s="9" t="inlineStr">
+        <is>
+          <t>루트킷(사용자·커널 은폐)</t>
+        </is>
+      </c>
+      <c r="E24" s="9" t="inlineStr">
+        <is>
+          <t>루트킷으로 프로세스·파일·연결을 하위 계층에서 은폐</t>
+        </is>
+      </c>
+      <c r="F24" s="9" t="inlineStr">
+        <is>
+          <t>- 공격자는 루트킷으로 프로세스·파일·연결을 하위 계층에서 숨겨 탐지·분석을 방해할 수 있음
+- 레거시로는 존재 자체를 알기 어려워 장기 잠복에 쓰임</t>
+        </is>
+      </c>
+      <c r="G24" s="9" t="inlineStr">
+        <is>
+          <t>커널·펌웨어 하위 계층 · 파일리스·인메모리</t>
+        </is>
+      </c>
+      <c r="H24" s="8" t="inlineStr">
+        <is>
+          <t>행위·네트워크·아이덴티티</t>
+        </is>
+      </c>
+      <c r="I24" s="9" t="inlineStr">
+        <is>
+          <t>Windows · Linux</t>
+        </is>
+      </c>
+      <c r="J24" s="8" t="inlineStr">
+        <is>
+          <t>중</t>
+        </is>
+      </c>
+      <c r="K24" s="8" t="inlineStr">
+        <is>
+          <t>중</t>
+        </is>
+      </c>
+      <c r="L24" s="13" t="inlineStr">
+        <is>
+          <t>보통</t>
+        </is>
+      </c>
+      <c r="M24" s="8" t="n">
+        <v>36</v>
+      </c>
+      <c r="N24" s="28" t="inlineStr">
+        <is>
+          <t>ATT&amp;CK 사례·KEV 다수</t>
+        </is>
+      </c>
+      <c r="O24" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="P24" s="8" t="n">
+        <v>32</v>
+      </c>
+      <c r="Q24" s="8" t="inlineStr"/>
+      <c r="R24" s="9" t="inlineStr">
+        <is>
+          <t>■ 탐지
+- 커널 무결성·드라이버 서명과 메모리·부트 무결성 검증으로 은폐를 탐지(NIST SI-7·SI-4)
+■ 대응
+- 커널 무결성 보호(HVCI)·보안 부팅과 하위 계층 텔레메트리를 확보(NIST SI-7·SI-4)</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="9" t="inlineStr">
+        <is>
+          <t>[ST] 은닉</t>
+        </is>
+      </c>
+      <c r="B25" s="9" t="inlineStr">
+        <is>
+          <t>ENT-ST-06</t>
+        </is>
+      </c>
+      <c r="C25" s="9" t="inlineStr">
+        <is>
+          <t>펌웨어·부트 수준 은닉</t>
+        </is>
+      </c>
+      <c r="D25" s="9" t="inlineStr">
+        <is>
+          <t>펌웨어·부트킷(UEFI) 지속·은닉</t>
+        </is>
+      </c>
+      <c r="E25" s="9" t="inlineStr">
+        <is>
+          <t>펌웨어·부트킷(UEFI)으로 OS 아래 지속·은닉</t>
+        </is>
+      </c>
+      <c r="F25" s="9" t="inlineStr">
+        <is>
+          <t>- 공격자는 OS 아래 펌웨어·부트 단계에 임플란트를 심어 재설치·디스크 교체에도 지속할 수 있음
+- OS 보안 제품의 가시성 밖이라 레거시·EDR 모두 사실상 공백임</t>
+        </is>
+      </c>
+      <c r="G25" s="9" t="inlineStr">
+        <is>
+          <t>커널·펌웨어 하위 계층</t>
+        </is>
+      </c>
+      <c r="H25" s="8" t="inlineStr">
+        <is>
+          <t>행위·네트워크·아이덴티티</t>
+        </is>
+      </c>
+      <c r="I25" s="9" t="inlineStr">
+        <is>
+          <t>펌웨어 · Windows</t>
+        </is>
+      </c>
+      <c r="J25" s="8" t="inlineStr">
+        <is>
+          <t>중</t>
+        </is>
+      </c>
+      <c r="K25" s="8" t="inlineStr">
+        <is>
+          <t>중</t>
+        </is>
+      </c>
+      <c r="L25" s="13" t="inlineStr">
+        <is>
+          <t>보통</t>
+        </is>
+      </c>
+      <c r="M25" s="8" t="n">
+        <v>26</v>
+      </c>
+      <c r="N25" s="27" t="inlineStr">
+        <is>
+          <t>실제 사고 확인</t>
+        </is>
+      </c>
+      <c r="O25" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="P25" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q25" s="8" t="inlineStr"/>
+      <c r="R25" s="9" t="inlineStr">
+        <is>
+          <t>■ 탐지
+- 펌웨어·부트 무결성 측정(보안 부팅·측정 부팅)과 펌웨어 버전·해시 변화를 점검(NIST SI-7)
+■ 대응
+- 보안 부팅·펌웨어 무결성 검증·업데이트와 펌웨어 공급 신뢰를 관리(NIST SI-7·CM-7)</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="9" t="inlineStr">
+        <is>
+          <t>[DM] 방어 무력화</t>
+        </is>
+      </c>
+      <c r="B26" s="9" t="inlineStr">
+        <is>
+          <t>ENT-DM-01.1</t>
+        </is>
+      </c>
+      <c r="C26" s="9" t="inlineStr">
+        <is>
           <t>보안 도구 무력화·드라이버 로드</t>
         </is>
       </c>
-      <c r="D20" s="9" t="inlineStr">
+      <c r="D26" s="9" t="inlineStr">
         <is>
           <t>보안 도구 무력화(EDR 변조·BYOVD EDR 킬러)</t>
         </is>
       </c>
-      <c r="E20" s="9" t="inlineStr">
+      <c r="E26" s="9" t="inlineStr">
         <is>
           <t>서명된 취약 드라이버로 EDR·백신을 커널에서 무력화(BYOVD)</t>
         </is>
       </c>
-      <c r="F20" s="9" t="inlineStr">
+      <c r="F26" s="9" t="inlineStr">
         <is>
           <t>- 공격자는 서명된 취약 드라이버를 올려 EDR·백신을 커널에서 무력화할 수 있음
 - 보안 도구 자체가 꺼지므로 이후 단계가 전부 가려지고, 여러 랜섬웨어·국가배후가 EDR 킬러를 공유함</t>
         </is>
       </c>
-      <c r="G20" s="9" t="inlineStr">
+      <c r="G26" s="9" t="inlineStr">
         <is>
           <t>커널·펌웨어 하위 계층 · 서명된 정상 도구 악용</t>
         </is>
       </c>
-      <c r="H20" s="8" t="inlineStr">
+      <c r="H26" s="8" t="inlineStr">
         <is>
           <t>행위·네트워크·아이덴티티</t>
         </is>
       </c>
-      <c r="I20" s="9" t="inlineStr">
+      <c r="I26" s="9" t="inlineStr">
         <is>
           <t>Windows</t>
         </is>
       </c>
-      <c r="J20" s="8" t="inlineStr">
+      <c r="J26" s="8" t="inlineStr">
         <is>
           <t>상</t>
         </is>
       </c>
-      <c r="K20" s="8" t="inlineStr">
+      <c r="K26" s="8" t="inlineStr">
         <is>
           <t>중</t>
         </is>
       </c>
-      <c r="L20" s="12" t="inlineStr">
+      <c r="L26" s="12" t="inlineStr">
         <is>
           <t>높음</t>
         </is>
       </c>
-      <c r="M20" s="8" t="n">
+      <c r="M26" s="8" t="n">
         <v>8</v>
       </c>
-      <c r="N20" s="27" t="inlineStr">
+      <c r="N26" s="27" t="inlineStr">
         <is>
           <t>실제 사고 확인</t>
         </is>
       </c>
-      <c r="O20" s="8" t="n">
+      <c r="O26" s="8" t="n">
         <v>7</v>
       </c>
-      <c r="P20" s="8" t="n">
+      <c r="P26" s="8" t="n">
         <v>155</v>
       </c>
-      <c r="Q20" s="8" t="inlineStr"/>
-      <c r="R20" s="9" t="inlineStr">
+      <c r="Q26" s="8" t="inlineStr"/>
+      <c r="R26" s="9" t="inlineStr">
         <is>
           <t>■ 탐지
 - 보안 서비스 중지·드라이버 로드와 EDR 텔레메트리 단절을 행위·네트워크 기반으로 탐지(NIST SI-4·SI-7)
@@ -19491,84 +20043,84 @@
         </is>
       </c>
     </row>
-    <row r="21">
-      <c r="A21" s="9" t="inlineStr">
-        <is>
-          <t>[DE] 방어 회피</t>
-        </is>
-      </c>
-      <c r="B21" s="9" t="inlineStr">
-        <is>
-          <t>ENT-DE-01.2</t>
-        </is>
-      </c>
-      <c r="C21" s="9" t="inlineStr">
+    <row r="27">
+      <c r="A27" s="9" t="inlineStr">
+        <is>
+          <t>[DM] 방어 무력화</t>
+        </is>
+      </c>
+      <c r="B27" s="9" t="inlineStr">
+        <is>
+          <t>ENT-DM-01.2</t>
+        </is>
+      </c>
+      <c r="C27" s="9" t="inlineStr">
         <is>
           <t>보안 도구 무력화·드라이버 로드</t>
         </is>
       </c>
-      <c r="D21" s="9" t="inlineStr">
+      <c r="D27" s="9" t="inlineStr">
         <is>
           <t>취약·악성 드라이버 로드(커널)</t>
         </is>
       </c>
-      <c r="E21" s="9" t="inlineStr">
+      <c r="E27" s="9" t="inlineStr">
         <is>
           <t>취약·악성 드라이버 로드로 커널 은닉·무력화 토대 마련</t>
         </is>
       </c>
-      <c r="F21" s="9" t="inlineStr">
+      <c r="F27" s="9" t="inlineStr">
         <is>
           <t>- 공격자는 취약·악성 드라이버를 커널에 올려 은닉·무력화의 토대를 만들 수 있음
 - 커널 계층이라 상위 보안 제품이 보지 못함</t>
         </is>
       </c>
-      <c r="G21" s="9" t="inlineStr">
+      <c r="G27" s="9" t="inlineStr">
         <is>
           <t>커널·펌웨어 하위 계층</t>
         </is>
       </c>
-      <c r="H21" s="8" t="inlineStr">
+      <c r="H27" s="8" t="inlineStr">
         <is>
           <t>행위·네트워크·아이덴티티</t>
         </is>
       </c>
-      <c r="I21" s="9" t="inlineStr">
+      <c r="I27" s="9" t="inlineStr">
         <is>
           <t>Windows</t>
         </is>
       </c>
-      <c r="J21" s="8" t="inlineStr">
+      <c r="J27" s="8" t="inlineStr">
         <is>
           <t>상</t>
         </is>
       </c>
-      <c r="K21" s="8" t="inlineStr">
+      <c r="K27" s="8" t="inlineStr">
         <is>
           <t>중</t>
         </is>
       </c>
-      <c r="L21" s="12" t="inlineStr">
+      <c r="L27" s="12" t="inlineStr">
         <is>
           <t>높음</t>
         </is>
       </c>
-      <c r="M21" s="8" t="n">
+      <c r="M27" s="8" t="n">
         <v>12</v>
       </c>
-      <c r="N21" s="27" t="inlineStr">
+      <c r="N27" s="27" t="inlineStr">
         <is>
           <t>실제 사고 확인</t>
         </is>
       </c>
-      <c r="O21" s="8" t="n">
+      <c r="O27" s="8" t="n">
         <v>3</v>
       </c>
-      <c r="P21" s="8" t="n">
+      <c r="P27" s="8" t="n">
         <v>140</v>
       </c>
-      <c r="Q21" s="8" t="inlineStr"/>
-      <c r="R21" s="9" t="inlineStr">
+      <c r="Q27" s="8" t="inlineStr"/>
+      <c r="R27" s="9" t="inlineStr">
         <is>
           <t>■ 탐지
 - 신규 커널 드라이버 로드와 취약 드라이버 서명·해시를 차단 목록과 대조(NIST SI-7·SI-4)
@@ -19578,522 +20130,6 @@
         </is>
       </c>
     </row>
-    <row r="22">
-      <c r="A22" s="9" t="inlineStr">
-        <is>
-          <t>[DE] 방어 회피</t>
-        </is>
-      </c>
-      <c r="B22" s="9" t="inlineStr">
-        <is>
-          <t>ENT-DE-03</t>
-        </is>
-      </c>
-      <c r="C22" s="9" t="inlineStr">
-        <is>
-          <t>지표 삭제</t>
-        </is>
-      </c>
-      <c r="D22" s="9" t="inlineStr">
-        <is>
-          <t>지표 삭제(이벤트 로그·파일 삭제)</t>
-        </is>
-      </c>
-      <c r="E22" s="9" t="inlineStr">
-        <is>
-          <t>이벤트 로그·파일 삭제로 레거시 SIEM 탐지·분석 무력화</t>
-        </is>
-      </c>
-      <c r="F22" s="9" t="inlineStr">
-        <is>
-          <t>- 공격자는 이벤트 로그·파일을 지워 레거시 SIEM 탐지와 사후 분석을 무력화할 수 있음
-- 원격·불변 로그가 없으면 흔적이 사라져 추적이 어려워짐</t>
-        </is>
-      </c>
-      <c r="G22" s="9" t="inlineStr">
-        <is>
-          <t>시그니처 회피</t>
-        </is>
-      </c>
-      <c r="H22" s="8" t="inlineStr">
-        <is>
-          <t>행위·네트워크·아이덴티티</t>
-        </is>
-      </c>
-      <c r="I22" s="9" t="inlineStr">
-        <is>
-          <t>Windows · Linux</t>
-        </is>
-      </c>
-      <c r="J22" s="8" t="inlineStr">
-        <is>
-          <t>상</t>
-        </is>
-      </c>
-      <c r="K22" s="8" t="inlineStr">
-        <is>
-          <t>중</t>
-        </is>
-      </c>
-      <c r="L22" s="12" t="inlineStr">
-        <is>
-          <t>높음</t>
-        </is>
-      </c>
-      <c r="M22" s="8" t="n">
-        <v>13</v>
-      </c>
-      <c r="N22" s="27" t="inlineStr">
-        <is>
-          <t>실제 사고 확인</t>
-        </is>
-      </c>
-      <c r="O22" s="8" t="n">
-        <v>2</v>
-      </c>
-      <c r="P22" s="8" t="n">
-        <v>335</v>
-      </c>
-      <c r="Q22" s="8" t="inlineStr"/>
-      <c r="R22" s="9" t="inlineStr">
-        <is>
-          <t>■ 탐지
-- 로그 삭제·감사 정책 변경 이벤트와 원격 수집 로그의 공백을 모니터링(NIST AU-6·SI-4)
-■ 대응
-- 원격·불변 로그 전송과 로그 삭제 방지·보존 정책을 적용(NIST AU-9·AU-6)</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="9" t="inlineStr">
-        <is>
-          <t>[DE] 방어 회피</t>
-        </is>
-      </c>
-      <c r="B23" s="9" t="inlineStr">
-        <is>
-          <t>ENT-DE-04</t>
-        </is>
-      </c>
-      <c r="C23" s="9" t="inlineStr">
-        <is>
-          <t>위장(정상 이름·서명)</t>
-        </is>
-      </c>
-      <c r="D23" s="9" t="inlineStr">
-        <is>
-          <t>위장(정상 이름·경로·서명 가장)</t>
-        </is>
-      </c>
-      <c r="E23" s="9" t="inlineStr">
-        <is>
-          <t>정상 이름·경로·서명 가장(위장)으로 눈·규칙 탐지 회피</t>
-        </is>
-      </c>
-      <c r="F23" s="9" t="inlineStr">
-        <is>
-          <t>- 공격자는 정상 프로세스·경로·서명으로 위장해 사람 눈과 규칙 기반 탐지를 피할 수 있음
-- 정상처럼 보여 레거시가 구분하기 어려우나 단독 피해는 제한적임</t>
-        </is>
-      </c>
-      <c r="G23" s="9" t="inlineStr">
-        <is>
-          <t>서명된 정상 도구 악용 · 시그니처 회피</t>
-        </is>
-      </c>
-      <c r="H23" s="8" t="inlineStr">
-        <is>
-          <t>EDR·XDR</t>
-        </is>
-      </c>
-      <c r="I23" s="9" t="inlineStr">
-        <is>
-          <t>Windows · Linux · macOS</t>
-        </is>
-      </c>
-      <c r="J23" s="8" t="inlineStr">
-        <is>
-          <t>중</t>
-        </is>
-      </c>
-      <c r="K23" s="8" t="inlineStr">
-        <is>
-          <t>중</t>
-        </is>
-      </c>
-      <c r="L23" s="13" t="inlineStr">
-        <is>
-          <t>보통</t>
-        </is>
-      </c>
-      <c r="M23" s="8" t="n">
-        <v>45</v>
-      </c>
-      <c r="N23" s="28" t="inlineStr">
-        <is>
-          <t>ATT&amp;CK 사례·KEV 다수</t>
-        </is>
-      </c>
-      <c r="O23" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="P23" s="8" t="n">
-        <v>60</v>
-      </c>
-      <c r="Q23" s="8" t="inlineStr"/>
-      <c r="R23" s="9" t="inlineStr">
-        <is>
-          <t>■ 탐지
-- 정상 이름과 다른 경로·서명·해시 불일치를 무결성·행위 기반으로 탐지(NIST SI-4·SI-7)
-■ 대응
-- 바이너리 무결성·서명 검증과 정상 경로 기준선 대조를 적용(NIST SI-7·SI-4)</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="9" t="inlineStr">
-        <is>
-          <t>[DE] 방어 회피</t>
-        </is>
-      </c>
-      <c r="B24" s="9" t="inlineStr">
-        <is>
-          <t>ENT-DE-05</t>
-        </is>
-      </c>
-      <c r="C24" s="9" t="inlineStr">
-        <is>
-          <t>파일·정보 난독화</t>
-        </is>
-      </c>
-      <c r="D24" s="9" t="inlineStr">
-        <is>
-          <t>파일·정보 난독화·암호화</t>
-        </is>
-      </c>
-      <c r="E24" s="9" t="inlineStr">
-        <is>
-          <t>패킹·인코딩·암호화 난독화로 시그니처·정적 분석 회피</t>
-        </is>
-      </c>
-      <c r="F24" s="9" t="inlineStr">
-        <is>
-          <t>- 공격자는 페이로드를 패킹·인코딩·암호화해 시그니처·정적 분석을 회피할 수 있음
-- 변종 양산으로 레거시 AV를 지속 우회하나 단독 피해는 제한적임</t>
-        </is>
-      </c>
-      <c r="G24" s="9" t="inlineStr">
-        <is>
-          <t>시그니처 회피 · 파일리스·인메모리</t>
-        </is>
-      </c>
-      <c r="H24" s="8" t="inlineStr">
-        <is>
-          <t>EDR·XDR</t>
-        </is>
-      </c>
-      <c r="I24" s="9" t="inlineStr">
-        <is>
-          <t>Windows · Linux · macOS</t>
-        </is>
-      </c>
-      <c r="J24" s="8" t="inlineStr">
-        <is>
-          <t>중</t>
-        </is>
-      </c>
-      <c r="K24" s="8" t="inlineStr">
-        <is>
-          <t>중</t>
-        </is>
-      </c>
-      <c r="L24" s="13" t="inlineStr">
-        <is>
-          <t>보통</t>
-        </is>
-      </c>
-      <c r="M24" s="8" t="n">
-        <v>40</v>
-      </c>
-      <c r="N24" s="28" t="inlineStr">
-        <is>
-          <t>ATT&amp;CK 사례·KEV 다수</t>
-        </is>
-      </c>
-      <c r="O24" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="P24" s="8" t="n">
-        <v>160</v>
-      </c>
-      <c r="Q24" s="8" t="inlineStr"/>
-      <c r="R24" s="9" t="inlineStr">
-        <is>
-          <t>■ 탐지
-- 실행 시점 행위·언패킹과 비정상 인코딩·엔트로피를 행위 기반으로 탐지(NIST SI-3·SI-4)
-■ 대응
-- 시그니처 의존을 줄이고 행위 기반·샌드박스 분석을 병행(NIST SI-3·SI-4)</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="9" t="inlineStr">
-        <is>
-          <t>[DE] 방어 회피</t>
-        </is>
-      </c>
-      <c r="B25" s="9" t="inlineStr">
-        <is>
-          <t>ENT-DE-06</t>
-        </is>
-      </c>
-      <c r="C25" s="9" t="inlineStr">
-        <is>
-          <t>인메모리·반사 로딩</t>
-        </is>
-      </c>
-      <c r="D25" s="9" t="inlineStr">
-        <is>
-          <t>인메모리·반사 코드 로딩</t>
-        </is>
-      </c>
-      <c r="E25" s="9" t="inlineStr">
-        <is>
-          <t>인메모리·반사 코드 로딩으로 파일 기반 AV 원천 회피</t>
-        </is>
-      </c>
-      <c r="F25" s="9" t="inlineStr">
-        <is>
-          <t>- 공격자는 디스크를 거치지 않고 메모리에서 페이로드를 로드·실행할 수 있음
-- 파일 기반 AV·시그니처가 원천적으로 보지 못해 행위·메모리 기반 탐지가 필요함</t>
-        </is>
-      </c>
-      <c r="G25" s="9" t="inlineStr">
-        <is>
-          <t>파일리스·인메모리 · 시그니처 회피</t>
-        </is>
-      </c>
-      <c r="H25" s="8" t="inlineStr">
-        <is>
-          <t>행위·네트워크·아이덴티티</t>
-        </is>
-      </c>
-      <c r="I25" s="9" t="inlineStr">
-        <is>
-          <t>Windows</t>
-        </is>
-      </c>
-      <c r="J25" s="8" t="inlineStr">
-        <is>
-          <t>중</t>
-        </is>
-      </c>
-      <c r="K25" s="8" t="inlineStr">
-        <is>
-          <t>중</t>
-        </is>
-      </c>
-      <c r="L25" s="13" t="inlineStr">
-        <is>
-          <t>보통</t>
-        </is>
-      </c>
-      <c r="M25" s="8" t="n">
-        <v>35</v>
-      </c>
-      <c r="N25" s="28" t="inlineStr">
-        <is>
-          <t>ATT&amp;CK 사례·KEV 다수</t>
-        </is>
-      </c>
-      <c r="O25" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="P25" s="8" t="n">
-        <v>32</v>
-      </c>
-      <c r="Q25" s="8" t="inlineStr"/>
-      <c r="R25" s="9" t="inlineStr">
-        <is>
-          <t>■ 탐지
-- 메모리 영역 할당·실행과 비정상 로딩을 EDR 메모리 스캔으로 탐지(NIST SI-3·SI-4)
-■ 대응
-- 메모리 가시성(EDR)·공격 표면 축소와 스크립트 실행 통제를 적용(NIST SI-3·SI-4)</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="9" t="inlineStr">
-        <is>
-          <t>[DE] 방어 회피</t>
-        </is>
-      </c>
-      <c r="B26" s="9" t="inlineStr">
-        <is>
-          <t>ENT-DE-07</t>
-        </is>
-      </c>
-      <c r="C26" s="9" t="inlineStr">
-        <is>
-          <t>루트킷</t>
-        </is>
-      </c>
-      <c r="D26" s="9" t="inlineStr">
-        <is>
-          <t>루트킷(사용자·커널 은폐)</t>
-        </is>
-      </c>
-      <c r="E26" s="9" t="inlineStr">
-        <is>
-          <t>루트킷으로 프로세스·파일·연결을 하위 계층에서 은폐</t>
-        </is>
-      </c>
-      <c r="F26" s="9" t="inlineStr">
-        <is>
-          <t>- 공격자는 루트킷으로 프로세스·파일·연결을 하위 계층에서 숨겨 탐지·분석을 방해할 수 있음
-- 레거시로는 존재 자체를 알기 어려워 장기 잠복에 쓰임</t>
-        </is>
-      </c>
-      <c r="G26" s="9" t="inlineStr">
-        <is>
-          <t>커널·펌웨어 하위 계층 · 파일리스·인메모리</t>
-        </is>
-      </c>
-      <c r="H26" s="8" t="inlineStr">
-        <is>
-          <t>행위·네트워크·아이덴티티</t>
-        </is>
-      </c>
-      <c r="I26" s="9" t="inlineStr">
-        <is>
-          <t>Windows · Linux</t>
-        </is>
-      </c>
-      <c r="J26" s="8" t="inlineStr">
-        <is>
-          <t>중</t>
-        </is>
-      </c>
-      <c r="K26" s="8" t="inlineStr">
-        <is>
-          <t>중</t>
-        </is>
-      </c>
-      <c r="L26" s="13" t="inlineStr">
-        <is>
-          <t>보통</t>
-        </is>
-      </c>
-      <c r="M26" s="8" t="n">
-        <v>36</v>
-      </c>
-      <c r="N26" s="28" t="inlineStr">
-        <is>
-          <t>ATT&amp;CK 사례·KEV 다수</t>
-        </is>
-      </c>
-      <c r="O26" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="P26" s="8" t="n">
-        <v>32</v>
-      </c>
-      <c r="Q26" s="8" t="inlineStr"/>
-      <c r="R26" s="9" t="inlineStr">
-        <is>
-          <t>■ 탐지
-- 커널 무결성·드라이버 서명과 메모리·부트 무결성 검증으로 은폐를 탐지(NIST SI-7·SI-4)
-■ 대응
-- 커널 무결성 보호(HVCI)·보안 부팅과 하위 계층 텔레메트리를 확보(NIST SI-7·SI-4)</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="9" t="inlineStr">
-        <is>
-          <t>[DE] 방어 회피</t>
-        </is>
-      </c>
-      <c r="B27" s="9" t="inlineStr">
-        <is>
-          <t>ENT-DE-08</t>
-        </is>
-      </c>
-      <c r="C27" s="9" t="inlineStr">
-        <is>
-          <t>펌웨어·부트 수준 은닉</t>
-        </is>
-      </c>
-      <c r="D27" s="9" t="inlineStr">
-        <is>
-          <t>펌웨어·부트킷(UEFI) 지속·은닉</t>
-        </is>
-      </c>
-      <c r="E27" s="9" t="inlineStr">
-        <is>
-          <t>펌웨어·부트킷(UEFI)으로 OS 아래 지속·은닉</t>
-        </is>
-      </c>
-      <c r="F27" s="9" t="inlineStr">
-        <is>
-          <t>- 공격자는 OS 아래 펌웨어·부트 단계에 임플란트를 심어 재설치·디스크 교체에도 지속할 수 있음
-- OS 보안 제품의 가시성 밖이라 레거시·EDR 모두 사실상 공백임</t>
-        </is>
-      </c>
-      <c r="G27" s="9" t="inlineStr">
-        <is>
-          <t>커널·펌웨어 하위 계층</t>
-        </is>
-      </c>
-      <c r="H27" s="8" t="inlineStr">
-        <is>
-          <t>행위·네트워크·아이덴티티</t>
-        </is>
-      </c>
-      <c r="I27" s="9" t="inlineStr">
-        <is>
-          <t>펌웨어 · Windows</t>
-        </is>
-      </c>
-      <c r="J27" s="8" t="inlineStr">
-        <is>
-          <t>중</t>
-        </is>
-      </c>
-      <c r="K27" s="8" t="inlineStr">
-        <is>
-          <t>중</t>
-        </is>
-      </c>
-      <c r="L27" s="13" t="inlineStr">
-        <is>
-          <t>보통</t>
-        </is>
-      </c>
-      <c r="M27" s="8" t="n">
-        <v>26</v>
-      </c>
-      <c r="N27" s="27" t="inlineStr">
-        <is>
-          <t>실제 사고 확인</t>
-        </is>
-      </c>
-      <c r="O27" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="P27" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q27" s="8" t="inlineStr"/>
-      <c r="R27" s="9" t="inlineStr">
-        <is>
-          <t>■ 탐지
-- 펌웨어·부트 무결성 측정(보안 부팅·측정 부팅)과 펌웨어 버전·해시 변화를 점검(NIST SI-7)
-■ 대응
-- 보안 부팅·펌웨어 무결성 검증·업데이트와 펌웨어 공급 신뢰를 관리(NIST SI-7·CM-7)</t>
-        </is>
-      </c>
-    </row>
     <row r="28">
       <c r="A28" s="9" t="inlineStr">
         <is>
@@ -20639,7 +20675,7 @@
       <c r="F34" s="9" t="inlineStr">
         <is>
           <t>- 공격자는 설치된 보안 제품을 확인해 회피·무력화를 준비할 수 있음
-- 사전 단계라 직접 피해는 없으나 이후 방어 회피로 이어짐</t>
+- 사전 단계라 직접 피해는 없으나 이후 은닉·방어 무력화로 이어짐</t>
         </is>
       </c>
       <c r="G34" s="9" t="inlineStr">
@@ -22350,7 +22386,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O13"/>
+  <dimension ref="A1:O14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -22678,30 +22714,30 @@
     <row r="6">
       <c r="A6" s="9" t="inlineStr">
         <is>
-          <t>[DE] 방어 회피</t>
+          <t>[ST] 은닉</t>
         </is>
       </c>
       <c r="B6" s="9" t="inlineStr">
         <is>
-          <t>EDR 변조·BYOVD·지표 삭제·위장·난독화·인메모리·루트킷·펌웨어 — 레거시가 체계적으로 공백인 영역(ATT&amp;CK 미커버 148개 중 다수)</t>
+          <t>위장·난독화·암호화·인메모리·반사 로딩·루트킷·펌웨어·지표 삭제 — 정상 행위에 섞여 탐지를 피하는 영역(ATT&amp;CK v19 구 방어 회피 TA0005 유지)</t>
         </is>
       </c>
       <c r="C6" s="9" t="inlineStr">
         <is>
-          <t>클라우드 로그 무력화는 CL · AI 기반 적대적 회피는 AI(연계)</t>
+          <t>클라우드 로그 영역은 CL · AI 기반 적대적 회피는 AI(연계)</t>
         </is>
       </c>
       <c r="D6" s="9" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E6" s="9" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="F6" s="9" t="n">
         <v>0</v>
       </c>
       <c r="G6" s="9" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H6" s="9" t="n">
         <v>5</v>
@@ -22710,7 +22746,7 @@
         <v>0</v>
       </c>
       <c r="J6" s="9" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="K6" s="9" t="n">
         <v>4</v>
@@ -22722,66 +22758,122 @@
         <v>0</v>
       </c>
       <c r="N6" s="9" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="O6" s="9" t="inlineStr">
         <is>
-          <t>ENT-DE-01.1 보안 도구 무력화(EDR 변조·BYOVD EDR 킬러)(높음)
-ENT-DE-01.2 취약·악성 드라이버 로드(커널)(높음)
-ENT-DE-03 지표 삭제(이벤트 로그·파일 삭제)(높음)</t>
+          <t>ENT-ST-01 지표 삭제(이벤트 로그·파일 삭제)(높음)
+ENT-ST-06 펌웨어·부트킷(UEFI) 지속·은닉(보통)
+ENT-ST-04 인메모리·반사 코드 로딩(보통)</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="9" t="inlineStr">
         <is>
-          <t>[CA] 자격증명 접근</t>
+          <t>[DM] 방어 무력화</t>
         </is>
       </c>
       <c r="B7" s="9" t="inlineStr">
         <is>
-          <t>LSASS 덤프·캐시 자격증명·Kerberoasting·입력 캡처로 호스트·도메인 자격증명을 탈취 — 이후 정상 인증으로 확산하는 발판</t>
+          <t>EDR 변조·BYOVD·취약 드라이버 로드 — 보안 통제를 직접 끄거나 떨어뜨리는 영역(ATT&amp;CK v19 신설 TA0112)</t>
         </is>
       </c>
       <c r="C7" s="9" t="inlineStr">
         <is>
-          <t>저장·노출된 비밀·토큰 재사용은 ID(연계)</t>
+          <t>클라우드 로그 무력화는 CL(연계) · AI 기반 적대적 회피는 AI(연계)</t>
         </is>
       </c>
       <c r="D7" s="9" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E7" s="9" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F7" s="9" t="n">
         <v>0</v>
       </c>
       <c r="G7" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H7" s="9" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I7" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J7" s="9" t="n">
         <v>2</v>
       </c>
       <c r="K7" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="L7" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="M7" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="N7" s="9" t="n">
+        <v>7</v>
+      </c>
+      <c r="O7" s="9" t="inlineStr">
+        <is>
+          <t>ENT-DM-01.1 보안 도구 무력화(EDR 변조·BYOVD EDR 킬러)(높음)
+ENT-DM-01.2 취약·악성 드라이버 로드(커널)(높음)</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="9" t="inlineStr">
+        <is>
+          <t>[CA] 자격증명 접근</t>
+        </is>
+      </c>
+      <c r="B8" s="9" t="inlineStr">
+        <is>
+          <t>LSASS 덤프·캐시 자격증명·Kerberoasting·입력 캡처로 호스트·도메인 자격증명을 탈취 — 이후 정상 인증으로 확산하는 발판</t>
+        </is>
+      </c>
+      <c r="C8" s="9" t="inlineStr">
+        <is>
+          <t>저장·노출된 비밀·토큰 재사용은 ID(연계)</t>
+        </is>
+      </c>
+      <c r="D8" s="9" t="n">
+        <v>3</v>
+      </c>
+      <c r="E8" s="9" t="n">
+        <v>4</v>
+      </c>
+      <c r="F8" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="G8" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="L7" s="9" t="n">
+      <c r="H8" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="I8" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="M7" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="N7" s="9" t="n">
+      <c r="J8" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="K8" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="L8" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="M8" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="N8" s="9" t="n">
         <v>5</v>
       </c>
-      <c r="O7" s="9" t="inlineStr">
+      <c r="O8" s="9" t="inlineStr">
         <is>
           <t>ENT-CA-01.1 OS 자격증명 덤프(LSASS 메모리)(높음)
 ENT-CA-03 Kerberoasting·AS-REP 로스팅(보통)
@@ -22789,56 +22881,56 @@
         </is>
       </c>
     </row>
-    <row r="8">
-      <c r="A8" s="9" t="inlineStr">
+    <row r="9">
+      <c r="A9" s="9" t="inlineStr">
         <is>
           <t>[DI] 탐색</t>
         </is>
       </c>
-      <c r="B8" s="9" t="inlineStr">
+      <c r="B9" s="9" t="inlineStr">
         <is>
           <t>호스트·네트워크·AD 열거로 표적·경로를 파악 — 정상 질의라 레거시가 공백(미커버 49개 중 38개)</t>
         </is>
       </c>
-      <c r="C8" s="9" t="inlineStr">
+      <c r="C9" s="9" t="inlineStr">
         <is>
           <t>클라우드 자원 탐색은 CL(연계)</t>
         </is>
       </c>
-      <c r="D8" s="9" t="n">
+      <c r="D9" s="9" t="n">
         <v>3</v>
       </c>
-      <c r="E8" s="9" t="n">
+      <c r="E9" s="9" t="n">
         <v>3</v>
       </c>
-      <c r="F8" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="G8" s="9" t="n">
+      <c r="F9" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="G9" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="H8" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="I8" s="9" t="n">
+      <c r="H9" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="I9" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="J8" s="9" t="n">
+      <c r="J9" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="K8" s="9" t="n">
+      <c r="K9" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="L8" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="M8" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="N8" s="9" t="n">
+      <c r="L9" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="M9" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="N9" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="O8" s="9" t="inlineStr">
+      <c r="O9" s="9" t="inlineStr">
         <is>
           <t>ENT-DI-02 도메인·AD 열거(계정·신뢰·공유)(높음)
 ENT-DI-01 호스트·시스템·네트워크 구성 탐색(높음)
@@ -22846,56 +22938,56 @@
         </is>
       </c>
     </row>
-    <row r="9">
-      <c r="A9" s="9" t="inlineStr">
+    <row r="10">
+      <c r="A10" s="9" t="inlineStr">
         <is>
           <t>[LM] 측면 이동</t>
         </is>
       </c>
-      <c r="B9" s="9" t="inlineStr">
+      <c r="B10" s="9" t="inlineStr">
         <is>
           <t>원격 서비스·대체 인증 자료·도구 전송·원격 취약점으로 내부 확산 — 정상 프로토콜·인증을 써 레거시가 구분하기 어려움</t>
         </is>
       </c>
-      <c r="C9" s="9" t="inlineStr">
+      <c r="C10" s="9" t="inlineStr">
         <is>
           <t>토큰·티켓 위조 등 신원 전용은 ID(연계)</t>
         </is>
       </c>
-      <c r="D9" s="9" t="n">
+      <c r="D10" s="9" t="n">
         <v>4</v>
       </c>
-      <c r="E9" s="9" t="n">
+      <c r="E10" s="9" t="n">
         <v>4</v>
       </c>
-      <c r="F9" s="9" t="n">
+      <c r="F10" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="G9" s="9" t="n">
+      <c r="G10" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="H9" s="9" t="n">
+      <c r="H10" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="I9" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="J9" s="9" t="n">
+      <c r="I10" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="J10" s="9" t="n">
         <v>4</v>
       </c>
-      <c r="K9" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="L9" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="M9" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="N9" s="9" t="n">
+      <c r="K10" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="L10" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="M10" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="N10" s="9" t="n">
         <v>7</v>
       </c>
-      <c r="O9" s="9" t="inlineStr">
+      <c r="O10" s="9" t="inlineStr">
         <is>
           <t>ENT-LM-04 원격 서비스 취약점 악용(웜 확산)(매우 높음)
 ENT-LM-01 원격 서비스 악용(RDP·SMB·WinRM)(높음)
@@ -22903,112 +22995,112 @@
         </is>
       </c>
     </row>
-    <row r="10">
-      <c r="A10" s="9" t="inlineStr">
+    <row r="11">
+      <c r="A11" s="9" t="inlineStr">
         <is>
           <t>[CO] 수집</t>
         </is>
       </c>
-      <c r="B10" s="9" t="inlineStr">
+      <c r="B11" s="9" t="inlineStr">
         <is>
           <t>로컬·공유 데이터 수집과 스테이징 — 반출 전 단계</t>
         </is>
       </c>
-      <c r="C10" s="9" t="inlineStr">
+      <c r="C11" s="9" t="inlineStr">
         <is>
           <t>클라우드 스토리지·메일 수집은 CL(연계)</t>
         </is>
       </c>
-      <c r="D10" s="9" t="n">
+      <c r="D11" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="E10" s="9" t="n">
+      <c r="E11" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="F10" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="G10" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="H10" s="9" t="n">
+      <c r="F11" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="G11" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="H11" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="I10" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="J10" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="K10" s="9" t="n">
+      <c r="I11" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="J11" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="K11" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="L10" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="M10" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="N10" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="O10" s="9" t="inlineStr">
+      <c r="L11" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="M11" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="N11" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="O11" s="9" t="inlineStr">
         <is>
           <t>ENT-CO-01 로컬·네트워크 공유 데이터 수집(보통)
 ENT-CO-02 수집 데이터 압축·암호화 스테이징(보통)</t>
         </is>
       </c>
     </row>
-    <row r="11">
-      <c r="A11" s="9" t="inlineStr">
+    <row r="12">
+      <c r="A12" s="9" t="inlineStr">
         <is>
           <t>[C2] 명령·제어</t>
         </is>
       </c>
-      <c r="B11" s="9" t="inlineStr">
+      <c r="B12" s="9" t="inlineStr">
         <is>
           <t>암호화 채널·정상 포트·웹 서비스·도메인 프런팅·프록시·DNS로 통제 트래픽을 숨김 — 레거시가 거의 공백(미커버 45개 중 43개)</t>
         </is>
       </c>
-      <c r="C11" s="9" t="inlineStr">
+      <c r="C12" s="9" t="inlineStr">
         <is>
           <t>클라우드 서비스 경유 C2는 CL · AI 서비스 경유 C2는 AI(연계)</t>
         </is>
       </c>
-      <c r="D11" s="9" t="n">
+      <c r="D12" s="9" t="n">
         <v>5</v>
       </c>
-      <c r="E11" s="9" t="n">
+      <c r="E12" s="9" t="n">
         <v>6</v>
       </c>
-      <c r="F11" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="G11" s="9" t="n">
+      <c r="F12" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="G12" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="H11" s="9" t="n">
+      <c r="H12" s="9" t="n">
         <v>4</v>
       </c>
-      <c r="I11" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="J11" s="9" t="n">
+      <c r="I12" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="J12" s="9" t="n">
         <v>4</v>
       </c>
-      <c r="K11" s="9" t="n">
+      <c r="K12" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="L11" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="M11" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="N11" s="9" t="n">
+      <c r="L12" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="M12" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="N12" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="O11" s="9" t="inlineStr">
+      <c r="O12" s="9" t="inlineStr">
         <is>
           <t>ENT-C2-01.2 응용 계층 프로토콜(HTTPS) C2(높음)
 ENT-C2-05 인그레스 도구 전송(페이로드 반입)(높음)
@@ -23016,112 +23108,112 @@
         </is>
       </c>
     </row>
-    <row r="12">
-      <c r="A12" s="9" t="inlineStr">
+    <row r="13">
+      <c r="A13" s="9" t="inlineStr">
         <is>
           <t>[EF] 반출</t>
         </is>
       </c>
-      <c r="B12" s="9" t="inlineStr">
+      <c r="B13" s="9" t="inlineStr">
         <is>
           <t>C2 채널·웹 서비스·대체 프로토콜로 데이터를 빼냄 — 정상 암호화 트래픽에 섞여 레거시 DLP·IDS가 놓침</t>
         </is>
       </c>
-      <c r="C12" s="9" t="inlineStr">
+      <c r="C13" s="9" t="inlineStr">
         <is>
           <t>클라우드 계정 간 전송·미러링 반출은 CL(연계)</t>
         </is>
       </c>
-      <c r="D12" s="9" t="n">
+      <c r="D13" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="E12" s="9" t="n">
+      <c r="E13" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="F12" s="9" t="n">
+      <c r="F13" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="G12" s="9" t="n">
+      <c r="G13" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="H12" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="I12" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="J12" s="9" t="n">
+      <c r="H13" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="I13" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="J13" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="K12" s="9" t="n">
+      <c r="K13" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="L12" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="M12" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="N12" s="9" t="n">
+      <c r="L13" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="M13" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="N13" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="O12" s="9" t="inlineStr">
+      <c r="O13" s="9" t="inlineStr">
         <is>
           <t>ENT-EF-02 정상 웹 서비스·대체 프로토콜 경유 반출(매우 높음)
 ENT-EF-01 C2 채널 경유 반출(높음)</t>
         </is>
       </c>
     </row>
-    <row r="13">
-      <c r="A13" s="9" t="inlineStr">
+    <row r="14">
+      <c r="A14" s="9" t="inlineStr">
         <is>
           <t>[IM] 영향</t>
         </is>
       </c>
-      <c r="B13" s="9" t="inlineStr">
+      <c r="B14" s="9" t="inlineStr">
         <is>
           <t>암호화(랜섬웨어)·복구 방해·파괴·서비스 중지·갈취 — 레거시가 막지 못한 침해의 최종 피해</t>
         </is>
       </c>
-      <c r="C13" s="9" t="inlineStr">
+      <c r="C14" s="9" t="inlineStr">
         <is>
           <t>클라우드·OT 영향은 CL·OT(연계)</t>
         </is>
       </c>
-      <c r="D13" s="9" t="n">
+      <c r="D14" s="9" t="n">
         <v>5</v>
       </c>
-      <c r="E13" s="9" t="n">
+      <c r="E14" s="9" t="n">
         <v>5</v>
       </c>
-      <c r="F13" s="9" t="n">
+      <c r="F14" s="9" t="n">
         <v>3</v>
       </c>
-      <c r="G13" s="9" t="n">
+      <c r="G14" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="H13" s="9" t="n">
+      <c r="H14" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="I13" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="J13" s="9" t="n">
+      <c r="I14" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="J14" s="9" t="n">
         <v>5</v>
       </c>
-      <c r="K13" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="L13" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="M13" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="N13" s="9" t="n">
+      <c r="K14" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="L14" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="M14" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="N14" s="9" t="n">
         <v>11</v>
       </c>
-      <c r="O13" s="9" t="inlineStr">
+      <c r="O14" s="9" t="inlineStr">
         <is>
           <t>ENT-IM-01 데이터 암호화(사람 운영 랜섬웨어)(매우 높음)
 ENT-IM-05 금전 탈취·이중 협박 갈취(매우 높음)
@@ -23204,7 +23296,7 @@
       <c r="E4" s="9" t="inlineStr">
         <is>
           <t>ENT-LM-04 원격 서비스 취약점 악용(웜 확산)(매우 높음)
-ENT-DE-03 지표 삭제(이벤트 로그·파일 삭제)(높음)
+ENT-ST-01 지표 삭제(이벤트 로그·파일 삭제)(높음)
 ENT-EX-03 서명된 정상 바이너리 프록시 실행(LOLBin)(보통)</t>
         </is>
       </c>
@@ -23255,7 +23347,7 @@
         <is>
           <t>ENT-IM-01 데이터 암호화(사람 운영 랜섬웨어)(매우 높음)
 ENT-IM-02 복구 방해(섀도 카피·백업 삭제)(매우 높음)
-ENT-DE-01.1 보안 도구 무력화(EDR 변조·BYOVD EDR 킬러)(높음)</t>
+ENT-DM-01.1 보안 도구 무력화(EDR 변조·BYOVD EDR 킬러)(높음)</t>
         </is>
       </c>
     </row>
@@ -23353,8 +23445,8 @@
       </c>
       <c r="E10" s="9" t="inlineStr">
         <is>
-          <t>ENT-DE-01.1 보안 도구 무력화(EDR 변조·BYOVD EDR 킬러)(높음)
-ENT-DE-01.2 취약·악성 드라이버 로드(커널)(높음)
+          <t>ENT-DM-01.1 보안 도구 무력화(EDR 변조·BYOVD EDR 킬러)(높음)
+ENT-DM-01.2 취약·악성 드라이버 로드(커널)(높음)
 ENT-IM-03 데이터 파괴·와이퍼(높음)</t>
         </is>
       </c>
@@ -23705,12 +23797,12 @@
       </c>
       <c r="C9" s="9" t="inlineStr">
         <is>
-          <t>방어 회피</t>
+          <t>방어 무력화</t>
         </is>
       </c>
       <c r="D9" s="9" t="inlineStr">
         <is>
-          <t>ENT-DE-01.1, ENT-PV-04</t>
+          <t>ENT-DM-01.1, ENT-PV-04</t>
         </is>
       </c>
       <c r="E9" s="9" t="inlineStr">
@@ -24089,12 +24181,12 @@
       </c>
       <c r="C21" s="9" t="inlineStr">
         <is>
-          <t>방어 회피</t>
+          <t>은닉</t>
         </is>
       </c>
       <c r="D21" s="9" t="inlineStr">
         <is>
-          <t>ENT-DE-05, ENT-DE-04</t>
+          <t>ENT-ST-03, ENT-ST-02</t>
         </is>
       </c>
       <c r="E21" s="9" t="inlineStr">
@@ -24121,12 +24213,12 @@
       </c>
       <c r="C22" s="9" t="inlineStr">
         <is>
-          <t>방어 회피</t>
+          <t>은닉</t>
         </is>
       </c>
       <c r="D22" s="9" t="inlineStr">
         <is>
-          <t>ENT-DE-03</t>
+          <t>ENT-ST-01</t>
         </is>
       </c>
       <c r="E22" s="9" t="inlineStr">
@@ -24153,12 +24245,12 @@
       </c>
       <c r="C23" s="9" t="inlineStr">
         <is>
-          <t>방어 회피</t>
+          <t>은닉</t>
         </is>
       </c>
       <c r="D23" s="9" t="inlineStr">
         <is>
-          <t>ENT-DE-08</t>
+          <t>ENT-ST-06</t>
         </is>
       </c>
       <c r="E23" s="9" t="inlineStr">
@@ -24185,12 +24277,12 @@
       </c>
       <c r="C24" s="9" t="inlineStr">
         <is>
-          <t>방어 회피</t>
+          <t>은닉</t>
         </is>
       </c>
       <c r="D24" s="9" t="inlineStr">
         <is>
-          <t>ENT-DE-08</t>
+          <t>ENT-ST-06</t>
         </is>
       </c>
       <c r="E24" s="9" t="inlineStr">
@@ -24360,7 +24452,7 @@
       <c r="K2" s="9" t="inlineStr"/>
       <c r="L2" s="9" t="inlineStr">
         <is>
-          <t>ENT-DE-01.1, ENT-DE-01.2</t>
+          <t>ENT-DM-01.1, ENT-DM-01.2</t>
         </is>
       </c>
       <c r="M2" s="9" t="inlineStr"/>
@@ -24488,7 +24580,7 @@
       <c r="K4" s="9" t="inlineStr"/>
       <c r="L4" s="9" t="inlineStr">
         <is>
-          <t>ENT-IA-01, ENT-DE-03</t>
+          <t>ENT-IA-01, ENT-ST-01</t>
         </is>
       </c>
       <c r="M4" s="9" t="inlineStr"/>
@@ -24552,7 +24644,7 @@
       <c r="K5" s="9" t="inlineStr"/>
       <c r="L5" s="9" t="inlineStr">
         <is>
-          <t>ENT-IM-01, ENT-DE-01.1</t>
+          <t>ENT-IM-01, ENT-DM-01.1</t>
         </is>
       </c>
       <c r="M5" s="9" t="inlineStr"/>
@@ -24616,7 +24708,7 @@
       <c r="K6" s="9" t="inlineStr"/>
       <c r="L6" s="9" t="inlineStr">
         <is>
-          <t>ENT-IA-02, ENT-EX-03, ENT-CA-01.1, ENT-DI-02, ENT-DE-01.1, ENT-IM-02, ENT-IM-05</t>
+          <t>ENT-IA-02, ENT-EX-03, ENT-CA-01.1, ENT-DI-02, ENT-DM-01.1, ENT-IM-02, ENT-IM-05</t>
         </is>
       </c>
       <c r="M6" s="9" t="inlineStr"/>
@@ -24680,7 +24772,7 @@
       <c r="K7" s="9" t="inlineStr"/>
       <c r="L7" s="9" t="inlineStr">
         <is>
-          <t>ENT-DE-01.2, ENT-DE-01.1</t>
+          <t>ENT-DM-01.2, ENT-DM-01.1</t>
         </is>
       </c>
       <c r="M7" s="9" t="inlineStr"/>
@@ -24880,7 +24972,7 @@
       <c r="K10" s="9" t="inlineStr"/>
       <c r="L10" s="9" t="inlineStr">
         <is>
-          <t>ENT-DE-01.1, ENT-DE-01.2, ENT-PV-04</t>
+          <t>ENT-DM-01.1, ENT-DM-01.2, ENT-PV-04</t>
         </is>
       </c>
       <c r="M10" s="9" t="inlineStr">
@@ -25016,7 +25108,7 @@
       <c r="K12" s="9" t="inlineStr"/>
       <c r="L12" s="9" t="inlineStr">
         <is>
-          <t>ENT-EX-01.1, ENT-CA-01.1, ENT-DI-02, ENT-LM-01, ENT-DE-01.1, ENT-IM-01, ENT-IM-02</t>
+          <t>ENT-EX-01.1, ENT-CA-01.1, ENT-DI-02, ENT-LM-01, ENT-DM-01.1, ENT-IM-01, ENT-IM-02</t>
         </is>
       </c>
       <c r="M12" s="9" t="inlineStr">
@@ -25356,7 +25448,7 @@
       <c r="K17" s="9" t="inlineStr"/>
       <c r="L17" s="9" t="inlineStr">
         <is>
-          <t>ENT-IA-01, ENT-EX-01.1, ENT-EX-03, ENT-DI-01, ENT-DI-02, ENT-CA-01.1, ENT-LM-01, ENT-DE-03</t>
+          <t>ENT-IA-01, ENT-EX-01.1, ENT-EX-03, ENT-DI-01, ENT-DI-02, ENT-CA-01.1, ENT-LM-01, ENT-ST-01</t>
         </is>
       </c>
       <c r="M17" s="9" t="inlineStr">
@@ -25492,7 +25584,7 @@
       <c r="K19" s="9" t="inlineStr"/>
       <c r="L19" s="9" t="inlineStr">
         <is>
-          <t>ENT-IA-02, ENT-DE-01.1, ENT-LM-01, ENT-LM-03, ENT-IM-01</t>
+          <t>ENT-IA-02, ENT-DM-01.1, ENT-LM-01, ENT-LM-03, ENT-IM-01</t>
         </is>
       </c>
       <c r="M19" s="9" t="inlineStr">
@@ -25760,7 +25852,7 @@
       <c r="K23" s="9" t="inlineStr"/>
       <c r="L23" s="9" t="inlineStr">
         <is>
-          <t>ENT-IM-01, ENT-IM-02, ENT-IM-04, ENT-DE-01.1</t>
+          <t>ENT-IM-01, ENT-IM-02, ENT-IM-04, ENT-DM-01.1</t>
         </is>
       </c>
       <c r="M23" s="9" t="inlineStr"/>
@@ -25893,7 +25985,7 @@
       <c r="K25" s="9" t="inlineStr"/>
       <c r="L25" s="9" t="inlineStr">
         <is>
-          <t>ENT-DE-08</t>
+          <t>ENT-ST-06</t>
         </is>
       </c>
       <c r="M25" s="9" t="inlineStr"/>
@@ -25957,7 +26049,7 @@
       <c r="K26" s="9" t="inlineStr"/>
       <c r="L26" s="9" t="inlineStr">
         <is>
-          <t>ENT-DE-08</t>
+          <t>ENT-ST-06</t>
         </is>
       </c>
       <c r="M26" s="9" t="inlineStr">
